--- a/data/May/InternalDailyReport_May.xlsx
+++ b/data/May/InternalDailyReport_May.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE927E16-E7A2-4870-9867-931B51DD6093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{853ED2FA-1DF7-4264-B905-FC7C4C40DBFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="7" r:id="rId1"/>
@@ -22,7 +22,8 @@
     <sheet name="09-05" sheetId="13" r:id="rId7"/>
     <sheet name="11-05" sheetId="14" r:id="rId8"/>
     <sheet name="12-05" sheetId="15" r:id="rId9"/>
-    <sheet name="Sheet1" sheetId="19" r:id="rId10"/>
+    <sheet name="13-05" sheetId="16" r:id="rId10"/>
+    <sheet name="Sheet1" sheetId="19" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01-05'!$A$2:$P$56</definedName>
@@ -34,7 +35,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'09-05'!$A$2:$P$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'11-05'!$A$2:$P$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'12-05'!$A$2:$P$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Sheet1!$A$2:$E$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'13-05'!$A$2:$P$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Sheet1!$A$2:$E$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -76,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3298" uniqueCount="1054">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3614" uniqueCount="1142">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -3000,6 +3002,216 @@
     <t>4 đơn</t>
   </si>
   <si>
+    <t>Thiên Nga</t>
+  </si>
+  <si>
+    <t>HD020151</t>
+  </si>
+  <si>
+    <t>S5.02 Vinhomes grand park, Nguyễn Xiển, Long Mỹ</t>
+  </si>
+  <si>
+    <t>12-05-2026</t>
+  </si>
+  <si>
+    <t>kim xuyến</t>
+  </si>
+  <si>
+    <t>HD019918</t>
+  </si>
+  <si>
+    <t>1002 tạ quang bửu p6</t>
+  </si>
+  <si>
+    <t>AT 12-05</t>
+  </si>
+  <si>
+    <t>Bella Tran (Lê Huy)</t>
+  </si>
+  <si>
+    <t>HD020184</t>
+  </si>
+  <si>
+    <t>67B đường T5, phường Tây Thạnh</t>
+  </si>
+  <si>
+    <t>Phạm Oanh</t>
+  </si>
+  <si>
+    <t>HD020045</t>
+  </si>
+  <si>
+    <t>Cty Eidaikake xưởng 2. đường số 8 phường tân thuận đông đường huỳnh tấn phát kcxtt</t>
+  </si>
+  <si>
+    <t>Trần Thị Kim Phương</t>
+  </si>
+  <si>
+    <t>HD020054</t>
+  </si>
+  <si>
+    <t>1870\1\98\14a tỉnh lộ 10 tân tạo bình tân</t>
+  </si>
+  <si>
+    <t>Hoàng Thị Hồng</t>
+  </si>
+  <si>
+    <t>HD020036</t>
+  </si>
+  <si>
+    <t>Eco green tòa E nguyễn văn linh tân thuận tây</t>
+  </si>
+  <si>
+    <t>Trinh Kim</t>
+  </si>
+  <si>
+    <t>HD020079</t>
+  </si>
+  <si>
+    <t>2117A/9 Phạm Thế Hiển phường 6</t>
+  </si>
+  <si>
+    <t>HD020221</t>
+  </si>
+  <si>
+    <t>90a /10/10 Âu duong lân p3</t>
+  </si>
+  <si>
+    <t>Thu Thủy</t>
+  </si>
+  <si>
+    <t>HD020187</t>
+  </si>
+  <si>
+    <t>287 Kinh Dương Vương, P An Lạc</t>
+  </si>
+  <si>
+    <t>Đoàn Ngọc</t>
+  </si>
+  <si>
+    <t>HD020082</t>
+  </si>
+  <si>
+    <t>137/2 bình long</t>
+  </si>
+  <si>
+    <t>đơn chuyển AT 12-05</t>
+  </si>
+  <si>
+    <t>Thế Diễm</t>
+  </si>
+  <si>
+    <t>HD020049</t>
+  </si>
+  <si>
+    <t>159 Võ Nguyên Giáp, P Thảo Điền Chung cư Masteri Thảo Điền (Tháp 3)</t>
+  </si>
+  <si>
+    <t>Trần Thị Ngọc Trâm</t>
+  </si>
+  <si>
+    <t>HD020123</t>
+  </si>
+  <si>
+    <t>5/1H đường số 11 Bình Thọ</t>
+  </si>
+  <si>
+    <t>Bella</t>
+  </si>
+  <si>
+    <t>HD020155</t>
+  </si>
+  <si>
+    <t>209/8 nguyễn duy cung, P12</t>
+  </si>
+  <si>
+    <t>Lọ Lem</t>
+  </si>
+  <si>
+    <t>HD020148</t>
+  </si>
+  <si>
+    <t>484B no trang long p13</t>
+  </si>
+  <si>
+    <t>Hải Anh</t>
+  </si>
+  <si>
+    <t>HDO1778410597940_472532</t>
+  </si>
+  <si>
+    <t>L-1506, chung cư One Verandah, số 2 Bát Nàn p. Thạnh Mỹ Lợi</t>
+  </si>
+  <si>
+    <t>Hoang Yen</t>
+  </si>
+  <si>
+    <t>HD020081</t>
+  </si>
+  <si>
+    <t>652/7A Cộng Hoà - P13</t>
+  </si>
+  <si>
+    <t>HẠNH NARIN</t>
+  </si>
+  <si>
+    <t>Nguyễn My</t>
+  </si>
+  <si>
+    <t>HD020162</t>
+  </si>
+  <si>
+    <t>Tk18/3 nguyễn cảnh chân p cầu kho</t>
+  </si>
+  <si>
+    <t>Chị Quyên fb An Nhiên</t>
+  </si>
+  <si>
+    <t>HD020066</t>
+  </si>
+  <si>
+    <t>510 Ngô Gia Tự, P.An Đông</t>
+  </si>
+  <si>
+    <t>HD020192</t>
+  </si>
+  <si>
+    <t>#301 Pham Ngu Lao Street</t>
+  </si>
+  <si>
+    <t>HD020091</t>
+  </si>
+  <si>
+    <t>594/7 điện biên phủ p10</t>
+  </si>
+  <si>
+    <t>Tram Hoang Ngoc</t>
+  </si>
+  <si>
+    <t>HD020186</t>
+  </si>
+  <si>
+    <t>105K 15 hồ thị kỷ vườn lài</t>
+  </si>
+  <si>
+    <t>Phương Anh Chu</t>
+  </si>
+  <si>
+    <t>HD020219</t>
+  </si>
+  <si>
+    <t>Chung cư Grand Riverside - 278 Bến Vân Đồn P2</t>
+  </si>
+  <si>
+    <t>Em Na</t>
+  </si>
+  <si>
+    <t>Xe Khải Nam</t>
+  </si>
+  <si>
+    <t>at 12-05</t>
+  </si>
+  <si>
     <t>THÁNG 5</t>
   </si>
   <si>
@@ -3030,214 +3242,268 @@
     <t>Lợi nhuận</t>
   </si>
   <si>
-    <t>Thế Diễm</t>
-  </si>
-  <si>
-    <t>HD020049</t>
-  </si>
-  <si>
-    <t>159 Võ Nguyên Giáp, P Thảo Điền Chung cư Masteri Thảo Điền (Tháp 3)</t>
-  </si>
-  <si>
-    <t>12-05-2026</t>
-  </si>
-  <si>
-    <t>kim xuyến</t>
-  </si>
-  <si>
-    <t>HD019918</t>
-  </si>
-  <si>
-    <t>1002 tạ quang bửu p6</t>
-  </si>
-  <si>
-    <t>AT 12-05</t>
-  </si>
-  <si>
-    <t>Trần Thị Ngọc Trâm</t>
-  </si>
-  <si>
-    <t>HD020123</t>
-  </si>
-  <si>
-    <t>5/1H đường số 11 Bình Thọ</t>
-  </si>
-  <si>
-    <t>Nguyễn My</t>
-  </si>
-  <si>
-    <t>HD020162</t>
-  </si>
-  <si>
-    <t>Tk18/3 nguyễn cảnh chân p cầu kho</t>
-  </si>
-  <si>
-    <t>Bella</t>
-  </si>
-  <si>
-    <t>HD020155</t>
-  </si>
-  <si>
-    <t>209/8 nguyễn duy cung, P12</t>
-  </si>
-  <si>
-    <t>Lọ Lem</t>
-  </si>
-  <si>
-    <t>HD020148</t>
-  </si>
-  <si>
-    <t>484B no trang long p13</t>
-  </si>
-  <si>
-    <t>Bella Tran (Lê Huy)</t>
-  </si>
-  <si>
-    <t>HD020184</t>
-  </si>
-  <si>
-    <t>67B đường T5, phường Tây Thạnh</t>
-  </si>
-  <si>
-    <t>Phạm Oanh</t>
-  </si>
-  <si>
-    <t>HD020045</t>
-  </si>
-  <si>
-    <t>Cty Eidaikake xưởng 2. đường số 8 phường tân thuận đông đường huỳnh tấn phát kcxtt</t>
-  </si>
-  <si>
-    <t>Chị Quyên fb An Nhiên</t>
-  </si>
-  <si>
-    <t>HD020066</t>
-  </si>
-  <si>
-    <t>510 Ngô Gia Tự, P.An Đông</t>
-  </si>
-  <si>
-    <t>HD020192</t>
-  </si>
-  <si>
-    <t>#301 Pham Ngu Lao Street</t>
-  </si>
-  <si>
-    <t>Hải Anh</t>
-  </si>
-  <si>
-    <t>HDO1778410597940_472532</t>
-  </si>
-  <si>
-    <t>L-1506, chung cư One Verandah, số 2 Bát Nàn p. Thạnh Mỹ Lợi</t>
-  </si>
-  <si>
-    <t>Trần Thị Kim Phương</t>
-  </si>
-  <si>
-    <t>HD020054</t>
-  </si>
-  <si>
-    <t>1870\1\98\14a tỉnh lộ 10 tân tạo bình tân</t>
-  </si>
-  <si>
-    <t>HD020091</t>
-  </si>
-  <si>
-    <t>594/7 điện biên phủ p10</t>
-  </si>
-  <si>
-    <t>Hoàng Thị Hồng</t>
-  </si>
-  <si>
-    <t>HD020036</t>
-  </si>
-  <si>
-    <t>Eco green tòa E nguyễn văn linh tân thuận tây</t>
-  </si>
-  <si>
-    <t>Trinh Kim</t>
-  </si>
-  <si>
-    <t>HD020079</t>
-  </si>
-  <si>
-    <t>2117A/9 Phạm Thế Hiển phường 6</t>
-  </si>
-  <si>
-    <t>Hoang Yen</t>
-  </si>
-  <si>
-    <t>HD020081</t>
-  </si>
-  <si>
-    <t>652/7A Cộng Hoà - P13</t>
-  </si>
-  <si>
-    <t>Thiên Nga</t>
-  </si>
-  <si>
-    <t>HD020151</t>
-  </si>
-  <si>
-    <t>S5.02 Vinhomes grand park, Nguyễn Xiển, Long Mỹ</t>
-  </si>
-  <si>
-    <t>HD020221</t>
-  </si>
-  <si>
-    <t>90a /10/10 Âu duong lân p3</t>
-  </si>
-  <si>
-    <t>Tram Hoang Ngoc</t>
-  </si>
-  <si>
-    <t>HD020186</t>
-  </si>
-  <si>
-    <t>105K 15 hồ thị kỷ vườn lài</t>
-  </si>
-  <si>
-    <t>Thu Thủy</t>
-  </si>
-  <si>
-    <t>HD020187</t>
-  </si>
-  <si>
-    <t>287 Kinh Dương Vương, P An Lạc</t>
-  </si>
-  <si>
-    <t>Phương Anh Chu</t>
-  </si>
-  <si>
-    <t>HD020219</t>
-  </si>
-  <si>
-    <t>Chung cư Grand Riverside - 278 Bến Vân Đồn P2</t>
-  </si>
-  <si>
-    <t>Đoàn Ngọc</t>
-  </si>
-  <si>
-    <t>HD020082</t>
-  </si>
-  <si>
-    <t>137/2 bình long</t>
-  </si>
-  <si>
-    <t>HẠNH NARIN</t>
-  </si>
-  <si>
-    <t>Em Na</t>
-  </si>
-  <si>
-    <t>Xe Khải Nam</t>
-  </si>
-  <si>
-    <t>at 12-05</t>
-  </si>
-  <si>
-    <t>đơn chuyển AT 12-05</t>
+    <t>huỳnh như</t>
+  </si>
+  <si>
+    <t>HD020300</t>
+  </si>
+  <si>
+    <t>387/12 phan văn trị chợ quán</t>
+  </si>
+  <si>
+    <t>13-05-2026</t>
+  </si>
+  <si>
+    <t>Sun Na</t>
+  </si>
+  <si>
+    <t>HD020281</t>
+  </si>
+  <si>
+    <t>Chung cư cardinal court toà B</t>
+  </si>
+  <si>
+    <t>AT 13-05</t>
+  </si>
+  <si>
+    <t>Roxy Nguyen</t>
+  </si>
+  <si>
+    <t>HD020452</t>
+  </si>
+  <si>
+    <t>965/14c quang Trung, P.14</t>
+  </si>
+  <si>
+    <t>Nho Nhỏ</t>
+  </si>
+  <si>
+    <t>HD020360</t>
+  </si>
+  <si>
+    <t>Số 35 đường 34 phường linh đông</t>
+  </si>
+  <si>
+    <t>tran Bảo Châu</t>
+  </si>
+  <si>
+    <t>HD020279</t>
+  </si>
+  <si>
+    <t>654/6 lạc long quân p9</t>
+  </si>
+  <si>
+    <t>Đoan Trang</t>
+  </si>
+  <si>
+    <t>HD020499</t>
+  </si>
+  <si>
+    <t>Chung cư CitiEsto, Đ. 33-CL, Cát Lái, B02-07, Phường Cát Lái</t>
+  </si>
+  <si>
+    <t>Linh Đan</t>
+  </si>
+  <si>
+    <t>HD020536</t>
+  </si>
+  <si>
+    <t>Saigon Royal; Tháp AP1, 34-35 Bến Vân Đồn, P. 12</t>
+  </si>
+  <si>
+    <t>Thanh Phương</t>
+  </si>
+  <si>
+    <t>HD020444</t>
+  </si>
+  <si>
+    <t>Tòa nhà C22 Building S6 G26, đường C22, Phường 12</t>
+  </si>
+  <si>
+    <t>Kim Nhân</t>
+  </si>
+  <si>
+    <t>HD020448</t>
+  </si>
+  <si>
+    <t>5M1/10 An Hạ</t>
+  </si>
+  <si>
+    <t>Mie Mie</t>
+  </si>
+  <si>
+    <t>HD020255</t>
+  </si>
+  <si>
+    <t>38 đường số 3, phường Tân Phú</t>
+  </si>
+  <si>
+    <t>HD020451</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Kim Thoa</t>
+  </si>
+  <si>
+    <t>HD020457</t>
+  </si>
+  <si>
+    <t>số 25a đường 22 tình hưng hòa a</t>
+  </si>
+  <si>
+    <t>gộp, shop chịu ship</t>
+  </si>
+  <si>
+    <t>Bé Ty - fb Anh Lan</t>
+  </si>
+  <si>
+    <t>HD020293</t>
+  </si>
+  <si>
+    <t>532/3/6 Kinh Dương Vương, Phường An Lạc</t>
+  </si>
+  <si>
+    <t>Tâm Vũ</t>
+  </si>
+  <si>
+    <t>HD020429</t>
+  </si>
+  <si>
+    <t>100/40/56 lê văn duyệt, phường gia định (p1 cũ)</t>
+  </si>
+  <si>
+    <t>FB NGUYỄN THỊ TRÚC NGÂN</t>
+  </si>
+  <si>
+    <t>HD020315</t>
+  </si>
+  <si>
+    <t>Số 78 Đường Số 7, P. Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>suz, fb Bei Bei</t>
+  </si>
+  <si>
+    <t>HD020337</t>
+  </si>
+  <si>
+    <t>256- 258 Lý thường kiết p14 (chung cư xi grand) Lock A2</t>
+  </si>
+  <si>
+    <t>Thanh Hương-Hương Missi</t>
+  </si>
+  <si>
+    <t>HD020496</t>
+  </si>
+  <si>
+    <t>215 Nam Kì Khởi Nghĩa Phường Võ Thị Sáu</t>
+  </si>
+  <si>
+    <t>(phan pham ngô nhi)</t>
+  </si>
+  <si>
+    <t>HD020453</t>
+  </si>
+  <si>
+    <t>403 đường tân sơn - phường an hội tây</t>
+  </si>
+  <si>
+    <t>Heng Roza (EV35382)</t>
+  </si>
+  <si>
+    <t>HD019725</t>
+  </si>
+  <si>
+    <t>Kim Tuyến</t>
+  </si>
+  <si>
+    <t>HD012977</t>
+  </si>
+  <si>
+    <t>718/3/12 trần hưng đạo p2</t>
+  </si>
+  <si>
+    <t>zalo tuyền hoàng</t>
+  </si>
+  <si>
+    <t>HD020393</t>
+  </si>
+  <si>
+    <t>433/11/2 Lê Đức Thọ, Phường Gò Vấp (phường 17 CŨ)</t>
+  </si>
+  <si>
+    <t>HD020460</t>
+  </si>
+  <si>
+    <t>Nytha</t>
+  </si>
+  <si>
+    <t>HD020287</t>
+  </si>
+  <si>
+    <t>392/2 ung văn khiêm p25</t>
+  </si>
+  <si>
+    <t>Hồng Phấn</t>
+  </si>
+  <si>
+    <t>HD020494</t>
+  </si>
+  <si>
+    <t>Ship Sảnh RS4 chung cư richstar 278 hoà bình, p.phú thạnh</t>
+  </si>
+  <si>
+    <t>Đoàn Kim</t>
+  </si>
+  <si>
+    <t>HD020450</t>
+  </si>
+  <si>
+    <t>Block D, chung cư floria đường số 1, tân hưng</t>
+  </si>
+  <si>
+    <t>HD020509</t>
+  </si>
+  <si>
+    <t>số 25a đường 22 bình hưng hòa a</t>
+  </si>
+  <si>
+    <t>lindsiepham</t>
+  </si>
+  <si>
+    <t>HD020177</t>
+  </si>
+  <si>
+    <t>landmark 5b vinhomes central park</t>
+  </si>
+  <si>
+    <t>HD020295</t>
+  </si>
+  <si>
+    <t>36 Lê Lai phường bảy Hiền</t>
+  </si>
+  <si>
+    <t>HD020486</t>
+  </si>
+  <si>
+    <t>Mai Mai</t>
+  </si>
+  <si>
+    <t>HD020230</t>
+  </si>
+  <si>
+    <t>21b lý van phức tân định</t>
+  </si>
+  <si>
+    <t>nguyễn minh hải</t>
+  </si>
+  <si>
+    <t>No. 17, Street No. 13, Binh Hung Hoa Ward</t>
+  </si>
+  <si>
+    <t>at 13-05</t>
+  </si>
+  <si>
+    <t>401 quang trung f10</t>
   </si>
 </sst>
 </file>
@@ -3391,7 +3657,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3428,13 +3694,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6458,8 +6722,8 @@
       <c r="B65" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C65" s="37"/>
-      <c r="D65" s="37"/>
+      <c r="C65" s="32"/>
+      <c r="D65" s="32"/>
       <c r="K65" s="2" t="s">
         <v>206</v>
       </c>
@@ -6475,8 +6739,8 @@
       <c r="B66" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C66" s="37"/>
-      <c r="D66" s="37"/>
+      <c r="C66" s="32"/>
+      <c r="D66" s="32"/>
       <c r="L66" s="13">
         <f>SUBTOTAL(9,L61:L65)</f>
         <v>9140</v>
@@ -6497,11 +6761,11 @@
       <c r="B68" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C68" s="38">
+      <c r="C68" s="33">
         <f>C64+C65+C66</f>
         <v>35295</v>
       </c>
-      <c r="D68" s="38"/>
+      <c r="D68" s="33"/>
       <c r="E68" s="1" t="s">
         <v>211</v>
       </c>
@@ -6719,6 +6983,1964 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A2:R61"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="54.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="18.42578125" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="8" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="15"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="15"/>
+      <c r="B3" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F3" s="16">
+        <v>7</v>
+      </c>
+      <c r="G3" s="16">
+        <v>980</v>
+      </c>
+      <c r="H3" s="16">
+        <v>30</v>
+      </c>
+      <c r="I3" s="16">
+        <f t="shared" ref="I3:I34" si="0">G3-H3</f>
+        <v>950</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G4" s="16">
+        <v>845</v>
+      </c>
+      <c r="H4" s="16">
+        <v>25</v>
+      </c>
+      <c r="I4" s="16">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="G5" s="18">
+        <v>35</v>
+      </c>
+      <c r="H5" s="18">
+        <v>35</v>
+      </c>
+      <c r="I5" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M5" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="15"/>
+      <c r="B6" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F6" s="16">
+        <v>7</v>
+      </c>
+      <c r="G6" s="16">
+        <v>900</v>
+      </c>
+      <c r="H6" s="16">
+        <v>30</v>
+      </c>
+      <c r="I6" s="16">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>1089</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="16">
+        <v>1570</v>
+      </c>
+      <c r="H7" s="16">
+        <v>35</v>
+      </c>
+      <c r="I7" s="16">
+        <f t="shared" si="0"/>
+        <v>1535</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M7" s="20" t="s">
+        <v>1090</v>
+      </c>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15">
+        <v>1</v>
+      </c>
+      <c r="R7" s="10">
+        <f>H7</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="15"/>
+      <c r="B8" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="16">
+        <v>3930</v>
+      </c>
+      <c r="H8" s="16">
+        <v>40</v>
+      </c>
+      <c r="I8" s="16">
+        <f t="shared" si="0"/>
+        <v>3890</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="15"/>
+      <c r="B9" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="16">
+        <v>0</v>
+      </c>
+      <c r="H9" s="16">
+        <v>30</v>
+      </c>
+      <c r="I9" s="16">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="15">
+        <v>1</v>
+      </c>
+      <c r="R9" s="10">
+        <f>H9</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>744</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="16">
+        <v>0</v>
+      </c>
+      <c r="H10" s="16">
+        <v>30</v>
+      </c>
+      <c r="I10" s="16">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15">
+        <v>1</v>
+      </c>
+      <c r="R10" s="10">
+        <f>H10</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="15"/>
+      <c r="B11" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>637</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>639</v>
+      </c>
+      <c r="F11" s="16">
+        <v>9</v>
+      </c>
+      <c r="G11" s="16">
+        <v>880</v>
+      </c>
+      <c r="H11" s="16">
+        <v>30</v>
+      </c>
+      <c r="I11" s="16">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="15"/>
+      <c r="B12" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="16">
+        <v>875</v>
+      </c>
+      <c r="H12" s="16">
+        <v>25</v>
+      </c>
+      <c r="I12" s="16">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F13" s="16">
+        <v>7</v>
+      </c>
+      <c r="G13" s="16">
+        <v>0</v>
+      </c>
+      <c r="H13" s="16">
+        <v>30</v>
+      </c>
+      <c r="I13" s="16">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15">
+        <v>1</v>
+      </c>
+      <c r="R13" s="10">
+        <f>H13</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="15"/>
+      <c r="B14" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="16">
+        <v>780</v>
+      </c>
+      <c r="H14" s="16">
+        <v>0</v>
+      </c>
+      <c r="I14" s="16">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M14" s="20" t="s">
+        <v>377</v>
+      </c>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="16">
+        <v>50</v>
+      </c>
+      <c r="H15" s="16">
+        <v>50</v>
+      </c>
+      <c r="I15" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="16">
+        <v>875</v>
+      </c>
+      <c r="H16" s="16">
+        <v>25</v>
+      </c>
+      <c r="I16" s="16">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="15"/>
+      <c r="B17" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="G17" s="16">
+        <v>0</v>
+      </c>
+      <c r="H17" s="16">
+        <v>30</v>
+      </c>
+      <c r="I17" s="16">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15">
+        <v>1</v>
+      </c>
+      <c r="R17" s="10">
+        <f>H17</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="15"/>
+      <c r="B18" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F18" s="16">
+        <v>2</v>
+      </c>
+      <c r="G18" s="16">
+        <v>920</v>
+      </c>
+      <c r="H18" s="16">
+        <v>30</v>
+      </c>
+      <c r="I18" s="16">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="16">
+        <v>870</v>
+      </c>
+      <c r="H19" s="16">
+        <v>20</v>
+      </c>
+      <c r="I19" s="16">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="15"/>
+      <c r="Q19" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="15"/>
+      <c r="B20" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20" s="16">
+        <v>20</v>
+      </c>
+      <c r="H20" s="16">
+        <v>20</v>
+      </c>
+      <c r="I20" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="15"/>
+      <c r="Q20" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="15"/>
+      <c r="B21" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>1108</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="16">
+        <v>0</v>
+      </c>
+      <c r="H21" s="16">
+        <v>25</v>
+      </c>
+      <c r="I21" s="16">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="15">
+        <v>1</v>
+      </c>
+      <c r="R21" s="10">
+        <f>H21</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="16">
+        <v>875</v>
+      </c>
+      <c r="H22" s="16">
+        <v>25</v>
+      </c>
+      <c r="I22" s="16">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="15"/>
+      <c r="B23" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="G23" s="16">
+        <v>0</v>
+      </c>
+      <c r="H23" s="16">
+        <v>20</v>
+      </c>
+      <c r="I23" s="16">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="15">
+        <v>1</v>
+      </c>
+      <c r="R23" s="10">
+        <f>H23</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="15"/>
+      <c r="B24" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="G24" s="16">
+        <v>840</v>
+      </c>
+      <c r="H24" s="16">
+        <v>20</v>
+      </c>
+      <c r="I24" s="16">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="16">
+        <v>30</v>
+      </c>
+      <c r="H25" s="16">
+        <v>30</v>
+      </c>
+      <c r="I25" s="16">
+        <f>G25-H25</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M25" s="15"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="15"/>
+      <c r="P25" s="15"/>
+      <c r="Q25" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" s="16">
+        <v>3955</v>
+      </c>
+      <c r="H26" s="16">
+        <v>35</v>
+      </c>
+      <c r="I26" s="16">
+        <f>G26-H26</f>
+        <v>3920</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="16">
+        <v>815</v>
+      </c>
+      <c r="H27" s="16">
+        <v>25</v>
+      </c>
+      <c r="I27" s="16">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J27" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K27" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F28" s="16">
+        <v>4</v>
+      </c>
+      <c r="G28" s="16">
+        <v>765</v>
+      </c>
+      <c r="H28" s="16">
+        <v>25</v>
+      </c>
+      <c r="I28" s="16">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G29" s="16">
+        <v>25</v>
+      </c>
+      <c r="H29" s="16">
+        <v>25</v>
+      </c>
+      <c r="I29" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="15"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="15"/>
+      <c r="B30" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F30" s="16">
+        <v>10</v>
+      </c>
+      <c r="G30" s="16">
+        <v>725</v>
+      </c>
+      <c r="H30" s="16">
+        <v>25</v>
+      </c>
+      <c r="I30" s="16">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M30" s="15"/>
+      <c r="N30" s="15"/>
+      <c r="O30" s="15"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="15"/>
+      <c r="B31" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F31" s="16">
+        <v>3</v>
+      </c>
+      <c r="G31" s="16">
+        <v>765</v>
+      </c>
+      <c r="H31" s="16">
+        <v>25</v>
+      </c>
+      <c r="I31" s="16">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J31" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K31" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M31" s="15"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="15"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="15"/>
+      <c r="B32" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F32" s="16">
+        <v>5</v>
+      </c>
+      <c r="G32" s="16">
+        <v>1115</v>
+      </c>
+      <c r="H32" s="16">
+        <v>25</v>
+      </c>
+      <c r="I32" s="16">
+        <f t="shared" si="0"/>
+        <v>1090</v>
+      </c>
+      <c r="J32" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K32" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" s="15"/>
+      <c r="B33" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G33" s="16">
+        <v>815</v>
+      </c>
+      <c r="H33" s="16">
+        <v>25</v>
+      </c>
+      <c r="I33" s="16">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K33" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M33" s="15"/>
+      <c r="N33" s="15"/>
+      <c r="O33" s="15"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="17"/>
+      <c r="B34" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F34" s="18">
+        <v>4</v>
+      </c>
+      <c r="G34" s="18">
+        <v>45</v>
+      </c>
+      <c r="H34" s="18">
+        <v>25</v>
+      </c>
+      <c r="I34" s="18">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="J34" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="K34" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" s="17" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M34" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" s="15"/>
+      <c r="B35" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F35" s="16">
+        <v>1</v>
+      </c>
+      <c r="G35" s="16">
+        <v>765</v>
+      </c>
+      <c r="H35" s="16">
+        <v>25</v>
+      </c>
+      <c r="I35" s="16">
+        <f t="shared" ref="I35" si="1">G35-H35</f>
+        <v>740</v>
+      </c>
+      <c r="J35" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K35" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M35" s="15"/>
+      <c r="N35" s="15"/>
+      <c r="O35" s="15"/>
+      <c r="P35" s="15"/>
+      <c r="Q35" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D37" s="1">
+        <f>COUNTA(D3:D35)</f>
+        <v>30</v>
+      </c>
+      <c r="G37" s="1">
+        <f t="shared" ref="G37:Q37" si="2">SUBTOTAL(9,G3:G35)</f>
+        <v>25065</v>
+      </c>
+      <c r="H37" s="1">
+        <f t="shared" si="2"/>
+        <v>895</v>
+      </c>
+      <c r="I37" s="1">
+        <f t="shared" si="2"/>
+        <v>24170</v>
+      </c>
+      <c r="J37" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N37" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O37" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P37" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q37" s="1">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H38">
+        <f>-5*17</f>
+        <v>-85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="D39" s="34"/>
+      <c r="E39" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="H39">
+        <f>-7*25</f>
+        <v>-175</v>
+      </c>
+      <c r="K39" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="L39" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="M39" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="O39" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C40" s="35">
+        <f>SUMIFS(I$3:I$35,B$3:B$35,A$39,L$3:L$35,A$40)</f>
+        <v>24170</v>
+      </c>
+      <c r="D40" s="35"/>
+      <c r="E40" s="3">
+        <f>SUMIFS(Q$3:Q$35,B$3:B$35,A$39,L$3:L$35,A$40)</f>
+        <v>33</v>
+      </c>
+      <c r="F40" t="s">
+        <v>196</v>
+      </c>
+      <c r="H40">
+        <f>-1*30</f>
+        <v>-30</v>
+      </c>
+      <c r="K40" t="s">
+        <v>197</v>
+      </c>
+      <c r="L40">
+        <f>SUMIFS(G$3:G$35,J$3:J$35,K$39)</f>
+        <v>5835</v>
+      </c>
+      <c r="M40">
+        <f>SUMIFS(Q$3:Q$35,J$3:J$35,K$39)-INT(COUNTIFS(J$3:J$35,K$39,M$3:M$35,"*gộp*")/2)</f>
+        <v>9</v>
+      </c>
+      <c r="O40" t="s">
+        <v>135</v>
+      </c>
+      <c r="P40">
+        <f>L45</f>
+        <v>5655</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B41" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C41" s="36">
+        <v>0</v>
+      </c>
+      <c r="D41" s="36"/>
+      <c r="K41" t="s">
+        <v>200</v>
+      </c>
+      <c r="L41">
+        <f>-SUMIFS(H$3:H$35,J$3:J$35,K$39)+M41*5</f>
+        <v>-180</v>
+      </c>
+      <c r="M41">
+        <f>SUMIFS(Q$3:Q$35,J$3:J$35,K$39)-INT(COUNTIFS(J$3:J$35,K$39,M$3:M$35,"*gộp*")/2)</f>
+        <v>9</v>
+      </c>
+      <c r="O41" t="s">
+        <v>1140</v>
+      </c>
+      <c r="P41">
+        <f>L53</f>
+        <v>10555</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B42" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C42" s="36">
+        <f>-SUMIFS(I$3:I$35,B$3:B$35,A$39,P$3:P$35,"xx",N$3:N$35,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="D42" s="36"/>
+      <c r="E42" s="2">
+        <f>SUMIFS(Q$3:Q$35,B$3:B$35,A$39,P$3:P$35,"xx",N$3:N$35,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="K42" t="s">
+        <v>202</v>
+      </c>
+      <c r="O42" t="s">
+        <v>21</v>
+      </c>
+      <c r="P42">
+        <f>L61</f>
+        <v>8096</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B43" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C43" s="34">
+        <f>SUBTOTAL(9,C40:C42)</f>
+        <v>24170</v>
+      </c>
+      <c r="D43" s="34"/>
+      <c r="E43">
+        <f>E40</f>
+        <v>33</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="O43" t="s">
+        <v>207</v>
+      </c>
+      <c r="P43">
+        <f>-C47</f>
+        <v>-24170</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B44" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="K44" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="O44" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="P44" s="4">
+        <f>SUBTOTAL(9,P40:P43)</f>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B45" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
+      <c r="L45" s="13">
+        <f>SUBTOTAL(9,L40:L44)</f>
+        <v>5655</v>
+      </c>
+      <c r="M45" s="13">
+        <f>M40</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B47" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C47" s="33">
+        <f>C43+C44+C45</f>
+        <v>24170</v>
+      </c>
+      <c r="D47" s="33"/>
+      <c r="E47" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>1061</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K48" t="s">
+        <v>197</v>
+      </c>
+      <c r="L48">
+        <f>SUMIFS(G$3:G$35,J$3:J$35,K$47)</f>
+        <v>10845</v>
+      </c>
+      <c r="M48">
+        <f>SUMIFS(Q$3:Q$35,J$3:J$35,K$47)-INT(COUNTIFS(J$3:J$35,K$47,M$3:M$35,"*gộp*")/2)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K49" t="s">
+        <v>200</v>
+      </c>
+      <c r="L49">
+        <f>SUM(H38:H40)</f>
+        <v>-290</v>
+      </c>
+      <c r="M49">
+        <f>SUMIFS(Q$3:Q$35,J$3:J$35,K$47)-INT(COUNTIFS(J$3:J$35,K$47,M$3:M$35,"*gộp*")/2)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K50" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="51" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K51" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="52" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K52" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="53" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L53" s="13">
+        <f>SUBTOTAL(9,L48:L52)</f>
+        <v>10555</v>
+      </c>
+      <c r="M53" s="13">
+        <f>M48</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K55" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L55" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="M55" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="56" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K56" t="s">
+        <v>197</v>
+      </c>
+      <c r="L56">
+        <f>SUMIFS(G$3:G$35,J$3:J$35,K$55)</f>
+        <v>8385</v>
+      </c>
+      <c r="M56">
+        <f>SUMIFS(Q$3:Q$35,J$3:J$35,K$55)-INT(COUNTIFS(J$3:J$35,K$55,M$3:M$35,"*gộp*")/2)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K57" t="s">
+        <v>200</v>
+      </c>
+      <c r="L57">
+        <f>-SUMIFS(H$3:H$35,J$3:J$35,K$55)+M57*5</f>
+        <v>-225</v>
+      </c>
+      <c r="M57">
+        <f>SUMIFS(Q$3:Q$35,J$3:J$35,K$55)-INT(COUNTIFS(J$3:J$35,K$55,M$3:M$35,"*gộp*")/2)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K58" t="s">
+        <v>202</v>
+      </c>
+      <c r="L58">
+        <f>-M58*2</f>
+        <v>-64</v>
+      </c>
+      <c r="M58">
+        <f>E43-(COUNTIFS(M$3:M$35,"*gộp*")/2)-COUNTIFS(M$3:M$35,"*đơn trả*")-COUNTIFS(M$3:M$35,"*hàng tỉnh*")</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="59" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K59" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="60" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K60" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="61" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L61" s="13">
+        <f>SUBTOTAL(9,L56:L60)</f>
+        <v>8096</v>
+      </c>
+      <c r="M61" s="13">
+        <f>M56</f>
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P35" xr:uid="{00000000-0009-0000-0000-00000A000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P35">
+      <sortCondition ref="J2:J35"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D9B982-EAEB-4F31-86BF-4D059AFDEA27}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
@@ -6737,7 +8959,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>974</v>
+        <v>1044</v>
       </c>
       <c r="B1" s="5">
         <v>2026</v>
@@ -6745,19 +8967,19 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>975</v>
+        <v>1045</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>976</v>
+        <v>1046</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>977</v>
+        <v>1047</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>978</v>
+        <v>1048</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>979</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -6954,7 +9176,7 @@
         <v>46154</v>
       </c>
       <c r="B12" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A12,"dd-mm")&amp;"'!L3:L200"),TEXT(A12,"dd-mm")&amp;"-"&amp;B$1),0)</f>
+        <f t="shared" ca="1" si="1"/>
         <v>25</v>
       </c>
       <c r="C12" s="8">
@@ -6976,11 +9198,11 @@
       </c>
       <c r="B13" s="8">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C13" s="8">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="8" cm="1">
         <f t="array" aca="1" ref="D13" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A13,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
@@ -6988,7 +9210,7 @@
       </c>
       <c r="E13" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -7308,16 +9530,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D29" s="9" t="s">
-        <v>980</v>
+        <v>1050</v>
       </c>
       <c r="E29" s="9">
         <f ca="1">SUBTOTAL(9,E4:E28)</f>
-        <v>276</v>
+        <v>308</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D30" s="9" t="s">
-        <v>981</v>
+        <v>1051</v>
       </c>
       <c r="E30" s="9" cm="1">
         <f t="array" ref="E30" ca="1">SUMPRODUCT(
@@ -7329,29 +9551,29 @@
         ),
     0)
 )</f>
-        <v>1078</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D31" s="9" t="s">
-        <v>982</v>
+        <v>1052</v>
       </c>
       <c r="E31" s="9">
         <f ca="1">-E29*2</f>
-        <v>-552</v>
+        <v>-616</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D32" s="9" t="s">
-        <v>983</v>
+        <v>1053</v>
       </c>
       <c r="E32" s="9">
         <f ca="1">SUBTOTAL(9,E30:E31)</f>
-        <v>526</v>
+        <v>598</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E28" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
+  <autoFilter ref="A2:E28" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C3:D28">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -8756,8 +10978,8 @@
       <c r="B35" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C35" s="37"/>
-      <c r="D35" s="37"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
       <c r="K35" s="2" t="s">
         <v>206</v>
       </c>
@@ -8773,8 +10995,8 @@
       <c r="B36" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C36" s="37"/>
-      <c r="D36" s="37"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
       <c r="L36" s="13">
         <f>SUBTOTAL(9,L31:L35)</f>
         <v>2401</v>
@@ -8795,11 +11017,11 @@
       <c r="B38" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C38" s="38">
+      <c r="C38" s="33">
         <f>C34+C35+C36</f>
         <v>6225</v>
       </c>
-      <c r="D38" s="38"/>
+      <c r="D38" s="33"/>
       <c r="E38" s="1" t="s">
         <v>211</v>
       </c>
@@ -11657,8 +13879,8 @@
       <c r="B64" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C64" s="37"/>
-      <c r="D64" s="37"/>
+      <c r="C64" s="32"/>
+      <c r="D64" s="32"/>
       <c r="K64" s="2" t="s">
         <v>206</v>
       </c>
@@ -11674,10 +13896,10 @@
       <c r="B65" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C65" s="37">
+      <c r="C65" s="32">
         <v>-30</v>
       </c>
-      <c r="D65" s="37"/>
+      <c r="D65" s="32"/>
       <c r="L65" s="13">
         <f>SUBTOTAL(9,L60:L64)</f>
         <v>21245</v>
@@ -11691,11 +13913,11 @@
       <c r="B67" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C67" s="38">
+      <c r="C67" s="33">
         <f>C63+C64+C65</f>
         <v>37860</v>
       </c>
-      <c r="D67" s="38"/>
+      <c r="D67" s="33"/>
       <c r="E67" s="1" t="s">
         <v>211</v>
       </c>
@@ -13546,8 +15768,8 @@
       <c r="B43" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="37"/>
-      <c r="D43" s="37"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
       <c r="K43" s="2" t="s">
         <v>206</v>
       </c>
@@ -13563,8 +15785,8 @@
       <c r="B44" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C44" s="37"/>
-      <c r="D44" s="37"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
       <c r="L44" s="13">
         <f>SUBTOTAL(9,L39:L43)</f>
         <v>11135</v>
@@ -13578,11 +15800,11 @@
       <c r="B46" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C46" s="38">
+      <c r="C46" s="33">
         <f>C42+C43+C44</f>
         <v>22325</v>
       </c>
-      <c r="D46" s="38"/>
+      <c r="D46" s="33"/>
       <c r="E46" s="1" t="s">
         <v>211</v>
       </c>
@@ -15576,8 +17798,8 @@
       <c r="B45" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C45" s="37"/>
-      <c r="D45" s="37"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
       <c r="K45" s="2" t="s">
         <v>206</v>
       </c>
@@ -15593,8 +17815,8 @@
       <c r="B46" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C46" s="37"/>
-      <c r="D46" s="37"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
       <c r="L46" s="13">
         <f>SUBTOTAL(9,L41:L45)</f>
         <v>5021</v>
@@ -15615,11 +17837,11 @@
       <c r="B48" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C48" s="38">
+      <c r="C48" s="33">
         <f>C44+C45+C46</f>
         <v>17615</v>
       </c>
-      <c r="D48" s="38"/>
+      <c r="D48" s="33"/>
       <c r="E48" s="1" t="s">
         <v>211</v>
       </c>
@@ -17809,8 +20031,8 @@
       <c r="B48" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C48" s="37"/>
-      <c r="D48" s="37"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
       <c r="K48" s="2" t="s">
         <v>206</v>
       </c>
@@ -17826,8 +20048,8 @@
       <c r="B49" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C49" s="37"/>
-      <c r="D49" s="37"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
       <c r="L49" s="13">
         <f>SUBTOTAL(9,L44:L48)</f>
         <v>3645</v>
@@ -17841,11 +20063,11 @@
       <c r="B51" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C51" s="38">
+      <c r="C51" s="33">
         <f>C47+C48+C49</f>
         <v>15491</v>
       </c>
-      <c r="D51" s="38"/>
+      <c r="D51" s="33"/>
       <c r="E51" s="1" t="s">
         <v>211</v>
       </c>
@@ -19703,8 +21925,8 @@
       <c r="B42" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C42" s="37"/>
-      <c r="D42" s="37"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
       <c r="K42" s="2" t="s">
         <v>206</v>
       </c>
@@ -19720,8 +21942,8 @@
       <c r="B43" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C43" s="37"/>
-      <c r="D43" s="37"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
       <c r="L43" s="13">
         <f>SUBTOTAL(9,L38:L42)</f>
         <v>3183</v>
@@ -19735,11 +21957,11 @@
       <c r="B45" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C45" s="38">
+      <c r="C45" s="33">
         <f>C41+C42+C43</f>
         <v>27540</v>
       </c>
-      <c r="D45" s="38"/>
+      <c r="D45" s="33"/>
       <c r="E45" s="1" t="s">
         <v>211</v>
       </c>
@@ -21184,14 +23406,14 @@
         <v>2</v>
       </c>
       <c r="G30" s="16">
-        <v>790</v>
+        <v>820</v>
       </c>
       <c r="H30" s="16">
         <v>30</v>
       </c>
       <c r="I30" s="16">
         <f t="shared" si="0"/>
-        <v>760</v>
+        <v>790</v>
       </c>
       <c r="J30" s="15" t="s">
         <v>21</v>
@@ -22661,7 +24883,7 @@
       </c>
       <c r="G64" s="1">
         <f t="shared" ref="G64:Q64" si="2">SUBTOTAL(9,G3:G62)</f>
-        <v>43360</v>
+        <v>43390</v>
       </c>
       <c r="H64" s="1">
         <f t="shared" si="2"/>
@@ -22669,7 +24891,7 @@
       </c>
       <c r="I64" s="1">
         <f t="shared" si="2"/>
-        <v>41700</v>
+        <v>41730</v>
       </c>
       <c r="J64" s="1">
         <f t="shared" si="2"/>
@@ -22754,7 +24976,7 @@
       </c>
       <c r="C67" s="35">
         <f>SUMIFS(I$3:I$62,B$3:B$62,A$66,L$3:L$62,A$67)</f>
-        <v>38340</v>
+        <v>38370</v>
       </c>
       <c r="D67" s="35"/>
       <c r="E67" s="3">
@@ -22835,7 +25057,7 @@
       </c>
       <c r="P69">
         <f>L88</f>
-        <v>10526</v>
+        <v>10556</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
@@ -22844,7 +25066,7 @@
       </c>
       <c r="C70" s="34">
         <f>SUBTOTAL(9,C67:C69)</f>
-        <v>34980</v>
+        <v>35010</v>
       </c>
       <c r="D70" s="34"/>
       <c r="E70">
@@ -22859,15 +25081,15 @@
       </c>
       <c r="P70">
         <f>-C74</f>
-        <v>-34980</v>
+        <v>-35010</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B71" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C71" s="37"/>
-      <c r="D71" s="37"/>
+      <c r="C71" s="32"/>
+      <c r="D71" s="32"/>
       <c r="K71" s="2" t="s">
         <v>206</v>
       </c>
@@ -22883,8 +25105,8 @@
       <c r="B72" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C72" s="37"/>
-      <c r="D72" s="37"/>
+      <c r="C72" s="32"/>
+      <c r="D72" s="32"/>
       <c r="L72" s="13">
         <f>SUBTOTAL(9,L67:L71)</f>
         <v>15015</v>
@@ -22898,11 +25120,11 @@
       <c r="B74" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C74" s="38">
+      <c r="C74" s="33">
         <f>C70+C71+C72</f>
-        <v>34980</v>
-      </c>
-      <c r="D74" s="38"/>
+        <v>35010</v>
+      </c>
+      <c r="D74" s="33"/>
       <c r="E74" s="1" t="s">
         <v>211</v>
       </c>
@@ -22990,7 +25212,7 @@
       </c>
       <c r="L83">
         <f>SUMIFS(G$3:G$62,J$3:J$62,K$82)</f>
-        <v>10980</v>
+        <v>11010</v>
       </c>
       <c r="M83">
         <f>SUMIFS(Q$3:Q$62,J$3:J$62,K$82)-INT(COUNTIFS(J$3:J$62,K$82,M$3:M$62,"*gộp*")/2)</f>
@@ -23036,7 +25258,7 @@
     <row r="88" spans="11:13" x14ac:dyDescent="0.25">
       <c r="L88" s="13">
         <f>SUBTOTAL(9,L83:L87)</f>
-        <v>10526</v>
+        <v>10556</v>
       </c>
       <c r="M88" s="13">
         <f>M83</f>
@@ -23143,13 +25365,13 @@
         <v>17</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>1032</v>
+        <v>974</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>1033</v>
+        <v>975</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>1034</v>
+        <v>976</v>
       </c>
       <c r="F3" s="16">
         <v>9</v>
@@ -23171,7 +25393,7 @@
         <v>21</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M3" s="15"/>
       <c r="N3" s="15"/>
@@ -23187,13 +25409,13 @@
         <v>17</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>988</v>
+        <v>978</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>989</v>
+        <v>979</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>990</v>
+        <v>980</v>
       </c>
       <c r="F4" s="16">
         <v>8</v>
@@ -23209,13 +25431,13 @@
         <v>990</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>991</v>
+        <v>981</v>
       </c>
       <c r="K4" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M4" s="15"/>
       <c r="N4" s="15"/>
@@ -23231,13 +25453,13 @@
         <v>17</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>1004</v>
+        <v>982</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>1005</v>
+        <v>983</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>1006</v>
+        <v>984</v>
       </c>
       <c r="F5" s="15" t="s">
         <v>46</v>
@@ -23253,13 +25475,13 @@
         <v>-25</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>991</v>
+        <v>981</v>
       </c>
       <c r="K5" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M5" s="15"/>
       <c r="N5" s="15"/>
@@ -23279,13 +25501,13 @@
         <v>17</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>1007</v>
+        <v>985</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>1008</v>
+        <v>986</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>1009</v>
+        <v>987</v>
       </c>
       <c r="F6" s="16">
         <v>7</v>
@@ -23301,13 +25523,13 @@
         <v>370</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>991</v>
+        <v>981</v>
       </c>
       <c r="K6" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M6" s="15"/>
       <c r="N6" s="15"/>
@@ -23323,13 +25545,13 @@
         <v>17</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>1018</v>
+        <v>988</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>1019</v>
+        <v>989</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>26</v>
@@ -23345,13 +25567,13 @@
         <v>890</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>991</v>
+        <v>981</v>
       </c>
       <c r="K7" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M7" s="15"/>
       <c r="N7" s="15"/>
@@ -23367,13 +25589,13 @@
         <v>17</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>1023</v>
+        <v>991</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>1024</v>
+        <v>992</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>1025</v>
+        <v>993</v>
       </c>
       <c r="F8" s="16">
         <v>7</v>
@@ -23389,13 +25611,13 @@
         <v>890</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>991</v>
+        <v>981</v>
       </c>
       <c r="K8" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
@@ -23411,13 +25633,13 @@
         <v>17</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>1026</v>
+        <v>994</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>1027</v>
+        <v>995</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>1028</v>
+        <v>996</v>
       </c>
       <c r="F9" s="16">
         <v>8</v>
@@ -23433,13 +25655,13 @@
         <v>950</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>991</v>
+        <v>981</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M9" s="15"/>
       <c r="N9" s="15"/>
@@ -23458,10 +25680,10 @@
         <v>549</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>1035</v>
+        <v>997</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>1036</v>
+        <v>998</v>
       </c>
       <c r="F10" s="16">
         <v>8</v>
@@ -23477,13 +25699,13 @@
         <v>870</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>991</v>
+        <v>981</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M10" s="15"/>
       <c r="N10" s="15"/>
@@ -23499,13 +25721,13 @@
         <v>17</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>1040</v>
+        <v>999</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>1041</v>
+        <v>1000</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>1042</v>
+        <v>1001</v>
       </c>
       <c r="F11" s="15" t="s">
         <v>26</v>
@@ -23521,13 +25743,13 @@
         <v>640</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>991</v>
+        <v>981</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
@@ -23543,13 +25765,13 @@
         <v>17</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>1046</v>
+        <v>1002</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>1047</v>
+        <v>1003</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>1048</v>
+        <v>1004</v>
       </c>
       <c r="F12" s="15" t="s">
         <v>26</v>
@@ -23565,13 +25787,13 @@
         <v>890</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>991</v>
+        <v>981</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M12" s="15"/>
       <c r="N12" s="15"/>
@@ -23609,7 +25831,7 @@
         <v>890</v>
       </c>
       <c r="J13" s="28" t="s">
-        <v>991</v>
+        <v>981</v>
       </c>
       <c r="K13" s="28" t="s">
         <v>21</v>
@@ -23618,7 +25840,7 @@
         <v>813</v>
       </c>
       <c r="M13" s="28" t="s">
-        <v>1053</v>
+        <v>1005</v>
       </c>
       <c r="N13" s="28"/>
       <c r="O13" s="28"/>
@@ -23633,13 +25855,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>984</v>
+        <v>1006</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>985</v>
+        <v>1007</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>986</v>
+        <v>1008</v>
       </c>
       <c r="F14" s="16">
         <v>2</v>
@@ -23661,7 +25883,7 @@
         <v>21</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M14" s="15"/>
       <c r="N14" s="15"/>
@@ -23677,13 +25899,13 @@
         <v>17</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>992</v>
+        <v>1009</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>993</v>
+        <v>1010</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>994</v>
+        <v>1011</v>
       </c>
       <c r="F15" s="15" t="s">
         <v>81</v>
@@ -23705,7 +25927,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M15" s="15"/>
       <c r="N15" s="15"/>
@@ -23721,13 +25943,13 @@
         <v>17</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>998</v>
+        <v>1012</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>999</v>
+        <v>1013</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>1000</v>
+        <v>1014</v>
       </c>
       <c r="F16" s="15" t="s">
         <v>77</v>
@@ -23749,7 +25971,7 @@
         <v>21</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M16" s="15"/>
       <c r="N16" s="15"/>
@@ -23769,13 +25991,13 @@
         <v>17</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>1001</v>
+        <v>1015</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>1002</v>
+        <v>1016</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>1003</v>
+        <v>1017</v>
       </c>
       <c r="F17" s="15" t="s">
         <v>85</v>
@@ -23797,7 +26019,7 @@
         <v>21</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M17" s="15"/>
       <c r="N17" s="15"/>
@@ -23813,13 +26035,13 @@
         <v>17</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="F18" s="16">
         <v>2</v>
@@ -23841,7 +26063,7 @@
         <v>21</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M18" s="15"/>
       <c r="N18" s="15"/>
@@ -23857,13 +26079,13 @@
         <v>17</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>1029</v>
+        <v>1021</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>1030</v>
+        <v>1022</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>1031</v>
+        <v>1023</v>
       </c>
       <c r="F19" s="15" t="s">
         <v>95</v>
@@ -23885,7 +26107,7 @@
         <v>21</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M19" s="15"/>
       <c r="N19" s="15"/>
@@ -23903,7 +26125,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>1049</v>
+        <v>1024</v>
       </c>
       <c r="D20" s="15"/>
       <c r="E20" s="15" t="s">
@@ -23929,7 +26151,7 @@
         <v>21</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M20" s="15"/>
       <c r="N20" s="15"/>
@@ -23949,13 +26171,13 @@
         <v>17</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>995</v>
+        <v>1025</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>996</v>
+        <v>1026</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>997</v>
+        <v>1027</v>
       </c>
       <c r="F21" s="16">
         <v>1</v>
@@ -23977,7 +26199,7 @@
         <v>21</v>
       </c>
       <c r="L21" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M21" s="15"/>
       <c r="N21" s="15"/>
@@ -23993,13 +26215,13 @@
         <v>17</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>1010</v>
+        <v>1028</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>1011</v>
+        <v>1029</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>1012</v>
+        <v>1030</v>
       </c>
       <c r="F22" s="16">
         <v>5</v>
@@ -24021,7 +26243,7 @@
         <v>21</v>
       </c>
       <c r="L22" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M22" s="20" t="s">
         <v>167</v>
@@ -24046,10 +26268,10 @@
         <v>791</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>1013</v>
+        <v>1031</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>1014</v>
+        <v>1032</v>
       </c>
       <c r="F23" s="16">
         <v>1</v>
@@ -24071,7 +26293,7 @@
         <v>21</v>
       </c>
       <c r="L23" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M23" s="15"/>
       <c r="N23" s="15"/>
@@ -24081,7 +26303,7 @@
         <v>1</v>
       </c>
       <c r="R23" s="10">
-        <f t="shared" ref="R23:R24" si="1">H23</f>
+        <f>H23</f>
         <v>25</v>
       </c>
     </row>
@@ -24094,10 +26316,10 @@
         <v>706</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>1021</v>
+        <v>1033</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>1022</v>
+        <v>1034</v>
       </c>
       <c r="F24" s="16">
         <v>10</v>
@@ -24119,7 +26341,7 @@
         <v>21</v>
       </c>
       <c r="L24" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M24" s="15"/>
       <c r="N24" s="15"/>
@@ -24129,7 +26351,7 @@
         <v>1</v>
       </c>
       <c r="R24" s="10">
-        <f t="shared" si="1"/>
+        <f>H24</f>
         <v>25</v>
       </c>
     </row>
@@ -24139,13 +26361,13 @@
         <v>17</v>
       </c>
       <c r="C25" s="15" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E25" s="15" t="s">
         <v>1037</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>1038</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>1039</v>
       </c>
       <c r="F25" s="16">
         <v>10</v>
@@ -24167,7 +26389,7 @@
         <v>21</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
@@ -24183,13 +26405,13 @@
         <v>17</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="F26" s="16">
         <v>4</v>
@@ -24211,7 +26433,7 @@
         <v>21</v>
       </c>
       <c r="L26" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M26" s="15"/>
       <c r="N26" s="15"/>
@@ -24229,11 +26451,11 @@
         <v>17</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>1050</v>
+        <v>1041</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="15" t="s">
-        <v>1051</v>
+        <v>1042</v>
       </c>
       <c r="F27" s="16">
         <v>5</v>
@@ -24255,7 +26477,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M27" s="15"/>
       <c r="N27" s="15"/>
@@ -24303,7 +26525,7 @@
         <v>21</v>
       </c>
       <c r="L28" s="15" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="M28" s="15"/>
       <c r="N28" s="15"/>
@@ -24313,78 +26535,53 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A29" s="32"/>
-      <c r="B29" s="32"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
-      <c r="L29" s="32"/>
-      <c r="M29" s="32"/>
-      <c r="N29" s="32"/>
-      <c r="O29" s="32"/>
-      <c r="P29" s="32"/>
-      <c r="Q29" s="32"/>
-      <c r="R29" s="32"/>
-    </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30" s="32"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="33">
+      <c r="D30" s="1">
         <f>COUNTA(D3:D28)</f>
         <v>23</v>
       </c>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="33">
-        <f t="shared" ref="G30:Q30" si="2">SUBTOTAL(9,G3:G28)</f>
+      <c r="G30" s="1">
+        <f t="shared" ref="G30:Q30" si="1">SUBTOTAL(9,G3:G28)</f>
         <v>18875</v>
       </c>
-      <c r="H30" s="33">
-        <f t="shared" si="2"/>
+      <c r="H30" s="1">
+        <f t="shared" si="1"/>
         <v>735</v>
       </c>
-      <c r="I30" s="33">
-        <f t="shared" si="2"/>
+      <c r="I30" s="1">
+        <f t="shared" si="1"/>
         <v>18140</v>
       </c>
-      <c r="J30" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K30" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L30" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M30" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N30" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O30" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P30" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="33">
-        <f t="shared" si="2"/>
+      <c r="J30" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N30" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O30" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P30" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="1">
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
     </row>
@@ -24424,7 +26621,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>195</v>
@@ -24480,7 +26677,7 @@
         <v>7</v>
       </c>
       <c r="O34" t="s">
-        <v>1052</v>
+        <v>1043</v>
       </c>
       <c r="P34">
         <f>L46</f>
@@ -24547,8 +26744,8 @@
       <c r="B37" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
       <c r="K37" s="2" t="s">
         <v>206</v>
       </c>
@@ -24564,8 +26761,8 @@
       <c r="B38" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C38" s="37"/>
-      <c r="D38" s="37"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
       <c r="L38" s="13">
         <f>SUBTOTAL(9,L33:L37)</f>
         <v>5160</v>
@@ -24586,16 +26783,16 @@
       <c r="B40" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C40" s="38">
+      <c r="C40" s="33">
         <f>C36+C37+C38</f>
         <v>17250</v>
       </c>
-      <c r="D40" s="38"/>
+      <c r="D40" s="33"/>
       <c r="E40" s="1" t="s">
         <v>211</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>991</v>
+        <v>981</v>
       </c>
       <c r="L40" s="11" t="s">
         <v>193</v>
@@ -24718,15 +26915,15 @@
       <c r="B47" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C47" s="37"/>
-      <c r="D47" s="37"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B48" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C48" s="37"/>
-      <c r="D48" s="37"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
       <c r="K48" s="11" t="s">
         <v>135</v>
       </c>
@@ -24754,11 +26951,11 @@
       <c r="B50" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C50" s="38">
+      <c r="C50" s="33">
         <f>C46+C47+C48</f>
         <v>890</v>
       </c>
-      <c r="D50" s="38"/>
+      <c r="D50" s="33"/>
       <c r="E50" s="1" t="s">
         <v>211</v>
       </c>
@@ -24793,7 +26990,7 @@
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.25">
       <c r="K54" s="2" t="s">
-        <v>1053</v>
+        <v>1005</v>
       </c>
       <c r="L54" s="23">
         <v>-915</v>
@@ -24875,7 +27072,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P28" xr:uid="{00000000-0009-0000-0000-000009000000}">
+  <autoFilter ref="A2:P28" xr:uid="{00000000-0009-0000-0000-000008000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P28">
       <sortCondition ref="J2:J28"/>
     </sortState>

--- a/data/May/InternalDailyReport_May.xlsx
+++ b/data/May/InternalDailyReport_May.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91E1A20-E297-448F-A84E-12C356277CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2E20BA-AC9A-46FC-A7BF-907A28B07787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="7" r:id="rId1"/>
@@ -27,7 +27,8 @@
     <sheet name="15-05" sheetId="20" r:id="rId12"/>
     <sheet name="16-05" sheetId="21" r:id="rId13"/>
     <sheet name="18-05" sheetId="22" r:id="rId14"/>
-    <sheet name="Sheet1" sheetId="19" r:id="rId15"/>
+    <sheet name="19-05" sheetId="23" r:id="rId15"/>
+    <sheet name="Sheet1" sheetId="19" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01-05'!$A$2:$P$56</definedName>
@@ -44,7 +45,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'15-05'!$A$2:$P$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'16-05'!$A$2:$P$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'18-05'!$A$2:$P$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">Sheet1!$A$2:$E$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'19-05'!$A$2:$P$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">Sheet1!$A$2:$E$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -86,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5011" uniqueCount="1524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5282" uniqueCount="1593">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -4351,6 +4353,285 @@
     <t>at 16-05</t>
   </si>
   <si>
+    <t>Quỳnh Nga</t>
+  </si>
+  <si>
+    <t>HD021747</t>
+  </si>
+  <si>
+    <t>56/7 đường Tân Hoà 2 phường Hiệp Phú</t>
+  </si>
+  <si>
+    <t>18-05-2026</t>
+  </si>
+  <si>
+    <t>Hợp Vũ</t>
+  </si>
+  <si>
+    <t>HD021640</t>
+  </si>
+  <si>
+    <t>2A Phan Chu Trinh, P Hiệp Phú</t>
+  </si>
+  <si>
+    <t>AT 18-05</t>
+  </si>
+  <si>
+    <t>HD021621</t>
+  </si>
+  <si>
+    <t>Heng Roza (EV38382)</t>
+  </si>
+  <si>
+    <t>HD020691</t>
+  </si>
+  <si>
+    <t>HD021855</t>
+  </si>
+  <si>
+    <t>Ngọc Hồng Thương</t>
+  </si>
+  <si>
+    <t>HD021553</t>
+  </si>
+  <si>
+    <t>51 đường 81 tân quy</t>
+  </si>
+  <si>
+    <t>PIMVIPA 3883</t>
+  </si>
+  <si>
+    <t>HD021837</t>
+  </si>
+  <si>
+    <t>Gia Tuệ</t>
+  </si>
+  <si>
+    <t>HD021808</t>
+  </si>
+  <si>
+    <t>42/32 trần đại nghĩa, tân tạo a</t>
+  </si>
+  <si>
+    <t>HSM RIDA CHUON</t>
+  </si>
+  <si>
+    <t>HD021615</t>
+  </si>
+  <si>
+    <t>177c đường số 1 bình hưng hòa b</t>
+  </si>
+  <si>
+    <t>Nga Còi</t>
+  </si>
+  <si>
+    <t>Sửa xe Anh Sơn, liên ấp 2,3,4 Vĩnh Lộc A</t>
+  </si>
+  <si>
+    <t>HD021418</t>
+  </si>
+  <si>
+    <t>Central premium lock A</t>
+  </si>
+  <si>
+    <t>Ái Nương</t>
+  </si>
+  <si>
+    <t>HD021666</t>
+  </si>
+  <si>
+    <t>154/33 au dương lân phường 3</t>
+  </si>
+  <si>
+    <t>chị Bích Huyền</t>
+  </si>
+  <si>
+    <t>HD021868</t>
+  </si>
+  <si>
+    <t>Số 4 đường số 22 kdc bình hưng</t>
+  </si>
+  <si>
+    <t>Chị Bích Huyền</t>
+  </si>
+  <si>
+    <t>HD021775</t>
+  </si>
+  <si>
+    <t>số 4 đường số 22 kdc bình hưng</t>
+  </si>
+  <si>
+    <t>Phuong Nguyen</t>
+  </si>
+  <si>
+    <t>HD021530</t>
+  </si>
+  <si>
+    <t>Eco green toà I, HR30710, 39 Nguyễn Văn linh</t>
+  </si>
+  <si>
+    <t>Ngann Lee</t>
+  </si>
+  <si>
+    <t>HD021534</t>
+  </si>
+  <si>
+    <t>360 lạc long quân phường 5 (phường hòa bình)</t>
+  </si>
+  <si>
+    <t>NIKI</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Mỹ Phúc</t>
+  </si>
+  <si>
+    <t>HD021574</t>
+  </si>
+  <si>
+    <t>nha The Sun Avenue (tòa S5) 28 Mai Chí Thọ, An Phú</t>
+  </si>
+  <si>
+    <t>HD021424</t>
+  </si>
+  <si>
+    <t>Hoàng Trâm Anh</t>
+  </si>
+  <si>
+    <t>HD021810</t>
+  </si>
+  <si>
+    <t>11 Nguyễn Bá Huân phường thảo điền</t>
+  </si>
+  <si>
+    <t>Trúc Nguyễn</t>
+  </si>
+  <si>
+    <t>HD021871</t>
+  </si>
+  <si>
+    <t>38 Đường 6 Linh Chiếu</t>
+  </si>
+  <si>
+    <t>như fb Đặng Tố Trinh</t>
+  </si>
+  <si>
+    <t>HD021866</t>
+  </si>
+  <si>
+    <t>Đối diện 110/42 đường số 5 phường 17</t>
+  </si>
+  <si>
+    <t>Nguyễn Thảo Uyên</t>
+  </si>
+  <si>
+    <t>HD021746</t>
+  </si>
+  <si>
+    <t>15/32/56 võ duy ninh p22</t>
+  </si>
+  <si>
+    <t>HD021539</t>
+  </si>
+  <si>
+    <t>129/34 Nguyễn Văn Công, P. 3</t>
+  </si>
+  <si>
+    <t>MC Phương Nhi</t>
+  </si>
+  <si>
+    <t>HD021829</t>
+  </si>
+  <si>
+    <t>99 Trần Bá Giao An Nhơn</t>
+  </si>
+  <si>
+    <t>Ngân Ngân</t>
+  </si>
+  <si>
+    <t>HD021620</t>
+  </si>
+  <si>
+    <t>74B/148 thống nhất p15</t>
+  </si>
+  <si>
+    <t>Vân Thuỳ</t>
+  </si>
+  <si>
+    <t>HD021612</t>
+  </si>
+  <si>
+    <t>497/73/5 phan văn trị Phường 5</t>
+  </si>
+  <si>
+    <t>SU ANH</t>
+  </si>
+  <si>
+    <t>Hong Nho + NGUYỄN THỊ DIỄM CHI</t>
+  </si>
+  <si>
+    <t>29/7 Yên Thế, Phường 2</t>
+  </si>
+  <si>
+    <t>Gia Huy nhận của ELIS NGUYỄN ( singapore)</t>
+  </si>
+  <si>
+    <t>HD021334</t>
+  </si>
+  <si>
+    <t>2/11 Đường Thiên Phước, Phường 9</t>
+  </si>
+  <si>
+    <t>Ngọc - fb Naila Unner</t>
+  </si>
+  <si>
+    <t>HD021827</t>
+  </si>
+  <si>
+    <t>Rivergate</t>
+  </si>
+  <si>
+    <t>HD021876</t>
+  </si>
+  <si>
+    <t>Ngọc</t>
+  </si>
+  <si>
+    <t>HD021842</t>
+  </si>
+  <si>
+    <t>222 pasteur, phường xuân hòa</t>
+  </si>
+  <si>
+    <t>Thinh HB</t>
+  </si>
+  <si>
+    <t>HD021608</t>
+  </si>
+  <si>
+    <t>17 cô giang, phường cầu ông lãnh</t>
+  </si>
+  <si>
+    <t>Trân Nguyễn</t>
+  </si>
+  <si>
+    <t>HD021600</t>
+  </si>
+  <si>
+    <t>177 Nguyễn Đình Chiểu, p. Xuân Hòa</t>
+  </si>
+  <si>
+    <t>Tô Tô</t>
+  </si>
+  <si>
+    <t>HD021603</t>
+  </si>
+  <si>
+    <t>46 Lê Thị Riêng, phường Bến Thành</t>
+  </si>
+  <si>
+    <t>at 18-05</t>
+  </si>
+  <si>
     <t>THÁNG 5</t>
   </si>
   <si>
@@ -4381,283 +4662,211 @@
     <t>Lợi nhuận</t>
   </si>
   <si>
-    <t>SU ANH</t>
-  </si>
-  <si>
-    <t>18-05-2026</t>
-  </si>
-  <si>
-    <t>NIKI</t>
-  </si>
-  <si>
-    <t>AT 18-05</t>
-  </si>
-  <si>
-    <t>Hong Nho + NGUYỄN THỊ DIỄM CHI</t>
-  </si>
-  <si>
-    <t>29/7 Yên Thế, Phường 2</t>
-  </si>
-  <si>
-    <t>HD021621</t>
-  </si>
-  <si>
-    <t>Heng Roza (EV38382)</t>
-  </si>
-  <si>
-    <t>HD020691</t>
-  </si>
-  <si>
-    <t>Gia Huy nhận của ELIS NGUYỄN ( singapore)</t>
-  </si>
-  <si>
-    <t>HD021334</t>
-  </si>
-  <si>
-    <t>2/11 Đường Thiên Phước, Phường 9</t>
-  </si>
-  <si>
-    <t>HD021855</t>
-  </si>
-  <si>
-    <t>Quỳnh Nga</t>
-  </si>
-  <si>
-    <t>HD021747</t>
-  </si>
-  <si>
-    <t>56/7 đường Tân Hoà 2 phường Hiệp Phú</t>
-  </si>
-  <si>
-    <t>Ngọc - fb Naila Unner</t>
-  </si>
-  <si>
-    <t>HD021827</t>
-  </si>
-  <si>
-    <t>Rivergate</t>
-  </si>
-  <si>
-    <t>HD021876</t>
-  </si>
-  <si>
-    <t>Ngọc Hồng Thương</t>
-  </si>
-  <si>
-    <t>HD021553</t>
-  </si>
-  <si>
-    <t>51 đường 81 tân quy</t>
-  </si>
-  <si>
-    <t>PIMVIPA 3883</t>
-  </si>
-  <si>
-    <t>HD021837</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Mỹ Phúc</t>
-  </si>
-  <si>
-    <t>HD021574</t>
-  </si>
-  <si>
-    <t>nha The Sun Avenue (tòa S5) 28 Mai Chí Thọ, An Phú</t>
-  </si>
-  <si>
-    <t>HD021424</t>
-  </si>
-  <si>
-    <t>Gia Tuệ</t>
-  </si>
-  <si>
-    <t>HD021808</t>
-  </si>
-  <si>
-    <t>42/32 trần đại nghĩa, tân tạo a</t>
-  </si>
-  <si>
-    <t>Ngọc</t>
-  </si>
-  <si>
-    <t>HD021842</t>
-  </si>
-  <si>
-    <t>222 pasteur, phường xuân hòa</t>
-  </si>
-  <si>
-    <t>Hoàng Trâm Anh</t>
-  </si>
-  <si>
-    <t>HD021810</t>
-  </si>
-  <si>
-    <t>11 Nguyễn Bá Huân phường thảo điền</t>
-  </si>
-  <si>
-    <t>HSM RIDA CHUON</t>
-  </si>
-  <si>
-    <t>HD021615</t>
-  </si>
-  <si>
-    <t>177c đường số 1 bình hưng hòa b</t>
-  </si>
-  <si>
-    <t>Trúc Nguyễn</t>
-  </si>
-  <si>
-    <t>HD021871</t>
-  </si>
-  <si>
-    <t>38 Đường 6 Linh Chiếu</t>
-  </si>
-  <si>
-    <t>Nga Còi</t>
-  </si>
-  <si>
-    <t>Sửa xe Anh Sơn, liên ấp 2,3,4 Vĩnh Lộc A</t>
-  </si>
-  <si>
-    <t>Hợp Vũ</t>
-  </si>
-  <si>
-    <t>HD021640</t>
-  </si>
-  <si>
-    <t>2A Phan Chu Trinh, P Hiệp Phú</t>
-  </si>
-  <si>
-    <t>như fb Đặng Tố Trinh</t>
-  </si>
-  <si>
-    <t>HD021866</t>
-  </si>
-  <si>
-    <t>Đối diện 110/42 đường số 5 phường 17</t>
-  </si>
-  <si>
-    <t>Thinh HB</t>
-  </si>
-  <si>
-    <t>HD021608</t>
-  </si>
-  <si>
-    <t>17 cô giang, phường cầu ông lãnh</t>
-  </si>
-  <si>
-    <t>Nguyễn Thảo Uyên</t>
-  </si>
-  <si>
-    <t>HD021746</t>
-  </si>
-  <si>
-    <t>15/32/56 võ duy ninh p22</t>
-  </si>
-  <si>
-    <t>HD021418</t>
-  </si>
-  <si>
-    <t>Central premium lock A</t>
-  </si>
-  <si>
-    <t>Ái Nương</t>
-  </si>
-  <si>
-    <t>HD021666</t>
-  </si>
-  <si>
-    <t>154/33 au dương lân phường 3</t>
-  </si>
-  <si>
-    <t>Trân Nguyễn</t>
-  </si>
-  <si>
-    <t>HD021600</t>
-  </si>
-  <si>
-    <t>177 Nguyễn Đình Chiểu, p. Xuân Hòa</t>
-  </si>
-  <si>
-    <t>Tô Tô</t>
-  </si>
-  <si>
-    <t>HD021603</t>
-  </si>
-  <si>
-    <t>46 Lê Thị Riêng, phường Bến Thành</t>
-  </si>
-  <si>
-    <t>HD021539</t>
-  </si>
-  <si>
-    <t>129/34 Nguyễn Văn Công, P. 3</t>
-  </si>
-  <si>
-    <t>MC Phương Nhi</t>
-  </si>
-  <si>
-    <t>HD021829</t>
-  </si>
-  <si>
-    <t>99 Trần Bá Giao An Nhơn</t>
-  </si>
-  <si>
-    <t>chị Bích Huyền</t>
-  </si>
-  <si>
-    <t>HD021868</t>
-  </si>
-  <si>
-    <t>Số 4 đường số 22 kdc bình hưng</t>
-  </si>
-  <si>
-    <t>Chị Bích Huyền</t>
-  </si>
-  <si>
-    <t>HD021775</t>
-  </si>
-  <si>
-    <t>số 4 đường số 22 kdc bình hưng</t>
-  </si>
-  <si>
-    <t>Ngân Ngân</t>
-  </si>
-  <si>
-    <t>HD021620</t>
-  </si>
-  <si>
-    <t>74B/148 thống nhất p15</t>
-  </si>
-  <si>
-    <t>Phuong Nguyen</t>
-  </si>
-  <si>
-    <t>HD021530</t>
-  </si>
-  <si>
-    <t>Eco green toà I, HR30710, 39 Nguyễn Văn linh</t>
-  </si>
-  <si>
-    <t>Vân Thuỳ</t>
-  </si>
-  <si>
-    <t>HD021612</t>
-  </si>
-  <si>
-    <t>497/73/5 phan văn trị Phường 5</t>
-  </si>
-  <si>
-    <t>Ngann Lee</t>
-  </si>
-  <si>
-    <t>HD021534</t>
-  </si>
-  <si>
-    <t>360 lạc long quân phường 5 (phường hòa bình)</t>
-  </si>
-  <si>
-    <t>at 18-05</t>
+    <t>Nguyễn Trương Phương Oanh</t>
+  </si>
+  <si>
+    <t>HD021780</t>
+  </si>
+  <si>
+    <t>125/42/2 Bùi Đình Tuý, phường 14</t>
+  </si>
+  <si>
+    <t>19-05-2026</t>
+  </si>
+  <si>
+    <t>HD021999</t>
+  </si>
+  <si>
+    <t>AT 19-05</t>
+  </si>
+  <si>
+    <t>Bảo Ngân</t>
+  </si>
+  <si>
+    <t>HD021981</t>
+  </si>
+  <si>
+    <t>62 đường 36, Khu đô thị Vạn Phúc</t>
+  </si>
+  <si>
+    <t>YẾN</t>
+  </si>
+  <si>
+    <t>HD022130</t>
+  </si>
+  <si>
+    <t>Số 21 đường 10, khu Khang Điền, P.Phước Long B</t>
+  </si>
+  <si>
+    <t>HD021937</t>
+  </si>
+  <si>
+    <t>Trường Ruby Hồng Ngọc, số 4 Lê Quát, Phường Tân Thới Hoà</t>
+  </si>
+  <si>
+    <t>HD021909</t>
+  </si>
+  <si>
+    <t>Chung cư Tecco, block C, đường Nguyễn Cửu Phú, phường Tân Tạo</t>
+  </si>
+  <si>
+    <t>HD022145</t>
+  </si>
+  <si>
+    <t>chung cư botanica premier block C2 Hồng Hà</t>
+  </si>
+  <si>
+    <t>Trang Gpe / Wang Yu Hua</t>
+  </si>
+  <si>
+    <t>HD021970</t>
+  </si>
+  <si>
+    <t>Số 192 Trần Bá Giao, Phường 5</t>
+  </si>
+  <si>
+    <t>Thiều Phương Nhi</t>
+  </si>
+  <si>
+    <t>HD022153</t>
+  </si>
+  <si>
+    <t>115 Phan Huy Thực, P.Tân Hưng</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Hà Vy</t>
+  </si>
+  <si>
+    <t>HD021917</t>
+  </si>
+  <si>
+    <t>30/8 trịnh đình thảo p. Hòa Thạnh</t>
+  </si>
+  <si>
+    <t>Khả Hân</t>
+  </si>
+  <si>
+    <t>HD021776</t>
+  </si>
+  <si>
+    <t>10 Tạ Hiện Cát Lái</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Thương Hoài</t>
+  </si>
+  <si>
+    <t>HD022106</t>
+  </si>
+  <si>
+    <t>32/4/17 khu phố 3, đường 21, phường Cát Lái</t>
+  </si>
+  <si>
+    <t>Nguyễn Võ Thụy Hương (Hoàng Ngân)</t>
+  </si>
+  <si>
+    <t>HD022099</t>
+  </si>
+  <si>
+    <t>Châu Nguyễn</t>
+  </si>
+  <si>
+    <t>HD021967</t>
+  </si>
+  <si>
+    <t>chung cu eco green block H</t>
+  </si>
+  <si>
+    <t>Phạm Ngọc Thương</t>
+  </si>
+  <si>
+    <t>HD022114</t>
+  </si>
+  <si>
+    <t>23/53 Nơ Trang Long, p7</t>
+  </si>
+  <si>
+    <t>Hiền Hiền</t>
+  </si>
+  <si>
+    <t>HD022103</t>
+  </si>
+  <si>
+    <t>163/25/42 Tô Hiến Thành p13</t>
+  </si>
+  <si>
+    <t>Eny Nguyen</t>
+  </si>
+  <si>
+    <t>HD022152</t>
+  </si>
+  <si>
+    <t>362/26 lê văn lương, tân hưng</t>
+  </si>
+  <si>
+    <t>Ngọc Trang</t>
+  </si>
+  <si>
+    <t>HD022158</t>
+  </si>
+  <si>
+    <t>Foxshop 28 Lê Văn Duyệt, P1</t>
+  </si>
+  <si>
+    <t>HD021846</t>
+  </si>
+  <si>
+    <t>Ivy Tran</t>
+  </si>
+  <si>
+    <t>HD021976</t>
+  </si>
+  <si>
+    <t>128/3 Nguyễn Sơn, Phú Thọ Hoà</t>
+  </si>
+  <si>
+    <t>HD022101</t>
+  </si>
+  <si>
+    <t>khun leang 092559972</t>
+  </si>
+  <si>
+    <t>HD021974</t>
+  </si>
+  <si>
+    <t>nhà xe khải nam</t>
+  </si>
+  <si>
+    <t>Ivy Nguyen</t>
+  </si>
+  <si>
+    <t>HD022104</t>
+  </si>
+  <si>
+    <t>296 gia phú p1</t>
+  </si>
+  <si>
+    <t>BELLA TRẦN</t>
+  </si>
+  <si>
+    <t>66đường 17 p10</t>
+  </si>
+  <si>
+    <t>GENY</t>
+  </si>
+  <si>
+    <t>B12 Đ. Bạch Đằng, Phường 2</t>
+  </si>
+  <si>
+    <t>NT Hải Yến</t>
+  </si>
+  <si>
+    <t>123 khu dân cư Tân Tiến, Tân Thới Hiệp</t>
+  </si>
+  <si>
+    <t>LEMONA</t>
+  </si>
+  <si>
+    <t>at 19-05</t>
   </si>
 </sst>
 </file>
@@ -16532,7 +16741,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A2:Q75"/>
+  <dimension ref="A2:R75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -16553,7 +16762,7 @@
     <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
@@ -16604,19 +16813,19 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="20"/>
       <c r="B3" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>1444</v>
+        <v>1421</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>1445</v>
+        <v>1422</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>1446</v>
+        <v>1423</v>
       </c>
       <c r="F3" s="21">
         <v>9</v>
@@ -16628,7 +16837,7 @@
         <v>30</v>
       </c>
       <c r="I3" s="21">
-        <f>G3-H3</f>
+        <f t="shared" ref="I3:I41" si="0">G3-H3</f>
         <v>820</v>
       </c>
       <c r="J3" s="20" t="s">
@@ -16638,7 +16847,7 @@
         <v>21</v>
       </c>
       <c r="L3" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M3" s="20"/>
       <c r="N3" s="20"/>
@@ -16648,19 +16857,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="20"/>
       <c r="B4" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>1477</v>
+        <v>1425</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>1478</v>
+        <v>1426</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>1479</v>
+        <v>1427</v>
       </c>
       <c r="F4" s="21">
         <v>9</v>
@@ -16672,7 +16881,7 @@
         <v>30</v>
       </c>
       <c r="I4" s="21">
-        <f>G4-H4</f>
+        <f t="shared" si="0"/>
         <v>570</v>
       </c>
       <c r="J4" s="20" t="s">
@@ -16682,7 +16891,7 @@
         <v>21</v>
       </c>
       <c r="L4" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M4" s="20"/>
       <c r="N4" s="20"/>
@@ -16692,7 +16901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
         <v>16</v>
       </c>
@@ -16716,17 +16925,17 @@
         <v>30</v>
       </c>
       <c r="I5" s="21">
-        <f>G5-H5</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J5" s="20" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="K5" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L5" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M5" s="20"/>
       <c r="N5" s="20"/>
@@ -16735,8 +16944,12 @@
       <c r="Q5" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R5" s="15">
+        <f>H5</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="22"/>
       <c r="B6" s="22" t="s">
         <v>17</v>
@@ -16745,7 +16958,7 @@
         <v>1352</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>1437</v>
+        <v>1429</v>
       </c>
       <c r="E6" s="22" t="s">
         <v>1354</v>
@@ -16760,17 +16973,17 @@
         <v>30</v>
       </c>
       <c r="I6" s="23">
-        <f>G6-H6</f>
+        <f t="shared" si="0"/>
         <v>350</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="K6" s="22" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="22" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M6" s="22" t="s">
         <v>126</v>
@@ -16782,16 +16995,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="20"/>
       <c r="B7" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>1438</v>
+        <v>1430</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>1439</v>
+        <v>1431</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>744</v>
@@ -16806,17 +17019,17 @@
         <v>30</v>
       </c>
       <c r="I7" s="21">
-        <f>G7-H7</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J7" s="20" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="K7" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L7" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M7" s="20"/>
       <c r="N7" s="20"/>
@@ -16825,8 +17038,12 @@
       <c r="Q7" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R7" s="15">
+        <f t="shared" ref="R7:R13" si="1">H7</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="20"/>
       <c r="B8" s="20" t="s">
         <v>17</v>
@@ -16835,7 +17052,7 @@
         <v>1065</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>1443</v>
+        <v>1432</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>1067</v>
@@ -16850,17 +17067,17 @@
         <v>30</v>
       </c>
       <c r="I8" s="21">
-        <f>G8-H8</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J8" s="20" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="K8" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L8" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M8" s="20"/>
       <c r="N8" s="20"/>
@@ -16869,20 +17086,24 @@
       <c r="Q8" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R8" s="15">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="20"/>
       <c r="B9" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>1451</v>
+        <v>1433</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>1452</v>
+        <v>1434</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>1453</v>
+        <v>1435</v>
       </c>
       <c r="F9" s="21">
         <v>7</v>
@@ -16894,17 +17115,17 @@
         <v>30</v>
       </c>
       <c r="I9" s="21">
-        <f>G9-H9</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="K9" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L9" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M9" s="20"/>
       <c r="N9" s="20"/>
@@ -16913,17 +17134,21 @@
       <c r="Q9" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R9" s="15">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="20"/>
       <c r="B10" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>1454</v>
+        <v>1436</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>1455</v>
+        <v>1437</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>632</v>
@@ -16938,17 +17163,17 @@
         <v>25</v>
       </c>
       <c r="I10" s="21">
-        <f>G10-H10</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J10" s="20" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="K10" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L10" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M10" s="20"/>
       <c r="N10" s="20"/>
@@ -16957,20 +17182,24 @@
       <c r="Q10" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R10" s="15">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="20"/>
       <c r="B11" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>1460</v>
+        <v>1438</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>1461</v>
+        <v>1439</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>1462</v>
+        <v>1440</v>
       </c>
       <c r="F11" s="20" t="s">
         <v>26</v>
@@ -16982,17 +17211,17 @@
         <v>30</v>
       </c>
       <c r="I11" s="21">
-        <f>G11-H11</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="K11" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L11" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M11" s="20"/>
       <c r="N11" s="20"/>
@@ -17001,20 +17230,24 @@
       <c r="Q11" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R11" s="15">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="20"/>
       <c r="B12" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>1469</v>
+        <v>1441</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>1470</v>
+        <v>1442</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>1471</v>
+        <v>1443</v>
       </c>
       <c r="F12" s="20" t="s">
         <v>26</v>
@@ -17026,17 +17259,17 @@
         <v>30</v>
       </c>
       <c r="I12" s="21">
-        <f>G12-H12</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J12" s="20" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="K12" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L12" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M12" s="20"/>
       <c r="N12" s="20"/>
@@ -17045,18 +17278,22 @@
       <c r="Q12" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R12" s="15">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="22"/>
       <c r="B13" s="22" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>1475</v>
+        <v>1444</v>
       </c>
       <c r="D13" s="22"/>
       <c r="E13" s="22" t="s">
-        <v>1476</v>
+        <v>1445</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>139</v>
@@ -17068,17 +17305,17 @@
         <v>35</v>
       </c>
       <c r="I13" s="23">
-        <f>G13-H13</f>
+        <f t="shared" si="0"/>
         <v>-35</v>
       </c>
       <c r="J13" s="22" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="K13" s="22" t="s">
         <v>21</v>
       </c>
       <c r="L13" s="22" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M13" s="22" t="s">
         <v>126</v>
@@ -17089,8 +17326,12 @@
       <c r="Q13" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R13" s="30">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="20"/>
       <c r="B14" s="20" t="s">
         <v>17</v>
@@ -17099,10 +17340,10 @@
         <v>1239</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>1489</v>
+        <v>1446</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>1490</v>
+        <v>1447</v>
       </c>
       <c r="F14" s="21">
         <v>8</v>
@@ -17114,17 +17355,17 @@
         <v>30</v>
       </c>
       <c r="I14" s="21">
-        <f>G14-H14</f>
+        <f t="shared" si="0"/>
         <v>950</v>
       </c>
       <c r="J14" s="20" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="K14" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L14" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M14" s="20"/>
       <c r="N14" s="20"/>
@@ -17134,19 +17375,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="20"/>
       <c r="B15" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>1491</v>
+        <v>1448</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>1492</v>
+        <v>1449</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>1493</v>
+        <v>1450</v>
       </c>
       <c r="F15" s="21">
         <v>8</v>
@@ -17158,17 +17399,17 @@
         <v>30</v>
       </c>
       <c r="I15" s="21">
-        <f>G15-H15</f>
+        <f t="shared" si="0"/>
         <v>350</v>
       </c>
       <c r="J15" s="20" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L15" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M15" s="20"/>
       <c r="N15" s="20"/>
@@ -17178,19 +17419,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="20"/>
       <c r="B16" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>1505</v>
+        <v>1451</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>1506</v>
+        <v>1452</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>1507</v>
+        <v>1453</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>139</v>
@@ -17202,17 +17443,17 @@
         <v>35</v>
       </c>
       <c r="I16" s="21">
-        <f>G16-H16</f>
+        <f t="shared" si="0"/>
         <v>660</v>
       </c>
       <c r="J16" s="20" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="K16" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L16" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M16" s="25" t="s">
         <v>377</v>
@@ -17224,19 +17465,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="20"/>
       <c r="B17" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>1508</v>
+        <v>1454</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>1509</v>
+        <v>1455</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>1510</v>
+        <v>1456</v>
       </c>
       <c r="F17" s="20" t="s">
         <v>139</v>
@@ -17248,17 +17489,17 @@
         <v>0</v>
       </c>
       <c r="I17" s="21">
-        <f>G17-H17</f>
+        <f t="shared" si="0"/>
         <v>820</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="K17" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L17" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M17" s="25" t="s">
         <v>377</v>
@@ -17270,19 +17511,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="20"/>
       <c r="B18" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>1514</v>
+        <v>1457</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>1515</v>
+        <v>1458</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>1516</v>
+        <v>1459</v>
       </c>
       <c r="F18" s="21">
         <v>7</v>
@@ -17294,17 +17535,17 @@
         <v>30</v>
       </c>
       <c r="I18" s="21">
-        <f>G18-H18</f>
+        <f t="shared" si="0"/>
         <v>950</v>
       </c>
       <c r="J18" s="20" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="K18" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L18" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M18" s="20"/>
       <c r="N18" s="20"/>
@@ -17314,19 +17555,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="20"/>
       <c r="B19" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>1520</v>
+        <v>1460</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>1521</v>
+        <v>1461</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>1522</v>
+        <v>1462</v>
       </c>
       <c r="F19" s="21">
         <v>11</v>
@@ -17338,17 +17579,17 @@
         <v>25</v>
       </c>
       <c r="I19" s="21">
-        <f>G19-H19</f>
+        <f t="shared" si="0"/>
         <v>960</v>
       </c>
       <c r="J19" s="20" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="K19" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L19" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M19" s="20"/>
       <c r="N19" s="20"/>
@@ -17358,7 +17599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
         <v>16</v>
       </c>
@@ -17366,7 +17607,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>1433</v>
+        <v>1463</v>
       </c>
       <c r="D20" s="20"/>
       <c r="E20" s="20" t="s">
@@ -17382,7 +17623,7 @@
         <v>60</v>
       </c>
       <c r="I20" s="21">
-        <f>G20-H20</f>
+        <f t="shared" si="0"/>
         <v>-60</v>
       </c>
       <c r="J20" s="20" t="s">
@@ -17392,7 +17633,7 @@
         <v>21</v>
       </c>
       <c r="L20" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M20" s="20"/>
       <c r="N20" s="20"/>
@@ -17401,8 +17642,12 @@
       <c r="Q20" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R20" s="15">
+        <f>H20</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
         <v>16</v>
       </c>
@@ -17426,7 +17671,7 @@
         <v>30</v>
       </c>
       <c r="I21" s="21">
-        <f>G21-H21</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J21" s="20" t="s">
@@ -17436,7 +17681,7 @@
         <v>21</v>
       </c>
       <c r="L21" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M21" s="20"/>
       <c r="N21" s="20"/>
@@ -17446,7 +17691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>16</v>
       </c>
@@ -17470,7 +17715,7 @@
         <v>35</v>
       </c>
       <c r="I22" s="21">
-        <f>G22-H22</f>
+        <f t="shared" si="0"/>
         <v>560</v>
       </c>
       <c r="J22" s="20" t="s">
@@ -17480,7 +17725,7 @@
         <v>21</v>
       </c>
       <c r="L22" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M22" s="20"/>
       <c r="N22" s="20"/>
@@ -17490,19 +17735,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="20"/>
       <c r="B23" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>1456</v>
+        <v>1464</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>1457</v>
+        <v>1465</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>1458</v>
+        <v>1466</v>
       </c>
       <c r="F23" s="21">
         <v>2</v>
@@ -17514,7 +17759,7 @@
         <v>30</v>
       </c>
       <c r="I23" s="21">
-        <f>G23-H23</f>
+        <f t="shared" si="0"/>
         <v>860</v>
       </c>
       <c r="J23" s="20" t="s">
@@ -17524,7 +17769,7 @@
         <v>21</v>
       </c>
       <c r="L23" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M23" s="20"/>
       <c r="N23" s="20"/>
@@ -17534,7 +17779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="20"/>
       <c r="B24" s="20" t="s">
         <v>17</v>
@@ -17543,7 +17788,7 @@
         <v>1006</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>1459</v>
+        <v>1467</v>
       </c>
       <c r="E24" s="20" t="s">
         <v>1008</v>
@@ -17558,7 +17803,7 @@
         <v>30</v>
       </c>
       <c r="I24" s="21">
-        <f>G24-H24</f>
+        <f t="shared" si="0"/>
         <v>350</v>
       </c>
       <c r="J24" s="20" t="s">
@@ -17568,7 +17813,7 @@
         <v>21</v>
       </c>
       <c r="L24" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M24" s="20"/>
       <c r="N24" s="20"/>
@@ -17578,19 +17823,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="20"/>
       <c r="B25" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="F25" s="21">
         <v>2</v>
@@ -17602,7 +17847,7 @@
         <v>30</v>
       </c>
       <c r="I25" s="21">
-        <f>G25-H25</f>
+        <f t="shared" si="0"/>
         <v>990</v>
       </c>
       <c r="J25" s="20" t="s">
@@ -17612,7 +17857,7 @@
         <v>21</v>
       </c>
       <c r="L25" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M25" s="20"/>
       <c r="N25" s="20"/>
@@ -17622,19 +17867,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="20"/>
       <c r="B26" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="20" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D26" s="20" t="s">
         <v>1472</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="E26" s="20" t="s">
         <v>1473</v>
-      </c>
-      <c r="E26" s="20" t="s">
-        <v>1474</v>
       </c>
       <c r="F26" s="20" t="s">
         <v>81</v>
@@ -17646,7 +17891,7 @@
         <v>30</v>
       </c>
       <c r="I26" s="21">
-        <f>G26-H26</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J26" s="20" t="s">
@@ -17656,7 +17901,7 @@
         <v>21</v>
       </c>
       <c r="L26" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M26" s="20"/>
       <c r="N26" s="20"/>
@@ -17665,20 +17910,24 @@
       <c r="Q26" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R26" s="15">
+        <f>H26</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="22"/>
       <c r="B27" s="22" t="s">
         <v>17</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>1480</v>
+        <v>1474</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>1481</v>
+        <v>1475</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>1482</v>
+        <v>1476</v>
       </c>
       <c r="F27" s="22" t="s">
         <v>77</v>
@@ -17690,7 +17939,7 @@
         <v>25</v>
       </c>
       <c r="I27" s="23">
-        <f>G27-H27</f>
+        <f t="shared" si="0"/>
         <v>270</v>
       </c>
       <c r="J27" s="22" t="s">
@@ -17700,7 +17949,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="22" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M27" s="22" t="s">
         <v>126</v>
@@ -17712,19 +17961,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="20"/>
       <c r="B28" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>1486</v>
+        <v>1477</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>1487</v>
+        <v>1478</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>1488</v>
+        <v>1479</v>
       </c>
       <c r="F28" s="20" t="s">
         <v>85</v>
@@ -17736,7 +17985,7 @@
         <v>20</v>
       </c>
       <c r="I28" s="21">
-        <f>G28-H28</f>
+        <f t="shared" si="0"/>
         <v>1170</v>
       </c>
       <c r="J28" s="20" t="s">
@@ -17746,7 +17995,7 @@
         <v>21</v>
       </c>
       <c r="L28" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M28" s="20"/>
       <c r="N28" s="20"/>
@@ -17756,7 +18005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="20"/>
       <c r="B29" s="20" t="s">
         <v>17</v>
@@ -17765,10 +18014,10 @@
         <v>483</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>1500</v>
+        <v>1480</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>1501</v>
+        <v>1481</v>
       </c>
       <c r="F29" s="20" t="s">
         <v>77</v>
@@ -17780,7 +18029,7 @@
         <v>25</v>
       </c>
       <c r="I29" s="21">
-        <f>G29-H29</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J29" s="20" t="s">
@@ -17790,7 +18039,7 @@
         <v>21</v>
       </c>
       <c r="L29" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M29" s="20"/>
       <c r="N29" s="20"/>
@@ -17799,20 +18048,24 @@
       <c r="Q29" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R29" s="15">
+        <f>H29</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="20"/>
       <c r="B30" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>1502</v>
+        <v>1482</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>1503</v>
+        <v>1483</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>1504</v>
+        <v>1484</v>
       </c>
       <c r="F30" s="20" t="s">
         <v>77</v>
@@ -17824,7 +18077,7 @@
         <v>25</v>
       </c>
       <c r="I30" s="21">
-        <f>G30-H30</f>
+        <f t="shared" si="0"/>
         <v>860</v>
       </c>
       <c r="J30" s="20" t="s">
@@ -17834,7 +18087,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M30" s="20"/>
       <c r="N30" s="20"/>
@@ -17844,19 +18097,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="20"/>
       <c r="B31" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>1511</v>
+        <v>1485</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>1512</v>
+        <v>1486</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>1513</v>
+        <v>1487</v>
       </c>
       <c r="F31" s="20" t="s">
         <v>77</v>
@@ -17868,7 +18121,7 @@
         <v>25</v>
       </c>
       <c r="I31" s="21">
-        <f>G31-H31</f>
+        <f t="shared" si="0"/>
         <v>890</v>
       </c>
       <c r="J31" s="20" t="s">
@@ -17878,7 +18131,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M31" s="20"/>
       <c r="N31" s="20"/>
@@ -17888,19 +18141,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="20"/>
       <c r="B32" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>1517</v>
+        <v>1488</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>1518</v>
+        <v>1489</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>1519</v>
+        <v>1490</v>
       </c>
       <c r="F32" s="20" t="s">
         <v>77</v>
@@ -17912,7 +18165,7 @@
         <v>25</v>
       </c>
       <c r="I32" s="21">
-        <f>G32-H32</f>
+        <f t="shared" si="0"/>
         <v>790</v>
       </c>
       <c r="J32" s="20" t="s">
@@ -17922,7 +18175,7 @@
         <v>21</v>
       </c>
       <c r="L32" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M32" s="20"/>
       <c r="N32" s="20"/>
@@ -17932,7 +18185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
         <v>16</v>
       </c>
@@ -17940,7 +18193,7 @@
         <v>17</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>1431</v>
+        <v>1491</v>
       </c>
       <c r="D33" s="20"/>
       <c r="E33" s="20" t="s">
@@ -17956,7 +18209,7 @@
         <v>30</v>
       </c>
       <c r="I33" s="21">
-        <f>G33-H33</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J33" s="20" t="s">
@@ -17966,7 +18219,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M33" s="20"/>
       <c r="N33" s="20"/>
@@ -17975,8 +18228,12 @@
       <c r="Q33" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R33" s="15">
+        <f>H33</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="20" t="s">
         <v>16</v>
       </c>
@@ -17984,11 +18241,11 @@
         <v>17</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>1435</v>
+        <v>1492</v>
       </c>
       <c r="D34" s="20"/>
       <c r="E34" s="20" t="s">
-        <v>1436</v>
+        <v>1493</v>
       </c>
       <c r="F34" s="20" t="s">
         <v>95</v>
@@ -18000,7 +18257,7 @@
         <v>30</v>
       </c>
       <c r="I34" s="21">
-        <f>G34-H34</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J34" s="20" t="s">
@@ -18010,7 +18267,7 @@
         <v>21</v>
       </c>
       <c r="L34" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M34" s="20"/>
       <c r="N34" s="20"/>
@@ -18020,19 +18277,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="20"/>
       <c r="B35" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>1440</v>
+        <v>1494</v>
       </c>
       <c r="D35" s="20" t="s">
-        <v>1441</v>
+        <v>1495</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>1442</v>
+        <v>1496</v>
       </c>
       <c r="F35" s="20" t="s">
         <v>95</v>
@@ -18044,7 +18301,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="21">
-        <f>G35-H35</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J35" s="20" t="s">
@@ -18054,7 +18311,7 @@
         <v>21</v>
       </c>
       <c r="L35" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M35" s="20"/>
       <c r="N35" s="20"/>
@@ -18063,20 +18320,24 @@
       <c r="Q35" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R35" s="15">
+        <f>H35</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="20"/>
       <c r="B36" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>1447</v>
+        <v>1497</v>
       </c>
       <c r="D36" s="20" t="s">
-        <v>1448</v>
+        <v>1498</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>1449</v>
+        <v>1499</v>
       </c>
       <c r="F36" s="21">
         <v>4</v>
@@ -18088,7 +18349,7 @@
         <v>25</v>
       </c>
       <c r="I36" s="21">
-        <f>G36-H36</f>
+        <f t="shared" si="0"/>
         <v>1050</v>
       </c>
       <c r="J36" s="20" t="s">
@@ -18098,7 +18359,7 @@
         <v>21</v>
       </c>
       <c r="L36" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M36" s="20"/>
       <c r="N36" s="20"/>
@@ -18108,7 +18369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="20"/>
       <c r="B37" s="20" t="s">
         <v>17</v>
@@ -18117,7 +18378,7 @@
         <v>607</v>
       </c>
       <c r="D37" s="20" t="s">
-        <v>1450</v>
+        <v>1500</v>
       </c>
       <c r="E37" s="20" t="s">
         <v>609</v>
@@ -18132,7 +18393,7 @@
         <v>25</v>
       </c>
       <c r="I37" s="21">
-        <f>G37-H37</f>
+        <f t="shared" si="0"/>
         <v>1040</v>
       </c>
       <c r="J37" s="20" t="s">
@@ -18142,7 +18403,7 @@
         <v>21</v>
       </c>
       <c r="L37" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M37" s="20"/>
       <c r="N37" s="20"/>
@@ -18152,19 +18413,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="22"/>
       <c r="B38" s="22" t="s">
         <v>17</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>1463</v>
+        <v>1501</v>
       </c>
       <c r="D38" s="22" t="s">
-        <v>1464</v>
+        <v>1502</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>1465</v>
+        <v>1503</v>
       </c>
       <c r="F38" s="23">
         <v>3</v>
@@ -18176,7 +18437,7 @@
         <v>25</v>
       </c>
       <c r="I38" s="23">
-        <f>G38-H38</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J38" s="22" t="s">
@@ -18186,7 +18447,7 @@
         <v>21</v>
       </c>
       <c r="L38" s="22" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M38" s="22" t="s">
         <v>126</v>
@@ -18198,19 +18459,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="20"/>
       <c r="B39" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>1483</v>
+        <v>1504</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>1484</v>
+        <v>1505</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>1485</v>
+        <v>1506</v>
       </c>
       <c r="F39" s="21">
         <v>1</v>
@@ -18222,7 +18483,7 @@
         <v>25</v>
       </c>
       <c r="I39" s="21">
-        <f>G39-H39</f>
+        <f t="shared" si="0"/>
         <v>890</v>
       </c>
       <c r="J39" s="20" t="s">
@@ -18232,7 +18493,7 @@
         <v>21</v>
       </c>
       <c r="L39" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M39" s="20"/>
       <c r="N39" s="20"/>
@@ -18242,19 +18503,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="20"/>
       <c r="B40" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>1494</v>
+        <v>1507</v>
       </c>
       <c r="D40" s="20" t="s">
-        <v>1495</v>
+        <v>1508</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>1496</v>
+        <v>1509</v>
       </c>
       <c r="F40" s="21">
         <v>3</v>
@@ -18266,7 +18527,7 @@
         <v>25</v>
       </c>
       <c r="I40" s="21">
-        <f>G40-H40</f>
+        <f t="shared" si="0"/>
         <v>740</v>
       </c>
       <c r="J40" s="20" t="s">
@@ -18276,7 +18537,7 @@
         <v>21</v>
       </c>
       <c r="L40" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M40" s="20"/>
       <c r="N40" s="20"/>
@@ -18286,19 +18547,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="20"/>
       <c r="B41" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>1497</v>
+        <v>1510</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>1498</v>
+        <v>1511</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>1499</v>
+        <v>1512</v>
       </c>
       <c r="F41" s="21">
         <v>1</v>
@@ -18310,7 +18571,7 @@
         <v>25</v>
       </c>
       <c r="I41" s="21">
-        <f>G41-H41</f>
+        <f t="shared" si="0"/>
         <v>830</v>
       </c>
       <c r="J41" s="20" t="s">
@@ -18320,7 +18581,7 @@
         <v>21</v>
       </c>
       <c r="L41" s="20" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="M41" s="20"/>
       <c r="N41" s="20"/>
@@ -18330,63 +18591,63 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D43" s="6">
         <f>COUNTA(D3:D41)</f>
         <v>32</v>
       </c>
       <c r="G43" s="6">
-        <f t="shared" ref="G43:Q43" si="0">SUBTOTAL(9,G3:G41)</f>
+        <f t="shared" ref="G43:Q43" si="2">SUBTOTAL(9,G3:G41)</f>
         <v>18415</v>
       </c>
       <c r="H43" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1105</v>
       </c>
       <c r="I43" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>17310</v>
       </c>
       <c r="J43" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K43" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L43" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M43" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N43" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O43" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P43" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q43" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="H44">
         <f>-8*17</f>
         <v>-136</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>17</v>
       </c>
@@ -18414,9 +18675,9 @@
         <v>194</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>195</v>
@@ -18456,7 +18717,7 @@
         <v>4540</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
         <v>199</v>
       </c>
@@ -18483,7 +18744,7 @@
         <v>6614</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B48" s="7" t="s">
         <v>201</v>
       </c>
@@ -18500,7 +18761,7 @@
         <v>202</v>
       </c>
       <c r="O48" t="s">
-        <v>1523</v>
+        <v>1513</v>
       </c>
       <c r="P48">
         <f>L67</f>
@@ -18653,7 +18914,7 @@
     </row>
     <row r="61" spans="2:16" x14ac:dyDescent="0.25">
       <c r="K61" s="16" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="L61" s="16" t="s">
         <v>193</v>
@@ -18776,7 +19037,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P41" xr:uid="{00000000-0009-0000-0000-00000E000000}">
+  <autoFilter ref="A2:P41" xr:uid="{00000000-0009-0000-0000-00000D000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P41">
       <sortCondition ref="J2:J41"/>
     </sortState>
@@ -18796,6 +19057,1775 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+  <dimension ref="A2:R63"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="61.28515625" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="8.7109375" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="20"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>1533</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>1534</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>1535</v>
+      </c>
+      <c r="F3" s="21">
+        <v>9</v>
+      </c>
+      <c r="G3" s="21">
+        <v>830</v>
+      </c>
+      <c r="H3" s="21">
+        <v>30</v>
+      </c>
+      <c r="I3" s="21">
+        <f>G3-H3</f>
+        <v>800</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>1528</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="G4" s="21">
+        <v>735</v>
+      </c>
+      <c r="H4" s="21">
+        <v>35</v>
+      </c>
+      <c r="I4" s="21">
+        <f>G4-H4</f>
+        <v>700</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>1529</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>837</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>1536</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>1537</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="21">
+        <v>985</v>
+      </c>
+      <c r="H5" s="21">
+        <v>25</v>
+      </c>
+      <c r="I5" s="21">
+        <f>G5-H5</f>
+        <v>960</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>1529</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>745</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>1538</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>1539</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" s="21">
+        <v>860</v>
+      </c>
+      <c r="H6" s="21">
+        <v>30</v>
+      </c>
+      <c r="I6" s="21">
+        <f>G6-H6</f>
+        <v>830</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>1529</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>1545</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>1546</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>1547</v>
+      </c>
+      <c r="F7" s="21">
+        <v>7</v>
+      </c>
+      <c r="G7" s="21">
+        <v>850</v>
+      </c>
+      <c r="H7" s="21">
+        <v>30</v>
+      </c>
+      <c r="I7" s="21">
+        <f>G7-H7</f>
+        <v>820</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>1529</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>1549</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>1550</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="21">
+        <v>1115</v>
+      </c>
+      <c r="H8" s="21">
+        <v>25</v>
+      </c>
+      <c r="I8" s="21">
+        <f>G8-H8</f>
+        <v>1090</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>1529</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>1557</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>1558</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="F9" s="21">
+        <v>6</v>
+      </c>
+      <c r="G9" s="21">
+        <v>0</v>
+      </c>
+      <c r="H9" s="21">
+        <v>25</v>
+      </c>
+      <c r="I9" s="21">
+        <f>G9-H9</f>
+        <v>-25</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>1529</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20">
+        <v>1</v>
+      </c>
+      <c r="R9" s="15">
+        <f>H9</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>1559</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>1560</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>1561</v>
+      </c>
+      <c r="F10" s="21">
+        <v>7</v>
+      </c>
+      <c r="G10" s="21">
+        <v>850</v>
+      </c>
+      <c r="H10" s="21">
+        <v>30</v>
+      </c>
+      <c r="I10" s="21">
+        <f>G10-H10</f>
+        <v>820</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>1529</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>1568</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>1569</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>1570</v>
+      </c>
+      <c r="F11" s="21">
+        <v>7</v>
+      </c>
+      <c r="G11" s="21">
+        <v>380</v>
+      </c>
+      <c r="H11" s="21">
+        <v>30</v>
+      </c>
+      <c r="I11" s="21">
+        <f>G11-H11</f>
+        <v>350</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>1529</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="20"/>
+      <c r="B12" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>1575</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>1577</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="21">
+        <v>0</v>
+      </c>
+      <c r="H12" s="21">
+        <v>25</v>
+      </c>
+      <c r="I12" s="21">
+        <f>G12-H12</f>
+        <v>-25</v>
+      </c>
+      <c r="J12" s="20" t="s">
+        <v>1529</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20">
+        <v>1</v>
+      </c>
+      <c r="R12" s="15">
+        <f>H12</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F13" s="21">
+        <v>6</v>
+      </c>
+      <c r="G13" s="21">
+        <v>765</v>
+      </c>
+      <c r="H13" s="21">
+        <v>25</v>
+      </c>
+      <c r="I13" s="21">
+        <f>G13-H13</f>
+        <v>740</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>1529</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>1585</v>
+      </c>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20" t="s">
+        <v>1586</v>
+      </c>
+      <c r="F14" s="21">
+        <v>6</v>
+      </c>
+      <c r="G14" s="21">
+        <v>40</v>
+      </c>
+      <c r="H14" s="21">
+        <v>40</v>
+      </c>
+      <c r="I14" s="21">
+        <f>G14-H14</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>1529</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>1525</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>1526</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" s="21">
+        <v>0</v>
+      </c>
+      <c r="H15" s="21">
+        <v>20</v>
+      </c>
+      <c r="I15" s="21">
+        <f>G15-H15</f>
+        <v>-20</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20">
+        <v>1</v>
+      </c>
+      <c r="R15" s="15">
+        <f>H15</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>1530</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>1531</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>1532</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="21">
+        <v>1020</v>
+      </c>
+      <c r="H16" s="21">
+        <v>30</v>
+      </c>
+      <c r="I16" s="21">
+        <f>G16-H16</f>
+        <v>990</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>1543</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>1544</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="21">
+        <v>0</v>
+      </c>
+      <c r="H17" s="21">
+        <v>25</v>
+      </c>
+      <c r="I17" s="21">
+        <f>G17-H17</f>
+        <v>-25</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20">
+        <v>1</v>
+      </c>
+      <c r="R17" s="15">
+        <f>H17</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>1551</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>1552</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>1553</v>
+      </c>
+      <c r="F18" s="21">
+        <v>2</v>
+      </c>
+      <c r="G18" s="21">
+        <v>1020</v>
+      </c>
+      <c r="H18" s="21">
+        <v>30</v>
+      </c>
+      <c r="I18" s="21">
+        <f>G18-H18</f>
+        <v>990</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F19" s="21">
+        <v>2</v>
+      </c>
+      <c r="G19" s="21">
+        <v>0</v>
+      </c>
+      <c r="H19" s="21">
+        <v>30</v>
+      </c>
+      <c r="I19" s="21">
+        <f>G19-H19</f>
+        <v>-30</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20">
+        <v>1</v>
+      </c>
+      <c r="R19" s="15">
+        <f t="shared" ref="R19:R21" si="0">H19</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20" s="21">
+        <v>0</v>
+      </c>
+      <c r="H20" s="21">
+        <v>20</v>
+      </c>
+      <c r="I20" s="21">
+        <f>G20-H20</f>
+        <v>-20</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20">
+        <v>1</v>
+      </c>
+      <c r="R20" s="15">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>1571</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>1572</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>1573</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G21" s="21">
+        <v>0</v>
+      </c>
+      <c r="H21" s="21">
+        <v>20</v>
+      </c>
+      <c r="I21" s="21">
+        <f>G21-H21</f>
+        <v>-20</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20">
+        <v>1</v>
+      </c>
+      <c r="R21" s="15">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>770</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>772</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G22" s="21">
+        <v>1420</v>
+      </c>
+      <c r="H22" s="21">
+        <v>20</v>
+      </c>
+      <c r="I22" s="21">
+        <f>G22-H22</f>
+        <v>1400</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>1589</v>
+      </c>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20" t="s">
+        <v>1590</v>
+      </c>
+      <c r="F23" s="21">
+        <v>12</v>
+      </c>
+      <c r="G23" s="21">
+        <v>0</v>
+      </c>
+      <c r="H23" s="21">
+        <v>60</v>
+      </c>
+      <c r="I23" s="21">
+        <f>G23-H23</f>
+        <v>-60</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20">
+        <v>1</v>
+      </c>
+      <c r="R23" s="15">
+        <f t="shared" ref="R23:R24" si="1">H23</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>1591</v>
+      </c>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="F24" s="21">
+        <v>12</v>
+      </c>
+      <c r="G24" s="21">
+        <v>0</v>
+      </c>
+      <c r="H24" s="21">
+        <v>60</v>
+      </c>
+      <c r="I24" s="21">
+        <f>G24-H24</f>
+        <v>-60</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20">
+        <v>1</v>
+      </c>
+      <c r="R24" s="15">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>510</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>1540</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>1541</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G25" s="21">
+        <v>1015</v>
+      </c>
+      <c r="H25" s="21">
+        <v>25</v>
+      </c>
+      <c r="I25" s="21">
+        <f>G25-H25</f>
+        <v>990</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K25" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="20"/>
+      <c r="B26" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>1565</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>1566</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>1567</v>
+      </c>
+      <c r="F26" s="21">
+        <v>10</v>
+      </c>
+      <c r="G26" s="21">
+        <v>1665</v>
+      </c>
+      <c r="H26" s="21">
+        <v>25</v>
+      </c>
+      <c r="I26" s="21">
+        <f>G26-H26</f>
+        <v>1640</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K26" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>627</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>1578</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>629</v>
+      </c>
+      <c r="F27" s="23">
+        <v>1</v>
+      </c>
+      <c r="G27" s="23">
+        <v>25</v>
+      </c>
+      <c r="H27" s="23">
+        <v>25</v>
+      </c>
+      <c r="I27" s="23">
+        <f>G27-H27</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M27" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="20"/>
+      <c r="B28" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>1579</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>1580</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>1581</v>
+      </c>
+      <c r="F28" s="21">
+        <v>5</v>
+      </c>
+      <c r="G28" s="21">
+        <v>0</v>
+      </c>
+      <c r="H28" s="21">
+        <v>25</v>
+      </c>
+      <c r="I28" s="21">
+        <f>G28-H28</f>
+        <v>-25</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K28" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20">
+        <v>1</v>
+      </c>
+      <c r="R28" s="15">
+        <f t="shared" ref="R28:R29" si="2">H28</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>1587</v>
+      </c>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20" t="s">
+        <v>1588</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G29" s="21">
+        <v>0</v>
+      </c>
+      <c r="H29" s="21">
+        <v>50</v>
+      </c>
+      <c r="I29" s="21">
+        <f>G29-H29</f>
+        <v>-50</v>
+      </c>
+      <c r="J29" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K29" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="20" t="s">
+        <v>1527</v>
+      </c>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20">
+        <v>1</v>
+      </c>
+      <c r="R29" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D31" s="6">
+        <f>COUNTA(D3:D29)</f>
+        <v>23</v>
+      </c>
+      <c r="G31" s="6">
+        <f t="shared" ref="G31:Q31" si="3">SUBTOTAL(9,G3:G29)</f>
+        <v>13575</v>
+      </c>
+      <c r="H31" s="6">
+        <f t="shared" si="3"/>
+        <v>815</v>
+      </c>
+      <c r="I31" s="6">
+        <f t="shared" si="3"/>
+        <v>12760</v>
+      </c>
+      <c r="J31" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M31" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N31" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O31" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P31" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="6">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H32">
+        <f>-10*17</f>
+        <v>-170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D33" s="5"/>
+      <c r="E33" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H33">
+        <f>-1*30</f>
+        <v>-30</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="O33" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C34" s="4">
+        <f>SUMIFS(I$3:I$29,B$3:B$29,A$33,L$3:L$29,A$34)</f>
+        <v>12760</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="8">
+        <f>SUMIFS(Q$3:Q$29,B$3:B$29,A$33,L$3:L$29,A$34)</f>
+        <v>27</v>
+      </c>
+      <c r="F34" t="s">
+        <v>196</v>
+      </c>
+      <c r="K34" t="s">
+        <v>197</v>
+      </c>
+      <c r="L34">
+        <f>SUMIFS(G$3:G$29,J$3:J$29,K$33)</f>
+        <v>3460</v>
+      </c>
+      <c r="M34">
+        <f>SUMIFS(Q$3:Q$29,J$3:J$29,K$33)-INT(COUNTIFS(J$3:J$29,K$33,M$3:M$29,"*gộp*")/2)</f>
+        <v>10</v>
+      </c>
+      <c r="O34" t="s">
+        <v>21</v>
+      </c>
+      <c r="P34">
+        <f>L39</f>
+        <v>3141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B35" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C35" s="3">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3"/>
+      <c r="K35" t="s">
+        <v>200</v>
+      </c>
+      <c r="L35">
+        <f>-SUMIFS(H$3:H$29,J$3:J$29,K$33)+M35*5</f>
+        <v>-265</v>
+      </c>
+      <c r="M35">
+        <f>SUMIFS(Q$3:Q$29,J$3:J$29,K$33)-INT(COUNTIFS(J$3:J$29,K$33,M$3:M$29,"*gộp*")/2)</f>
+        <v>10</v>
+      </c>
+      <c r="O35" t="s">
+        <v>1592</v>
+      </c>
+      <c r="P35">
+        <f>L47</f>
+        <v>6380</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B36" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C36" s="3">
+        <f>-SUMIFS(I$3:I$29,B$3:B$29,A$33,P$3:P$29,"xx",N$3:N$29,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="3"/>
+      <c r="E36" s="7">
+        <f>SUMIFS(Q$3:Q$29,B$3:B$29,A$33,P$3:P$29,"xx",N$3:N$29,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="K36" t="s">
+        <v>202</v>
+      </c>
+      <c r="L36">
+        <f>-M36*2</f>
+        <v>-54</v>
+      </c>
+      <c r="M36">
+        <f>E37-(COUNTIFS(M$3:M$29,"*gộp*")/2)-COUNTIFS(M$3:M$29,"*đơn trả*")-COUNTIFS(M$3:M$29,"*hàng tỉnh*")</f>
+        <v>27</v>
+      </c>
+      <c r="O36" t="s">
+        <v>20</v>
+      </c>
+      <c r="P36">
+        <f>L55</f>
+        <v>805</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B37" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C37" s="5">
+        <f>SUBTOTAL(9,C34:C36)</f>
+        <v>12760</v>
+      </c>
+      <c r="D37" s="5"/>
+      <c r="E37">
+        <f>E34</f>
+        <v>27</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="O37" t="s">
+        <v>135</v>
+      </c>
+      <c r="P37">
+        <f>L63</f>
+        <v>2580</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B38" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="K38" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O38" t="s">
+        <v>207</v>
+      </c>
+      <c r="P38">
+        <f>-C41</f>
+        <v>-12760</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B39" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="L39" s="18">
+        <f>SUBTOTAL(9,L34:L38)</f>
+        <v>3141</v>
+      </c>
+      <c r="M39" s="18">
+        <f>M34</f>
+        <v>10</v>
+      </c>
+      <c r="O39" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P39" s="9">
+        <f>SUBTOTAL(9,P34:P38)</f>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B41" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C41" s="1">
+        <f>C37+C38+C39</f>
+        <v>12760</v>
+      </c>
+      <c r="D41" s="1"/>
+      <c r="E41" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>1529</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K42" t="s">
+        <v>197</v>
+      </c>
+      <c r="L42">
+        <f>SUMIFS(G$3:G$29,J$3:J$29,K$41)</f>
+        <v>6580</v>
+      </c>
+      <c r="M42">
+        <f>SUMIFS(Q$3:Q$29,J$3:J$29,K$41)-INT(COUNTIFS(J$3:J$29,K$41,M$3:M$29,"*gộp*")/2)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K43" t="s">
+        <v>200</v>
+      </c>
+      <c r="L43">
+        <f>SUM(H32:H33)</f>
+        <v>-200</v>
+      </c>
+      <c r="M43">
+        <f>SUMIFS(Q$3:Q$29,J$3:J$29,K$41)-INT(COUNTIFS(J$3:J$29,K$41,M$3:M$29,"*gộp*")/2)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K44" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K45" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K46" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L47" s="18">
+        <f>SUBTOTAL(9,L42:L46)</f>
+        <v>6380</v>
+      </c>
+      <c r="M47" s="18">
+        <f>M42</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K49" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="50" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K50" t="s">
+        <v>197</v>
+      </c>
+      <c r="L50">
+        <f>SUMIFS(G$3:G$29,J$3:J$29,K$49)</f>
+        <v>830</v>
+      </c>
+      <c r="M50">
+        <f>SUMIFS(Q$3:Q$29,J$3:J$29,K$49)-INT(COUNTIFS(J$3:J$29,K$49,M$3:M$29,"*gộp*")/2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K51" t="s">
+        <v>200</v>
+      </c>
+      <c r="L51">
+        <f>-SUMIFS(H$3:H$29,J$3:J$29,K$49)+M51*5</f>
+        <v>-25</v>
+      </c>
+      <c r="M51">
+        <f>SUMIFS(Q$3:Q$29,J$3:J$29,K$49)-INT(COUNTIFS(J$3:J$29,K$49,M$3:M$29,"*gộp*")/2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K52" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="53" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K53" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="54" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K54" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="55" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L55" s="18">
+        <f>SUBTOTAL(9,L50:L54)</f>
+        <v>805</v>
+      </c>
+      <c r="M55" s="18">
+        <f>M50</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K57" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="58" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K58" t="s">
+        <v>197</v>
+      </c>
+      <c r="L58">
+        <f>SUMIFS(G$3:G$29,J$3:J$29,K$57)</f>
+        <v>2705</v>
+      </c>
+      <c r="M58">
+        <f>SUMIFS(Q$3:Q$29,J$3:J$29,K$57)-INT(COUNTIFS(J$3:J$29,K$57,M$3:M$29,"*gộp*")/2)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K59" t="s">
+        <v>200</v>
+      </c>
+      <c r="L59">
+        <f>-SUMIFS(H$3:H$29,J$3:J$29,K$57)+M59*5</f>
+        <v>-125</v>
+      </c>
+      <c r="M59">
+        <f>SUMIFS(Q$3:Q$29,J$3:J$29,K$57)-INT(COUNTIFS(J$3:J$29,K$57,M$3:M$29,"*gộp*")/2)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K60" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="61" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K61" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="62" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K62" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="63" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L63" s="18">
+        <f>SUBTOTAL(9,L58:L62)</f>
+        <v>2580</v>
+      </c>
+      <c r="M63" s="18">
+        <f>M58</f>
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P29" xr:uid="{00000000-0009-0000-0000-00000F000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P29">
+      <sortCondition ref="J2:J29"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D9B982-EAEB-4F31-86BF-4D059AFDEA27}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
@@ -18814,7 +20844,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>1421</v>
+        <v>1514</v>
       </c>
       <c r="B1" s="10">
         <v>2026</v>
@@ -18822,19 +20852,19 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>1422</v>
+        <v>1515</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>1423</v>
+        <v>1516</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>1424</v>
+        <v>1517</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>1425</v>
+        <v>1518</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>1426</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -19137,7 +21167,7 @@
       </c>
       <c r="B17" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C17" s="13">
         <f t="shared" ca="1" si="2"/>
@@ -19149,7 +21179,7 @@
       </c>
       <c r="E17" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -19364,16 +21394,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D28" s="14" t="s">
-        <v>1427</v>
+        <v>1520</v>
       </c>
       <c r="E28" s="14">
         <f ca="1">SUBTOTAL(9,E4:E27)</f>
-        <v>447</v>
+        <v>474</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D29" s="14" t="s">
-        <v>1428</v>
+        <v>1521</v>
       </c>
       <c r="E29" s="14" cm="1">
         <f t="array" ref="E29" ca="1">SUMPRODUCT(
@@ -19385,29 +21415,29 @@
         ),
     0)
 )</f>
-        <v>1826</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D30" s="14" t="s">
-        <v>1429</v>
+        <v>1522</v>
       </c>
       <c r="E30" s="14">
         <f ca="1">-E28*2</f>
-        <v>-894</v>
+        <v>-948</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D31" s="14" t="s">
-        <v>1430</v>
+        <v>1523</v>
       </c>
       <c r="E31" s="14">
         <f ca="1">SUBTOTAL(9,E29:E30)</f>
-        <v>932</v>
+        <v>1024</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E27" xr:uid="{00000000-0009-0000-0000-00000D000000}"/>
+  <autoFilter ref="A2:E27" xr:uid="{00000000-0009-0000-0000-00000E000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C3:D27">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/data/May/InternalDailyReport_May.xlsx
+++ b/data/May/InternalDailyReport_May.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2E20BA-AC9A-46FC-A7BF-907A28B07787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DEBE668-34DC-4B9F-BB7B-8E3B736B0E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="7" r:id="rId1"/>
@@ -28,7 +28,8 @@
     <sheet name="16-05" sheetId="21" r:id="rId13"/>
     <sheet name="18-05" sheetId="22" r:id="rId14"/>
     <sheet name="19-05" sheetId="23" r:id="rId15"/>
-    <sheet name="Sheet1" sheetId="19" r:id="rId16"/>
+    <sheet name="20-05" sheetId="24" r:id="rId16"/>
+    <sheet name="Sheet1" sheetId="19" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01-05'!$A$2:$P$56</definedName>
@@ -46,7 +47,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'16-05'!$A$2:$P$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'18-05'!$A$2:$P$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'19-05'!$A$2:$P$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">Sheet1!$A$2:$E$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'20-05'!$A$2:$P$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">Sheet1!$A$2:$E$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -88,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5282" uniqueCount="1593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5602" uniqueCount="1669">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -4632,6 +4634,213 @@
     <t>at 18-05</t>
   </si>
   <si>
+    <t>YẾN</t>
+  </si>
+  <si>
+    <t>HD022130</t>
+  </si>
+  <si>
+    <t>Số 21 đường 10, khu Khang Điền, P.Phước Long B</t>
+  </si>
+  <si>
+    <t>19-05-2026</t>
+  </si>
+  <si>
+    <t>HD021999</t>
+  </si>
+  <si>
+    <t>AT 19-05</t>
+  </si>
+  <si>
+    <t>HD021937</t>
+  </si>
+  <si>
+    <t>Trường Ruby Hồng Ngọc, số 4 Lê Quát, Phường Tân Thới Hoà</t>
+  </si>
+  <si>
+    <t>HD021909</t>
+  </si>
+  <si>
+    <t>Chung cư Tecco, block C, đường Nguyễn Cửu Phú, phường Tân Tạo</t>
+  </si>
+  <si>
+    <t>Thiều Phương Nhi</t>
+  </si>
+  <si>
+    <t>HD022153</t>
+  </si>
+  <si>
+    <t>115 Phan Huy Thực, P.Tân Hưng</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Hà Vy</t>
+  </si>
+  <si>
+    <t>HD021917</t>
+  </si>
+  <si>
+    <t>30/8 trịnh đình thảo p. Hòa Thạnh</t>
+  </si>
+  <si>
+    <t>Nguyễn Võ Thụy Hương (Hoàng Ngân)</t>
+  </si>
+  <si>
+    <t>HD022099</t>
+  </si>
+  <si>
+    <t>Châu Nguyễn</t>
+  </si>
+  <si>
+    <t>HD021967</t>
+  </si>
+  <si>
+    <t>chung cu eco green block H</t>
+  </si>
+  <si>
+    <t>Eny Nguyen</t>
+  </si>
+  <si>
+    <t>HD022152</t>
+  </si>
+  <si>
+    <t>362/26 lê văn lương, tân hưng</t>
+  </si>
+  <si>
+    <t>Ivy Tran</t>
+  </si>
+  <si>
+    <t>HD021976</t>
+  </si>
+  <si>
+    <t>128/3 Nguyễn Sơn, Phú Thọ Hoà</t>
+  </si>
+  <si>
+    <t>Ivy Nguyen</t>
+  </si>
+  <si>
+    <t>HD022104</t>
+  </si>
+  <si>
+    <t>296 gia phú p1</t>
+  </si>
+  <si>
+    <t>BELLA TRẦN</t>
+  </si>
+  <si>
+    <t>66đường 17 p10</t>
+  </si>
+  <si>
+    <t>Nguyễn Trương Phương Oanh</t>
+  </si>
+  <si>
+    <t>HD021780</t>
+  </si>
+  <si>
+    <t>125/42/2 Bùi Đình Tuý, phường 14</t>
+  </si>
+  <si>
+    <t>Bảo Ngân</t>
+  </si>
+  <si>
+    <t>HD021981</t>
+  </si>
+  <si>
+    <t>62 đường 36, Khu đô thị Vạn Phúc</t>
+  </si>
+  <si>
+    <t>Trang Gpe / Wang Yu Hua</t>
+  </si>
+  <si>
+    <t>HD021970</t>
+  </si>
+  <si>
+    <t>Số 192 Trần Bá Giao, Phường 5</t>
+  </si>
+  <si>
+    <t>Khả Hân</t>
+  </si>
+  <si>
+    <t>HD021776</t>
+  </si>
+  <si>
+    <t>10 Tạ Hiện Cát Lái</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Thương Hoài</t>
+  </si>
+  <si>
+    <t>HD022106</t>
+  </si>
+  <si>
+    <t>32/4/17 khu phố 3, đường 21, phường Cát Lái</t>
+  </si>
+  <si>
+    <t>Phạm Ngọc Thương</t>
+  </si>
+  <si>
+    <t>HD022114</t>
+  </si>
+  <si>
+    <t>23/53 Nơ Trang Long, p7</t>
+  </si>
+  <si>
+    <t>Ngọc Trang</t>
+  </si>
+  <si>
+    <t>HD022158</t>
+  </si>
+  <si>
+    <t>Foxshop 28 Lê Văn Duyệt, P1</t>
+  </si>
+  <si>
+    <t>HD021846</t>
+  </si>
+  <si>
+    <t>NT Hải Yến</t>
+  </si>
+  <si>
+    <t>123 khu dân cư Tân Tiến, Tân Thới Hiệp</t>
+  </si>
+  <si>
+    <t>LEMONA</t>
+  </si>
+  <si>
+    <t>HD022145</t>
+  </si>
+  <si>
+    <t>chung cư botanica premier block C2 Hồng Hà</t>
+  </si>
+  <si>
+    <t>Hiền Hiền</t>
+  </si>
+  <si>
+    <t>HD022103</t>
+  </si>
+  <si>
+    <t>163/25/42 Tô Hiến Thành p13</t>
+  </si>
+  <si>
+    <t>HD022101</t>
+  </si>
+  <si>
+    <t>khun leang 092559972</t>
+  </si>
+  <si>
+    <t>HD021974</t>
+  </si>
+  <si>
+    <t>nhà xe khải nam</t>
+  </si>
+  <si>
+    <t>GENY</t>
+  </si>
+  <si>
+    <t>B12 Đ. Bạch Đằng, Phường 2</t>
+  </si>
+  <si>
+    <t>at 19-05</t>
+  </si>
+  <si>
     <t>THÁNG 5</t>
   </si>
   <si>
@@ -4662,211 +4871,232 @@
     <t>Lợi nhuận</t>
   </si>
   <si>
-    <t>Nguyễn Trương Phương Oanh</t>
-  </si>
-  <si>
-    <t>HD021780</t>
-  </si>
-  <si>
-    <t>125/42/2 Bùi Đình Tuý, phường 14</t>
-  </si>
-  <si>
-    <t>19-05-2026</t>
-  </si>
-  <si>
-    <t>HD021999</t>
-  </si>
-  <si>
-    <t>AT 19-05</t>
-  </si>
-  <si>
-    <t>Bảo Ngân</t>
-  </si>
-  <si>
-    <t>HD021981</t>
-  </si>
-  <si>
-    <t>62 đường 36, Khu đô thị Vạn Phúc</t>
-  </si>
-  <si>
-    <t>YẾN</t>
-  </si>
-  <si>
-    <t>HD022130</t>
-  </si>
-  <si>
-    <t>Số 21 đường 10, khu Khang Điền, P.Phước Long B</t>
-  </si>
-  <si>
-    <t>HD021937</t>
-  </si>
-  <si>
-    <t>Trường Ruby Hồng Ngọc, số 4 Lê Quát, Phường Tân Thới Hoà</t>
-  </si>
-  <si>
-    <t>HD021909</t>
-  </si>
-  <si>
-    <t>Chung cư Tecco, block C, đường Nguyễn Cửu Phú, phường Tân Tạo</t>
-  </si>
-  <si>
-    <t>HD022145</t>
-  </si>
-  <si>
-    <t>chung cư botanica premier block C2 Hồng Hà</t>
-  </si>
-  <si>
-    <t>Trang Gpe / Wang Yu Hua</t>
-  </si>
-  <si>
-    <t>HD021970</t>
-  </si>
-  <si>
-    <t>Số 192 Trần Bá Giao, Phường 5</t>
-  </si>
-  <si>
-    <t>Thiều Phương Nhi</t>
-  </si>
-  <si>
-    <t>HD022153</t>
-  </si>
-  <si>
-    <t>115 Phan Huy Thực, P.Tân Hưng</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Hà Vy</t>
-  </si>
-  <si>
-    <t>HD021917</t>
-  </si>
-  <si>
-    <t>30/8 trịnh đình thảo p. Hòa Thạnh</t>
-  </si>
-  <si>
-    <t>Khả Hân</t>
-  </si>
-  <si>
-    <t>HD021776</t>
-  </si>
-  <si>
-    <t>10 Tạ Hiện Cát Lái</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Thương Hoài</t>
-  </si>
-  <si>
-    <t>HD022106</t>
-  </si>
-  <si>
-    <t>32/4/17 khu phố 3, đường 21, phường Cát Lái</t>
-  </si>
-  <si>
-    <t>Nguyễn Võ Thụy Hương (Hoàng Ngân)</t>
-  </si>
-  <si>
-    <t>HD022099</t>
-  </si>
-  <si>
-    <t>Châu Nguyễn</t>
-  </si>
-  <si>
-    <t>HD021967</t>
-  </si>
-  <si>
-    <t>chung cu eco green block H</t>
-  </si>
-  <si>
-    <t>Phạm Ngọc Thương</t>
-  </si>
-  <si>
-    <t>HD022114</t>
-  </si>
-  <si>
-    <t>23/53 Nơ Trang Long, p7</t>
-  </si>
-  <si>
-    <t>Hiền Hiền</t>
-  </si>
-  <si>
-    <t>HD022103</t>
-  </si>
-  <si>
-    <t>163/25/42 Tô Hiến Thành p13</t>
-  </si>
-  <si>
-    <t>Eny Nguyen</t>
-  </si>
-  <si>
-    <t>HD022152</t>
-  </si>
-  <si>
-    <t>362/26 lê văn lương, tân hưng</t>
-  </si>
-  <si>
-    <t>Ngọc Trang</t>
-  </si>
-  <si>
-    <t>HD022158</t>
-  </si>
-  <si>
-    <t>Foxshop 28 Lê Văn Duyệt, P1</t>
-  </si>
-  <si>
-    <t>HD021846</t>
-  </si>
-  <si>
-    <t>Ivy Tran</t>
-  </si>
-  <si>
-    <t>HD021976</t>
-  </si>
-  <si>
-    <t>128/3 Nguyễn Sơn, Phú Thọ Hoà</t>
-  </si>
-  <si>
-    <t>HD022101</t>
-  </si>
-  <si>
-    <t>khun leang 092559972</t>
-  </si>
-  <si>
-    <t>HD021974</t>
-  </si>
-  <si>
-    <t>nhà xe khải nam</t>
-  </si>
-  <si>
-    <t>Ivy Nguyen</t>
-  </si>
-  <si>
-    <t>HD022104</t>
-  </si>
-  <si>
-    <t>296 gia phú p1</t>
-  </si>
-  <si>
-    <t>BELLA TRẦN</t>
-  </si>
-  <si>
-    <t>66đường 17 p10</t>
-  </si>
-  <si>
-    <t>GENY</t>
-  </si>
-  <si>
-    <t>B12 Đ. Bạch Đằng, Phường 2</t>
-  </si>
-  <si>
-    <t>NT Hải Yến</t>
-  </si>
-  <si>
-    <t>123 khu dân cư Tân Tiến, Tân Thới Hiệp</t>
-  </si>
-  <si>
-    <t>LEMONA</t>
-  </si>
-  <si>
-    <t>at 19-05</t>
+    <t>20-05-2026</t>
+  </si>
+  <si>
+    <t>Jess-9244</t>
+  </si>
+  <si>
+    <t>275/14B1 Dạng Nguyên Cẩn, Phường Phú Lâm</t>
+  </si>
+  <si>
+    <t>AT 20-05</t>
+  </si>
+  <si>
+    <t>VICKY TRẦN</t>
+  </si>
+  <si>
+    <t>Đắc Hội Express 127/17 bình lợi p13</t>
+  </si>
+  <si>
+    <t>hsu_myat to</t>
+  </si>
+  <si>
+    <t>HD022406</t>
+  </si>
+  <si>
+    <t>2A/14, Nguyễn Thị Minh Khai, P. Đakao</t>
+  </si>
+  <si>
+    <t>Bé Hiền - fb Yudy Phạm</t>
+  </si>
+  <si>
+    <t>HD022410</t>
+  </si>
+  <si>
+    <t>336/20 nguyễn văn luông p12</t>
+  </si>
+  <si>
+    <t>Trần Lê Trâm Anh</t>
+  </si>
+  <si>
+    <t>HD022426</t>
+  </si>
+  <si>
+    <t>Mr Quốc - VTS-64591HCR</t>
+  </si>
+  <si>
+    <t>HD022211</t>
+  </si>
+  <si>
+    <t>HD022200</t>
+  </si>
+  <si>
+    <t>Vincom đồng khởi, 45 lý tự trọng, căn hộ 2604</t>
+  </si>
+  <si>
+    <t>HD022255</t>
+  </si>
+  <si>
+    <t>Tòa nhà C22 Building Số G5, Đường C22, Phường 12</t>
+  </si>
+  <si>
+    <t>Thanh Yến</t>
+  </si>
+  <si>
+    <t>HD022266</t>
+  </si>
+  <si>
+    <t>188/4 đường thới an 16 phường thới an</t>
+  </si>
+  <si>
+    <t>HƯƠNG</t>
+  </si>
+  <si>
+    <t>HD022382</t>
+  </si>
+  <si>
+    <t>7g đường số 8 tân hưng</t>
+  </si>
+  <si>
+    <t>Vận</t>
+  </si>
+  <si>
+    <t>HD022293</t>
+  </si>
+  <si>
+    <t>Tháp RS6, chung cư Richstar 2, số 239 Hoà Bình, phường Phú Thạnh</t>
+  </si>
+  <si>
+    <t>nguyen lý</t>
+  </si>
+  <si>
+    <t>HD022279</t>
+  </si>
+  <si>
+    <t>62/7h ấp 3 xã xuaabn thơi thượng</t>
+  </si>
+  <si>
+    <t>Ý nhi</t>
+  </si>
+  <si>
+    <t>HD022414</t>
+  </si>
+  <si>
+    <t>53 phạm ngọc thạch p6</t>
+  </si>
+  <si>
+    <t>CUS19950/pelpanhaketya</t>
+  </si>
+  <si>
+    <t>HD022206</t>
+  </si>
+  <si>
+    <t>270B Lý thường kiệt, khu phố 1, Phường 6</t>
+  </si>
+  <si>
+    <t>Alice Nguyễn</t>
+  </si>
+  <si>
+    <t>HD022396</t>
+  </si>
+  <si>
+    <t>Amsumalin Abu</t>
+  </si>
+  <si>
+    <t>HD022399</t>
+  </si>
+  <si>
+    <t>03 trương quốc dung p8</t>
+  </si>
+  <si>
+    <t>HD022286</t>
+  </si>
+  <si>
+    <t>179/13A hoà bình Phường Hiệp Tân</t>
+  </si>
+  <si>
+    <t>Lyly My</t>
+  </si>
+  <si>
+    <t>HD022377</t>
+  </si>
+  <si>
+    <t>50/26 thanh xuân 24 thới an</t>
+  </si>
+  <si>
+    <t>HD022240</t>
+  </si>
+  <si>
+    <t>Mỹ Phượng</t>
+  </si>
+  <si>
+    <t>HD022263</t>
+  </si>
+  <si>
+    <t>1414 huỳnh tấn phát p phú mỹ</t>
+  </si>
+  <si>
+    <t>Huyentran Nguyen</t>
+  </si>
+  <si>
+    <t>HD022374</t>
+  </si>
+  <si>
+    <t>86-88 pasteur</t>
+  </si>
+  <si>
+    <t>linh</t>
+  </si>
+  <si>
+    <t>HD022244</t>
+  </si>
+  <si>
+    <t>358/2/2 cmt8</t>
+  </si>
+  <si>
+    <t>Any</t>
+  </si>
+  <si>
+    <t>HD022412</t>
+  </si>
+  <si>
+    <t>101 đông hưng thuận42 phường tân hưng thuận</t>
+  </si>
+  <si>
+    <t>ms Linh</t>
+  </si>
+  <si>
+    <t>HD022275</t>
+  </si>
+  <si>
+    <t>141A đường số 1 phường Thông Tây Hội</t>
+  </si>
+  <si>
+    <t>HD022267</t>
+  </si>
+  <si>
+    <t>HD022402</t>
+  </si>
+  <si>
+    <t>Thương</t>
+  </si>
+  <si>
+    <t>HD022196</t>
+  </si>
+  <si>
+    <t>181 đường số 79 phường tân quy</t>
+  </si>
+  <si>
+    <t>Moon Nguyễn</t>
+  </si>
+  <si>
+    <t>HD022375</t>
+  </si>
+  <si>
+    <t>16 kim ngân, khu dân cư phong phu 4, xã phong phú</t>
+  </si>
+  <si>
+    <t>Ngoc_Ann tiktok gingeri 16:39</t>
+  </si>
+  <si>
+    <t>HD022381</t>
+  </si>
+  <si>
+    <t>1/7 nguyễn văn yên tân thới hoà</t>
+  </si>
+  <si>
+    <t>at 20-05</t>
   </si>
 </sst>
 </file>
@@ -19136,13 +19366,13 @@
         <v>17</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>1533</v>
+        <v>1514</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>1534</v>
+        <v>1515</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>1535</v>
+        <v>1516</v>
       </c>
       <c r="F3" s="21">
         <v>9</v>
@@ -19154,7 +19384,7 @@
         <v>30</v>
       </c>
       <c r="I3" s="21">
-        <f>G3-H3</f>
+        <f t="shared" ref="I3:I29" si="0">G3-H3</f>
         <v>800</v>
       </c>
       <c r="J3" s="20" t="s">
@@ -19164,7 +19394,7 @@
         <v>21</v>
       </c>
       <c r="L3" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M3" s="20"/>
       <c r="N3" s="20"/>
@@ -19183,7 +19413,7 @@
         <v>331</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>1528</v>
+        <v>1518</v>
       </c>
       <c r="E4" s="20" t="s">
         <v>333</v>
@@ -19198,17 +19428,17 @@
         <v>35</v>
       </c>
       <c r="I4" s="21">
-        <f>G4-H4</f>
+        <f t="shared" si="0"/>
         <v>700</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>1529</v>
+        <v>1519</v>
       </c>
       <c r="K4" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L4" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M4" s="20"/>
       <c r="N4" s="20"/>
@@ -19227,10 +19457,10 @@
         <v>837</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>1536</v>
+        <v>1520</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>1537</v>
+        <v>1521</v>
       </c>
       <c r="F5" s="20" t="s">
         <v>46</v>
@@ -19242,17 +19472,17 @@
         <v>25</v>
       </c>
       <c r="I5" s="21">
-        <f>G5-H5</f>
+        <f t="shared" si="0"/>
         <v>960</v>
       </c>
       <c r="J5" s="20" t="s">
-        <v>1529</v>
+        <v>1519</v>
       </c>
       <c r="K5" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L5" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M5" s="20"/>
       <c r="N5" s="20"/>
@@ -19271,10 +19501,10 @@
         <v>745</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>1538</v>
+        <v>1522</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>1539</v>
+        <v>1523</v>
       </c>
       <c r="F6" s="20" t="s">
         <v>95</v>
@@ -19286,17 +19516,17 @@
         <v>30</v>
       </c>
       <c r="I6" s="21">
-        <f>G6-H6</f>
+        <f t="shared" si="0"/>
         <v>830</v>
       </c>
       <c r="J6" s="20" t="s">
-        <v>1529</v>
+        <v>1519</v>
       </c>
       <c r="K6" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M6" s="20"/>
       <c r="N6" s="20"/>
@@ -19312,13 +19542,13 @@
         <v>17</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>1545</v>
+        <v>1524</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>1546</v>
+        <v>1525</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>1547</v>
+        <v>1526</v>
       </c>
       <c r="F7" s="21">
         <v>7</v>
@@ -19330,17 +19560,17 @@
         <v>30</v>
       </c>
       <c r="I7" s="21">
-        <f>G7-H7</f>
+        <f t="shared" si="0"/>
         <v>820</v>
       </c>
       <c r="J7" s="20" t="s">
-        <v>1529</v>
+        <v>1519</v>
       </c>
       <c r="K7" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L7" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M7" s="20"/>
       <c r="N7" s="20"/>
@@ -19356,13 +19586,13 @@
         <v>17</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>1548</v>
+        <v>1527</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>1549</v>
+        <v>1528</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>1550</v>
+        <v>1529</v>
       </c>
       <c r="F8" s="20" t="s">
         <v>46</v>
@@ -19374,17 +19604,17 @@
         <v>25</v>
       </c>
       <c r="I8" s="21">
-        <f>G8-H8</f>
+        <f t="shared" si="0"/>
         <v>1090</v>
       </c>
       <c r="J8" s="20" t="s">
-        <v>1529</v>
+        <v>1519</v>
       </c>
       <c r="K8" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L8" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M8" s="20"/>
       <c r="N8" s="20"/>
@@ -19400,10 +19630,10 @@
         <v>17</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>1557</v>
+        <v>1530</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>1558</v>
+        <v>1531</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>219</v>
@@ -19418,17 +19648,17 @@
         <v>25</v>
       </c>
       <c r="I9" s="21">
-        <f>G9-H9</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>1529</v>
+        <v>1519</v>
       </c>
       <c r="K9" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L9" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M9" s="20"/>
       <c r="N9" s="20"/>
@@ -19448,13 +19678,13 @@
         <v>17</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>1559</v>
+        <v>1532</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>1560</v>
+        <v>1533</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>1561</v>
+        <v>1534</v>
       </c>
       <c r="F10" s="21">
         <v>7</v>
@@ -19466,17 +19696,17 @@
         <v>30</v>
       </c>
       <c r="I10" s="21">
-        <f>G10-H10</f>
+        <f t="shared" si="0"/>
         <v>820</v>
       </c>
       <c r="J10" s="20" t="s">
-        <v>1529</v>
+        <v>1519</v>
       </c>
       <c r="K10" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L10" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M10" s="20"/>
       <c r="N10" s="20"/>
@@ -19492,13 +19722,13 @@
         <v>17</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>1568</v>
+        <v>1535</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>1569</v>
+        <v>1536</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>1570</v>
+        <v>1537</v>
       </c>
       <c r="F11" s="21">
         <v>7</v>
@@ -19510,17 +19740,17 @@
         <v>30</v>
       </c>
       <c r="I11" s="21">
-        <f>G11-H11</f>
+        <f t="shared" si="0"/>
         <v>350</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>1529</v>
+        <v>1519</v>
       </c>
       <c r="K11" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L11" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M11" s="20"/>
       <c r="N11" s="20"/>
@@ -19536,13 +19766,13 @@
         <v>17</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>1575</v>
+        <v>1538</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>1576</v>
+        <v>1539</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>1577</v>
+        <v>1540</v>
       </c>
       <c r="F12" s="20" t="s">
         <v>46</v>
@@ -19554,17 +19784,17 @@
         <v>25</v>
       </c>
       <c r="I12" s="21">
-        <f>G12-H12</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J12" s="20" t="s">
-        <v>1529</v>
+        <v>1519</v>
       </c>
       <c r="K12" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L12" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M12" s="20"/>
       <c r="N12" s="20"/>
@@ -19584,13 +19814,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>1582</v>
+        <v>1541</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>1583</v>
+        <v>1542</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>1584</v>
+        <v>1543</v>
       </c>
       <c r="F13" s="21">
         <v>6</v>
@@ -19602,17 +19832,17 @@
         <v>25</v>
       </c>
       <c r="I13" s="21">
-        <f>G13-H13</f>
+        <f t="shared" si="0"/>
         <v>740</v>
       </c>
       <c r="J13" s="20" t="s">
-        <v>1529</v>
+        <v>1519</v>
       </c>
       <c r="K13" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L13" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M13" s="20"/>
       <c r="N13" s="20"/>
@@ -19630,11 +19860,11 @@
         <v>17</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>1585</v>
+        <v>1544</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="20" t="s">
-        <v>1586</v>
+        <v>1545</v>
       </c>
       <c r="F14" s="21">
         <v>6</v>
@@ -19646,17 +19876,17 @@
         <v>40</v>
       </c>
       <c r="I14" s="21">
-        <f>G14-H14</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J14" s="20" t="s">
-        <v>1529</v>
+        <v>1519</v>
       </c>
       <c r="K14" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L14" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M14" s="20"/>
       <c r="N14" s="20"/>
@@ -19672,13 +19902,13 @@
         <v>17</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>1524</v>
+        <v>1546</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>1525</v>
+        <v>1547</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>1526</v>
+        <v>1548</v>
       </c>
       <c r="F15" s="20" t="s">
         <v>85</v>
@@ -19690,7 +19920,7 @@
         <v>20</v>
       </c>
       <c r="I15" s="21">
-        <f>G15-H15</f>
+        <f t="shared" si="0"/>
         <v>-20</v>
       </c>
       <c r="J15" s="20" t="s">
@@ -19700,7 +19930,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M15" s="20"/>
       <c r="N15" s="20"/>
@@ -19720,13 +19950,13 @@
         <v>17</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>1530</v>
+        <v>1549</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>1531</v>
+        <v>1550</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>1532</v>
+        <v>1551</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>81</v>
@@ -19738,7 +19968,7 @@
         <v>30</v>
       </c>
       <c r="I16" s="21">
-        <f>G16-H16</f>
+        <f t="shared" si="0"/>
         <v>990</v>
       </c>
       <c r="J16" s="20" t="s">
@@ -19748,7 +19978,7 @@
         <v>21</v>
       </c>
       <c r="L16" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M16" s="20"/>
       <c r="N16" s="20"/>
@@ -19764,13 +19994,13 @@
         <v>17</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>1542</v>
+        <v>1552</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>1543</v>
+        <v>1553</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>1544</v>
+        <v>1554</v>
       </c>
       <c r="F17" s="20" t="s">
         <v>77</v>
@@ -19782,7 +20012,7 @@
         <v>25</v>
       </c>
       <c r="I17" s="21">
-        <f>G17-H17</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J17" s="20" t="s">
@@ -19792,7 +20022,7 @@
         <v>21</v>
       </c>
       <c r="L17" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M17" s="20"/>
       <c r="N17" s="20"/>
@@ -19812,13 +20042,13 @@
         <v>17</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>1553</v>
+        <v>1557</v>
       </c>
       <c r="F18" s="21">
         <v>2</v>
@@ -19830,7 +20060,7 @@
         <v>30</v>
       </c>
       <c r="I18" s="21">
-        <f>G18-H18</f>
+        <f t="shared" si="0"/>
         <v>990</v>
       </c>
       <c r="J18" s="20" t="s">
@@ -19840,7 +20070,7 @@
         <v>21</v>
       </c>
       <c r="L18" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M18" s="20"/>
       <c r="N18" s="20"/>
@@ -19856,13 +20086,13 @@
         <v>17</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>1554</v>
+        <v>1558</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>1556</v>
+        <v>1560</v>
       </c>
       <c r="F19" s="21">
         <v>2</v>
@@ -19874,7 +20104,7 @@
         <v>30</v>
       </c>
       <c r="I19" s="21">
-        <f>G19-H19</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J19" s="20" t="s">
@@ -19884,7 +20114,7 @@
         <v>21</v>
       </c>
       <c r="L19" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M19" s="20"/>
       <c r="N19" s="20"/>
@@ -19894,7 +20124,7 @@
         <v>1</v>
       </c>
       <c r="R19" s="15">
-        <f t="shared" ref="R19:R21" si="0">H19</f>
+        <f>H19</f>
         <v>30</v>
       </c>
     </row>
@@ -19904,13 +20134,13 @@
         <v>17</v>
       </c>
       <c r="C20" s="20" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D20" s="20" t="s">
         <v>1562</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="E20" s="20" t="s">
         <v>1563</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>1564</v>
       </c>
       <c r="F20" s="20" t="s">
         <v>85</v>
@@ -19922,7 +20152,7 @@
         <v>20</v>
       </c>
       <c r="I20" s="21">
-        <f>G20-H20</f>
+        <f t="shared" si="0"/>
         <v>-20</v>
       </c>
       <c r="J20" s="20" t="s">
@@ -19932,7 +20162,7 @@
         <v>21</v>
       </c>
       <c r="L20" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M20" s="20"/>
       <c r="N20" s="20"/>
@@ -19942,7 +20172,7 @@
         <v>1</v>
       </c>
       <c r="R20" s="15">
-        <f t="shared" si="0"/>
+        <f>H20</f>
         <v>20</v>
       </c>
     </row>
@@ -19952,13 +20182,13 @@
         <v>17</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>1571</v>
+        <v>1564</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>1572</v>
+        <v>1565</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>1573</v>
+        <v>1566</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>85</v>
@@ -19970,7 +20200,7 @@
         <v>20</v>
       </c>
       <c r="I21" s="21">
-        <f>G21-H21</f>
+        <f t="shared" si="0"/>
         <v>-20</v>
       </c>
       <c r="J21" s="20" t="s">
@@ -19980,7 +20210,7 @@
         <v>21</v>
       </c>
       <c r="L21" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M21" s="20"/>
       <c r="N21" s="20"/>
@@ -19990,7 +20220,7 @@
         <v>1</v>
       </c>
       <c r="R21" s="15">
-        <f t="shared" si="0"/>
+        <f>H21</f>
         <v>20</v>
       </c>
     </row>
@@ -20003,7 +20233,7 @@
         <v>770</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>1574</v>
+        <v>1567</v>
       </c>
       <c r="E22" s="20" t="s">
         <v>772</v>
@@ -20018,7 +20248,7 @@
         <v>20</v>
       </c>
       <c r="I22" s="21">
-        <f>G22-H22</f>
+        <f t="shared" si="0"/>
         <v>1400</v>
       </c>
       <c r="J22" s="20" t="s">
@@ -20028,7 +20258,7 @@
         <v>21</v>
       </c>
       <c r="L22" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M22" s="20"/>
       <c r="N22" s="20"/>
@@ -20046,11 +20276,11 @@
         <v>17</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>1589</v>
+        <v>1568</v>
       </c>
       <c r="D23" s="20"/>
       <c r="E23" s="20" t="s">
-        <v>1590</v>
+        <v>1569</v>
       </c>
       <c r="F23" s="21">
         <v>12</v>
@@ -20062,7 +20292,7 @@
         <v>60</v>
       </c>
       <c r="I23" s="21">
-        <f>G23-H23</f>
+        <f t="shared" si="0"/>
         <v>-60</v>
       </c>
       <c r="J23" s="20" t="s">
@@ -20072,7 +20302,7 @@
         <v>21</v>
       </c>
       <c r="L23" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M23" s="20"/>
       <c r="N23" s="20"/>
@@ -20082,7 +20312,7 @@
         <v>1</v>
       </c>
       <c r="R23" s="15">
-        <f t="shared" ref="R23:R24" si="1">H23</f>
+        <f>H23</f>
         <v>60</v>
       </c>
     </row>
@@ -20094,7 +20324,7 @@
         <v>17</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>1591</v>
+        <v>1570</v>
       </c>
       <c r="D24" s="20"/>
       <c r="E24" s="20" t="s">
@@ -20110,7 +20340,7 @@
         <v>60</v>
       </c>
       <c r="I24" s="21">
-        <f>G24-H24</f>
+        <f t="shared" si="0"/>
         <v>-60</v>
       </c>
       <c r="J24" s="20" t="s">
@@ -20120,7 +20350,7 @@
         <v>21</v>
       </c>
       <c r="L24" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M24" s="20"/>
       <c r="N24" s="20"/>
@@ -20130,7 +20360,7 @@
         <v>1</v>
       </c>
       <c r="R24" s="15">
-        <f t="shared" si="1"/>
+        <f>H24</f>
         <v>60</v>
       </c>
     </row>
@@ -20143,10 +20373,10 @@
         <v>510</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>1540</v>
+        <v>1571</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>1541</v>
+        <v>1572</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>95</v>
@@ -20158,7 +20388,7 @@
         <v>25</v>
       </c>
       <c r="I25" s="21">
-        <f>G25-H25</f>
+        <f t="shared" si="0"/>
         <v>990</v>
       </c>
       <c r="J25" s="20" t="s">
@@ -20168,7 +20398,7 @@
         <v>21</v>
       </c>
       <c r="L25" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M25" s="20"/>
       <c r="N25" s="20"/>
@@ -20184,13 +20414,13 @@
         <v>17</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>1565</v>
+        <v>1573</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>1566</v>
+        <v>1574</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>1567</v>
+        <v>1575</v>
       </c>
       <c r="F26" s="21">
         <v>10</v>
@@ -20202,7 +20432,7 @@
         <v>25</v>
       </c>
       <c r="I26" s="21">
-        <f>G26-H26</f>
+        <f t="shared" si="0"/>
         <v>1640</v>
       </c>
       <c r="J26" s="20" t="s">
@@ -20212,7 +20442,7 @@
         <v>21</v>
       </c>
       <c r="L26" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M26" s="20"/>
       <c r="N26" s="20"/>
@@ -20231,7 +20461,7 @@
         <v>627</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="E27" s="22" t="s">
         <v>629</v>
@@ -20246,7 +20476,7 @@
         <v>25</v>
       </c>
       <c r="I27" s="23">
-        <f>G27-H27</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J27" s="22" t="s">
@@ -20256,7 +20486,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="22" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M27" s="22" t="s">
         <v>126</v>
@@ -20274,13 +20504,13 @@
         <v>17</v>
       </c>
       <c r="C28" s="20" t="s">
+        <v>1577</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>1578</v>
+      </c>
+      <c r="E28" s="20" t="s">
         <v>1579</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>1580</v>
-      </c>
-      <c r="E28" s="20" t="s">
-        <v>1581</v>
       </c>
       <c r="F28" s="21">
         <v>5</v>
@@ -20292,7 +20522,7 @@
         <v>25</v>
       </c>
       <c r="I28" s="21">
-        <f>G28-H28</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J28" s="20" t="s">
@@ -20302,7 +20532,7 @@
         <v>21</v>
       </c>
       <c r="L28" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M28" s="20"/>
       <c r="N28" s="20"/>
@@ -20312,7 +20542,7 @@
         <v>1</v>
       </c>
       <c r="R28" s="15">
-        <f t="shared" ref="R28:R29" si="2">H28</f>
+        <f>H28</f>
         <v>25</v>
       </c>
     </row>
@@ -20324,11 +20554,11 @@
         <v>17</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>1587</v>
+        <v>1580</v>
       </c>
       <c r="D29" s="20"/>
       <c r="E29" s="20" t="s">
-        <v>1588</v>
+        <v>1581</v>
       </c>
       <c r="F29" s="20" t="s">
         <v>95</v>
@@ -20340,7 +20570,7 @@
         <v>50</v>
       </c>
       <c r="I29" s="21">
-        <f>G29-H29</f>
+        <f t="shared" si="0"/>
         <v>-50</v>
       </c>
       <c r="J29" s="20" t="s">
@@ -20350,7 +20580,7 @@
         <v>21</v>
       </c>
       <c r="L29" s="20" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="M29" s="20"/>
       <c r="N29" s="20"/>
@@ -20360,7 +20590,7 @@
         <v>1</v>
       </c>
       <c r="R29" s="15">
-        <f t="shared" si="2"/>
+        <f>H29</f>
         <v>50</v>
       </c>
     </row>
@@ -20370,47 +20600,47 @@
         <v>23</v>
       </c>
       <c r="G31" s="6">
-        <f t="shared" ref="G31:Q31" si="3">SUBTOTAL(9,G3:G29)</f>
+        <f t="shared" ref="G31:Q31" si="1">SUBTOTAL(9,G3:G29)</f>
         <v>13575</v>
       </c>
       <c r="H31" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>815</v>
       </c>
       <c r="I31" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>12760</v>
       </c>
       <c r="J31" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K31" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L31" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M31" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N31" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O31" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P31" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q31" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
     </row>
@@ -20450,7 +20680,7 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>195</v>
@@ -20506,7 +20736,7 @@
         <v>10</v>
       </c>
       <c r="O35" t="s">
-        <v>1592</v>
+        <v>1582</v>
       </c>
       <c r="P35">
         <f>L47</f>
@@ -20621,7 +20851,7 @@
         <v>211</v>
       </c>
       <c r="K41" s="16" t="s">
-        <v>1529</v>
+        <v>1519</v>
       </c>
       <c r="L41" s="16" t="s">
         <v>193</v>
@@ -20806,7 +21036,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P29" xr:uid="{00000000-0009-0000-0000-00000F000000}">
+  <autoFilter ref="A2:P29" xr:uid="{00000000-0009-0000-0000-00000E000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P29">
       <sortCondition ref="J2:J29"/>
     </sortState>
@@ -20826,6 +21056,2030 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+  <dimension ref="A2:R68"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="61.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="19" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>1658</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>1134</v>
+      </c>
+      <c r="F3" s="21">
+        <v>9</v>
+      </c>
+      <c r="G3" s="21">
+        <v>900</v>
+      </c>
+      <c r="H3" s="21">
+        <v>30</v>
+      </c>
+      <c r="I3" s="21">
+        <f>G3-H3</f>
+        <v>870</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>1594</v>
+      </c>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20" t="s">
+        <v>1595</v>
+      </c>
+      <c r="F4" s="21">
+        <v>6</v>
+      </c>
+      <c r="G4" s="21">
+        <v>0</v>
+      </c>
+      <c r="H4" s="21">
+        <v>30</v>
+      </c>
+      <c r="I4" s="21">
+        <f>G4-H4</f>
+        <v>-30</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>1596</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20">
+        <v>1</v>
+      </c>
+      <c r="R4" s="15">
+        <f>H4</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>1603</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>1604</v>
+      </c>
+      <c r="F5" s="21">
+        <v>6</v>
+      </c>
+      <c r="G5" s="21">
+        <v>1875</v>
+      </c>
+      <c r="H5" s="21">
+        <v>25</v>
+      </c>
+      <c r="I5" s="21">
+        <f>G5-H5</f>
+        <v>1850</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>1596</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>1605</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>1606</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>1637</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="21">
+        <v>895</v>
+      </c>
+      <c r="H6" s="21">
+        <v>25</v>
+      </c>
+      <c r="I6" s="21">
+        <f>G6-H6</f>
+        <v>870</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>1596</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M6" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>1605</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>1636</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>1637</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="21">
+        <v>770</v>
+      </c>
+      <c r="H7" s="21">
+        <v>0</v>
+      </c>
+      <c r="I7" s="21">
+        <f>G7-H7</f>
+        <v>770</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>1596</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M7" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>1607</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="21">
+        <v>810</v>
+      </c>
+      <c r="H8" s="21">
+        <v>30</v>
+      </c>
+      <c r="I8" s="21">
+        <f>G8-H8</f>
+        <v>780</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>1596</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>1613</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>1614</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F9" s="21">
+        <v>12</v>
+      </c>
+      <c r="G9" s="21">
+        <v>850</v>
+      </c>
+      <c r="H9" s="21">
+        <v>30</v>
+      </c>
+      <c r="I9" s="21">
+        <f>G9-H9</f>
+        <v>820</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>1596</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>1616</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>1617</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>1618</v>
+      </c>
+      <c r="F10" s="21">
+        <v>7</v>
+      </c>
+      <c r="G10" s="21">
+        <v>0</v>
+      </c>
+      <c r="H10" s="21">
+        <v>30</v>
+      </c>
+      <c r="I10" s="21">
+        <f>G10-H10</f>
+        <v>-30</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>1596</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20">
+        <v>1</v>
+      </c>
+      <c r="R10" s="15">
+        <f>H10</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>1619</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="21">
+        <v>375</v>
+      </c>
+      <c r="H11" s="21">
+        <v>25</v>
+      </c>
+      <c r="I11" s="21">
+        <f>G11-H11</f>
+        <v>350</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>1596</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="20"/>
+      <c r="B12" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>1622</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>1624</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G12" s="21">
+        <v>825</v>
+      </c>
+      <c r="H12" s="21">
+        <v>35</v>
+      </c>
+      <c r="I12" s="21">
+        <f>G12-H12</f>
+        <v>790</v>
+      </c>
+      <c r="J12" s="20" t="s">
+        <v>1596</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>1631</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>1632</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>1270</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="21">
+        <v>0</v>
+      </c>
+      <c r="H13" s="21">
+        <v>30</v>
+      </c>
+      <c r="I13" s="21">
+        <f>G13-H13</f>
+        <v>-30</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>1596</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20">
+        <v>1</v>
+      </c>
+      <c r="R13" s="15">
+        <f>H13</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>1639</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>1640</v>
+      </c>
+      <c r="F14" s="21">
+        <v>12</v>
+      </c>
+      <c r="G14" s="21">
+        <v>1530</v>
+      </c>
+      <c r="H14" s="21">
+        <v>30</v>
+      </c>
+      <c r="I14" s="21">
+        <f>G14-H14</f>
+        <v>1500</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>1596</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>1642</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>1643</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>1644</v>
+      </c>
+      <c r="F15" s="21">
+        <v>7</v>
+      </c>
+      <c r="G15" s="21">
+        <v>1020</v>
+      </c>
+      <c r="H15" s="21">
+        <v>30</v>
+      </c>
+      <c r="I15" s="21">
+        <f>G15-H15</f>
+        <v>990</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>1596</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>1651</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F16" s="21">
+        <v>12</v>
+      </c>
+      <c r="G16" s="21">
+        <v>0</v>
+      </c>
+      <c r="H16" s="21">
+        <v>30</v>
+      </c>
+      <c r="I16" s="21">
+        <f>G16-H16</f>
+        <v>-30</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>1596</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20">
+        <v>1</v>
+      </c>
+      <c r="R16" s="15">
+        <f>H16</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>1657</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>1453</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="G17" s="21">
+        <v>695</v>
+      </c>
+      <c r="H17" s="21">
+        <v>35</v>
+      </c>
+      <c r="I17" s="21">
+        <f>G17-H17</f>
+        <v>660</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>1596</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>1660</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F18" s="21">
+        <v>7</v>
+      </c>
+      <c r="G18" s="21">
+        <v>2710</v>
+      </c>
+      <c r="H18" s="21">
+        <v>35</v>
+      </c>
+      <c r="I18" s="21">
+        <f>G18-H18</f>
+        <v>2675</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>1596</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M18" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20">
+        <v>1</v>
+      </c>
+      <c r="R18" s="15">
+        <f>H18</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>1663</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>1664</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="G19" s="21">
+        <v>1685</v>
+      </c>
+      <c r="H19" s="21">
+        <v>35</v>
+      </c>
+      <c r="I19" s="21">
+        <f>G19-H19</f>
+        <v>1650</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>1596</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>1665</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>1667</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" s="21">
+        <v>855</v>
+      </c>
+      <c r="H20" s="21">
+        <v>25</v>
+      </c>
+      <c r="I20" s="21">
+        <f>G20-H20</f>
+        <v>830</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>1596</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="21">
+        <v>30</v>
+      </c>
+      <c r="H21" s="21">
+        <v>30</v>
+      </c>
+      <c r="I21" s="21">
+        <f>G21-H21</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="21">
+        <v>0</v>
+      </c>
+      <c r="H22" s="21">
+        <v>30</v>
+      </c>
+      <c r="I22" s="21">
+        <f>G22-H22</f>
+        <v>-30</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20">
+        <v>1</v>
+      </c>
+      <c r="R22" s="15">
+        <f t="shared" ref="R22:R23" si="0">H22</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20" t="s">
+        <v>1598</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G23" s="21">
+        <v>0</v>
+      </c>
+      <c r="H23" s="21">
+        <v>35</v>
+      </c>
+      <c r="I23" s="21">
+        <f>G23-H23</f>
+        <v>-35</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20">
+        <v>1</v>
+      </c>
+      <c r="R23" s="15">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="20"/>
+      <c r="B24" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>1654</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>1655</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" s="21">
+        <v>595</v>
+      </c>
+      <c r="H24" s="21">
+        <v>25</v>
+      </c>
+      <c r="I24" s="21">
+        <f>G24-H24</f>
+        <v>570</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M24" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20">
+        <v>1</v>
+      </c>
+      <c r="R24" s="15">
+        <f>H24</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>1601</v>
+      </c>
+      <c r="F25" s="21">
+        <v>1</v>
+      </c>
+      <c r="G25" s="21">
+        <v>0</v>
+      </c>
+      <c r="H25" s="21">
+        <v>25</v>
+      </c>
+      <c r="I25" s="21">
+        <f>G25-H25</f>
+        <v>-25</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K25" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20">
+        <v>1</v>
+      </c>
+      <c r="R25" s="15">
+        <f t="shared" ref="R25:R26" si="1">H25</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="20"/>
+      <c r="B26" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>796</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>1609</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>1610</v>
+      </c>
+      <c r="F26" s="21">
+        <v>1</v>
+      </c>
+      <c r="G26" s="21">
+        <v>0</v>
+      </c>
+      <c r="H26" s="21">
+        <v>25</v>
+      </c>
+      <c r="I26" s="21">
+        <f>G26-H26</f>
+        <v>-25</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K26" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20">
+        <v>1</v>
+      </c>
+      <c r="R26" s="15">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="20"/>
+      <c r="B27" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>1611</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>1612</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G27" s="21">
+        <v>25</v>
+      </c>
+      <c r="H27" s="21">
+        <v>25</v>
+      </c>
+      <c r="I27" s="21">
+        <f>G27-H27</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K27" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="20"/>
+      <c r="B28" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>1625</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>1626</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F28" s="21">
+        <v>3</v>
+      </c>
+      <c r="G28" s="21">
+        <v>0</v>
+      </c>
+      <c r="H28" s="21">
+        <v>25</v>
+      </c>
+      <c r="I28" s="21">
+        <f>G28-H28</f>
+        <v>-25</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K28" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20">
+        <v>1</v>
+      </c>
+      <c r="R28" s="15">
+        <f t="shared" ref="R28:R30" si="2">H28</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>1629</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>1630</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G29" s="21">
+        <v>0</v>
+      </c>
+      <c r="H29" s="21">
+        <v>25</v>
+      </c>
+      <c r="I29" s="21">
+        <f>G29-H29</f>
+        <v>-25</v>
+      </c>
+      <c r="J29" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K29" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20">
+        <v>1</v>
+      </c>
+      <c r="R29" s="15">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="20"/>
+      <c r="B30" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>1633</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>1634</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>1635</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="G30" s="21">
+        <v>0</v>
+      </c>
+      <c r="H30" s="21">
+        <v>20</v>
+      </c>
+      <c r="I30" s="21">
+        <f>G30-H30</f>
+        <v>-20</v>
+      </c>
+      <c r="J30" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K30" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20">
+        <v>1</v>
+      </c>
+      <c r="R30" s="15">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>585</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>1641</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>587</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G31" s="21">
+        <v>875</v>
+      </c>
+      <c r="H31" s="21">
+        <v>25</v>
+      </c>
+      <c r="I31" s="21">
+        <f>G31-H31</f>
+        <v>850</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K31" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="20"/>
+      <c r="B32" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>1645</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>1646</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>1647</v>
+      </c>
+      <c r="F32" s="21">
+        <v>1</v>
+      </c>
+      <c r="G32" s="21">
+        <v>1015</v>
+      </c>
+      <c r="H32" s="21">
+        <v>25</v>
+      </c>
+      <c r="I32" s="21">
+        <f>G32-H32</f>
+        <v>990</v>
+      </c>
+      <c r="J32" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K32" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" s="20"/>
+      <c r="B33" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>1648</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>1649</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>1650</v>
+      </c>
+      <c r="F33" s="21">
+        <v>3</v>
+      </c>
+      <c r="G33" s="21">
+        <v>915</v>
+      </c>
+      <c r="H33" s="21">
+        <v>25</v>
+      </c>
+      <c r="I33" s="21">
+        <f>G33-H33</f>
+        <v>890</v>
+      </c>
+      <c r="J33" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K33" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="20" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="26"/>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="26" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>1550</v>
+      </c>
+      <c r="E34" s="26" t="s">
+        <v>1551</v>
+      </c>
+      <c r="F34" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="G34" s="27">
+        <v>1020</v>
+      </c>
+      <c r="H34" s="27">
+        <v>30</v>
+      </c>
+      <c r="I34" s="27">
+        <f>G34-H34</f>
+        <v>990</v>
+      </c>
+      <c r="J34" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="K34" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" s="26" t="s">
+        <v>1517</v>
+      </c>
+      <c r="M34" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="N34" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="O34" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="P34" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q34" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D36" s="6">
+        <f>COUNTA(D3:D34)</f>
+        <v>28</v>
+      </c>
+      <c r="G36" s="6">
+        <f t="shared" ref="G36:Q36" si="3">SUBTOTAL(9,G3:G34)</f>
+        <v>20270</v>
+      </c>
+      <c r="H36" s="6">
+        <f t="shared" si="3"/>
+        <v>880</v>
+      </c>
+      <c r="I36" s="6">
+        <f t="shared" si="3"/>
+        <v>19390</v>
+      </c>
+      <c r="J36" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M36" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N36" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O36" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P36" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="6">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H37">
+        <f>-8*17</f>
+        <v>-136</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D38" s="5"/>
+      <c r="E38" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H38">
+        <f>-5*25</f>
+        <v>-125</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="O38" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C39" s="4">
+        <f>SUMIFS(I$3:I$34,B$3:B$34,A$38,L$3:L$34,A$39)</f>
+        <v>18400</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="8">
+        <f>SUMIFS(Q$3:Q$34,B$3:B$34,A$38,L$3:L$34,A$39)</f>
+        <v>31</v>
+      </c>
+      <c r="F39" t="s">
+        <v>196</v>
+      </c>
+      <c r="H39">
+        <f>-3*30</f>
+        <v>-90</v>
+      </c>
+      <c r="K39" t="s">
+        <v>197</v>
+      </c>
+      <c r="L39">
+        <f>SUMIFS(G$3:G$34,J$3:J$34,K$38)</f>
+        <v>625</v>
+      </c>
+      <c r="M39">
+        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$38)-INT(COUNTIFS(J$3:J$34,K$38,M$3:M$34,"*gộp*")/2)</f>
+        <v>4</v>
+      </c>
+      <c r="O39" t="s">
+        <v>21</v>
+      </c>
+      <c r="P39">
+        <f>L44</f>
+        <v>-528</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B40" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C40" s="3">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3"/>
+      <c r="K40" t="s">
+        <v>200</v>
+      </c>
+      <c r="L40">
+        <f>-SUMIFS(H$3:H$34,J$3:J$34,K$38)+M40*5</f>
+        <v>-100</v>
+      </c>
+      <c r="M40">
+        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$38)-INT(COUNTIFS(J$3:J$34,K$38,M$3:M$34,"*gộp*")/2)</f>
+        <v>4</v>
+      </c>
+      <c r="O40" t="s">
+        <v>1668</v>
+      </c>
+      <c r="P40">
+        <f>L52</f>
+        <v>14544</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B41" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C41" s="3">
+        <f>-SUMIFS(I$3:I$34,B$3:B$34,A$38,P$3:P$34,"xx",N$3:N$34,"x")</f>
+        <v>-990</v>
+      </c>
+      <c r="D41" s="3"/>
+      <c r="E41" s="7">
+        <f>SUMIFS(Q$3:Q$34,B$3:B$34,A$38,P$3:P$34,"xx",N$3:N$34,"x")</f>
+        <v>1</v>
+      </c>
+      <c r="K41" t="s">
+        <v>202</v>
+      </c>
+      <c r="L41">
+        <f>-M41*2</f>
+        <v>-58</v>
+      </c>
+      <c r="M41">
+        <f>E42-(COUNTIFS(M$3:M$34,"*gộp*")/2)-COUNTIFS(M$3:M$34,"*đơn trả*")-COUNTIFS(M$3:M$34,"*hàng tỉnh*")</f>
+        <v>29</v>
+      </c>
+      <c r="O41" t="s">
+        <v>135</v>
+      </c>
+      <c r="P41">
+        <f>L60</f>
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B42" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C42" s="5">
+        <f>SUBTOTAL(9,C39:C41)</f>
+        <v>17410</v>
+      </c>
+      <c r="D42" s="5"/>
+      <c r="E42">
+        <f>E39</f>
+        <v>31</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="L42" s="7">
+        <v>-995</v>
+      </c>
+      <c r="M42" t="s">
+        <v>288</v>
+      </c>
+      <c r="O42" t="s">
+        <v>20</v>
+      </c>
+      <c r="P42">
+        <f>L68</f>
+        <v>875</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B43" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="K43" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O43" t="s">
+        <v>207</v>
+      </c>
+      <c r="P43">
+        <f>-C46</f>
+        <v>-17410</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B44" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="L44" s="18">
+        <f>SUBTOTAL(9,L39:L43)</f>
+        <v>-528</v>
+      </c>
+      <c r="M44" s="18">
+        <f>M39</f>
+        <v>4</v>
+      </c>
+      <c r="O44" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P44" s="9">
+        <f>SUBTOTAL(9,P39:P43)</f>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B46" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C46" s="1">
+        <f>C42+C43+C44</f>
+        <v>17410</v>
+      </c>
+      <c r="D46" s="1"/>
+      <c r="E46" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>1596</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K47" t="s">
+        <v>197</v>
+      </c>
+      <c r="L47">
+        <f>SUMIFS(G$3:G$34,J$3:J$34,K$46)</f>
+        <v>14895</v>
+      </c>
+      <c r="M47">
+        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$46)-INT(COUNTIFS(J$3:J$34,K$46,M$3:M$34,"*gộp*")/2)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K48" t="s">
+        <v>200</v>
+      </c>
+      <c r="L48">
+        <f>SUM(H37:H39)</f>
+        <v>-351</v>
+      </c>
+      <c r="M48">
+        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$46)-INT(COUNTIFS(J$3:J$34,K$46,M$3:M$34,"*gộp*")/2)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K49" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="50" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K50" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="51" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K51" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="52" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L52" s="18">
+        <f>SUBTOTAL(9,L47:L51)</f>
+        <v>14544</v>
+      </c>
+      <c r="M52" s="18">
+        <f>M47</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K54" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="55" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K55" t="s">
+        <v>197</v>
+      </c>
+      <c r="L55">
+        <f>SUMIFS(G$3:G$34,J$3:J$34,K$54)</f>
+        <v>2830</v>
+      </c>
+      <c r="M55">
+        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$54)-INT(COUNTIFS(J$3:J$34,K$54,M$3:M$34,"*gộp*")/2)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K56" t="s">
+        <v>200</v>
+      </c>
+      <c r="L56">
+        <f>-SUMIFS(H$3:H$34,J$3:J$34,K$54)+M56*5</f>
+        <v>-175</v>
+      </c>
+      <c r="M56">
+        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$54)-INT(COUNTIFS(J$3:J$34,K$54,M$3:M$34,"*gộp*")/2)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K57" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="58" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K58" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="59" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K59" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="60" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L60" s="18">
+        <f>SUBTOTAL(9,L55:L59)</f>
+        <v>2655</v>
+      </c>
+      <c r="M60" s="18">
+        <f>M55</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K62" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="63" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K63" t="s">
+        <v>197</v>
+      </c>
+      <c r="L63">
+        <f>SUMIFS(G$3:G$34,J$3:J$34,K$62)</f>
+        <v>900</v>
+      </c>
+      <c r="M63">
+        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$62)-INT(COUNTIFS(J$3:J$34,K$62,M$3:M$34,"*gộp*")/2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K64" t="s">
+        <v>200</v>
+      </c>
+      <c r="L64">
+        <f>-SUMIFS(H$3:H$34,J$3:J$34,K$62)+M64*5</f>
+        <v>-25</v>
+      </c>
+      <c r="M64">
+        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$62)-INT(COUNTIFS(J$3:J$34,K$62,M$3:M$34,"*gộp*")/2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K65" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="66" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K66" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="67" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K67" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="68" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L68" s="18">
+        <f>SUBTOTAL(9,L63:L67)</f>
+        <v>875</v>
+      </c>
+      <c r="M68" s="18">
+        <f>M63</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P34" xr:uid="{00000000-0009-0000-0000-000010000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P34">
+      <sortCondition ref="J2:J34"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D9B982-EAEB-4F31-86BF-4D059AFDEA27}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
@@ -20844,7 +23098,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>1514</v>
+        <v>1583</v>
       </c>
       <c r="B1" s="10">
         <v>2026</v>
@@ -20852,19 +23106,19 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>1515</v>
+        <v>1584</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>1516</v>
+        <v>1585</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>1517</v>
+        <v>1586</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>1518</v>
+        <v>1587</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>1519</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -21188,19 +23442,19 @@
       </c>
       <c r="B18" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C18" s="13">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="13" cm="1">
         <f t="array" aca="1" ref="D18" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A18,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -21394,16 +23648,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D28" s="14" t="s">
-        <v>1520</v>
+        <v>1589</v>
       </c>
       <c r="E28" s="14">
         <f ca="1">SUBTOTAL(9,E4:E27)</f>
-        <v>474</v>
+        <v>503</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D29" s="14" t="s">
-        <v>1521</v>
+        <v>1590</v>
       </c>
       <c r="E29" s="14" cm="1">
         <f t="array" ref="E29" ca="1">SUMPRODUCT(
@@ -21415,29 +23669,29 @@
         ),
     0)
 )</f>
-        <v>1972</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D30" s="14" t="s">
-        <v>1522</v>
+        <v>1591</v>
       </c>
       <c r="E30" s="14">
         <f ca="1">-E28*2</f>
-        <v>-948</v>
+        <v>-1006</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D31" s="14" t="s">
-        <v>1523</v>
+        <v>1592</v>
       </c>
       <c r="E31" s="14">
         <f ca="1">SUBTOTAL(9,E29:E30)</f>
-        <v>1024</v>
+        <v>1102</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E27" xr:uid="{00000000-0009-0000-0000-00000E000000}"/>
+  <autoFilter ref="A2:E27" xr:uid="{00000000-0009-0000-0000-00000F000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C3:D27">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/data/May/InternalDailyReport_May.xlsx
+++ b/data/May/InternalDailyReport_May.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DEBE668-34DC-4B9F-BB7B-8E3B736B0E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4E1DC7-4A03-45B6-8C7D-9980CD23011F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="7" r:id="rId1"/>
@@ -29,7 +29,8 @@
     <sheet name="18-05" sheetId="22" r:id="rId14"/>
     <sheet name="19-05" sheetId="23" r:id="rId15"/>
     <sheet name="20-05" sheetId="24" r:id="rId16"/>
-    <sheet name="Sheet1" sheetId="19" r:id="rId17"/>
+    <sheet name="21-05" sheetId="25" r:id="rId17"/>
+    <sheet name="Sheet1" sheetId="19" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01-05'!$A$2:$P$56</definedName>
@@ -47,8 +48,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'16-05'!$A$2:$P$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'18-05'!$A$2:$P$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'19-05'!$A$2:$P$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'20-05'!$A$2:$P$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">Sheet1!$A$2:$E$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'20-05'!$A$2:$P$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'21-05'!$A$2:$P$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">Sheet1!$A$2:$E$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -90,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5602" uniqueCount="1669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6003" uniqueCount="1773">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -4841,6 +4843,237 @@
     <t>at 19-05</t>
   </si>
   <si>
+    <t>HD022402</t>
+  </si>
+  <si>
+    <t>20-05-2026</t>
+  </si>
+  <si>
+    <t>Jess-9244</t>
+  </si>
+  <si>
+    <t>275/14B1 Dạng Nguyên Cẩn, Phường Phú Lâm</t>
+  </si>
+  <si>
+    <t>AT 20-05</t>
+  </si>
+  <si>
+    <t>Bé Hiền - fb Yudy Phạm</t>
+  </si>
+  <si>
+    <t>HD022410</t>
+  </si>
+  <si>
+    <t>336/20 nguyễn văn luông p12</t>
+  </si>
+  <si>
+    <t>Trần Lê Trâm Anh</t>
+  </si>
+  <si>
+    <t>HD022426</t>
+  </si>
+  <si>
+    <t>179/13A hoà bình Phường Hiệp Tân</t>
+  </si>
+  <si>
+    <t>HD022286</t>
+  </si>
+  <si>
+    <t>Mr Quốc - VTS-64591HCR</t>
+  </si>
+  <si>
+    <t>HD022211</t>
+  </si>
+  <si>
+    <t>Thanh Yến</t>
+  </si>
+  <si>
+    <t>HD022266</t>
+  </si>
+  <si>
+    <t>188/4 đường thới an 16 phường thới an</t>
+  </si>
+  <si>
+    <t>HƯƠNG</t>
+  </si>
+  <si>
+    <t>HD022382</t>
+  </si>
+  <si>
+    <t>7g đường số 8 tân hưng</t>
+  </si>
+  <si>
+    <t>Vận</t>
+  </si>
+  <si>
+    <t>HD022293</t>
+  </si>
+  <si>
+    <t>Tháp RS6, chung cư Richstar 2, số 239 Hoà Bình, phường Phú Thạnh</t>
+  </si>
+  <si>
+    <t>nguyen lý</t>
+  </si>
+  <si>
+    <t>HD022279</t>
+  </si>
+  <si>
+    <t>62/7h ấp 3 xã xuaabn thơi thượng</t>
+  </si>
+  <si>
+    <t>Alice Nguyễn</t>
+  </si>
+  <si>
+    <t>HD022396</t>
+  </si>
+  <si>
+    <t>Lyly My</t>
+  </si>
+  <si>
+    <t>HD022377</t>
+  </si>
+  <si>
+    <t>50/26 thanh xuân 24 thới an</t>
+  </si>
+  <si>
+    <t>Mỹ Phượng</t>
+  </si>
+  <si>
+    <t>HD022263</t>
+  </si>
+  <si>
+    <t>1414 huỳnh tấn phát p phú mỹ</t>
+  </si>
+  <si>
+    <t>Any</t>
+  </si>
+  <si>
+    <t>HD022412</t>
+  </si>
+  <si>
+    <t>101 đông hưng thuận42 phường tân hưng thuận</t>
+  </si>
+  <si>
+    <t>HD022267</t>
+  </si>
+  <si>
+    <t>Thương</t>
+  </si>
+  <si>
+    <t>HD022196</t>
+  </si>
+  <si>
+    <t>181 đường số 79 phường tân quy</t>
+  </si>
+  <si>
+    <t>Moon Nguyễn</t>
+  </si>
+  <si>
+    <t>HD022375</t>
+  </si>
+  <si>
+    <t>16 kim ngân, khu dân cư phong phu 4, xã phong phú</t>
+  </si>
+  <si>
+    <t>Ngoc_Ann tiktok gingeri 16:39</t>
+  </si>
+  <si>
+    <t>HD022381</t>
+  </si>
+  <si>
+    <t>1/7 nguyễn văn yên tân thới hoà</t>
+  </si>
+  <si>
+    <t>VICKY TRẦN</t>
+  </si>
+  <si>
+    <t>Đắc Hội Express 127/17 bình lợi p13</t>
+  </si>
+  <si>
+    <t>ms Linh</t>
+  </si>
+  <si>
+    <t>HD022275</t>
+  </si>
+  <si>
+    <t>141A đường số 1 phường Thông Tây Hội</t>
+  </si>
+  <si>
+    <t>hsu_myat to</t>
+  </si>
+  <si>
+    <t>HD022406</t>
+  </si>
+  <si>
+    <t>2A/14, Nguyễn Thị Minh Khai, P. Đakao</t>
+  </si>
+  <si>
+    <t>HD022200</t>
+  </si>
+  <si>
+    <t>Vincom đồng khởi, 45 lý tự trọng, căn hộ 2604</t>
+  </si>
+  <si>
+    <t>HD022255</t>
+  </si>
+  <si>
+    <t>Tòa nhà C22 Building Số G5, Đường C22, Phường 12</t>
+  </si>
+  <si>
+    <t>Ý nhi</t>
+  </si>
+  <si>
+    <t>HD022414</t>
+  </si>
+  <si>
+    <t>53 phạm ngọc thạch p6</t>
+  </si>
+  <si>
+    <t>CUS19950/pelpanhaketya</t>
+  </si>
+  <si>
+    <t>HD022206</t>
+  </si>
+  <si>
+    <t>270B Lý thường kiệt, khu phố 1, Phường 6</t>
+  </si>
+  <si>
+    <t>Amsumalin Abu</t>
+  </si>
+  <si>
+    <t>HD022399</t>
+  </si>
+  <si>
+    <t>03 trương quốc dung p8</t>
+  </si>
+  <si>
+    <t>HD022240</t>
+  </si>
+  <si>
+    <t>Huyentran Nguyen</t>
+  </si>
+  <si>
+    <t>HD022374</t>
+  </si>
+  <si>
+    <t>86-88 pasteur</t>
+  </si>
+  <si>
+    <t>linh</t>
+  </si>
+  <si>
+    <t>HD022244</t>
+  </si>
+  <si>
+    <t>358/2/2 cmt8</t>
+  </si>
+  <si>
+    <t>at 20-05</t>
+  </si>
+  <si>
+    <t>2 đơn</t>
+  </si>
+  <si>
     <t>THÁNG 5</t>
   </si>
   <si>
@@ -4871,232 +5104,313 @@
     <t>Lợi nhuận</t>
   </si>
   <si>
-    <t>20-05-2026</t>
-  </si>
-  <si>
-    <t>Jess-9244</t>
-  </si>
-  <si>
-    <t>275/14B1 Dạng Nguyên Cẩn, Phường Phú Lâm</t>
-  </si>
-  <si>
-    <t>AT 20-05</t>
-  </si>
-  <si>
-    <t>VICKY TRẦN</t>
-  </si>
-  <si>
-    <t>Đắc Hội Express 127/17 bình lợi p13</t>
-  </si>
-  <si>
-    <t>hsu_myat to</t>
-  </si>
-  <si>
-    <t>HD022406</t>
-  </si>
-  <si>
-    <t>2A/14, Nguyễn Thị Minh Khai, P. Đakao</t>
-  </si>
-  <si>
-    <t>Bé Hiền - fb Yudy Phạm</t>
-  </si>
-  <si>
-    <t>HD022410</t>
-  </si>
-  <si>
-    <t>336/20 nguyễn văn luông p12</t>
-  </si>
-  <si>
-    <t>Trần Lê Trâm Anh</t>
-  </si>
-  <si>
-    <t>HD022426</t>
-  </si>
-  <si>
-    <t>Mr Quốc - VTS-64591HCR</t>
-  </si>
-  <si>
-    <t>HD022211</t>
-  </si>
-  <si>
-    <t>HD022200</t>
-  </si>
-  <si>
-    <t>Vincom đồng khởi, 45 lý tự trọng, căn hộ 2604</t>
-  </si>
-  <si>
-    <t>HD022255</t>
-  </si>
-  <si>
-    <t>Tòa nhà C22 Building Số G5, Đường C22, Phường 12</t>
-  </si>
-  <si>
-    <t>Thanh Yến</t>
-  </si>
-  <si>
-    <t>HD022266</t>
-  </si>
-  <si>
-    <t>188/4 đường thới an 16 phường thới an</t>
-  </si>
-  <si>
-    <t>HƯƠNG</t>
-  </si>
-  <si>
-    <t>HD022382</t>
-  </si>
-  <si>
-    <t>7g đường số 8 tân hưng</t>
-  </si>
-  <si>
-    <t>Vận</t>
-  </si>
-  <si>
-    <t>HD022293</t>
-  </si>
-  <si>
-    <t>Tháp RS6, chung cư Richstar 2, số 239 Hoà Bình, phường Phú Thạnh</t>
-  </si>
-  <si>
-    <t>nguyen lý</t>
-  </si>
-  <si>
-    <t>HD022279</t>
-  </si>
-  <si>
-    <t>62/7h ấp 3 xã xuaabn thơi thượng</t>
-  </si>
-  <si>
-    <t>Ý nhi</t>
-  </si>
-  <si>
-    <t>HD022414</t>
-  </si>
-  <si>
-    <t>53 phạm ngọc thạch p6</t>
-  </si>
-  <si>
-    <t>CUS19950/pelpanhaketya</t>
-  </si>
-  <si>
-    <t>HD022206</t>
-  </si>
-  <si>
-    <t>270B Lý thường kiệt, khu phố 1, Phường 6</t>
-  </si>
-  <si>
-    <t>Alice Nguyễn</t>
-  </si>
-  <si>
-    <t>HD022396</t>
-  </si>
-  <si>
-    <t>Amsumalin Abu</t>
-  </si>
-  <si>
-    <t>HD022399</t>
-  </si>
-  <si>
-    <t>03 trương quốc dung p8</t>
-  </si>
-  <si>
-    <t>HD022286</t>
-  </si>
-  <si>
-    <t>179/13A hoà bình Phường Hiệp Tân</t>
-  </si>
-  <si>
-    <t>Lyly My</t>
-  </si>
-  <si>
-    <t>HD022377</t>
-  </si>
-  <si>
-    <t>50/26 thanh xuân 24 thới an</t>
-  </si>
-  <si>
-    <t>HD022240</t>
-  </si>
-  <si>
-    <t>Mỹ Phượng</t>
-  </si>
-  <si>
-    <t>HD022263</t>
-  </si>
-  <si>
-    <t>1414 huỳnh tấn phát p phú mỹ</t>
-  </si>
-  <si>
-    <t>Huyentran Nguyen</t>
-  </si>
-  <si>
-    <t>HD022374</t>
-  </si>
-  <si>
-    <t>86-88 pasteur</t>
-  </si>
-  <si>
-    <t>linh</t>
-  </si>
-  <si>
-    <t>HD022244</t>
-  </si>
-  <si>
-    <t>358/2/2 cmt8</t>
-  </si>
-  <si>
-    <t>Any</t>
-  </si>
-  <si>
-    <t>HD022412</t>
-  </si>
-  <si>
-    <t>101 đông hưng thuận42 phường tân hưng thuận</t>
-  </si>
-  <si>
-    <t>ms Linh</t>
-  </si>
-  <si>
-    <t>HD022275</t>
-  </si>
-  <si>
-    <t>141A đường số 1 phường Thông Tây Hội</t>
-  </si>
-  <si>
-    <t>HD022267</t>
-  </si>
-  <si>
-    <t>HD022402</t>
-  </si>
-  <si>
-    <t>Thương</t>
-  </si>
-  <si>
-    <t>HD022196</t>
-  </si>
-  <si>
-    <t>181 đường số 79 phường tân quy</t>
-  </si>
-  <si>
-    <t>Moon Nguyễn</t>
-  </si>
-  <si>
-    <t>HD022375</t>
-  </si>
-  <si>
-    <t>16 kim ngân, khu dân cư phong phu 4, xã phong phú</t>
-  </si>
-  <si>
-    <t>Ngoc_Ann tiktok gingeri 16:39</t>
-  </si>
-  <si>
-    <t>HD022381</t>
-  </si>
-  <si>
-    <t>1/7 nguyễn văn yên tân thới hoà</t>
-  </si>
-  <si>
-    <t>at 20-05</t>
+    <t>Lý Thanh Tâm</t>
+  </si>
+  <si>
+    <t>HD022564</t>
+  </si>
+  <si>
+    <t>71/6/16 lê tấn bê an lạc</t>
+  </si>
+  <si>
+    <t>AT 21-05</t>
+  </si>
+  <si>
+    <t>21-05-2026</t>
+  </si>
+  <si>
+    <t>Anh Trúc Huỳnh</t>
+  </si>
+  <si>
+    <t>HD022586</t>
+  </si>
+  <si>
+    <t>Số 64 dg 38 hiep binh chanh</t>
+  </si>
+  <si>
+    <t>người nhận Hồng Sơn fb Duong Hyun</t>
+  </si>
+  <si>
+    <t>HD022495</t>
+  </si>
+  <si>
+    <t>135 Bạch Đằng, phường Tân Sơn Hòa (Phường 2) (CÔNG TY LÊ GIA EXPRESS)</t>
+  </si>
+  <si>
+    <t>BN182 miki chouchou Fb.</t>
+  </si>
+  <si>
+    <t>HD022533</t>
+  </si>
+  <si>
+    <t>163 Đường Trương Thị Hoa, phường Tân Thái Hiệp</t>
+  </si>
+  <si>
+    <t>Hana Le</t>
+  </si>
+  <si>
+    <t>HD022573</t>
+  </si>
+  <si>
+    <t>427/22 le van quoi binh tri dong A</t>
+  </si>
+  <si>
+    <t>Giap Anh Tuyet</t>
+  </si>
+  <si>
+    <t>HD022508</t>
+  </si>
+  <si>
+    <t>007 Lô B, Đường C6, Chung cư Tây Thạnh</t>
+  </si>
+  <si>
+    <t>Bùi Vĩ Thương</t>
+  </si>
+  <si>
+    <t>HD022636</t>
+  </si>
+  <si>
+    <t>3273 phạm thế hiển, p7</t>
+  </si>
+  <si>
+    <t>HD022429</t>
+  </si>
+  <si>
+    <t>HD022628</t>
+  </si>
+  <si>
+    <t>My Yến</t>
+  </si>
+  <si>
+    <t>HD022525</t>
+  </si>
+  <si>
+    <t>334/33/1C Chu văn an, phường 12</t>
+  </si>
+  <si>
+    <t>Hải Yến</t>
+  </si>
+  <si>
+    <t>HD003936</t>
+  </si>
+  <si>
+    <t>319/17 lê văn thọ p9</t>
+  </si>
+  <si>
+    <t>Hoang Linh Le</t>
+  </si>
+  <si>
+    <t>HD022460</t>
+  </si>
+  <si>
+    <t>314 Điện Biên Phủ, Phường Vườn Lài</t>
+  </si>
+  <si>
+    <t>Chị Oanh</t>
+  </si>
+  <si>
+    <t>HD022599</t>
+  </si>
+  <si>
+    <t>291 hùng vương phương an đông</t>
+  </si>
+  <si>
+    <t>HD022442</t>
+  </si>
+  <si>
+    <t>Thuy Thuy</t>
+  </si>
+  <si>
+    <t>HD022451</t>
+  </si>
+  <si>
+    <t>58E cao thắng,p5 (Viện chăm sóc da aperio)</t>
+  </si>
+  <si>
+    <t>Linh Ngô</t>
+  </si>
+  <si>
+    <t>HD022618</t>
+  </si>
+  <si>
+    <t>90 a lê lăng Phú thọ hoà</t>
+  </si>
+  <si>
+    <t>Lan Phạm</t>
+  </si>
+  <si>
+    <t>HD022621</t>
+  </si>
+  <si>
+    <t>685 âu cơ p tân thành - lô C</t>
+  </si>
+  <si>
+    <t>Sorinna items PhnomPenh ( Meng Kheang customer )</t>
+  </si>
+  <si>
+    <t>HD022445</t>
+  </si>
+  <si>
+    <t>301 phạm ngũ lão</t>
+  </si>
+  <si>
+    <t>01우준</t>
+  </si>
+  <si>
+    <t>HD022601</t>
+  </si>
+  <si>
+    <t>Đảo kim cương phường bình trưng tây</t>
+  </si>
+  <si>
+    <t>Phạm Thị Minh Tuyền</t>
+  </si>
+  <si>
+    <t>HD022341</t>
+  </si>
+  <si>
+    <t>352/4g lê văn quới, bình hưng hoà A</t>
+  </si>
+  <si>
+    <t>thuy vy</t>
+  </si>
+  <si>
+    <t>HD022620</t>
+  </si>
+  <si>
+    <t>chung cư Ruby - cổng 2, đường Tân Thắng, P. Tân Sơn Nhì</t>
+  </si>
+  <si>
+    <t>HD022604</t>
+  </si>
+  <si>
+    <t>Mỹ Vinh</t>
+  </si>
+  <si>
+    <t>HD022560</t>
+  </si>
+  <si>
+    <t>Aqua1 vinhome bason bến nghé</t>
+  </si>
+  <si>
+    <t>HD022503</t>
+  </si>
+  <si>
+    <t>Toà Aster - Urban green (đối diện Vạn Phúc)</t>
+  </si>
+  <si>
+    <t>HD022383</t>
+  </si>
+  <si>
+    <t>Nguyễn Yến Nhi</t>
+  </si>
+  <si>
+    <t>HD022491</t>
+  </si>
+  <si>
+    <t>Tháp v3 Chung cư sun rise city south 23 nguyễn hữu thọ tân hưng</t>
+  </si>
+  <si>
+    <t>Pé Thỏ</t>
+  </si>
+  <si>
+    <t>HD022455</t>
+  </si>
+  <si>
+    <t>1002 tạ quang bửu f6 Chung cư the pegasuite1 (zone1)</t>
+  </si>
+  <si>
+    <t>Khánh Thư Nguyen</t>
+  </si>
+  <si>
+    <t>HD022626</t>
+  </si>
+  <si>
+    <t>88 dien Hồng phường 1</t>
+  </si>
+  <si>
+    <t>chủ mau - fb Hana Ngo</t>
+  </si>
+  <si>
+    <t>HD022615</t>
+  </si>
+  <si>
+    <t>67 Trang từ phường 14</t>
+  </si>
+  <si>
+    <t>Quỳnh Nhi</t>
+  </si>
+  <si>
+    <t>HD022493</t>
+  </si>
+  <si>
+    <t>180/1T QL1A Tân Phú</t>
+  </si>
+  <si>
+    <t>Mỹ ý</t>
+  </si>
+  <si>
+    <t>HD022613</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Kim Hoàng</t>
+  </si>
+  <si>
+    <t>HD022430</t>
+  </si>
+  <si>
+    <t>265 Nơ Trang Long, phường Bình Lợi Trung</t>
+  </si>
+  <si>
+    <t>HD022342</t>
+  </si>
+  <si>
+    <t>320/14 nguyễn văn linh phường bình thuận</t>
+  </si>
+  <si>
+    <t>NHƯ- Khanh sale- airmy</t>
+  </si>
+  <si>
+    <t>HD022551</t>
+  </si>
+  <si>
+    <t>144C Trần Thị Trọng, Phường 15</t>
+  </si>
+  <si>
+    <t>Nguyễn Thanh Ngân</t>
+  </si>
+  <si>
+    <t>HD022575</t>
+  </si>
+  <si>
+    <t>159c /18a dạ nam, chánh hưng</t>
+  </si>
+  <si>
+    <t>Huỳnh Mẫn</t>
+  </si>
+  <si>
+    <t>HD022522</t>
+  </si>
+  <si>
+    <t>1362 tỉnh lộ 10 tân tạo</t>
+  </si>
+  <si>
+    <t>VVI EVA</t>
+  </si>
+  <si>
+    <t>141 Hùng Vương phường 4</t>
+  </si>
+  <si>
+    <t>PHƯƠNG DUNG</t>
+  </si>
+  <si>
+    <t>23/4A đường 48 khu phố 6 hiệp bình chánh</t>
+  </si>
+  <si>
+    <t>HD020811</t>
+  </si>
+  <si>
+    <t>at 21-05</t>
   </si>
 </sst>
 </file>
@@ -5250,7 +5564,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -5293,6 +5607,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -21057,7 +21374,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A2:R68"/>
+  <dimension ref="A2:R70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -21141,7 +21458,7 @@
         <v>1132</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>1658</v>
+        <v>1583</v>
       </c>
       <c r="E3" s="20" t="s">
         <v>1134</v>
@@ -21156,7 +21473,7 @@
         <v>30</v>
       </c>
       <c r="I3" s="21">
-        <f>G3-H3</f>
+        <f t="shared" ref="I3:I36" si="0">G3-H3</f>
         <v>870</v>
       </c>
       <c r="J3" s="20" t="s">
@@ -21166,7 +21483,7 @@
         <v>21</v>
       </c>
       <c r="L3" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M3" s="20"/>
       <c r="N3" s="20"/>
@@ -21184,11 +21501,11 @@
         <v>17</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>1594</v>
+        <v>1585</v>
       </c>
       <c r="D4" s="20"/>
       <c r="E4" s="20" t="s">
-        <v>1595</v>
+        <v>1586</v>
       </c>
       <c r="F4" s="21">
         <v>6</v>
@@ -21200,17 +21517,17 @@
         <v>30</v>
       </c>
       <c r="I4" s="21">
-        <f>G4-H4</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>1596</v>
+        <v>1587</v>
       </c>
       <c r="K4" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L4" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M4" s="20"/>
       <c r="N4" s="20"/>
@@ -21230,13 +21547,13 @@
         <v>17</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>1602</v>
+        <v>1588</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>1603</v>
+        <v>1589</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>1604</v>
+        <v>1590</v>
       </c>
       <c r="F5" s="21">
         <v>6</v>
@@ -21248,17 +21565,17 @@
         <v>25</v>
       </c>
       <c r="I5" s="21">
-        <f>G5-H5</f>
+        <f t="shared" si="0"/>
         <v>1850</v>
       </c>
       <c r="J5" s="20" t="s">
-        <v>1596</v>
+        <v>1587</v>
       </c>
       <c r="K5" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L5" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M5" s="20"/>
       <c r="N5" s="20"/>
@@ -21274,13 +21591,13 @@
         <v>17</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>1605</v>
+        <v>1591</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>1606</v>
+        <v>1592</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>1637</v>
+        <v>1593</v>
       </c>
       <c r="F6" s="20" t="s">
         <v>46</v>
@@ -21292,17 +21609,17 @@
         <v>25</v>
       </c>
       <c r="I6" s="21">
-        <f>G6-H6</f>
+        <f t="shared" si="0"/>
         <v>870</v>
       </c>
       <c r="J6" s="20" t="s">
-        <v>1596</v>
+        <v>1587</v>
       </c>
       <c r="K6" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M6" s="25" t="s">
         <v>377</v>
@@ -21320,13 +21637,13 @@
         <v>17</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>1605</v>
+        <v>1591</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>1636</v>
+        <v>1594</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>1637</v>
+        <v>1593</v>
       </c>
       <c r="F7" s="20" t="s">
         <v>46</v>
@@ -21338,17 +21655,17 @@
         <v>0</v>
       </c>
       <c r="I7" s="21">
-        <f>G7-H7</f>
+        <f t="shared" si="0"/>
         <v>770</v>
       </c>
       <c r="J7" s="20" t="s">
-        <v>1596</v>
+        <v>1587</v>
       </c>
       <c r="K7" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L7" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M7" s="25" t="s">
         <v>377</v>
@@ -21366,10 +21683,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>1607</v>
+        <v>1595</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>1608</v>
+        <v>1596</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>1267</v>
@@ -21384,17 +21701,17 @@
         <v>30</v>
       </c>
       <c r="I8" s="21">
-        <f>G8-H8</f>
+        <f t="shared" si="0"/>
         <v>780</v>
       </c>
       <c r="J8" s="20" t="s">
-        <v>1596</v>
+        <v>1587</v>
       </c>
       <c r="K8" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L8" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M8" s="20"/>
       <c r="N8" s="20"/>
@@ -21410,13 +21727,13 @@
         <v>17</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>1613</v>
+        <v>1597</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>1614</v>
+        <v>1598</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>1615</v>
+        <v>1599</v>
       </c>
       <c r="F9" s="21">
         <v>12</v>
@@ -21428,17 +21745,17 @@
         <v>30</v>
       </c>
       <c r="I9" s="21">
-        <f>G9-H9</f>
+        <f t="shared" si="0"/>
         <v>820</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>1596</v>
+        <v>1587</v>
       </c>
       <c r="K9" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L9" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M9" s="20"/>
       <c r="N9" s="20"/>
@@ -21454,13 +21771,13 @@
         <v>17</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>1616</v>
+        <v>1600</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>1617</v>
+        <v>1601</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>1618</v>
+        <v>1602</v>
       </c>
       <c r="F10" s="21">
         <v>7</v>
@@ -21472,17 +21789,17 @@
         <v>30</v>
       </c>
       <c r="I10" s="21">
-        <f>G10-H10</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J10" s="20" t="s">
-        <v>1596</v>
+        <v>1587</v>
       </c>
       <c r="K10" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L10" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M10" s="20"/>
       <c r="N10" s="20"/>
@@ -21502,13 +21819,13 @@
         <v>17</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>1619</v>
+        <v>1603</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>1620</v>
+        <v>1604</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>1621</v>
+        <v>1605</v>
       </c>
       <c r="F11" s="20" t="s">
         <v>46</v>
@@ -21520,17 +21837,17 @@
         <v>25</v>
       </c>
       <c r="I11" s="21">
-        <f>G11-H11</f>
+        <f t="shared" si="0"/>
         <v>350</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>1596</v>
+        <v>1587</v>
       </c>
       <c r="K11" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L11" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M11" s="20"/>
       <c r="N11" s="20"/>
@@ -21546,13 +21863,13 @@
         <v>17</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>1622</v>
+        <v>1606</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>1623</v>
+        <v>1607</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>1624</v>
+        <v>1608</v>
       </c>
       <c r="F12" s="20" t="s">
         <v>1335</v>
@@ -21564,17 +21881,17 @@
         <v>35</v>
       </c>
       <c r="I12" s="21">
-        <f>G12-H12</f>
+        <f t="shared" si="0"/>
         <v>790</v>
       </c>
       <c r="J12" s="20" t="s">
-        <v>1596</v>
+        <v>1587</v>
       </c>
       <c r="K12" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L12" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M12" s="20"/>
       <c r="N12" s="20"/>
@@ -21590,10 +21907,10 @@
         <v>17</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>1631</v>
+        <v>1609</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>1632</v>
+        <v>1610</v>
       </c>
       <c r="E13" s="20" t="s">
         <v>1270</v>
@@ -21608,17 +21925,17 @@
         <v>30</v>
       </c>
       <c r="I13" s="21">
-        <f>G13-H13</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J13" s="20" t="s">
-        <v>1596</v>
+        <v>1587</v>
       </c>
       <c r="K13" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L13" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M13" s="20"/>
       <c r="N13" s="20"/>
@@ -21638,13 +21955,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>1638</v>
+        <v>1611</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>1639</v>
+        <v>1612</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>1640</v>
+        <v>1613</v>
       </c>
       <c r="F14" s="21">
         <v>12</v>
@@ -21656,17 +21973,17 @@
         <v>30</v>
       </c>
       <c r="I14" s="21">
-        <f>G14-H14</f>
+        <f t="shared" si="0"/>
         <v>1500</v>
       </c>
       <c r="J14" s="20" t="s">
-        <v>1596</v>
+        <v>1587</v>
       </c>
       <c r="K14" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L14" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M14" s="20"/>
       <c r="N14" s="20"/>
@@ -21682,13 +21999,13 @@
         <v>17</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>1642</v>
+        <v>1614</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>1643</v>
+        <v>1615</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>1644</v>
+        <v>1616</v>
       </c>
       <c r="F15" s="21">
         <v>7</v>
@@ -21700,17 +22017,17 @@
         <v>30</v>
       </c>
       <c r="I15" s="21">
-        <f>G15-H15</f>
+        <f t="shared" si="0"/>
         <v>990</v>
       </c>
       <c r="J15" s="20" t="s">
-        <v>1596</v>
+        <v>1587</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L15" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M15" s="20"/>
       <c r="N15" s="20"/>
@@ -21726,13 +22043,13 @@
         <v>17</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>1651</v>
+        <v>1617</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>1652</v>
+        <v>1618</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>1653</v>
+        <v>1619</v>
       </c>
       <c r="F16" s="21">
         <v>12</v>
@@ -21744,17 +22061,17 @@
         <v>30</v>
       </c>
       <c r="I16" s="21">
-        <f>G16-H16</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J16" s="20" t="s">
-        <v>1596</v>
+        <v>1587</v>
       </c>
       <c r="K16" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L16" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M16" s="20"/>
       <c r="N16" s="20"/>
@@ -21777,7 +22094,7 @@
         <v>1451</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>1657</v>
+        <v>1620</v>
       </c>
       <c r="E17" s="20" t="s">
         <v>1453</v>
@@ -21792,17 +22109,17 @@
         <v>35</v>
       </c>
       <c r="I17" s="21">
-        <f>G17-H17</f>
+        <f t="shared" si="0"/>
         <v>660</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>1596</v>
+        <v>1587</v>
       </c>
       <c r="K17" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L17" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M17" s="20"/>
       <c r="N17" s="20"/>
@@ -21818,13 +22135,13 @@
         <v>17</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>1659</v>
+        <v>1621</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>1660</v>
+        <v>1622</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>1661</v>
+        <v>1623</v>
       </c>
       <c r="F18" s="21">
         <v>7</v>
@@ -21836,17 +22153,17 @@
         <v>35</v>
       </c>
       <c r="I18" s="21">
-        <f>G18-H18</f>
+        <f t="shared" si="0"/>
         <v>2675</v>
       </c>
       <c r="J18" s="20" t="s">
-        <v>1596</v>
+        <v>1587</v>
       </c>
       <c r="K18" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L18" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M18" s="25" t="s">
         <v>167</v>
@@ -21868,13 +22185,13 @@
         <v>17</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>1662</v>
+        <v>1624</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>1663</v>
+        <v>1625</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>1664</v>
+        <v>1626</v>
       </c>
       <c r="F19" s="20" t="s">
         <v>139</v>
@@ -21886,17 +22203,17 @@
         <v>35</v>
       </c>
       <c r="I19" s="21">
-        <f>G19-H19</f>
+        <f t="shared" si="0"/>
         <v>1650</v>
       </c>
       <c r="J19" s="20" t="s">
-        <v>1596</v>
+        <v>1587</v>
       </c>
       <c r="K19" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L19" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M19" s="20"/>
       <c r="N19" s="20"/>
@@ -21912,13 +22229,13 @@
         <v>17</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>1665</v>
+        <v>1627</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>1666</v>
+        <v>1628</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>1667</v>
+        <v>1629</v>
       </c>
       <c r="F20" s="20" t="s">
         <v>46</v>
@@ -21930,17 +22247,17 @@
         <v>25</v>
       </c>
       <c r="I20" s="21">
-        <f>G20-H20</f>
+        <f t="shared" si="0"/>
         <v>830</v>
       </c>
       <c r="J20" s="20" t="s">
-        <v>1596</v>
+        <v>1587</v>
       </c>
       <c r="K20" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L20" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M20" s="20"/>
       <c r="N20" s="20"/>
@@ -21974,7 +22291,7 @@
         <v>30</v>
       </c>
       <c r="I21" s="21">
-        <f>G21-H21</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J21" s="20" t="s">
@@ -21984,7 +22301,7 @@
         <v>21</v>
       </c>
       <c r="L21" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M21" s="20"/>
       <c r="N21" s="20"/>
@@ -22018,7 +22335,7 @@
         <v>30</v>
       </c>
       <c r="I22" s="21">
-        <f>G22-H22</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J22" s="20" t="s">
@@ -22028,7 +22345,7 @@
         <v>21</v>
       </c>
       <c r="L22" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M22" s="20"/>
       <c r="N22" s="20"/>
@@ -22038,7 +22355,7 @@
         <v>1</v>
       </c>
       <c r="R22" s="15">
-        <f t="shared" ref="R22:R23" si="0">H22</f>
+        <f>H22</f>
         <v>30</v>
       </c>
     </row>
@@ -22050,11 +22367,11 @@
         <v>17</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>1597</v>
+        <v>1630</v>
       </c>
       <c r="D23" s="20"/>
       <c r="E23" s="20" t="s">
-        <v>1598</v>
+        <v>1631</v>
       </c>
       <c r="F23" s="20" t="s">
         <v>85</v>
@@ -22066,7 +22383,7 @@
         <v>35</v>
       </c>
       <c r="I23" s="21">
-        <f>G23-H23</f>
+        <f t="shared" si="0"/>
         <v>-35</v>
       </c>
       <c r="J23" s="20" t="s">
@@ -22076,7 +22393,7 @@
         <v>21</v>
       </c>
       <c r="L23" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M23" s="20"/>
       <c r="N23" s="20"/>
@@ -22086,7 +22403,7 @@
         <v>1</v>
       </c>
       <c r="R23" s="15">
-        <f t="shared" si="0"/>
+        <f>H23</f>
         <v>35</v>
       </c>
     </row>
@@ -22096,13 +22413,13 @@
         <v>17</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>1654</v>
+        <v>1632</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>1655</v>
+        <v>1633</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>1656</v>
+        <v>1634</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>77</v>
@@ -22114,7 +22431,7 @@
         <v>25</v>
       </c>
       <c r="I24" s="21">
-        <f>G24-H24</f>
+        <f t="shared" si="0"/>
         <v>570</v>
       </c>
       <c r="J24" s="20" t="s">
@@ -22124,7 +22441,7 @@
         <v>21</v>
       </c>
       <c r="L24" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M24" s="25" t="s">
         <v>167</v>
@@ -22146,13 +22463,13 @@
         <v>17</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>1599</v>
+        <v>1635</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>1600</v>
+        <v>1636</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>1601</v>
+        <v>1637</v>
       </c>
       <c r="F25" s="21">
         <v>1</v>
@@ -22164,7 +22481,7 @@
         <v>25</v>
       </c>
       <c r="I25" s="21">
-        <f>G25-H25</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J25" s="20" t="s">
@@ -22174,7 +22491,7 @@
         <v>21</v>
       </c>
       <c r="L25" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M25" s="20"/>
       <c r="N25" s="20"/>
@@ -22184,7 +22501,7 @@
         <v>1</v>
       </c>
       <c r="R25" s="15">
-        <f t="shared" ref="R25:R26" si="1">H25</f>
+        <f>H25</f>
         <v>25</v>
       </c>
     </row>
@@ -22197,10 +22514,10 @@
         <v>796</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>1609</v>
+        <v>1638</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>1610</v>
+        <v>1639</v>
       </c>
       <c r="F26" s="21">
         <v>1</v>
@@ -22212,7 +22529,7 @@
         <v>25</v>
       </c>
       <c r="I26" s="21">
-        <f>G26-H26</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J26" s="20" t="s">
@@ -22222,7 +22539,7 @@
         <v>21</v>
       </c>
       <c r="L26" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M26" s="20"/>
       <c r="N26" s="20"/>
@@ -22232,7 +22549,7 @@
         <v>1</v>
       </c>
       <c r="R26" s="15">
-        <f t="shared" si="1"/>
+        <f>H26</f>
         <v>25</v>
       </c>
     </row>
@@ -22245,10 +22562,10 @@
         <v>1113</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>1611</v>
+        <v>1640</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>1612</v>
+        <v>1641</v>
       </c>
       <c r="F27" s="20" t="s">
         <v>95</v>
@@ -22260,7 +22577,7 @@
         <v>25</v>
       </c>
       <c r="I27" s="21">
-        <f>G27-H27</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J27" s="20" t="s">
@@ -22270,7 +22587,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M27" s="20"/>
       <c r="N27" s="20"/>
@@ -22286,13 +22603,13 @@
         <v>17</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>1625</v>
+        <v>1642</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>1626</v>
+        <v>1643</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>1627</v>
+        <v>1644</v>
       </c>
       <c r="F28" s="21">
         <v>3</v>
@@ -22304,7 +22621,7 @@
         <v>25</v>
       </c>
       <c r="I28" s="21">
-        <f>G28-H28</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J28" s="20" t="s">
@@ -22314,7 +22631,7 @@
         <v>21</v>
       </c>
       <c r="L28" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M28" s="20"/>
       <c r="N28" s="20"/>
@@ -22324,7 +22641,7 @@
         <v>1</v>
       </c>
       <c r="R28" s="15">
-        <f t="shared" ref="R28:R30" si="2">H28</f>
+        <f>H28</f>
         <v>25</v>
       </c>
     </row>
@@ -22334,13 +22651,13 @@
         <v>17</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>1628</v>
+        <v>1645</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>1629</v>
+        <v>1646</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>1630</v>
+        <v>1647</v>
       </c>
       <c r="F29" s="20" t="s">
         <v>95</v>
@@ -22352,7 +22669,7 @@
         <v>25</v>
       </c>
       <c r="I29" s="21">
-        <f>G29-H29</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J29" s="20" t="s">
@@ -22362,7 +22679,7 @@
         <v>21</v>
       </c>
       <c r="L29" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M29" s="20"/>
       <c r="N29" s="20"/>
@@ -22372,7 +22689,7 @@
         <v>1</v>
       </c>
       <c r="R29" s="15">
-        <f t="shared" si="2"/>
+        <f>H29</f>
         <v>25</v>
       </c>
     </row>
@@ -22382,13 +22699,13 @@
         <v>17</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>1633</v>
+        <v>1648</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>1634</v>
+        <v>1649</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>1635</v>
+        <v>1650</v>
       </c>
       <c r="F30" s="20" t="s">
         <v>406</v>
@@ -22400,7 +22717,7 @@
         <v>20</v>
       </c>
       <c r="I30" s="21">
-        <f>G30-H30</f>
+        <f t="shared" si="0"/>
         <v>-20</v>
       </c>
       <c r="J30" s="20" t="s">
@@ -22410,7 +22727,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M30" s="20"/>
       <c r="N30" s="20"/>
@@ -22420,7 +22737,7 @@
         <v>1</v>
       </c>
       <c r="R30" s="15">
-        <f t="shared" si="2"/>
+        <f>H30</f>
         <v>20</v>
       </c>
     </row>
@@ -22433,7 +22750,7 @@
         <v>585</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>1641</v>
+        <v>1651</v>
       </c>
       <c r="E31" s="20" t="s">
         <v>587</v>
@@ -22448,7 +22765,7 @@
         <v>25</v>
       </c>
       <c r="I31" s="21">
-        <f>G31-H31</f>
+        <f t="shared" si="0"/>
         <v>850</v>
       </c>
       <c r="J31" s="20" t="s">
@@ -22458,7 +22775,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M31" s="20"/>
       <c r="N31" s="20"/>
@@ -22474,13 +22791,13 @@
         <v>17</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>1645</v>
+        <v>1652</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>1646</v>
+        <v>1653</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>1647</v>
+        <v>1654</v>
       </c>
       <c r="F32" s="21">
         <v>1</v>
@@ -22492,7 +22809,7 @@
         <v>25</v>
       </c>
       <c r="I32" s="21">
-        <f>G32-H32</f>
+        <f t="shared" si="0"/>
         <v>990</v>
       </c>
       <c r="J32" s="20" t="s">
@@ -22502,7 +22819,7 @@
         <v>21</v>
       </c>
       <c r="L32" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M32" s="20"/>
       <c r="N32" s="20"/>
@@ -22518,13 +22835,13 @@
         <v>17</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>1648</v>
+        <v>1655</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>1649</v>
+        <v>1656</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>1650</v>
+        <v>1657</v>
       </c>
       <c r="F33" s="21">
         <v>3</v>
@@ -22536,7 +22853,7 @@
         <v>25</v>
       </c>
       <c r="I33" s="21">
-        <f>G33-H33</f>
+        <f t="shared" si="0"/>
         <v>890</v>
       </c>
       <c r="J33" s="20" t="s">
@@ -22546,7 +22863,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="20" t="s">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="M33" s="20"/>
       <c r="N33" s="20"/>
@@ -22562,26 +22879,26 @@
         <v>17</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>1549</v>
+        <v>751</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>1550</v>
+        <v>752</v>
       </c>
       <c r="E34" s="26" t="s">
-        <v>1551</v>
+        <v>753</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="G34" s="27">
-        <v>1020</v>
+        <v>820</v>
       </c>
       <c r="H34" s="27">
         <v>30</v>
       </c>
       <c r="I34" s="27">
-        <f>G34-H34</f>
-        <v>990</v>
+        <f t="shared" si="0"/>
+        <v>790</v>
       </c>
       <c r="J34" s="26" t="s">
         <v>271</v>
@@ -22590,7 +22907,7 @@
         <v>21</v>
       </c>
       <c r="L34" s="26" t="s">
-        <v>1517</v>
+        <v>733</v>
       </c>
       <c r="M34" s="26" t="s">
         <v>204</v>
@@ -22608,478 +22925,2940 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D36" s="6">
-        <f>COUNTA(D3:D34)</f>
-        <v>28</v>
-      </c>
-      <c r="G36" s="6">
-        <f t="shared" ref="G36:Q36" si="3">SUBTOTAL(9,G3:G34)</f>
-        <v>20270</v>
-      </c>
-      <c r="H36" s="6">
-        <f t="shared" si="3"/>
-        <v>880</v>
-      </c>
-      <c r="I36" s="6">
-        <f t="shared" si="3"/>
-        <v>19390</v>
-      </c>
-      <c r="J36" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K36" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L36" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M36" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N36" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O36" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P36" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q36" s="6">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H37">
+    <row r="35" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="26"/>
+      <c r="B35" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="26" t="s">
+        <v>834</v>
+      </c>
+      <c r="D35" s="26" t="s">
+        <v>835</v>
+      </c>
+      <c r="E35" s="26" t="s">
+        <v>836</v>
+      </c>
+      <c r="F35" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="G35" s="27">
+        <v>1185</v>
+      </c>
+      <c r="H35" s="27">
+        <v>35</v>
+      </c>
+      <c r="I35" s="27">
+        <f t="shared" si="0"/>
+        <v>1150</v>
+      </c>
+      <c r="J35" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="K35" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35" s="26" t="s">
+        <v>813</v>
+      </c>
+      <c r="M35" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="N35" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="O35" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="P35" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q35" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="26"/>
+      <c r="B36" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="26" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D36" s="26" t="s">
+        <v>1550</v>
+      </c>
+      <c r="E36" s="26" t="s">
+        <v>1551</v>
+      </c>
+      <c r="F36" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="G36" s="27">
+        <v>1020</v>
+      </c>
+      <c r="H36" s="27">
+        <v>30</v>
+      </c>
+      <c r="I36" s="27">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J36" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="K36" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="26" t="s">
+        <v>1517</v>
+      </c>
+      <c r="M36" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="N36" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="O36" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="P36" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q36" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D38" s="6">
+        <f>COUNTA(D3:D36)</f>
+        <v>30</v>
+      </c>
+      <c r="G38" s="6">
+        <f t="shared" ref="G38:Q38" si="1">SUBTOTAL(9,G3:G36)</f>
+        <v>22275</v>
+      </c>
+      <c r="H38" s="6">
+        <f t="shared" si="1"/>
+        <v>945</v>
+      </c>
+      <c r="I38" s="6">
+        <f t="shared" si="1"/>
+        <v>21330</v>
+      </c>
+      <c r="J38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q38" s="6">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H39">
         <f>-8*17</f>
         <v>-136</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C38" s="5" t="s">
+      <c r="I39">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="D38" s="5"/>
-      <c r="E38" s="9" t="s">
+      <c r="D40" s="5"/>
+      <c r="E40" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="H38">
+      <c r="H40">
         <f>-5*25</f>
         <v>-125</v>
       </c>
-      <c r="K38" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="L38" s="16" t="s">
+      <c r="I40">
+        <v>30</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="M38" s="16" t="s">
+      <c r="M40" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="O38" s="9" t="s">
+      <c r="O40" s="9" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>1593</v>
-      </c>
-      <c r="B39" s="8" t="s">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B41" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C39" s="4">
-        <f>SUMIFS(I$3:I$34,B$3:B$34,A$38,L$3:L$34,A$39)</f>
+      <c r="C41" s="4">
+        <f>SUMIFS(I$3:I$36,B$3:B$36,A$40,L$3:L$36,A$41)</f>
         <v>18400</v>
       </c>
-      <c r="D39" s="4"/>
-      <c r="E39" s="8">
-        <f>SUMIFS(Q$3:Q$34,B$3:B$34,A$38,L$3:L$34,A$39)</f>
+      <c r="D41" s="4"/>
+      <c r="E41" s="8">
+        <f>SUMIFS(Q$3:Q$36,B$3:B$36,A$40,L$3:L$36,A$41)</f>
         <v>31</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F41" t="s">
         <v>196</v>
       </c>
-      <c r="H39">
+      <c r="H41">
         <f>-3*30</f>
         <v>-90</v>
       </c>
-      <c r="K39" t="s">
+      <c r="K41" t="s">
         <v>197</v>
       </c>
-      <c r="L39">
-        <f>SUMIFS(G$3:G$34,J$3:J$34,K$38)</f>
+      <c r="L41">
+        <f>SUMIFS(G$3:G$36,J$3:J$36,K$40)</f>
         <v>625</v>
       </c>
-      <c r="M39">
-        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$38)-INT(COUNTIFS(J$3:J$34,K$38,M$3:M$34,"*gộp*")/2)</f>
+      <c r="M41">
+        <f>SUMIFS(Q$3:Q$36,J$3:J$36,K$40)-INT(COUNTIFS(J$3:J$36,K$40,M$3:M$36,"*gộp*")/2)</f>
         <v>4</v>
       </c>
-      <c r="O39" t="s">
-        <v>21</v>
-      </c>
-      <c r="P39">
-        <f>L44</f>
-        <v>-528</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B40" s="7" t="s">
+      <c r="O41" t="s">
+        <v>21</v>
+      </c>
+      <c r="P41">
+        <f>L46</f>
+        <v>-524</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B42" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="C40" s="3">
-        <v>0</v>
-      </c>
-      <c r="D40" s="3"/>
-      <c r="K40" t="s">
+      <c r="C42" s="3">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3"/>
+      <c r="K42" t="s">
         <v>200</v>
       </c>
-      <c r="L40">
-        <f>-SUMIFS(H$3:H$34,J$3:J$34,K$38)+M40*5</f>
+      <c r="L42">
+        <f>-SUMIFS(H$3:H$36,J$3:J$36,K$40)+M42*5</f>
         <v>-100</v>
       </c>
-      <c r="M40">
-        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$38)-INT(COUNTIFS(J$3:J$34,K$38,M$3:M$34,"*gộp*")/2)</f>
+      <c r="M42">
+        <f>SUMIFS(Q$3:Q$36,J$3:J$36,K$40)-INT(COUNTIFS(J$3:J$36,K$40,M$3:M$36,"*gộp*")/2)</f>
         <v>4</v>
       </c>
-      <c r="O40" t="s">
-        <v>1668</v>
-      </c>
-      <c r="P40">
-        <f>L52</f>
-        <v>14544</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B41" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="C41" s="3">
-        <f>-SUMIFS(I$3:I$34,B$3:B$34,A$38,P$3:P$34,"xx",N$3:N$34,"x")</f>
-        <v>-990</v>
-      </c>
-      <c r="D41" s="3"/>
-      <c r="E41" s="7">
-        <f>SUMIFS(Q$3:Q$34,B$3:B$34,A$38,P$3:P$34,"xx",N$3:N$34,"x")</f>
-        <v>1</v>
-      </c>
-      <c r="K41" t="s">
-        <v>202</v>
-      </c>
-      <c r="L41">
-        <f>-M41*2</f>
-        <v>-58</v>
-      </c>
-      <c r="M41">
-        <f>E42-(COUNTIFS(M$3:M$34,"*gộp*")/2)-COUNTIFS(M$3:M$34,"*đơn trả*")-COUNTIFS(M$3:M$34,"*hàng tỉnh*")</f>
-        <v>29</v>
-      </c>
-      <c r="O41" t="s">
-        <v>135</v>
-      </c>
-      <c r="P41">
-        <f>L60</f>
-        <v>2655</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B42" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="C42" s="5">
-        <f>SUBTOTAL(9,C39:C41)</f>
-        <v>17410</v>
-      </c>
-      <c r="D42" s="5"/>
-      <c r="E42">
-        <f>E39</f>
-        <v>31</v>
-      </c>
-      <c r="K42" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="L42" s="7">
-        <v>-995</v>
-      </c>
-      <c r="M42" t="s">
-        <v>288</v>
-      </c>
       <c r="O42" t="s">
-        <v>20</v>
+        <v>1658</v>
       </c>
       <c r="P42">
-        <f>L68</f>
-        <v>875</v>
+        <f>L54</f>
+        <v>12549</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C43" s="3">
+        <f>-SUMIFS(I$3:I$36,B$3:B$36,A$40,P$3:P$36,"xx",N$3:N$36,"x")</f>
+        <v>-2930</v>
+      </c>
+      <c r="D43" s="3"/>
+      <c r="E43" s="7">
+        <f>SUMIFS(Q$3:Q$36,B$3:B$36,A$40,P$3:P$36,"xx",N$3:N$36,"x")</f>
+        <v>3</v>
+      </c>
+      <c r="K43" t="s">
+        <v>202</v>
+      </c>
+      <c r="L43">
+        <f>-M43*2</f>
+        <v>-54</v>
+      </c>
+      <c r="M43">
+        <f>E44-(COUNTIFS(M$3:M$36,"*gộp*")/2)-COUNTIFS(M$3:M$36,"*đơn trả*")-COUNTIFS(M$3:M$36,"*hàng tỉnh*")</f>
+        <v>27</v>
+      </c>
+      <c r="O43" t="s">
+        <v>135</v>
+      </c>
+      <c r="P43">
+        <f>L62</f>
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B44" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C44" s="5">
+        <f>SUBTOTAL(9,C41:C43)</f>
+        <v>15470</v>
+      </c>
+      <c r="D44" s="5"/>
+      <c r="E44">
+        <f>E41</f>
+        <v>31</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="L44" s="28">
+        <v>-995</v>
+      </c>
+      <c r="M44" s="28" t="s">
+        <v>288</v>
+      </c>
+      <c r="O44" t="s">
+        <v>20</v>
+      </c>
+      <c r="P44">
+        <f>L70</f>
+        <v>875</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B45" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="K43" s="7" t="s">
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="K45" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="O43" t="s">
+      <c r="O45" t="s">
         <v>207</v>
       </c>
-      <c r="P43">
-        <f>-C46</f>
-        <v>-17410</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="17" t="s">
+      <c r="P45">
+        <f>-C48</f>
+        <v>-15470</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B46" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="L44" s="18">
-        <f>SUBTOTAL(9,L39:L43)</f>
-        <v>-528</v>
-      </c>
-      <c r="M44" s="18">
-        <f>M39</f>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="L46" s="18">
+        <f>SUBTOTAL(9,L41:L45)</f>
+        <v>-524</v>
+      </c>
+      <c r="M46" s="18">
+        <f>M41</f>
         <v>4</v>
       </c>
-      <c r="O44" s="9" t="s">
+      <c r="O46" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="P44" s="9">
-        <f>SUBTOTAL(9,P39:P43)</f>
-        <v>136</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B46" s="6" t="s">
+      <c r="P46" s="9">
+        <f>SUBTOTAL(9,P41:P45)</f>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B48" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="C46" s="1">
-        <f>C42+C43+C44</f>
-        <v>17410</v>
-      </c>
-      <c r="D46" s="1"/>
-      <c r="E46" s="6" t="s">
+      <c r="C48" s="1">
+        <f>C44+C45+C46</f>
+        <v>15470</v>
+      </c>
+      <c r="D48" s="1"/>
+      <c r="E48" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="K46" s="16" t="s">
-        <v>1596</v>
-      </c>
-      <c r="L46" s="16" t="s">
+      <c r="K48" s="16" t="s">
+        <v>1587</v>
+      </c>
+      <c r="L48" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="M46" s="16" t="s">
+      <c r="M48" s="16" t="s">
         <v>192</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K47" t="s">
-        <v>197</v>
-      </c>
-      <c r="L47">
-        <f>SUMIFS(G$3:G$34,J$3:J$34,K$46)</f>
-        <v>14895</v>
-      </c>
-      <c r="M47">
-        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$46)-INT(COUNTIFS(J$3:J$34,K$46,M$3:M$34,"*gộp*")/2)</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K48" t="s">
-        <v>200</v>
-      </c>
-      <c r="L48">
-        <f>SUM(H37:H39)</f>
-        <v>-351</v>
-      </c>
-      <c r="M48">
-        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$46)-INT(COUNTIFS(J$3:J$34,K$46,M$3:M$34,"*gộp*")/2)</f>
-        <v>16</v>
       </c>
     </row>
     <row r="49" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K49" t="s">
+        <v>197</v>
+      </c>
+      <c r="L49">
+        <f>SUMIFS(G$3:G$36,J$3:J$36,K$48)</f>
+        <v>14895</v>
+      </c>
+      <c r="M49">
+        <f>SUMIFS(Q$3:Q$36,J$3:J$36,K$48)-INT(COUNTIFS(J$3:J$36,K$48,M$3:M$36,"*gộp*")/2)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K50" t="s">
+        <v>200</v>
+      </c>
+      <c r="L50">
+        <f>SUM(H39:H41)</f>
+        <v>-351</v>
+      </c>
+      <c r="M50">
+        <f>SUMIFS(Q$3:Q$36,J$3:J$36,K$48)-INT(COUNTIFS(J$3:J$36,K$48,M$3:M$36,"*gộp*")/2)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K51" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="50" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K50" s="7" t="s">
+    <row r="52" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K52" s="7" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="51" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K51" s="7" t="s">
+      <c r="L52" s="38">
+        <f>-SUM(I34,I35,I39,I40)</f>
+        <v>-1995</v>
+      </c>
+      <c r="M52" s="28" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="53" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K53" s="7" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="52" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="L52" s="18">
-        <f>SUBTOTAL(9,L47:L51)</f>
-        <v>14544</v>
-      </c>
-      <c r="M52" s="18">
-        <f>M47</f>
+    <row r="54" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L54" s="18">
+        <f>SUBTOTAL(9,L49:L53)</f>
+        <v>12549</v>
+      </c>
+      <c r="M54" s="18">
+        <f>M49</f>
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K54" s="16" t="s">
+    <row r="56" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K56" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="L54" s="16" t="s">
+      <c r="L56" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="M54" s="16" t="s">
+      <c r="M56" s="16" t="s">
         <v>192</v>
-      </c>
-    </row>
-    <row r="55" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K55" t="s">
-        <v>197</v>
-      </c>
-      <c r="L55">
-        <f>SUMIFS(G$3:G$34,J$3:J$34,K$54)</f>
-        <v>2830</v>
-      </c>
-      <c r="M55">
-        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$54)-INT(COUNTIFS(J$3:J$34,K$54,M$3:M$34,"*gộp*")/2)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="56" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K56" t="s">
-        <v>200</v>
-      </c>
-      <c r="L56">
-        <f>-SUMIFS(H$3:H$34,J$3:J$34,K$54)+M56*5</f>
-        <v>-175</v>
-      </c>
-      <c r="M56">
-        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$54)-INT(COUNTIFS(J$3:J$34,K$54,M$3:M$34,"*gộp*")/2)</f>
-        <v>9</v>
       </c>
     </row>
     <row r="57" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K57" t="s">
+        <v>197</v>
+      </c>
+      <c r="L57">
+        <f>SUMIFS(G$3:G$36,J$3:J$36,K$56)</f>
+        <v>2830</v>
+      </c>
+      <c r="M57">
+        <f>SUMIFS(Q$3:Q$36,J$3:J$36,K$56)-INT(COUNTIFS(J$3:J$36,K$56,M$3:M$36,"*gộp*")/2)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K58" t="s">
+        <v>200</v>
+      </c>
+      <c r="L58">
+        <f>-SUMIFS(H$3:H$36,J$3:J$36,K$56)+M58*5</f>
+        <v>-175</v>
+      </c>
+      <c r="M58">
+        <f>SUMIFS(Q$3:Q$36,J$3:J$36,K$56)-INT(COUNTIFS(J$3:J$36,K$56,M$3:M$36,"*gộp*")/2)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K59" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="58" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K58" s="7" t="s">
+    <row r="60" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K60" s="7" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="59" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K59" s="7" t="s">
+    <row r="61" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K61" s="7" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="60" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="L60" s="18">
-        <f>SUBTOTAL(9,L55:L59)</f>
+    <row r="62" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L62" s="18">
+        <f>SUBTOTAL(9,L57:L61)</f>
         <v>2655</v>
       </c>
-      <c r="M60" s="18">
-        <f>M55</f>
+      <c r="M62" s="18">
+        <f>M57</f>
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K62" s="16" t="s">
+    <row r="64" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K64" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="L62" s="16" t="s">
+      <c r="L64" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="M62" s="16" t="s">
+      <c r="M64" s="16" t="s">
         <v>192</v>
-      </c>
-    </row>
-    <row r="63" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K63" t="s">
-        <v>197</v>
-      </c>
-      <c r="L63">
-        <f>SUMIFS(G$3:G$34,J$3:J$34,K$62)</f>
-        <v>900</v>
-      </c>
-      <c r="M63">
-        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$62)-INT(COUNTIFS(J$3:J$34,K$62,M$3:M$34,"*gộp*")/2)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K64" t="s">
-        <v>200</v>
-      </c>
-      <c r="L64">
-        <f>-SUMIFS(H$3:H$34,J$3:J$34,K$62)+M64*5</f>
-        <v>-25</v>
-      </c>
-      <c r="M64">
-        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$62)-INT(COUNTIFS(J$3:J$34,K$62,M$3:M$34,"*gộp*")/2)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="65" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K65" t="s">
+        <v>197</v>
+      </c>
+      <c r="L65">
+        <f>SUMIFS(G$3:G$36,J$3:J$36,K$64)</f>
+        <v>900</v>
+      </c>
+      <c r="M65">
+        <f>SUMIFS(Q$3:Q$36,J$3:J$36,K$64)-INT(COUNTIFS(J$3:J$36,K$64,M$3:M$36,"*gộp*")/2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K66" t="s">
+        <v>200</v>
+      </c>
+      <c r="L66">
+        <f>-SUMIFS(H$3:H$36,J$3:J$36,K$64)+M66*5</f>
+        <v>-25</v>
+      </c>
+      <c r="M66">
+        <f>SUMIFS(Q$3:Q$36,J$3:J$36,K$64)-INT(COUNTIFS(J$3:J$36,K$64,M$3:M$36,"*gộp*")/2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K67" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="66" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K66" s="7" t="s">
+    <row r="68" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K68" s="7" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="67" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K67" s="7" t="s">
+    <row r="69" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K69" s="7" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="68" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="L68" s="18">
-        <f>SUBTOTAL(9,L63:L67)</f>
+    <row r="70" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L70" s="18">
+        <f>SUBTOTAL(9,L65:L69)</f>
         <v>875</v>
       </c>
-      <c r="M68" s="18">
-        <f>M63</f>
+      <c r="M70" s="18">
+        <f>M65</f>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P34" xr:uid="{00000000-0009-0000-0000-000010000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P34">
-      <sortCondition ref="J2:J34"/>
+  <autoFilter ref="A2:P36" xr:uid="{00000000-0009-0000-0000-00000F000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P36">
+      <sortCondition ref="J2:J36"/>
     </sortState>
   </autoFilter>
   <mergeCells count="8">
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
     <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C48:D48"/>
     <mergeCell ref="C40:D40"/>
     <mergeCell ref="C41:D41"/>
     <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+  <dimension ref="A2:R69"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="49.28515625" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="68.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="19" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>1670</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="21">
+        <v>850</v>
+      </c>
+      <c r="H3" s="21">
+        <v>30</v>
+      </c>
+      <c r="I3" s="21">
+        <f>G3-H3</f>
+        <v>820</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>1684</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>1685</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>1686</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="21">
+        <v>470</v>
+      </c>
+      <c r="H4" s="21">
+        <v>30</v>
+      </c>
+      <c r="I4" s="21">
+        <f>G4-H4</f>
+        <v>440</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>1687</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>1688</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>1689</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="21">
+        <v>0</v>
+      </c>
+      <c r="H5" s="21">
+        <v>25</v>
+      </c>
+      <c r="I5" s="21">
+        <f>G5-H5</f>
+        <v>-25</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20">
+        <v>1</v>
+      </c>
+      <c r="R5" s="15">
+        <f>H5</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>1690</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>1691</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>1692</v>
+      </c>
+      <c r="F6" s="21">
+        <v>8</v>
+      </c>
+      <c r="G6" s="21">
+        <v>850</v>
+      </c>
+      <c r="H6" s="21">
+        <v>30</v>
+      </c>
+      <c r="I6" s="21">
+        <f>G6-H6</f>
+        <v>820</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>837</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>1694</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>1521</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="21">
+        <v>915</v>
+      </c>
+      <c r="H7" s="21">
+        <v>25</v>
+      </c>
+      <c r="I7" s="21">
+        <f>G7-H7</f>
+        <v>890</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>1711</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>1712</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>1713</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="21">
+        <v>1855</v>
+      </c>
+      <c r="H8" s="21">
+        <v>25</v>
+      </c>
+      <c r="I8" s="21">
+        <f>G8-H8</f>
+        <v>1830</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>1715</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>1716</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="21">
+        <v>795</v>
+      </c>
+      <c r="H9" s="21">
+        <v>25</v>
+      </c>
+      <c r="I9" s="21">
+        <f>G9-H9</f>
+        <v>770</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>1723</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>1725</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="21">
+        <v>1120</v>
+      </c>
+      <c r="H10" s="21">
+        <v>30</v>
+      </c>
+      <c r="I10" s="21">
+        <f>G10-H10</f>
+        <v>1090</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>1726</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>1728</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="21">
+        <v>0</v>
+      </c>
+      <c r="H11" s="21">
+        <v>25</v>
+      </c>
+      <c r="I11" s="21">
+        <f>G11-H11</f>
+        <v>-25</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20">
+        <v>1</v>
+      </c>
+      <c r="R11" s="15">
+        <f>H11</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="20"/>
+      <c r="B12" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>1729</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>1334</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G12" s="21">
+        <v>775</v>
+      </c>
+      <c r="H12" s="21">
+        <v>35</v>
+      </c>
+      <c r="I12" s="21">
+        <f>G12-H12</f>
+        <v>740</v>
+      </c>
+      <c r="J12" s="20" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>1735</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="21">
+        <v>710</v>
+      </c>
+      <c r="H13" s="21">
+        <v>30</v>
+      </c>
+      <c r="I13" s="21">
+        <f>G13-H13</f>
+        <v>680</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>1736</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>1737</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>1738</v>
+      </c>
+      <c r="F14" s="21">
+        <v>7</v>
+      </c>
+      <c r="G14" s="21">
+        <v>520</v>
+      </c>
+      <c r="H14" s="21">
+        <v>30</v>
+      </c>
+      <c r="I14" s="21">
+        <f>G14-H14</f>
+        <v>490</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>1740</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>1741</v>
+      </c>
+      <c r="F15" s="21">
+        <v>8</v>
+      </c>
+      <c r="G15" s="21">
+        <v>0</v>
+      </c>
+      <c r="H15" s="21">
+        <v>30</v>
+      </c>
+      <c r="I15" s="21">
+        <f>G15-H15</f>
+        <v>-30</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20">
+        <v>1</v>
+      </c>
+      <c r="R15" s="15">
+        <f t="shared" ref="R15:R16" si="0">H15</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>1745</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>1747</v>
+      </c>
+      <c r="F16" s="21">
+        <v>5</v>
+      </c>
+      <c r="G16" s="21">
+        <v>0</v>
+      </c>
+      <c r="H16" s="21">
+        <v>25</v>
+      </c>
+      <c r="I16" s="21">
+        <f>G16-H16</f>
+        <v>-25</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20">
+        <v>1</v>
+      </c>
+      <c r="R16" s="15">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>1748</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>1749</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>1750</v>
+      </c>
+      <c r="F17" s="21">
+        <v>9</v>
+      </c>
+      <c r="G17" s="21">
+        <v>520</v>
+      </c>
+      <c r="H17" s="21">
+        <v>30</v>
+      </c>
+      <c r="I17" s="21">
+        <f>G17-H17</f>
+        <v>490</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>1756</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>1757</v>
+      </c>
+      <c r="F18" s="21">
+        <v>7</v>
+      </c>
+      <c r="G18" s="21">
+        <v>990</v>
+      </c>
+      <c r="H18" s="21">
+        <v>30</v>
+      </c>
+      <c r="I18" s="21">
+        <f>G18-H18</f>
+        <v>960</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>1761</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>1762</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>1763</v>
+      </c>
+      <c r="F19" s="21">
+        <v>8</v>
+      </c>
+      <c r="G19" s="21">
+        <v>1020</v>
+      </c>
+      <c r="H19" s="21">
+        <v>30</v>
+      </c>
+      <c r="I19" s="21">
+        <f>G19-H19</f>
+        <v>990</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>1764</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>1766</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="21">
+        <v>860</v>
+      </c>
+      <c r="H20" s="21">
+        <v>30</v>
+      </c>
+      <c r="I20" s="21">
+        <f>G20-H20</f>
+        <v>830</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20" t="s">
+        <v>869</v>
+      </c>
+      <c r="F21" s="21">
+        <v>5</v>
+      </c>
+      <c r="G21" s="21">
+        <v>30</v>
+      </c>
+      <c r="H21" s="21">
+        <v>30</v>
+      </c>
+      <c r="I21" s="21">
+        <f>G21-H21</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>1675</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>1676</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G22" s="21">
+        <v>1500</v>
+      </c>
+      <c r="H22" s="21">
+        <v>30</v>
+      </c>
+      <c r="I22" s="21">
+        <f>G22-H22</f>
+        <v>1470</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>1681</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>1682</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>1683</v>
+      </c>
+      <c r="F23" s="21">
+        <v>12</v>
+      </c>
+      <c r="G23" s="21">
+        <v>0</v>
+      </c>
+      <c r="H23" s="21">
+        <v>30</v>
+      </c>
+      <c r="I23" s="21">
+        <f>G23-H23</f>
+        <v>-30</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20">
+        <v>1</v>
+      </c>
+      <c r="R23" s="15">
+        <f>H23</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="20"/>
+      <c r="B24" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>1693</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F24" s="21">
+        <v>2</v>
+      </c>
+      <c r="G24" s="21">
+        <v>720</v>
+      </c>
+      <c r="H24" s="21">
+        <v>30</v>
+      </c>
+      <c r="I24" s="21">
+        <f>G24-H24</f>
+        <v>690</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>1695</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>1696</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>1697</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G25" s="21">
+        <v>510</v>
+      </c>
+      <c r="H25" s="21">
+        <v>20</v>
+      </c>
+      <c r="I25" s="21">
+        <f>G25-H25</f>
+        <v>490</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K25" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="20"/>
+      <c r="B26" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>1698</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>1699</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>1700</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" s="21">
+        <v>0</v>
+      </c>
+      <c r="H26" s="21">
+        <v>25</v>
+      </c>
+      <c r="I26" s="21">
+        <f>G26-H26</f>
+        <v>-25</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K26" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20">
+        <v>1</v>
+      </c>
+      <c r="R26" s="15">
+        <f>H26</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="20"/>
+      <c r="B27" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>1720</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>1721</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>1722</v>
+      </c>
+      <c r="F27" s="21">
+        <v>2</v>
+      </c>
+      <c r="G27" s="21">
+        <v>850</v>
+      </c>
+      <c r="H27" s="21">
+        <v>30</v>
+      </c>
+      <c r="I27" s="21">
+        <f>G27-H27</f>
+        <v>820</v>
+      </c>
+      <c r="J27" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K27" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="20"/>
+      <c r="B28" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>1733</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>1734</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G28" s="21">
+        <v>520</v>
+      </c>
+      <c r="H28" s="21">
+        <v>30</v>
+      </c>
+      <c r="I28" s="21">
+        <f>G28-H28</f>
+        <v>490</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K28" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>1742</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>1743</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>1744</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G29" s="21">
+        <v>800</v>
+      </c>
+      <c r="H29" s="21">
+        <v>20</v>
+      </c>
+      <c r="I29" s="21">
+        <f>G29-H29</f>
+        <v>780</v>
+      </c>
+      <c r="J29" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K29" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="20"/>
+      <c r="B30" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>1752</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>685</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G30" s="21">
+        <v>0</v>
+      </c>
+      <c r="H30" s="21">
+        <v>25</v>
+      </c>
+      <c r="I30" s="21">
+        <f>G30-H30</f>
+        <v>-25</v>
+      </c>
+      <c r="J30" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K30" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20">
+        <v>1</v>
+      </c>
+      <c r="R30" s="15">
+        <f>H30</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>1754</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>1755</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G31" s="21">
+        <v>850</v>
+      </c>
+      <c r="H31" s="21">
+        <v>20</v>
+      </c>
+      <c r="I31" s="21">
+        <f>G31-H31</f>
+        <v>830</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K31" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="20"/>
+      <c r="B32" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>1758</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>1759</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>1760</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G32" s="21">
+        <v>0</v>
+      </c>
+      <c r="H32" s="21">
+        <v>25</v>
+      </c>
+      <c r="I32" s="21">
+        <f>G32-H32</f>
+        <v>-25</v>
+      </c>
+      <c r="J32" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K32" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20">
+        <v>1</v>
+      </c>
+      <c r="R32" s="15">
+        <f t="shared" ref="R32:R34" si="1">H32</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G33" s="21">
+        <v>0</v>
+      </c>
+      <c r="H33" s="21">
+        <v>40</v>
+      </c>
+      <c r="I33" s="21">
+        <f>G33-H33</f>
+        <v>-40</v>
+      </c>
+      <c r="J33" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K33" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20">
+        <v>1</v>
+      </c>
+      <c r="R33" s="15">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20" t="s">
+        <v>1770</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G34" s="21">
+        <v>0</v>
+      </c>
+      <c r="H34" s="21">
+        <v>30</v>
+      </c>
+      <c r="I34" s="21">
+        <f>G34-H34</f>
+        <v>-30</v>
+      </c>
+      <c r="J34" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K34" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M34" s="20"/>
+      <c r="N34" s="20"/>
+      <c r="O34" s="20"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="20">
+        <v>1</v>
+      </c>
+      <c r="R34" s="15">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" s="20"/>
+      <c r="B35" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>1678</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>1679</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F35" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G35" s="21">
+        <v>4400</v>
+      </c>
+      <c r="H35" s="21">
+        <v>35</v>
+      </c>
+      <c r="I35" s="21">
+        <f>G35-H35</f>
+        <v>4365</v>
+      </c>
+      <c r="J35" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K35" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M35" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="N35" s="20"/>
+      <c r="O35" s="20"/>
+      <c r="P35" s="20"/>
+      <c r="Q35" s="20">
+        <v>1</v>
+      </c>
+      <c r="R35" s="15">
+        <f>H35</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" s="20"/>
+      <c r="B36" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>1701</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>1702</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>1703</v>
+      </c>
+      <c r="F36" s="21">
+        <v>10</v>
+      </c>
+      <c r="G36" s="21">
+        <v>515</v>
+      </c>
+      <c r="H36" s="21">
+        <v>25</v>
+      </c>
+      <c r="I36" s="21">
+        <f>G36-H36</f>
+        <v>490</v>
+      </c>
+      <c r="J36" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K36" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M36" s="20"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
+      <c r="P36" s="20"/>
+      <c r="Q36" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37" s="20"/>
+      <c r="B37" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>1705</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>1706</v>
+      </c>
+      <c r="F37" s="21">
+        <v>5</v>
+      </c>
+      <c r="G37" s="21">
+        <v>895</v>
+      </c>
+      <c r="H37" s="21">
+        <v>25</v>
+      </c>
+      <c r="I37" s="21">
+        <f>G37-H37</f>
+        <v>870</v>
+      </c>
+      <c r="J37" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K37" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M37" s="20"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="20"/>
+      <c r="P37" s="20"/>
+      <c r="Q37" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38" s="20"/>
+      <c r="B38" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>1707</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>1279</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="G38" s="21">
+        <v>710</v>
+      </c>
+      <c r="H38" s="21">
+        <v>20</v>
+      </c>
+      <c r="I38" s="21">
+        <f>G38-H38</f>
+        <v>690</v>
+      </c>
+      <c r="J38" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K38" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L38" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M38" s="20"/>
+      <c r="N38" s="20"/>
+      <c r="O38" s="20"/>
+      <c r="P38" s="20"/>
+      <c r="Q38" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39" s="20"/>
+      <c r="B39" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>1708</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>1709</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>1710</v>
+      </c>
+      <c r="F39" s="21">
+        <v>3</v>
+      </c>
+      <c r="G39" s="21">
+        <v>515</v>
+      </c>
+      <c r="H39" s="21">
+        <v>25</v>
+      </c>
+      <c r="I39" s="21">
+        <f>G39-H39</f>
+        <v>490</v>
+      </c>
+      <c r="J39" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K39" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L39" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M39" s="20"/>
+      <c r="N39" s="20"/>
+      <c r="O39" s="20"/>
+      <c r="P39" s="20"/>
+      <c r="Q39" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40" s="20"/>
+      <c r="B40" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>1717</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>1718</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>1719</v>
+      </c>
+      <c r="F40" s="21">
+        <v>1</v>
+      </c>
+      <c r="G40" s="21">
+        <v>0</v>
+      </c>
+      <c r="H40" s="21">
+        <v>25</v>
+      </c>
+      <c r="I40" s="21">
+        <f>G40-H40</f>
+        <v>-25</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K40" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M40" s="20"/>
+      <c r="N40" s="20"/>
+      <c r="O40" s="20"/>
+      <c r="P40" s="20"/>
+      <c r="Q40" s="20">
+        <v>1</v>
+      </c>
+      <c r="R40" s="15">
+        <f>H40</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A41" s="20"/>
+      <c r="B41" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>1731</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>1732</v>
+      </c>
+      <c r="F41" s="21">
+        <v>1</v>
+      </c>
+      <c r="G41" s="21">
+        <v>915</v>
+      </c>
+      <c r="H41" s="21">
+        <v>25</v>
+      </c>
+      <c r="I41" s="21">
+        <f>G41-H41</f>
+        <v>890</v>
+      </c>
+      <c r="J41" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K41" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L41" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M41" s="20"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="20"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20" t="s">
+        <v>1768</v>
+      </c>
+      <c r="F42" s="21">
+        <v>5</v>
+      </c>
+      <c r="G42" s="21">
+        <v>30</v>
+      </c>
+      <c r="H42" s="21">
+        <v>30</v>
+      </c>
+      <c r="I42" s="21">
+        <f>G42-H42</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K42" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L42" s="20" t="s">
+        <v>1674</v>
+      </c>
+      <c r="M42" s="20"/>
+      <c r="N42" s="20"/>
+      <c r="O42" s="20"/>
+      <c r="P42" s="20"/>
+      <c r="Q42" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="26"/>
+      <c r="B43" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="26" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D43" s="26" t="s">
+        <v>1771</v>
+      </c>
+      <c r="E43" s="26" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F43" s="27">
+        <v>7</v>
+      </c>
+      <c r="G43" s="27">
+        <v>810</v>
+      </c>
+      <c r="H43" s="27">
+        <v>30</v>
+      </c>
+      <c r="I43" s="27">
+        <f>G43-H43</f>
+        <v>780</v>
+      </c>
+      <c r="J43" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="K43" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="L43" s="26" t="s">
+        <v>1135</v>
+      </c>
+      <c r="M43" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="N43" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="O43" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="P43" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q43" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D45" s="6">
+        <f>COUNTA(D3:D43)</f>
+        <v>37</v>
+      </c>
+      <c r="G45" s="6">
+        <f t="shared" ref="G45:Q45" si="2">SUBTOTAL(9,G3:G43)</f>
+        <v>26820</v>
+      </c>
+      <c r="H45" s="6">
+        <f t="shared" si="2"/>
+        <v>1140</v>
+      </c>
+      <c r="I45" s="6">
+        <f t="shared" si="2"/>
+        <v>25680</v>
+      </c>
+      <c r="J45" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L45" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M45" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N45" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O45" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P45" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q45" s="6">
+        <f t="shared" si="2"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H46">
+        <f>-12*17</f>
+        <v>-204</v>
+      </c>
+      <c r="I46">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A47" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D47" s="5"/>
+      <c r="E47" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H47">
+        <f>-6*25</f>
+        <v>-150</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>1673</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="O47" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C48" s="4">
+        <f>SUMIFS(I$3:I$43,B$3:B$43,A$47,L$3:L$43,A$48)</f>
+        <v>24900</v>
+      </c>
+      <c r="D48" s="4"/>
+      <c r="E48" s="8">
+        <f>SUMIFS(Q$3:Q$43,B$3:B$43,A$47,L$3:L$43,A$48)</f>
+        <v>40</v>
+      </c>
+      <c r="F48" t="s">
+        <v>196</v>
+      </c>
+      <c r="H48">
+        <f>-1*30</f>
+        <v>-30</v>
+      </c>
+      <c r="K48" t="s">
+        <v>197</v>
+      </c>
+      <c r="L48">
+        <f>SUMIFS(G$3:G$43,J$3:J$43,K$47)</f>
+        <v>12280</v>
+      </c>
+      <c r="M48">
+        <f>SUMIFS(Q$3:Q$43,J$3:J$43,K$47)-INT(COUNTIFS(J$3:J$43,K$47,M$3:M$43,"*gộp*")/2)</f>
+        <v>19</v>
+      </c>
+      <c r="O48" t="s">
+        <v>1772</v>
+      </c>
+      <c r="P48">
+        <f>L53</f>
+        <v>11099</v>
+      </c>
+    </row>
+    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B49" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C49" s="3">
+        <v>0</v>
+      </c>
+      <c r="D49" s="3"/>
+      <c r="K49" t="s">
+        <v>200</v>
+      </c>
+      <c r="L49">
+        <f>SUM(H46:H48)</f>
+        <v>-384</v>
+      </c>
+      <c r="M49">
+        <f>SUMIFS(Q$3:Q$43,J$3:J$43,K$47)-INT(COUNTIFS(J$3:J$43,K$47,M$3:M$43,"*gộp*")/2)</f>
+        <v>19</v>
+      </c>
+      <c r="O49" t="s">
+        <v>21</v>
+      </c>
+      <c r="P49">
+        <f>L61</f>
+        <v>5382</v>
+      </c>
+    </row>
+    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B50" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C50" s="3">
+        <f>-SUMIFS(I$3:I$43,B$3:B$43,A$47,P$3:P$43,"xx",N$3:N$43,"x")</f>
+        <v>-780</v>
+      </c>
+      <c r="D50" s="3"/>
+      <c r="E50" s="7">
+        <f>SUMIFS(Q$3:Q$43,B$3:B$43,A$47,P$3:P$43,"xx",N$3:N$43,"x")</f>
+        <v>1</v>
+      </c>
+      <c r="K50" t="s">
+        <v>202</v>
+      </c>
+      <c r="O50" t="s">
+        <v>135</v>
+      </c>
+      <c r="P50">
+        <f>L69</f>
+        <v>7810</v>
+      </c>
+    </row>
+    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B51" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C51" s="5">
+        <f>SUBTOTAL(9,C48:C50)</f>
+        <v>24120</v>
+      </c>
+      <c r="D51" s="5"/>
+      <c r="E51">
+        <f>E48</f>
+        <v>40</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="L51" s="28">
+        <v>-797</v>
+      </c>
+      <c r="M51" s="28" t="s">
+        <v>288</v>
+      </c>
+      <c r="O51" t="s">
+        <v>207</v>
+      </c>
+      <c r="P51">
+        <f>-C55</f>
+        <v>-24120</v>
+      </c>
+    </row>
+    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B52" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="K52" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O52" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P52" s="9">
+        <f>SUBTOTAL(9,P48:P51)</f>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B53" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="L53" s="18">
+        <f>SUBTOTAL(9,L48:L52)</f>
+        <v>11099</v>
+      </c>
+      <c r="M53" s="18">
+        <f>M48</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B55" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C55" s="1">
+        <f>C51+C52+C53</f>
+        <v>24120</v>
+      </c>
+      <c r="D55" s="1"/>
+      <c r="E55" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K56" t="s">
+        <v>197</v>
+      </c>
+      <c r="L56">
+        <f>SUMIFS(G$3:G$43,J$3:J$43,K$55)</f>
+        <v>5750</v>
+      </c>
+      <c r="M56">
+        <f>SUMIFS(Q$3:Q$43,J$3:J$43,K$55)-INT(COUNTIFS(J$3:J$43,K$55,M$3:M$43,"*gộp*")/2)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K57" t="s">
+        <v>200</v>
+      </c>
+      <c r="L57">
+        <f>-SUMIFS(H$3:H$43,J$3:J$43,K$55)+M57*5</f>
+        <v>-290</v>
+      </c>
+      <c r="M57">
+        <f>SUMIFS(Q$3:Q$43,J$3:J$43,K$55)-INT(COUNTIFS(J$3:J$43,K$55,M$3:M$43,"*gộp*")/2)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K58" t="s">
+        <v>202</v>
+      </c>
+      <c r="L58">
+        <f>-M58*2</f>
+        <v>-78</v>
+      </c>
+      <c r="M58">
+        <f>E51-(COUNTIFS(M$3:M$43,"*gộp*")/2)-COUNTIFS(M$3:M$43,"*đơn trả*")-COUNTIFS(M$3:M$43,"*hàng tỉnh*")</f>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="59" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K59" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="60" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K60" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="61" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="L61" s="18">
+        <f>SUBTOTAL(9,L56:L60)</f>
+        <v>5382</v>
+      </c>
+      <c r="M61" s="18">
+        <f>M56</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K63" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="64" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K64" t="s">
+        <v>197</v>
+      </c>
+      <c r="L64">
+        <f>SUMIFS(G$3:G$43,J$3:J$43,K$63)</f>
+        <v>7980</v>
+      </c>
+      <c r="M64">
+        <f>SUMIFS(Q$3:Q$43,J$3:J$43,K$63)-INT(COUNTIFS(J$3:J$43,K$63,M$3:M$43,"*gộp*")/2)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K65" t="s">
+        <v>200</v>
+      </c>
+      <c r="L65">
+        <f>-SUMIFS(H$3:H$43,J$3:J$43,K$63)+M65*5</f>
+        <v>-170</v>
+      </c>
+      <c r="M65">
+        <f>SUMIFS(Q$3:Q$43,J$3:J$43,K$63)-INT(COUNTIFS(J$3:J$43,K$63,M$3:M$43,"*gộp*")/2)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K66" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="67" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K67" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="68" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K68" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="69" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L69" s="18">
+        <f>SUBTOTAL(9,L64:L68)</f>
+        <v>7810</v>
+      </c>
+      <c r="M69" s="18">
+        <f>M64</f>
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P43" xr:uid="{00000000-0009-0000-0000-000011000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P43">
+      <sortCondition ref="J2:J43"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D9B982-EAEB-4F31-86BF-4D059AFDEA27}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
@@ -23098,7 +25877,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>1583</v>
+        <v>1660</v>
       </c>
       <c r="B1" s="10">
         <v>2026</v>
@@ -23106,19 +25885,19 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>1584</v>
+        <v>1661</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>1585</v>
+        <v>1662</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>1586</v>
+        <v>1663</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>1587</v>
+        <v>1664</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>1588</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -23450,11 +26229,11 @@
       </c>
       <c r="D18" s="13" cm="1">
         <f t="array" aca="1" ref="D18" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A18,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -23463,7 +26242,7 @@
       </c>
       <c r="B19" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C19" s="13">
         <f t="shared" ca="1" si="2"/>
@@ -23471,11 +26250,11 @@
       </c>
       <c r="D19" s="13" cm="1">
         <f t="array" aca="1" ref="D19" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A19,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -23648,16 +26427,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D28" s="14" t="s">
-        <v>1589</v>
+        <v>1666</v>
       </c>
       <c r="E28" s="14">
         <f ca="1">SUBTOTAL(9,E4:E27)</f>
-        <v>503</v>
+        <v>540</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D29" s="14" t="s">
-        <v>1590</v>
+        <v>1667</v>
       </c>
       <c r="E29" s="14" cm="1">
         <f t="array" ref="E29" ca="1">SUMPRODUCT(
@@ -23669,29 +26448,29 @@
         ),
     0)
 )</f>
-        <v>2108</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D30" s="14" t="s">
-        <v>1591</v>
+        <v>1668</v>
       </c>
       <c r="E30" s="14">
         <f ca="1">-E28*2</f>
-        <v>-1006</v>
+        <v>-1080</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D31" s="14" t="s">
-        <v>1592</v>
+        <v>1669</v>
       </c>
       <c r="E31" s="14">
         <f ca="1">SUBTOTAL(9,E29:E30)</f>
-        <v>1102</v>
+        <v>1148</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E27" xr:uid="{00000000-0009-0000-0000-00000F000000}"/>
+  <autoFilter ref="A2:E27" xr:uid="{00000000-0009-0000-0000-000010000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C3:D27">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/data/May/InternalDailyReport_May.xlsx
+++ b/data/May/InternalDailyReport_May.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4E1DC7-4A03-45B6-8C7D-9980CD23011F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0DCD8D2-C8D5-41CF-B06C-E8B0E1A095DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="7" r:id="rId1"/>
@@ -30,7 +30,9 @@
     <sheet name="19-05" sheetId="23" r:id="rId15"/>
     <sheet name="20-05" sheetId="24" r:id="rId16"/>
     <sheet name="21-05" sheetId="25" r:id="rId17"/>
-    <sheet name="Sheet1" sheetId="19" r:id="rId18"/>
+    <sheet name="22-05" sheetId="26" r:id="rId18"/>
+    <sheet name="23-05" sheetId="27" r:id="rId19"/>
+    <sheet name="Sheet1" sheetId="19" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01-05'!$A$2:$P$56</definedName>
@@ -49,8 +51,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'18-05'!$A$2:$P$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'19-05'!$A$2:$P$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'20-05'!$A$2:$P$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'21-05'!$A$2:$P$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">Sheet1!$A$2:$E$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'21-05'!$A$2:$P$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'22-05'!$A$2:$P$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'23-05'!$A$2:$P$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">Sheet1!$A$2:$E$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -92,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6003" uniqueCount="1773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6574" uniqueCount="1900">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -4903,7 +4907,7 @@
     <t>7g đường số 8 tân hưng</t>
   </si>
   <si>
-    <t>Vận</t>
+    <t>Vân</t>
   </si>
   <si>
     <t>HD022293</t>
@@ -5074,6 +5078,513 @@
     <t>2 đơn</t>
   </si>
   <si>
+    <t>Lý Thanh Tâm</t>
+  </si>
+  <si>
+    <t>HD022564</t>
+  </si>
+  <si>
+    <t>71/6/16 lê tấn bê an lạc</t>
+  </si>
+  <si>
+    <t>AT 21-05</t>
+  </si>
+  <si>
+    <t>21-05-2026</t>
+  </si>
+  <si>
+    <t>Hana Le</t>
+  </si>
+  <si>
+    <t>HD022573</t>
+  </si>
+  <si>
+    <t>427/22 le van quoi binh tri dong A</t>
+  </si>
+  <si>
+    <t>Giap Anh Tuyet</t>
+  </si>
+  <si>
+    <t>HD022508</t>
+  </si>
+  <si>
+    <t>007 Lô B, Đường C6, Chung cư Tây Thạnh</t>
+  </si>
+  <si>
+    <t>Bùi Vĩ Thương</t>
+  </si>
+  <si>
+    <t>HD022636</t>
+  </si>
+  <si>
+    <t>3273 phạm thế hiển, p7</t>
+  </si>
+  <si>
+    <t>HD022628</t>
+  </si>
+  <si>
+    <t>Linh Ngô</t>
+  </si>
+  <si>
+    <t>HD022618</t>
+  </si>
+  <si>
+    <t>90 a lê lăng Phú thọ hoà</t>
+  </si>
+  <si>
+    <t>Lan Phạm</t>
+  </si>
+  <si>
+    <t>HD022621</t>
+  </si>
+  <si>
+    <t>685 âu cơ p tân thành - lô C</t>
+  </si>
+  <si>
+    <t>Phạm Thị Minh Tuyền</t>
+  </si>
+  <si>
+    <t>HD022341</t>
+  </si>
+  <si>
+    <t>352/4g lê văn quới, bình hưng hoà A</t>
+  </si>
+  <si>
+    <t>thuy vy</t>
+  </si>
+  <si>
+    <t>HD022620</t>
+  </si>
+  <si>
+    <t>chung cư Ruby - cổng 2, đường Tân Thắng, P. Tân Sơn Nhì</t>
+  </si>
+  <si>
+    <t>HD022604</t>
+  </si>
+  <si>
+    <t>HD022383</t>
+  </si>
+  <si>
+    <t>Nguyễn Yến Nhi</t>
+  </si>
+  <si>
+    <t>HD022491</t>
+  </si>
+  <si>
+    <t>Tháp v3 Chung cư sun rise city south 23 nguyễn hữu thọ tân hưng</t>
+  </si>
+  <si>
+    <t>Pé Thỏ</t>
+  </si>
+  <si>
+    <t>HD022455</t>
+  </si>
+  <si>
+    <t>1002 tạ quang bửu f6 Chung cư the pegasuite1 (zone1)</t>
+  </si>
+  <si>
+    <t>chủ mau - fb Hana Ngo</t>
+  </si>
+  <si>
+    <t>HD022615</t>
+  </si>
+  <si>
+    <t>67 Trang từ phường 14</t>
+  </si>
+  <si>
+    <t>Quỳnh Nhi</t>
+  </si>
+  <si>
+    <t>HD022493</t>
+  </si>
+  <si>
+    <t>180/1T QL1A Tân Phú</t>
+  </si>
+  <si>
+    <t>HD022342</t>
+  </si>
+  <si>
+    <t>320/14 nguyễn văn linh phường bình thuận</t>
+  </si>
+  <si>
+    <t>Nguyễn Thanh Ngân</t>
+  </si>
+  <si>
+    <t>HD022575</t>
+  </si>
+  <si>
+    <t>159c /18a dạ nam, chánh hưng</t>
+  </si>
+  <si>
+    <t>Huỳnh Mẫn</t>
+  </si>
+  <si>
+    <t>HD022522</t>
+  </si>
+  <si>
+    <t>1362 tỉnh lộ 10 tân tạo</t>
+  </si>
+  <si>
+    <t>Anh Trúc Huỳnh</t>
+  </si>
+  <si>
+    <t>HD022586</t>
+  </si>
+  <si>
+    <t>Số 64 dg 38 hiep binh chanh</t>
+  </si>
+  <si>
+    <t>BN182 miki chouchou Fb.</t>
+  </si>
+  <si>
+    <t>HD022533</t>
+  </si>
+  <si>
+    <t>163 Đường Trương Thị Hoa, phường Tân Thái Hiệp</t>
+  </si>
+  <si>
+    <t>HD022429</t>
+  </si>
+  <si>
+    <t>My Yến</t>
+  </si>
+  <si>
+    <t>HD022525</t>
+  </si>
+  <si>
+    <t>334/33/1C Chu văn an, phường 12</t>
+  </si>
+  <si>
+    <t>Hải Yến</t>
+  </si>
+  <si>
+    <t>HD003936</t>
+  </si>
+  <si>
+    <t>319/17 lê văn thọ p9</t>
+  </si>
+  <si>
+    <t>01우준</t>
+  </si>
+  <si>
+    <t>HD022601</t>
+  </si>
+  <si>
+    <t>Đảo kim cương phường bình trưng tây</t>
+  </si>
+  <si>
+    <t>HD022503</t>
+  </si>
+  <si>
+    <t>Toà Aster - Urban green (đối diện Vạn Phúc)</t>
+  </si>
+  <si>
+    <t>Khánh Thư Nguyen</t>
+  </si>
+  <si>
+    <t>HD022626</t>
+  </si>
+  <si>
+    <t>88 dien Hồng phường 1</t>
+  </si>
+  <si>
+    <t>Mỹ ý</t>
+  </si>
+  <si>
+    <t>HD022613</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Kim Hoàng</t>
+  </si>
+  <si>
+    <t>HD022430</t>
+  </si>
+  <si>
+    <t>265 Nơ Trang Long, phường Bình Lợi Trung</t>
+  </si>
+  <si>
+    <t>NHƯ- Khanh sale- airmy</t>
+  </si>
+  <si>
+    <t>HD022551</t>
+  </si>
+  <si>
+    <t>144C Trần Thị Trọng, Phường 15</t>
+  </si>
+  <si>
+    <t>PHƯƠNG DUNG</t>
+  </si>
+  <si>
+    <t>23/4A đường 48 khu phố 6 hiệp bình chánh</t>
+  </si>
+  <si>
+    <t>người nhận Hồng Sơn fb Duong Hyun</t>
+  </si>
+  <si>
+    <t>HD022495</t>
+  </si>
+  <si>
+    <t>135 Bạch Đằng, phường Tân Sơn Hòa (Phường 2) (CÔNG TY LÊ GIA EXPRESS)</t>
+  </si>
+  <si>
+    <t>Hoang Linh Le</t>
+  </si>
+  <si>
+    <t>HD022460</t>
+  </si>
+  <si>
+    <t>314 Điện Biên Phủ, Phường Vườn Lài</t>
+  </si>
+  <si>
+    <t>Chị Oanh</t>
+  </si>
+  <si>
+    <t>HD022599</t>
+  </si>
+  <si>
+    <t>291 hùng vương phương an đông</t>
+  </si>
+  <si>
+    <t>HD022442</t>
+  </si>
+  <si>
+    <t>Thuy Thuy</t>
+  </si>
+  <si>
+    <t>HD022451</t>
+  </si>
+  <si>
+    <t>58E cao thắng,p5 (Viện chăm sóc da aperio)</t>
+  </si>
+  <si>
+    <t>Sorinna items PhnomPenh ( Meng Kheang customer )</t>
+  </si>
+  <si>
+    <t>HD022445</t>
+  </si>
+  <si>
+    <t>301 phạm ngũ lão</t>
+  </si>
+  <si>
+    <t>Mỹ Vinh</t>
+  </si>
+  <si>
+    <t>HD022560</t>
+  </si>
+  <si>
+    <t>Aqua1 vinhome bason bến nghé</t>
+  </si>
+  <si>
+    <t>VVI EVA</t>
+  </si>
+  <si>
+    <t>141 Hùng Vương phường 4</t>
+  </si>
+  <si>
+    <t>HD020811</t>
+  </si>
+  <si>
+    <t>at 21-05</t>
+  </si>
+  <si>
+    <t>HD022758</t>
+  </si>
+  <si>
+    <t>AT 22-05</t>
+  </si>
+  <si>
+    <t>22-05-2026</t>
+  </si>
+  <si>
+    <t>Trần Hương</t>
+  </si>
+  <si>
+    <t>HD022721</t>
+  </si>
+  <si>
+    <t>339 lê văn quới phường bình trị đông A</t>
+  </si>
+  <si>
+    <t>VTS-36588MNG</t>
+  </si>
+  <si>
+    <t>HD022692</t>
+  </si>
+  <si>
+    <t>kh ck shop 1710k</t>
+  </si>
+  <si>
+    <t>w3360</t>
+  </si>
+  <si>
+    <t>HD022791</t>
+  </si>
+  <si>
+    <t>624 Lê thị riêng,thới an</t>
+  </si>
+  <si>
+    <t>HD022655</t>
+  </si>
+  <si>
+    <t>Heng Roza</t>
+  </si>
+  <si>
+    <t>EV38382</t>
+  </si>
+  <si>
+    <t>315/18/6 Nguyễn Thị Tú, BHHB</t>
+  </si>
+  <si>
+    <t>Minh Hải zalo cẩm ngân</t>
+  </si>
+  <si>
+    <t>HD022896</t>
+  </si>
+  <si>
+    <t>Dung Dung</t>
+  </si>
+  <si>
+    <t>HD022794</t>
+  </si>
+  <si>
+    <t>125/191 nguyễn thị tần p2</t>
+  </si>
+  <si>
+    <t>Như Huỳnh</t>
+  </si>
+  <si>
+    <t>HD022787</t>
+  </si>
+  <si>
+    <t>16 đường 69 Tân Hưng</t>
+  </si>
+  <si>
+    <t>GUBY Fb Trương Ngọc</t>
+  </si>
+  <si>
+    <t>số 201/12 mã văn lò, P, bình trị đông a</t>
+  </si>
+  <si>
+    <t>HD022757</t>
+  </si>
+  <si>
+    <t>Nguyễn Chi</t>
+  </si>
+  <si>
+    <t>HD022759</t>
+  </si>
+  <si>
+    <t>51-53 duong số 57c f tân tạo</t>
+  </si>
+  <si>
+    <t>Ngọc Tiên</t>
+  </si>
+  <si>
+    <t>HD022897</t>
+  </si>
+  <si>
+    <t>59 trần hưng đạo p tân thành</t>
+  </si>
+  <si>
+    <t>HD022895</t>
+  </si>
+  <si>
+    <t>1123 quốc lộ la, tân tạo, chung cư an gia the star</t>
+  </si>
+  <si>
+    <t>Linh Chi Nguyễn</t>
+  </si>
+  <si>
+    <t>HD022915</t>
+  </si>
+  <si>
+    <t>54/24 đường 281 lý thường kiệt phường 15</t>
+  </si>
+  <si>
+    <t>HD022893</t>
+  </si>
+  <si>
+    <t>Diễm</t>
+  </si>
+  <si>
+    <t>HD022790</t>
+  </si>
+  <si>
+    <t>22/31/4 đường số 21, Phường 3</t>
+  </si>
+  <si>
+    <t>Nguyễn Loan</t>
+  </si>
+  <si>
+    <t>HD022726</t>
+  </si>
+  <si>
+    <t>91/33 nguyên hồng</t>
+  </si>
+  <si>
+    <t>HD022866</t>
+  </si>
+  <si>
+    <t>Hương Quỳnh (Nhượng)</t>
+  </si>
+  <si>
+    <t>HD022886</t>
+  </si>
+  <si>
+    <t>15/3 Lê Văn Huân, P13</t>
+  </si>
+  <si>
+    <t>Ivy Huyền</t>
+  </si>
+  <si>
+    <t>Số 5 Nhất Chi Mai phường 13</t>
+  </si>
+  <si>
+    <t>Đỗ Linh Chi</t>
+  </si>
+  <si>
+    <t>HD022673</t>
+  </si>
+  <si>
+    <t>86/36/3 Phố Quang, Phường Tân Sơn Hòa</t>
+  </si>
+  <si>
+    <t>Quỳnh Như</t>
+  </si>
+  <si>
+    <t>HD022888</t>
+  </si>
+  <si>
+    <t>66/68, Phổ Quang, Phường 2</t>
+  </si>
+  <si>
+    <t>Hạnh Hạnh</t>
+  </si>
+  <si>
+    <t>HD022865</t>
+  </si>
+  <si>
+    <t>334 tô hiến thành p14 Chung cư kingdom101 block a</t>
+  </si>
+  <si>
+    <t>Phạm Thùy Đan</t>
+  </si>
+  <si>
+    <t>HD022634</t>
+  </si>
+  <si>
+    <t>83/25b đường Hoà Hưng p12</t>
+  </si>
+  <si>
+    <t>Nguyễn Kim Ann</t>
+  </si>
+  <si>
+    <t>HD022824</t>
+  </si>
+  <si>
+    <t>at 22-05</t>
+  </si>
+  <si>
     <t>THÁNG 5</t>
   </si>
   <si>
@@ -5104,313 +5615,187 @@
     <t>Lợi nhuận</t>
   </si>
   <si>
-    <t>Lý Thanh Tâm</t>
-  </si>
-  <si>
-    <t>HD022564</t>
-  </si>
-  <si>
-    <t>71/6/16 lê tấn bê an lạc</t>
-  </si>
-  <si>
-    <t>AT 21-05</t>
-  </si>
-  <si>
-    <t>21-05-2026</t>
-  </si>
-  <si>
-    <t>Anh Trúc Huỳnh</t>
-  </si>
-  <si>
-    <t>HD022586</t>
-  </si>
-  <si>
-    <t>Số 64 dg 38 hiep binh chanh</t>
-  </si>
-  <si>
-    <t>người nhận Hồng Sơn fb Duong Hyun</t>
-  </si>
-  <si>
-    <t>HD022495</t>
-  </si>
-  <si>
-    <t>135 Bạch Đằng, phường Tân Sơn Hòa (Phường 2) (CÔNG TY LÊ GIA EXPRESS)</t>
-  </si>
-  <si>
-    <t>BN182 miki chouchou Fb.</t>
-  </si>
-  <si>
-    <t>HD022533</t>
-  </si>
-  <si>
-    <t>163 Đường Trương Thị Hoa, phường Tân Thái Hiệp</t>
-  </si>
-  <si>
-    <t>Hana Le</t>
-  </si>
-  <si>
-    <t>HD022573</t>
-  </si>
-  <si>
-    <t>427/22 le van quoi binh tri dong A</t>
-  </si>
-  <si>
-    <t>Giap Anh Tuyet</t>
-  </si>
-  <si>
-    <t>HD022508</t>
-  </si>
-  <si>
-    <t>007 Lô B, Đường C6, Chung cư Tây Thạnh</t>
-  </si>
-  <si>
-    <t>Bùi Vĩ Thương</t>
-  </si>
-  <si>
-    <t>HD022636</t>
-  </si>
-  <si>
-    <t>3273 phạm thế hiển, p7</t>
-  </si>
-  <si>
-    <t>HD022429</t>
-  </si>
-  <si>
-    <t>HD022628</t>
-  </si>
-  <si>
-    <t>My Yến</t>
-  </si>
-  <si>
-    <t>HD022525</t>
-  </si>
-  <si>
-    <t>334/33/1C Chu văn an, phường 12</t>
-  </si>
-  <si>
-    <t>Hải Yến</t>
-  </si>
-  <si>
-    <t>HD003936</t>
-  </si>
-  <si>
-    <t>319/17 lê văn thọ p9</t>
-  </si>
-  <si>
-    <t>Hoang Linh Le</t>
-  </si>
-  <si>
-    <t>HD022460</t>
-  </si>
-  <si>
-    <t>314 Điện Biên Phủ, Phường Vườn Lài</t>
-  </si>
-  <si>
-    <t>Chị Oanh</t>
-  </si>
-  <si>
-    <t>HD022599</t>
-  </si>
-  <si>
-    <t>291 hùng vương phương an đông</t>
-  </si>
-  <si>
-    <t>HD022442</t>
-  </si>
-  <si>
-    <t>Thuy Thuy</t>
-  </si>
-  <si>
-    <t>HD022451</t>
-  </si>
-  <si>
-    <t>58E cao thắng,p5 (Viện chăm sóc da aperio)</t>
-  </si>
-  <si>
-    <t>Linh Ngô</t>
-  </si>
-  <si>
-    <t>HD022618</t>
-  </si>
-  <si>
-    <t>90 a lê lăng Phú thọ hoà</t>
-  </si>
-  <si>
-    <t>Lan Phạm</t>
-  </si>
-  <si>
-    <t>HD022621</t>
-  </si>
-  <si>
-    <t>685 âu cơ p tân thành - lô C</t>
-  </si>
-  <si>
-    <t>Sorinna items PhnomPenh ( Meng Kheang customer )</t>
-  </si>
-  <si>
-    <t>HD022445</t>
-  </si>
-  <si>
-    <t>301 phạm ngũ lão</t>
-  </si>
-  <si>
-    <t>01우준</t>
-  </si>
-  <si>
-    <t>HD022601</t>
-  </si>
-  <si>
-    <t>Đảo kim cương phường bình trưng tây</t>
-  </si>
-  <si>
-    <t>Phạm Thị Minh Tuyền</t>
-  </si>
-  <si>
-    <t>HD022341</t>
-  </si>
-  <si>
-    <t>352/4g lê văn quới, bình hưng hoà A</t>
-  </si>
-  <si>
-    <t>thuy vy</t>
-  </si>
-  <si>
-    <t>HD022620</t>
-  </si>
-  <si>
-    <t>chung cư Ruby - cổng 2, đường Tân Thắng, P. Tân Sơn Nhì</t>
-  </si>
-  <si>
-    <t>HD022604</t>
-  </si>
-  <si>
-    <t>Mỹ Vinh</t>
-  </si>
-  <si>
-    <t>HD022560</t>
-  </si>
-  <si>
-    <t>Aqua1 vinhome bason bến nghé</t>
-  </si>
-  <si>
-    <t>HD022503</t>
-  </si>
-  <si>
-    <t>Toà Aster - Urban green (đối diện Vạn Phúc)</t>
-  </si>
-  <si>
-    <t>HD022383</t>
-  </si>
-  <si>
-    <t>Nguyễn Yến Nhi</t>
-  </si>
-  <si>
-    <t>HD022491</t>
-  </si>
-  <si>
-    <t>Tháp v3 Chung cư sun rise city south 23 nguyễn hữu thọ tân hưng</t>
-  </si>
-  <si>
-    <t>Pé Thỏ</t>
-  </si>
-  <si>
-    <t>HD022455</t>
-  </si>
-  <si>
-    <t>1002 tạ quang bửu f6 Chung cư the pegasuite1 (zone1)</t>
-  </si>
-  <si>
-    <t>Khánh Thư Nguyen</t>
-  </si>
-  <si>
-    <t>HD022626</t>
-  </si>
-  <si>
-    <t>88 dien Hồng phường 1</t>
-  </si>
-  <si>
-    <t>chủ mau - fb Hana Ngo</t>
-  </si>
-  <si>
-    <t>HD022615</t>
-  </si>
-  <si>
-    <t>67 Trang từ phường 14</t>
-  </si>
-  <si>
-    <t>Quỳnh Nhi</t>
-  </si>
-  <si>
-    <t>HD022493</t>
-  </si>
-  <si>
-    <t>180/1T QL1A Tân Phú</t>
-  </si>
-  <si>
-    <t>Mỹ ý</t>
-  </si>
-  <si>
-    <t>HD022613</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Kim Hoàng</t>
-  </si>
-  <si>
-    <t>HD022430</t>
-  </si>
-  <si>
-    <t>265 Nơ Trang Long, phường Bình Lợi Trung</t>
-  </si>
-  <si>
-    <t>HD022342</t>
-  </si>
-  <si>
-    <t>320/14 nguyễn văn linh phường bình thuận</t>
-  </si>
-  <si>
-    <t>NHƯ- Khanh sale- airmy</t>
-  </si>
-  <si>
-    <t>HD022551</t>
-  </si>
-  <si>
-    <t>144C Trần Thị Trọng, Phường 15</t>
-  </si>
-  <si>
-    <t>Nguyễn Thanh Ngân</t>
-  </si>
-  <si>
-    <t>HD022575</t>
-  </si>
-  <si>
-    <t>159c /18a dạ nam, chánh hưng</t>
-  </si>
-  <si>
-    <t>Huỳnh Mẫn</t>
-  </si>
-  <si>
-    <t>HD022522</t>
-  </si>
-  <si>
-    <t>1362 tỉnh lộ 10 tân tạo</t>
-  </si>
-  <si>
-    <t>VVI EVA</t>
-  </si>
-  <si>
-    <t>141 Hùng Vương phường 4</t>
-  </si>
-  <si>
-    <t>PHƯƠNG DUNG</t>
-  </si>
-  <si>
-    <t>23/4A đường 48 khu phố 6 hiệp bình chánh</t>
-  </si>
-  <si>
-    <t>HD020811</t>
-  </si>
-  <si>
-    <t>at 21-05</t>
+    <t>thanh (NHẬN HÀNG CHO TRÀ LY)</t>
+  </si>
+  <si>
+    <t>HD023142</t>
+  </si>
+  <si>
+    <t>404 VÕ VĂN TẦN</t>
+  </si>
+  <si>
+    <t>23-05-2026</t>
+  </si>
+  <si>
+    <t>Bảo Như</t>
+  </si>
+  <si>
+    <t>HD023066</t>
+  </si>
+  <si>
+    <t>e208 nguyễn hữu cảnh p22 toà nhà landmark 3</t>
+  </si>
+  <si>
+    <t>HD023055</t>
+  </si>
+  <si>
+    <t>AT 23-05</t>
+  </si>
+  <si>
+    <t>HD023069</t>
+  </si>
+  <si>
+    <t>HƯNG (hàng của Huyền Jendy)</t>
+  </si>
+  <si>
+    <t>HD023099</t>
+  </si>
+  <si>
+    <t>borameyyy</t>
+  </si>
+  <si>
+    <t>HD023106</t>
+  </si>
+  <si>
+    <t>Express M Village Nguyễn Du, Phòng 602</t>
+  </si>
+  <si>
+    <t>oanh fb Duong Tram</t>
+  </si>
+  <si>
+    <t>HD023118</t>
+  </si>
+  <si>
+    <t>346 bến vân đồn p1 Chung cư goldview a2</t>
+  </si>
+  <si>
+    <t>HD023108</t>
+  </si>
+  <si>
+    <t>41 Lê Quang Chiểu, Hiệp Tân</t>
+  </si>
+  <si>
+    <t>HD023121</t>
+  </si>
+  <si>
+    <t>624 Lê Thị Riêng, thới an</t>
+  </si>
+  <si>
+    <t>TONY ĐI ÚC</t>
+  </si>
+  <si>
+    <t>HD023116</t>
+  </si>
+  <si>
+    <t>965/16/11 QUANG TRUNG</t>
+  </si>
+  <si>
+    <t>HD022813</t>
+  </si>
+  <si>
+    <t>Trinh Trần</t>
+  </si>
+  <si>
+    <t>HD022990</t>
+  </si>
+  <si>
+    <t>22A truong dinh</t>
+  </si>
+  <si>
+    <t>Lê Chi</t>
+  </si>
+  <si>
+    <t>HD023140</t>
+  </si>
+  <si>
+    <t>270 quốc lộ 50 p6</t>
+  </si>
+  <si>
+    <t>Ngọc Nhi</t>
+  </si>
+  <si>
+    <t>HD023141</t>
+  </si>
+  <si>
+    <t>92 nguyễn hữu cảnh p.22 (cc sg pearl toà sapphire 1)</t>
+  </si>
+  <si>
+    <t>HD023115</t>
+  </si>
+  <si>
+    <t>363 Hùng Vương, An Đông</t>
+  </si>
+  <si>
+    <t>Mai Chi</t>
+  </si>
+  <si>
+    <t>HD023061</t>
+  </si>
+  <si>
+    <t>215 nguyễn thị minh khai</t>
+  </si>
+  <si>
+    <t>Phương Trang</t>
+  </si>
+  <si>
+    <t>HD023132</t>
+  </si>
+  <si>
+    <t>189b/a29 công quỳnh phường nguyễn cư trinh</t>
+  </si>
+  <si>
+    <t>HD023045</t>
+  </si>
+  <si>
+    <t>22/31/4 đường số 21, Phường 8 (phường Thông Tây Hội mới)</t>
+  </si>
+  <si>
+    <t>Như Ý Nguyễn</t>
+  </si>
+  <si>
+    <t>HD023113</t>
+  </si>
+  <si>
+    <t>24 Yên Thế, Phường 2</t>
+  </si>
+  <si>
+    <t>Cúc Phan</t>
+  </si>
+  <si>
+    <t>HD023112</t>
+  </si>
+  <si>
+    <t>A 12 liên ấp 1-2 vĩnh lộc b</t>
+  </si>
+  <si>
+    <t>HD023096</t>
+  </si>
+  <si>
+    <t>Trang Lê (note nhận đồ giúp chang)</t>
+  </si>
+  <si>
+    <t>HD023127</t>
+  </si>
+  <si>
+    <t>183/26 nguyễn hữu cảnh, f22</t>
+  </si>
+  <si>
+    <t>NGÂN HÀ</t>
+  </si>
+  <si>
+    <t>40 đường 53 p10</t>
+  </si>
+  <si>
+    <t>HÀ VY</t>
+  </si>
+  <si>
+    <t>482/10/26 nơ trang Long, p13</t>
+  </si>
+  <si>
+    <t>CAYLA</t>
+  </si>
+  <si>
+    <t>at 23-05</t>
   </si>
 </sst>
 </file>
@@ -23516,7 +23901,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
-  <dimension ref="A2:R69"/>
+  <dimension ref="A2:R70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -23597,13 +23982,13 @@
         <v>17</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>1670</v>
+        <v>1660</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>1671</v>
+        <v>1661</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>1672</v>
+        <v>1662</v>
       </c>
       <c r="F3" s="20" t="s">
         <v>26</v>
@@ -23615,17 +24000,17 @@
         <v>30</v>
       </c>
       <c r="I3" s="21">
-        <f>G3-H3</f>
+        <f t="shared" ref="I3:I44" si="0">G3-H3</f>
         <v>820</v>
       </c>
       <c r="J3" s="20" t="s">
-        <v>1673</v>
+        <v>1663</v>
       </c>
       <c r="K3" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L3" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M3" s="20"/>
       <c r="N3" s="20"/>
@@ -23641,13 +24026,13 @@
         <v>17</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>1684</v>
+        <v>1665</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>1685</v>
+        <v>1666</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>1686</v>
+        <v>1667</v>
       </c>
       <c r="F4" s="20" t="s">
         <v>26</v>
@@ -23659,17 +24044,17 @@
         <v>30</v>
       </c>
       <c r="I4" s="21">
-        <f>G4-H4</f>
+        <f t="shared" si="0"/>
         <v>440</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>1673</v>
+        <v>1663</v>
       </c>
       <c r="K4" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L4" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M4" s="20"/>
       <c r="N4" s="20"/>
@@ -23685,13 +24070,13 @@
         <v>17</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>1687</v>
+        <v>1668</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>1688</v>
+        <v>1669</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>1689</v>
+        <v>1670</v>
       </c>
       <c r="F5" s="20" t="s">
         <v>46</v>
@@ -23703,17 +24088,17 @@
         <v>25</v>
       </c>
       <c r="I5" s="21">
-        <f>G5-H5</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J5" s="20" t="s">
-        <v>1673</v>
+        <v>1663</v>
       </c>
       <c r="K5" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L5" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M5" s="20"/>
       <c r="N5" s="20"/>
@@ -23733,13 +24118,13 @@
         <v>17</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>1690</v>
+        <v>1671</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>1691</v>
+        <v>1672</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>1692</v>
+        <v>1673</v>
       </c>
       <c r="F6" s="21">
         <v>8</v>
@@ -23751,17 +24136,17 @@
         <v>30</v>
       </c>
       <c r="I6" s="21">
-        <f>G6-H6</f>
+        <f t="shared" si="0"/>
         <v>820</v>
       </c>
       <c r="J6" s="20" t="s">
-        <v>1673</v>
+        <v>1663</v>
       </c>
       <c r="K6" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M6" s="20"/>
       <c r="N6" s="20"/>
@@ -23780,7 +24165,7 @@
         <v>837</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>1694</v>
+        <v>1674</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>1521</v>
@@ -23795,17 +24180,17 @@
         <v>25</v>
       </c>
       <c r="I7" s="21">
-        <f>G7-H7</f>
+        <f t="shared" si="0"/>
         <v>890</v>
       </c>
       <c r="J7" s="20" t="s">
-        <v>1673</v>
+        <v>1663</v>
       </c>
       <c r="K7" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L7" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M7" s="20"/>
       <c r="N7" s="20"/>
@@ -23821,13 +24206,13 @@
         <v>17</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>1711</v>
+        <v>1675</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>1712</v>
+        <v>1676</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>1713</v>
+        <v>1677</v>
       </c>
       <c r="F8" s="20" t="s">
         <v>46</v>
@@ -23839,17 +24224,17 @@
         <v>25</v>
       </c>
       <c r="I8" s="21">
-        <f>G8-H8</f>
+        <f t="shared" si="0"/>
         <v>1830</v>
       </c>
       <c r="J8" s="20" t="s">
-        <v>1673</v>
+        <v>1663</v>
       </c>
       <c r="K8" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L8" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M8" s="20"/>
       <c r="N8" s="20"/>
@@ -23865,13 +24250,13 @@
         <v>17</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>1714</v>
+        <v>1678</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>1715</v>
+        <v>1679</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>1716</v>
+        <v>1680</v>
       </c>
       <c r="F9" s="20" t="s">
         <v>46</v>
@@ -23883,17 +24268,17 @@
         <v>25</v>
       </c>
       <c r="I9" s="21">
-        <f>G9-H9</f>
+        <f t="shared" si="0"/>
         <v>770</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>1673</v>
+        <v>1663</v>
       </c>
       <c r="K9" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L9" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M9" s="20"/>
       <c r="N9" s="20"/>
@@ -23909,13 +24294,13 @@
         <v>17</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>1723</v>
+        <v>1681</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>1724</v>
+        <v>1682</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>1725</v>
+        <v>1683</v>
       </c>
       <c r="F10" s="20" t="s">
         <v>26</v>
@@ -23927,17 +24312,17 @@
         <v>30</v>
       </c>
       <c r="I10" s="21">
-        <f>G10-H10</f>
+        <f t="shared" si="0"/>
         <v>1090</v>
       </c>
       <c r="J10" s="20" t="s">
-        <v>1673</v>
+        <v>1663</v>
       </c>
       <c r="K10" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L10" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M10" s="20"/>
       <c r="N10" s="20"/>
@@ -23953,13 +24338,13 @@
         <v>17</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>1726</v>
+        <v>1684</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>1727</v>
+        <v>1685</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>1728</v>
+        <v>1686</v>
       </c>
       <c r="F11" s="20" t="s">
         <v>46</v>
@@ -23971,17 +24356,17 @@
         <v>25</v>
       </c>
       <c r="I11" s="21">
-        <f>G11-H11</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>1673</v>
+        <v>1663</v>
       </c>
       <c r="K11" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L11" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M11" s="20"/>
       <c r="N11" s="20"/>
@@ -24004,7 +24389,7 @@
         <v>1332</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>1729</v>
+        <v>1687</v>
       </c>
       <c r="E12" s="20" t="s">
         <v>1334</v>
@@ -24019,17 +24404,17 @@
         <v>35</v>
       </c>
       <c r="I12" s="21">
-        <f>G12-H12</f>
+        <f t="shared" si="0"/>
         <v>740</v>
       </c>
       <c r="J12" s="20" t="s">
-        <v>1673</v>
+        <v>1663</v>
       </c>
       <c r="K12" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L12" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M12" s="20"/>
       <c r="N12" s="20"/>
@@ -24048,7 +24433,7 @@
         <v>1256</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>1735</v>
+        <v>1688</v>
       </c>
       <c r="E13" s="20" t="s">
         <v>1258</v>
@@ -24063,17 +24448,17 @@
         <v>30</v>
       </c>
       <c r="I13" s="21">
-        <f>G13-H13</f>
+        <f t="shared" si="0"/>
         <v>680</v>
       </c>
       <c r="J13" s="20" t="s">
-        <v>1673</v>
+        <v>1663</v>
       </c>
       <c r="K13" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L13" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M13" s="20"/>
       <c r="N13" s="20"/>
@@ -24089,13 +24474,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>1736</v>
+        <v>1689</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>1737</v>
+        <v>1690</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>1738</v>
+        <v>1691</v>
       </c>
       <c r="F14" s="21">
         <v>7</v>
@@ -24107,17 +24492,17 @@
         <v>30</v>
       </c>
       <c r="I14" s="21">
-        <f>G14-H14</f>
+        <f t="shared" si="0"/>
         <v>490</v>
       </c>
       <c r="J14" s="20" t="s">
-        <v>1673</v>
+        <v>1663</v>
       </c>
       <c r="K14" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L14" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M14" s="20"/>
       <c r="N14" s="20"/>
@@ -24133,13 +24518,13 @@
         <v>17</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>1739</v>
+        <v>1692</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>1740</v>
+        <v>1693</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>1741</v>
+        <v>1694</v>
       </c>
       <c r="F15" s="21">
         <v>8</v>
@@ -24151,17 +24536,17 @@
         <v>30</v>
       </c>
       <c r="I15" s="21">
-        <f>G15-H15</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J15" s="20" t="s">
-        <v>1673</v>
+        <v>1663</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L15" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M15" s="20"/>
       <c r="N15" s="20"/>
@@ -24171,7 +24556,7 @@
         <v>1</v>
       </c>
       <c r="R15" s="15">
-        <f t="shared" ref="R15:R16" si="0">H15</f>
+        <f>H15</f>
         <v>30</v>
       </c>
     </row>
@@ -24181,13 +24566,13 @@
         <v>17</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>1745</v>
+        <v>1695</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>1746</v>
+        <v>1696</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>1747</v>
+        <v>1697</v>
       </c>
       <c r="F16" s="21">
         <v>5</v>
@@ -24199,17 +24584,17 @@
         <v>25</v>
       </c>
       <c r="I16" s="21">
-        <f>G16-H16</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J16" s="20" t="s">
-        <v>1673</v>
+        <v>1663</v>
       </c>
       <c r="K16" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L16" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M16" s="20"/>
       <c r="N16" s="20"/>
@@ -24219,7 +24604,7 @@
         <v>1</v>
       </c>
       <c r="R16" s="15">
-        <f t="shared" si="0"/>
+        <f>H16</f>
         <v>25</v>
       </c>
     </row>
@@ -24229,13 +24614,13 @@
         <v>17</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>1748</v>
+        <v>1698</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>1749</v>
+        <v>1699</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>1750</v>
+        <v>1700</v>
       </c>
       <c r="F17" s="21">
         <v>9</v>
@@ -24247,17 +24632,17 @@
         <v>30</v>
       </c>
       <c r="I17" s="21">
-        <f>G17-H17</f>
+        <f t="shared" si="0"/>
         <v>490</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>1673</v>
+        <v>1663</v>
       </c>
       <c r="K17" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L17" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M17" s="20"/>
       <c r="N17" s="20"/>
@@ -24276,10 +24661,10 @@
         <v>1256</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>1756</v>
+        <v>1701</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>1757</v>
+        <v>1702</v>
       </c>
       <c r="F18" s="21">
         <v>7</v>
@@ -24291,17 +24676,17 @@
         <v>30</v>
       </c>
       <c r="I18" s="21">
-        <f>G18-H18</f>
+        <f t="shared" si="0"/>
         <v>960</v>
       </c>
       <c r="J18" s="20" t="s">
-        <v>1673</v>
+        <v>1663</v>
       </c>
       <c r="K18" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L18" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M18" s="20"/>
       <c r="N18" s="20"/>
@@ -24317,13 +24702,13 @@
         <v>17</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>1761</v>
+        <v>1703</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>1762</v>
+        <v>1704</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>1763</v>
+        <v>1705</v>
       </c>
       <c r="F19" s="21">
         <v>8</v>
@@ -24335,17 +24720,17 @@
         <v>30</v>
       </c>
       <c r="I19" s="21">
-        <f>G19-H19</f>
+        <f t="shared" si="0"/>
         <v>990</v>
       </c>
       <c r="J19" s="20" t="s">
-        <v>1673</v>
+        <v>1663</v>
       </c>
       <c r="K19" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L19" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M19" s="20"/>
       <c r="N19" s="20"/>
@@ -24361,13 +24746,13 @@
         <v>17</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>1764</v>
+        <v>1706</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>1765</v>
+        <v>1707</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>1766</v>
+        <v>1708</v>
       </c>
       <c r="F20" s="20" t="s">
         <v>26</v>
@@ -24379,17 +24764,17 @@
         <v>30</v>
       </c>
       <c r="I20" s="21">
-        <f>G20-H20</f>
+        <f t="shared" si="0"/>
         <v>830</v>
       </c>
       <c r="J20" s="20" t="s">
-        <v>1673</v>
+        <v>1663</v>
       </c>
       <c r="K20" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L20" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M20" s="20"/>
       <c r="N20" s="20"/>
@@ -24423,17 +24808,17 @@
         <v>30</v>
       </c>
       <c r="I21" s="21">
-        <f>G21-H21</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J21" s="20" t="s">
-        <v>1673</v>
+        <v>1663</v>
       </c>
       <c r="K21" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L21" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M21" s="20"/>
       <c r="N21" s="20"/>
@@ -24449,13 +24834,13 @@
         <v>17</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>1675</v>
+        <v>1709</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>1676</v>
+        <v>1710</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>1677</v>
+        <v>1711</v>
       </c>
       <c r="F22" s="20" t="s">
         <v>81</v>
@@ -24467,7 +24852,7 @@
         <v>30</v>
       </c>
       <c r="I22" s="21">
-        <f>G22-H22</f>
+        <f t="shared" si="0"/>
         <v>1470</v>
       </c>
       <c r="J22" s="20" t="s">
@@ -24477,7 +24862,7 @@
         <v>21</v>
       </c>
       <c r="L22" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M22" s="20"/>
       <c r="N22" s="20"/>
@@ -24493,13 +24878,13 @@
         <v>17</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>1681</v>
+        <v>1712</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>1682</v>
+        <v>1713</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>1683</v>
+        <v>1714</v>
       </c>
       <c r="F23" s="21">
         <v>12</v>
@@ -24511,7 +24896,7 @@
         <v>30</v>
       </c>
       <c r="I23" s="21">
-        <f>G23-H23</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J23" s="20" t="s">
@@ -24521,7 +24906,7 @@
         <v>21</v>
       </c>
       <c r="L23" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M23" s="20"/>
       <c r="N23" s="20"/>
@@ -24544,7 +24929,7 @@
         <v>1006</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>1693</v>
+        <v>1715</v>
       </c>
       <c r="E24" s="20" t="s">
         <v>1008</v>
@@ -24559,7 +24944,7 @@
         <v>30</v>
       </c>
       <c r="I24" s="21">
-        <f>G24-H24</f>
+        <f t="shared" si="0"/>
         <v>690</v>
       </c>
       <c r="J24" s="20" t="s">
@@ -24569,7 +24954,7 @@
         <v>21</v>
       </c>
       <c r="L24" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M24" s="20"/>
       <c r="N24" s="20"/>
@@ -24585,13 +24970,13 @@
         <v>17</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>1695</v>
+        <v>1716</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>1696</v>
+        <v>1717</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>1697</v>
+        <v>1718</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>85</v>
@@ -24603,7 +24988,7 @@
         <v>20</v>
       </c>
       <c r="I25" s="21">
-        <f>G25-H25</f>
+        <f t="shared" si="0"/>
         <v>490</v>
       </c>
       <c r="J25" s="20" t="s">
@@ -24613,7 +24998,7 @@
         <v>21</v>
       </c>
       <c r="L25" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M25" s="20"/>
       <c r="N25" s="20"/>
@@ -24629,13 +25014,13 @@
         <v>17</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>1698</v>
+        <v>1719</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>1699</v>
+        <v>1720</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>1700</v>
+        <v>1721</v>
       </c>
       <c r="F26" s="20" t="s">
         <v>77</v>
@@ -24647,7 +25032,7 @@
         <v>25</v>
       </c>
       <c r="I26" s="21">
-        <f>G26-H26</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J26" s="20" t="s">
@@ -24657,7 +25042,7 @@
         <v>21</v>
       </c>
       <c r="L26" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M26" s="20"/>
       <c r="N26" s="20"/>
@@ -24677,13 +25062,13 @@
         <v>17</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>1721</v>
+        <v>1723</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>1722</v>
+        <v>1724</v>
       </c>
       <c r="F27" s="21">
         <v>2</v>
@@ -24695,7 +25080,7 @@
         <v>30</v>
       </c>
       <c r="I27" s="21">
-        <f>G27-H27</f>
+        <f t="shared" si="0"/>
         <v>820</v>
       </c>
       <c r="J27" s="20" t="s">
@@ -24705,7 +25090,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M27" s="20"/>
       <c r="N27" s="20"/>
@@ -24724,10 +25109,10 @@
         <v>111</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>1733</v>
+        <v>1725</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>1734</v>
+        <v>1726</v>
       </c>
       <c r="F28" s="20" t="s">
         <v>81</v>
@@ -24739,7 +25124,7 @@
         <v>30</v>
       </c>
       <c r="I28" s="21">
-        <f>G28-H28</f>
+        <f t="shared" si="0"/>
         <v>490</v>
       </c>
       <c r="J28" s="20" t="s">
@@ -24749,7 +25134,7 @@
         <v>21</v>
       </c>
       <c r="L28" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M28" s="20"/>
       <c r="N28" s="20"/>
@@ -24765,13 +25150,13 @@
         <v>17</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>1742</v>
+        <v>1727</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>1743</v>
+        <v>1728</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>1744</v>
+        <v>1729</v>
       </c>
       <c r="F29" s="20" t="s">
         <v>85</v>
@@ -24783,7 +25168,7 @@
         <v>20</v>
       </c>
       <c r="I29" s="21">
-        <f>G29-H29</f>
+        <f t="shared" si="0"/>
         <v>780</v>
       </c>
       <c r="J29" s="20" t="s">
@@ -24793,7 +25178,7 @@
         <v>21</v>
       </c>
       <c r="L29" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M29" s="20"/>
       <c r="N29" s="20"/>
@@ -24809,10 +25194,10 @@
         <v>17</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>1751</v>
+        <v>1730</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>1752</v>
+        <v>1731</v>
       </c>
       <c r="E30" s="20" t="s">
         <v>685</v>
@@ -24827,7 +25212,7 @@
         <v>25</v>
       </c>
       <c r="I30" s="21">
-        <f>G30-H30</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J30" s="20" t="s">
@@ -24837,7 +25222,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M30" s="20"/>
       <c r="N30" s="20"/>
@@ -24857,13 +25242,13 @@
         <v>17</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>1753</v>
+        <v>1732</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>1754</v>
+        <v>1733</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>1755</v>
+        <v>1734</v>
       </c>
       <c r="F31" s="20" t="s">
         <v>85</v>
@@ -24875,7 +25260,7 @@
         <v>20</v>
       </c>
       <c r="I31" s="21">
-        <f>G31-H31</f>
+        <f t="shared" si="0"/>
         <v>830</v>
       </c>
       <c r="J31" s="20" t="s">
@@ -24885,7 +25270,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M31" s="20"/>
       <c r="N31" s="20"/>
@@ -24901,13 +25286,13 @@
         <v>17</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>1758</v>
+        <v>1735</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>1759</v>
+        <v>1736</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>1760</v>
+        <v>1737</v>
       </c>
       <c r="F32" s="20" t="s">
         <v>95</v>
@@ -24919,7 +25304,7 @@
         <v>25</v>
       </c>
       <c r="I32" s="21">
-        <f>G32-H32</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J32" s="20" t="s">
@@ -24929,7 +25314,7 @@
         <v>21</v>
       </c>
       <c r="L32" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M32" s="20"/>
       <c r="N32" s="20"/>
@@ -24939,7 +25324,7 @@
         <v>1</v>
       </c>
       <c r="R32" s="15">
-        <f t="shared" ref="R32:R34" si="1">H32</f>
+        <f>H32</f>
         <v>25</v>
       </c>
     </row>
@@ -24967,7 +25352,7 @@
         <v>40</v>
       </c>
       <c r="I33" s="21">
-        <f>G33-H33</f>
+        <f t="shared" si="0"/>
         <v>-40</v>
       </c>
       <c r="J33" s="20" t="s">
@@ -24977,7 +25362,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M33" s="20"/>
       <c r="N33" s="20"/>
@@ -24987,7 +25372,7 @@
         <v>1</v>
       </c>
       <c r="R33" s="15">
-        <f t="shared" si="1"/>
+        <f>H33</f>
         <v>40</v>
       </c>
     </row>
@@ -24999,11 +25384,11 @@
         <v>17</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>1769</v>
+        <v>1738</v>
       </c>
       <c r="D34" s="20"/>
       <c r="E34" s="20" t="s">
-        <v>1770</v>
+        <v>1739</v>
       </c>
       <c r="F34" s="20" t="s">
         <v>81</v>
@@ -25015,7 +25400,7 @@
         <v>30</v>
       </c>
       <c r="I34" s="21">
-        <f>G34-H34</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J34" s="20" t="s">
@@ -25025,7 +25410,7 @@
         <v>21</v>
       </c>
       <c r="L34" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M34" s="20"/>
       <c r="N34" s="20"/>
@@ -25035,7 +25420,7 @@
         <v>1</v>
       </c>
       <c r="R34" s="15">
-        <f t="shared" si="1"/>
+        <f>H34</f>
         <v>30</v>
       </c>
     </row>
@@ -25045,13 +25430,13 @@
         <v>17</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>1678</v>
+        <v>1740</v>
       </c>
       <c r="D35" s="20" t="s">
-        <v>1679</v>
+        <v>1741</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>1680</v>
+        <v>1742</v>
       </c>
       <c r="F35" s="20" t="s">
         <v>95</v>
@@ -25063,7 +25448,7 @@
         <v>35</v>
       </c>
       <c r="I35" s="21">
-        <f>G35-H35</f>
+        <f t="shared" si="0"/>
         <v>4365</v>
       </c>
       <c r="J35" s="20" t="s">
@@ -25073,7 +25458,7 @@
         <v>21</v>
       </c>
       <c r="L35" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M35" s="25" t="s">
         <v>167</v>
@@ -25095,13 +25480,13 @@
         <v>17</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>1701</v>
+        <v>1743</v>
       </c>
       <c r="D36" s="20" t="s">
-        <v>1702</v>
+        <v>1744</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>1703</v>
+        <v>1745</v>
       </c>
       <c r="F36" s="21">
         <v>10</v>
@@ -25113,7 +25498,7 @@
         <v>25</v>
       </c>
       <c r="I36" s="21">
-        <f>G36-H36</f>
+        <f t="shared" si="0"/>
         <v>490</v>
       </c>
       <c r="J36" s="20" t="s">
@@ -25123,7 +25508,7 @@
         <v>21</v>
       </c>
       <c r="L36" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M36" s="20"/>
       <c r="N36" s="20"/>
@@ -25139,13 +25524,13 @@
         <v>17</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>1704</v>
+        <v>1746</v>
       </c>
       <c r="D37" s="20" t="s">
-        <v>1705</v>
+        <v>1747</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>1706</v>
+        <v>1748</v>
       </c>
       <c r="F37" s="21">
         <v>5</v>
@@ -25157,7 +25542,7 @@
         <v>25</v>
       </c>
       <c r="I37" s="21">
-        <f>G37-H37</f>
+        <f t="shared" si="0"/>
         <v>870</v>
       </c>
       <c r="J37" s="20" t="s">
@@ -25167,7 +25552,7 @@
         <v>21</v>
       </c>
       <c r="L37" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M37" s="20"/>
       <c r="N37" s="20"/>
@@ -25186,7 +25571,7 @@
         <v>1277</v>
       </c>
       <c r="D38" s="20" t="s">
-        <v>1707</v>
+        <v>1749</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>1279</v>
@@ -25201,7 +25586,7 @@
         <v>20</v>
       </c>
       <c r="I38" s="21">
-        <f>G38-H38</f>
+        <f t="shared" si="0"/>
         <v>690</v>
       </c>
       <c r="J38" s="20" t="s">
@@ -25211,7 +25596,7 @@
         <v>21</v>
       </c>
       <c r="L38" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M38" s="20"/>
       <c r="N38" s="20"/>
@@ -25227,13 +25612,13 @@
         <v>17</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>1708</v>
+        <v>1750</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>1709</v>
+        <v>1751</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>1710</v>
+        <v>1752</v>
       </c>
       <c r="F39" s="21">
         <v>3</v>
@@ -25245,7 +25630,7 @@
         <v>25</v>
       </c>
       <c r="I39" s="21">
-        <f>G39-H39</f>
+        <f t="shared" si="0"/>
         <v>490</v>
       </c>
       <c r="J39" s="20" t="s">
@@ -25255,7 +25640,7 @@
         <v>21</v>
       </c>
       <c r="L39" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M39" s="20"/>
       <c r="N39" s="20"/>
@@ -25271,13 +25656,13 @@
         <v>17</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>1717</v>
+        <v>1753</v>
       </c>
       <c r="D40" s="20" t="s">
-        <v>1718</v>
+        <v>1754</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>1719</v>
+        <v>1755</v>
       </c>
       <c r="F40" s="21">
         <v>1</v>
@@ -25289,7 +25674,7 @@
         <v>25</v>
       </c>
       <c r="I40" s="21">
-        <f>G40-H40</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J40" s="20" t="s">
@@ -25299,7 +25684,7 @@
         <v>21</v>
       </c>
       <c r="L40" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M40" s="20"/>
       <c r="N40" s="20"/>
@@ -25319,13 +25704,13 @@
         <v>17</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>1730</v>
+        <v>1756</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>1731</v>
+        <v>1757</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>1732</v>
+        <v>1758</v>
       </c>
       <c r="F41" s="21">
         <v>1</v>
@@ -25337,7 +25722,7 @@
         <v>25</v>
       </c>
       <c r="I41" s="21">
-        <f>G41-H41</f>
+        <f t="shared" si="0"/>
         <v>890</v>
       </c>
       <c r="J41" s="20" t="s">
@@ -25347,7 +25732,7 @@
         <v>21</v>
       </c>
       <c r="L41" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M41" s="20"/>
       <c r="N41" s="20"/>
@@ -25365,11 +25750,11 @@
         <v>17</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>1767</v>
+        <v>1759</v>
       </c>
       <c r="D42" s="20"/>
       <c r="E42" s="20" t="s">
-        <v>1768</v>
+        <v>1760</v>
       </c>
       <c r="F42" s="21">
         <v>5</v>
@@ -25381,7 +25766,7 @@
         <v>30</v>
       </c>
       <c r="I42" s="21">
-        <f>G42-H42</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J42" s="20" t="s">
@@ -25391,7 +25776,7 @@
         <v>21</v>
       </c>
       <c r="L42" s="20" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="M42" s="20"/>
       <c r="N42" s="20"/>
@@ -25410,7 +25795,7 @@
         <v>1140</v>
       </c>
       <c r="D43" s="26" t="s">
-        <v>1771</v>
+        <v>1761</v>
       </c>
       <c r="E43" s="26" t="s">
         <v>1142</v>
@@ -25425,7 +25810,7 @@
         <v>30</v>
       </c>
       <c r="I43" s="27">
-        <f>G43-H43</f>
+        <f t="shared" si="0"/>
         <v>780</v>
       </c>
       <c r="J43" s="26" t="s">
@@ -25453,1032 +25838,3956 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D45" s="6">
-        <f>COUNTA(D3:D43)</f>
-        <v>37</v>
-      </c>
-      <c r="G45" s="6">
-        <f t="shared" ref="G45:Q45" si="2">SUBTOTAL(9,G3:G43)</f>
-        <v>26820</v>
-      </c>
-      <c r="H45" s="6">
-        <f t="shared" si="2"/>
+    <row r="44" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="26"/>
+      <c r="B44" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44" s="26" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D44" s="26" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E44" s="26" t="s">
+        <v>1605</v>
+      </c>
+      <c r="F44" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="G44" s="27">
+        <v>375</v>
+      </c>
+      <c r="H44" s="27">
+        <v>0</v>
+      </c>
+      <c r="I44" s="27">
+        <f t="shared" si="0"/>
+        <v>375</v>
+      </c>
+      <c r="J44" s="26" t="s">
+        <v>1587</v>
+      </c>
+      <c r="K44" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="L44" s="26" t="s">
+        <v>1584</v>
+      </c>
+      <c r="M44" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="N44" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="O44" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="P44" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q44" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D46" s="6">
+        <f>COUNTA(D3:D44)</f>
+        <v>38</v>
+      </c>
+      <c r="G46" s="6">
+        <f t="shared" ref="G46:Q46" si="1">SUBTOTAL(9,G3:G44)</f>
+        <v>27195</v>
+      </c>
+      <c r="H46" s="6">
+        <f t="shared" si="1"/>
         <v>1140</v>
       </c>
-      <c r="I45" s="6">
-        <f t="shared" si="2"/>
-        <v>25680</v>
-      </c>
-      <c r="J45" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K45" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L45" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M45" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N45" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O45" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P45" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q45" s="6">
-        <f t="shared" si="2"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="H46">
+      <c r="I46" s="6">
+        <f t="shared" si="1"/>
+        <v>26055</v>
+      </c>
+      <c r="J46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q46" s="6">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H47">
         <f>-12*17</f>
         <v>-204</v>
       </c>
-      <c r="I46">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C47" s="5" t="s">
+      <c r="I47">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="D47" s="5"/>
-      <c r="E47" s="9" t="s">
+      <c r="D48" s="5"/>
+      <c r="E48" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="H47">
+      <c r="H48">
         <f>-6*25</f>
         <v>-150</v>
       </c>
-      <c r="K47" s="16" t="s">
-        <v>1673</v>
-      </c>
-      <c r="L47" s="16" t="s">
+      <c r="K48" s="16" t="s">
+        <v>1663</v>
+      </c>
+      <c r="L48" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="M47" s="16" t="s">
+      <c r="M48" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="O47" s="9" t="s">
+      <c r="O48" s="9" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>1674</v>
-      </c>
-      <c r="B48" s="8" t="s">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B49" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C48" s="4">
-        <f>SUMIFS(I$3:I$43,B$3:B$43,A$47,L$3:L$43,A$48)</f>
+      <c r="C49" s="4">
+        <f>SUMIFS(I$3:I$44,B$3:B$44,A$48,L$3:L$44,A$49)</f>
         <v>24900</v>
       </c>
-      <c r="D48" s="4"/>
-      <c r="E48" s="8">
-        <f>SUMIFS(Q$3:Q$43,B$3:B$43,A$47,L$3:L$43,A$48)</f>
+      <c r="D49" s="4"/>
+      <c r="E49" s="8">
+        <f>SUMIFS(Q$3:Q$44,B$3:B$44,A$48,L$3:L$44,A$49)</f>
         <v>40</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F49" t="s">
         <v>196</v>
       </c>
-      <c r="H48">
+      <c r="H49">
         <f>-1*30</f>
         <v>-30</v>
       </c>
-      <c r="K48" t="s">
+      <c r="K49" t="s">
         <v>197</v>
       </c>
-      <c r="L48">
-        <f>SUMIFS(G$3:G$43,J$3:J$43,K$47)</f>
+      <c r="L49">
+        <f>SUMIFS(G$3:G$44,J$3:J$44,K$48)</f>
         <v>12280</v>
       </c>
-      <c r="M48">
-        <f>SUMIFS(Q$3:Q$43,J$3:J$43,K$47)-INT(COUNTIFS(J$3:J$43,K$47,M$3:M$43,"*gộp*")/2)</f>
+      <c r="M49">
+        <f>SUMIFS(Q$3:Q$44,J$3:J$44,K$48)-INT(COUNTIFS(J$3:J$44,K$48,M$3:M$44,"*gộp*")/2)</f>
         <v>19</v>
       </c>
-      <c r="O48" t="s">
-        <v>1772</v>
-      </c>
-      <c r="P48">
-        <f>L53</f>
-        <v>11099</v>
-      </c>
-    </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B49" s="7" t="s">
+      <c r="O49" t="s">
+        <v>1762</v>
+      </c>
+      <c r="P49">
+        <f>L54</f>
+        <v>10724</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B50" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="C49" s="3">
-        <v>0</v>
-      </c>
-      <c r="D49" s="3"/>
-      <c r="K49" t="s">
+      <c r="C50" s="3">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3"/>
+      <c r="K50" t="s">
         <v>200</v>
       </c>
-      <c r="L49">
-        <f>SUM(H46:H48)</f>
+      <c r="L50">
+        <f>SUM(H47:H49)</f>
         <v>-384</v>
       </c>
-      <c r="M49">
-        <f>SUMIFS(Q$3:Q$43,J$3:J$43,K$47)-INT(COUNTIFS(J$3:J$43,K$47,M$3:M$43,"*gộp*")/2)</f>
+      <c r="M50">
+        <f>SUMIFS(Q$3:Q$44,J$3:J$44,K$48)-INT(COUNTIFS(J$3:J$44,K$48,M$3:M$44,"*gộp*")/2)</f>
         <v>19</v>
       </c>
-      <c r="O49" t="s">
-        <v>21</v>
-      </c>
-      <c r="P49">
-        <f>L61</f>
+      <c r="O50" t="s">
+        <v>21</v>
+      </c>
+      <c r="P50">
+        <f>L62</f>
         <v>5382</v>
       </c>
     </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B50" s="7" t="s">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B51" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="C50" s="3">
-        <f>-SUMIFS(I$3:I$43,B$3:B$43,A$47,P$3:P$43,"xx",N$3:N$43,"x")</f>
-        <v>-780</v>
-      </c>
-      <c r="D50" s="3"/>
-      <c r="E50" s="7">
-        <f>SUMIFS(Q$3:Q$43,B$3:B$43,A$47,P$3:P$43,"xx",N$3:N$43,"x")</f>
-        <v>1</v>
-      </c>
-      <c r="K50" t="s">
+      <c r="C51" s="3">
+        <f>-SUMIFS(I$3:I$44,B$3:B$44,A$48,P$3:P$44,"xx",N$3:N$44,"x")</f>
+        <v>-1155</v>
+      </c>
+      <c r="D51" s="3"/>
+      <c r="E51" s="7">
+        <f>SUMIFS(Q$3:Q$44,B$3:B$44,A$48,P$3:P$44,"xx",N$3:N$44,"x")</f>
+        <v>2</v>
+      </c>
+      <c r="K51" t="s">
         <v>202</v>
       </c>
-      <c r="O50" t="s">
+      <c r="O51" t="s">
         <v>135</v>
       </c>
-      <c r="P50">
-        <f>L69</f>
+      <c r="P51">
+        <f>L70</f>
         <v>7810</v>
       </c>
     </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B51" s="9" t="s">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B52" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="C51" s="5">
-        <f>SUBTOTAL(9,C48:C50)</f>
-        <v>24120</v>
-      </c>
-      <c r="D51" s="5"/>
-      <c r="E51">
-        <f>E48</f>
+      <c r="C52" s="5">
+        <f>SUBTOTAL(9,C49:C51)</f>
+        <v>23745</v>
+      </c>
+      <c r="D52" s="5"/>
+      <c r="E52">
+        <f>E49</f>
         <v>40</v>
       </c>
-      <c r="K51" s="7" t="s">
+      <c r="K52" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="L51" s="28">
+      <c r="L52" s="28">
         <v>-797</v>
       </c>
-      <c r="M51" s="28" t="s">
+      <c r="M52" s="28" t="s">
         <v>288</v>
       </c>
-      <c r="O51" t="s">
+      <c r="O52" t="s">
         <v>207</v>
       </c>
-      <c r="P51">
-        <f>-C55</f>
-        <v>-24120</v>
-      </c>
-    </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B52" s="7" t="s">
+      <c r="P52">
+        <f>-C56</f>
+        <v>-23745</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B53" s="7" t="s">
         <v>205</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="K52" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="O52" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="P52" s="9">
-        <f>SUBTOTAL(9,P48:P51)</f>
-        <v>171</v>
-      </c>
-    </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B53" s="17" t="s">
-        <v>208</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
-      <c r="L53" s="18">
-        <f>SUBTOTAL(9,L48:L52)</f>
-        <v>11099</v>
-      </c>
-      <c r="M53" s="18">
-        <f>M48</f>
+      <c r="K53" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="L53" s="28">
+        <v>-375</v>
+      </c>
+      <c r="M53" s="28" t="s">
+        <v>288</v>
+      </c>
+      <c r="O53" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P53" s="9">
+        <f>SUBTOTAL(9,P49:P52)</f>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B54" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="L54" s="18">
+        <f>SUBTOTAL(9,L49:L53)</f>
+        <v>10724</v>
+      </c>
+      <c r="M54" s="18">
+        <f>M49</f>
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B55" s="6" t="s">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B56" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="C55" s="1">
-        <f>C51+C52+C53</f>
-        <v>24120</v>
-      </c>
-      <c r="D55" s="1"/>
-      <c r="E55" s="6" t="s">
+      <c r="C56" s="1">
+        <f>C52+C53+C54</f>
+        <v>23745</v>
+      </c>
+      <c r="D56" s="1"/>
+      <c r="E56" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="K55" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="L55" s="16" t="s">
+      <c r="K56" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L56" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="M55" s="16" t="s">
+      <c r="M56" s="16" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="K56" t="s">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K57" t="s">
         <v>197</v>
       </c>
-      <c r="L56">
-        <f>SUMIFS(G$3:G$43,J$3:J$43,K$55)</f>
+      <c r="L57">
+        <f>SUMIFS(G$3:G$44,J$3:J$44,K$56)</f>
         <v>5750</v>
       </c>
-      <c r="M56">
-        <f>SUMIFS(Q$3:Q$43,J$3:J$43,K$55)-INT(COUNTIFS(J$3:J$43,K$55,M$3:M$43,"*gộp*")/2)</f>
+      <c r="M57">
+        <f>SUMIFS(Q$3:Q$44,J$3:J$44,K$56)-INT(COUNTIFS(J$3:J$44,K$56,M$3:M$44,"*gộp*")/2)</f>
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="K57" t="s">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K58" t="s">
         <v>200</v>
       </c>
-      <c r="L57">
-        <f>-SUMIFS(H$3:H$43,J$3:J$43,K$55)+M57*5</f>
+      <c r="L58">
+        <f>-SUMIFS(H$3:H$44,J$3:J$44,K$56)+M58*5</f>
         <v>-290</v>
       </c>
-      <c r="M57">
-        <f>SUMIFS(Q$3:Q$43,J$3:J$43,K$55)-INT(COUNTIFS(J$3:J$43,K$55,M$3:M$43,"*gộp*")/2)</f>
+      <c r="M58">
+        <f>SUMIFS(Q$3:Q$44,J$3:J$44,K$56)-INT(COUNTIFS(J$3:J$44,K$56,M$3:M$44,"*gộp*")/2)</f>
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="K58" t="s">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K59" t="s">
         <v>202</v>
       </c>
-      <c r="L58">
-        <f>-M58*2</f>
+      <c r="L59">
+        <f>-M59*2</f>
         <v>-78</v>
       </c>
-      <c r="M58">
-        <f>E51-(COUNTIFS(M$3:M$43,"*gộp*")/2)-COUNTIFS(M$3:M$43,"*đơn trả*")-COUNTIFS(M$3:M$43,"*hàng tỉnh*")</f>
+      <c r="M59">
+        <f>E52-(COUNTIFS(M$3:M$44,"*gộp*")/2)-COUNTIFS(M$3:M$44,"*đơn trả*")-COUNTIFS(M$3:M$44,"*hàng tỉnh*")</f>
         <v>39</v>
       </c>
     </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="K59" s="7" t="s">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K60" s="7" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="60" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="K60" s="7" t="s">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K61" s="7" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="61" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="L61" s="18">
-        <f>SUBTOTAL(9,L56:L60)</f>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L62" s="18">
+        <f>SUBTOTAL(9,L57:L61)</f>
         <v>5382</v>
       </c>
-      <c r="M61" s="18">
-        <f>M56</f>
+      <c r="M62" s="18">
+        <f>M57</f>
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="K63" s="16" t="s">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K64" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="L63" s="16" t="s">
+      <c r="L64" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="M63" s="16" t="s">
+      <c r="M64" s="16" t="s">
         <v>192</v>
-      </c>
-    </row>
-    <row r="64" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="K64" t="s">
-        <v>197</v>
-      </c>
-      <c r="L64">
-        <f>SUMIFS(G$3:G$43,J$3:J$43,K$63)</f>
-        <v>7980</v>
-      </c>
-      <c r="M64">
-        <f>SUMIFS(Q$3:Q$43,J$3:J$43,K$63)-INT(COUNTIFS(J$3:J$43,K$63,M$3:M$43,"*gộp*")/2)</f>
-        <v>8</v>
       </c>
     </row>
     <row r="65" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K65" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="L65">
-        <f>-SUMIFS(H$3:H$43,J$3:J$43,K$63)+M65*5</f>
-        <v>-170</v>
+        <f>SUMIFS(G$3:G$44,J$3:J$44,K$64)</f>
+        <v>7980</v>
       </c>
       <c r="M65">
-        <f>SUMIFS(Q$3:Q$43,J$3:J$43,K$63)-INT(COUNTIFS(J$3:J$43,K$63,M$3:M$43,"*gộp*")/2)</f>
+        <f>SUMIFS(Q$3:Q$44,J$3:J$44,K$64)-INT(COUNTIFS(J$3:J$44,K$64,M$3:M$44,"*gộp*")/2)</f>
         <v>8</v>
       </c>
     </row>
     <row r="66" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K66" t="s">
+        <v>200</v>
+      </c>
+      <c r="L66">
+        <f>-SUMIFS(H$3:H$44,J$3:J$44,K$64)+M66*5</f>
+        <v>-170</v>
+      </c>
+      <c r="M66">
+        <f>SUMIFS(Q$3:Q$44,J$3:J$44,K$64)-INT(COUNTIFS(J$3:J$44,K$64,M$3:M$44,"*gộp*")/2)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K67" t="s">
         <v>202</v>
-      </c>
-    </row>
-    <row r="67" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K67" s="7" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="68" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K68" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="69" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K69" s="7" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="69" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="L69" s="18">
-        <f>SUBTOTAL(9,L64:L68)</f>
+    <row r="70" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L70" s="18">
+        <f>SUBTOTAL(9,L65:L69)</f>
         <v>7810</v>
       </c>
-      <c r="M69" s="18">
-        <f>M64</f>
+      <c r="M70" s="18">
+        <f>M65</f>
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P43" xr:uid="{00000000-0009-0000-0000-000011000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P43">
-      <sortCondition ref="J2:J43"/>
+  <autoFilter ref="A2:P44" xr:uid="{00000000-0009-0000-0000-000010000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P44">
+      <sortCondition ref="J2:J44"/>
     </sortState>
   </autoFilter>
   <mergeCells count="8">
-    <mergeCell ref="C52:D52"/>
     <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C56:D56"/>
     <mergeCell ref="C48:D48"/>
     <mergeCell ref="C49:D49"/>
     <mergeCell ref="C50:D50"/>
     <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C52:D52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D9B982-EAEB-4F31-86BF-4D059AFDEA27}">
-  <sheetPr>
-    <tabColor rgb="FF0070C0"/>
-  </sheetPr>
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+  <dimension ref="A2:R57"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="10" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="10"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="48.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>1660</v>
-      </c>
-      <c r="B1" s="10">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>1661</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>1662</v>
-      </c>
-      <c r="C2" s="11" t="s">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="19" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>1763</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>1254</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="G3" s="21">
+        <v>855</v>
+      </c>
+      <c r="H3" s="21">
+        <v>35</v>
+      </c>
+      <c r="I3" s="21">
+        <f t="shared" ref="I3:I31" si="0">G3-H3</f>
+        <v>820</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>1764</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>1766</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>1767</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>1768</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="21">
+        <v>400</v>
+      </c>
+      <c r="H4" s="21">
+        <v>30</v>
+      </c>
+      <c r="I4" s="21">
+        <f t="shared" si="0"/>
+        <v>370</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>1764</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>1770</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="21">
+        <v>0</v>
+      </c>
+      <c r="H5" s="21">
+        <v>30</v>
+      </c>
+      <c r="I5" s="21">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>1764</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M5" s="25" t="s">
+        <v>1771</v>
+      </c>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20">
+        <v>1</v>
+      </c>
+      <c r="R5" s="15">
+        <f>H5</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>1772</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>1773</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>1774</v>
+      </c>
+      <c r="F6" s="21">
+        <v>12</v>
+      </c>
+      <c r="G6" s="21">
+        <v>0</v>
+      </c>
+      <c r="H6" s="21">
+        <v>30</v>
+      </c>
+      <c r="I6" s="21">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>1764</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20">
+        <v>1</v>
+      </c>
+      <c r="R6" s="15">
+        <f>H6</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>1775</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F7" s="23">
+        <v>12</v>
+      </c>
+      <c r="G7" s="23">
+        <v>330</v>
+      </c>
+      <c r="H7" s="23">
+        <v>30</v>
+      </c>
+      <c r="I7" s="23">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>1764</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M7" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>1777</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>1778</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="21">
+        <v>0</v>
+      </c>
+      <c r="H8" s="21">
+        <v>30</v>
+      </c>
+      <c r="I8" s="21">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>1764</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20">
+        <v>1</v>
+      </c>
+      <c r="R8" s="15">
+        <f>H8</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>1779</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>1780</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>830</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="21">
+        <v>860</v>
+      </c>
+      <c r="H9" s="21">
+        <v>30</v>
+      </c>
+      <c r="I9" s="21">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>1764</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>1782</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F10" s="21">
+        <v>8</v>
+      </c>
+      <c r="G10" s="21">
+        <v>690</v>
+      </c>
+      <c r="H10" s="21">
+        <v>30</v>
+      </c>
+      <c r="I10" s="21">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>1764</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>1784</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>1785</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F11" s="21">
+        <v>7</v>
+      </c>
+      <c r="G11" s="21">
+        <v>920</v>
+      </c>
+      <c r="H11" s="21">
+        <v>30</v>
+      </c>
+      <c r="I11" s="21">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>1764</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="20"/>
+      <c r="B12" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>752</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>1788</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="21">
+        <v>820</v>
+      </c>
+      <c r="H12" s="21">
+        <v>30</v>
+      </c>
+      <c r="I12" s="21">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J12" s="20" t="s">
+        <v>1764</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M12" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>1789</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>1788</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="21">
+        <v>660</v>
+      </c>
+      <c r="H13" s="21">
+        <v>0</v>
+      </c>
+      <c r="I13" s="21">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>1764</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M13" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>1791</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>1792</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="21">
+        <v>510</v>
+      </c>
+      <c r="H14" s="21">
+        <v>30</v>
+      </c>
+      <c r="I14" s="21">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>1764</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>1794</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>1795</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="21">
+        <v>915</v>
+      </c>
+      <c r="H15" s="21">
+        <v>25</v>
+      </c>
+      <c r="I15" s="21">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>1764</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>895</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>1796</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>1797</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="21">
+        <v>850</v>
+      </c>
+      <c r="H16" s="21">
+        <v>30</v>
+      </c>
+      <c r="I16" s="21">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>1764</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>1799</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>1800</v>
+      </c>
+      <c r="F17" s="21">
+        <v>11</v>
+      </c>
+      <c r="G17" s="21">
+        <v>865</v>
+      </c>
+      <c r="H17" s="21">
+        <v>25</v>
+      </c>
+      <c r="I17" s="21">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>1764</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>591</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>1801</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>593</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" s="21">
+        <v>910</v>
+      </c>
+      <c r="H18" s="21">
+        <v>20</v>
+      </c>
+      <c r="I18" s="21">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" s="21">
+        <v>1155</v>
+      </c>
+      <c r="H19" s="21">
+        <v>25</v>
+      </c>
+      <c r="I19" s="21">
+        <f t="shared" si="0"/>
+        <v>1130</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>1806</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>1807</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="21">
+        <v>915</v>
+      </c>
+      <c r="H20" s="21">
+        <v>25</v>
+      </c>
+      <c r="I20" s="21">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>674</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>676</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G21" s="21">
+        <v>2520</v>
+      </c>
+      <c r="H21" s="21">
+        <v>30</v>
+      </c>
+      <c r="I21" s="21">
+        <f t="shared" si="0"/>
+        <v>2490</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>1810</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>1811</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" s="21">
+        <v>0</v>
+      </c>
+      <c r="H22" s="21">
+        <v>25</v>
+      </c>
+      <c r="I22" s="21">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20">
+        <v>1</v>
+      </c>
+      <c r="R22" s="15">
+        <f>H22</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>1812</v>
+      </c>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G23" s="21">
+        <v>40</v>
+      </c>
+      <c r="H23" s="21">
+        <v>40</v>
+      </c>
+      <c r="I23" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="20"/>
+      <c r="B24" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>1815</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>1816</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="21">
+        <v>0</v>
+      </c>
+      <c r="H24" s="21">
+        <v>25</v>
+      </c>
+      <c r="I24" s="21">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20">
+        <v>1</v>
+      </c>
+      <c r="R24" s="15">
+        <f>H24</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>1818</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>1819</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G25" s="21">
+        <v>1595</v>
+      </c>
+      <c r="H25" s="21">
+        <v>25</v>
+      </c>
+      <c r="I25" s="21">
+        <f t="shared" si="0"/>
+        <v>1570</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K25" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="20"/>
+      <c r="B26" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>1821</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>1822</v>
+      </c>
+      <c r="F26" s="21">
+        <v>10</v>
+      </c>
+      <c r="G26" s="21">
+        <v>915</v>
+      </c>
+      <c r="H26" s="21">
+        <v>25</v>
+      </c>
+      <c r="I26" s="21">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K26" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="20"/>
+      <c r="B27" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>1824</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F27" s="21">
+        <v>10</v>
+      </c>
+      <c r="G27" s="21">
+        <v>1225</v>
+      </c>
+      <c r="H27" s="21">
+        <v>25</v>
+      </c>
+      <c r="I27" s="21">
+        <f t="shared" si="0"/>
+        <v>1200</v>
+      </c>
+      <c r="J27" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K27" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="20"/>
+      <c r="B28" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>1827</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="F28" s="21">
+        <v>4</v>
+      </c>
+      <c r="G28" s="21">
+        <v>855</v>
+      </c>
+      <c r="H28" s="21">
+        <v>25</v>
+      </c>
+      <c r="I28" s="21">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K28" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="26"/>
+      <c r="B29" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="26" t="s">
+        <v>1595</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>1596</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="27">
+        <v>810</v>
+      </c>
+      <c r="H29" s="27">
+        <v>0</v>
+      </c>
+      <c r="I29" s="27">
+        <f t="shared" si="0"/>
+        <v>810</v>
+      </c>
+      <c r="J29" s="26" t="s">
+        <v>1587</v>
+      </c>
+      <c r="K29" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="26" t="s">
+        <v>1584</v>
+      </c>
+      <c r="M29" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="N29" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="O29" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="P29" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q29" s="26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="26"/>
+      <c r="B30" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>1687</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>1334</v>
+      </c>
+      <c r="F30" s="26" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G30" s="27">
+        <v>775</v>
+      </c>
+      <c r="H30" s="27">
+        <v>0</v>
+      </c>
+      <c r="I30" s="27">
+        <f t="shared" si="0"/>
+        <v>775</v>
+      </c>
+      <c r="J30" s="26" t="s">
         <v>1663</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="K30" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="26" t="s">
         <v>1664</v>
       </c>
-      <c r="E2" s="11" t="s">
-        <v>1665</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
-        <v>46143</v>
-      </c>
-      <c r="B3" s="13">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A3,"dd-mm")&amp;"'!L3:L200"),TEXT(A3,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>54</v>
-      </c>
-      <c r="C3" s="13">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A3,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D3" s="13" cm="1">
-        <f t="array" ref="D3" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A3,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="13">
-        <f t="shared" ref="E3:E27" ca="1" si="0">B3-C3-D3</f>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
-        <v>46146</v>
-      </c>
-      <c r="B4" s="13">
-        <f t="shared" ref="B4:B27" ca="1" si="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A4,"dd-mm")&amp;"-"&amp;B$1),0)</f>
+      <c r="M30" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="N30" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="O30" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="P30" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q30" s="26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="26"/>
+      <c r="B31" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="26" t="s">
+        <v>627</v>
+      </c>
+      <c r="D31" s="26" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E31" s="26" t="s">
+        <v>629</v>
+      </c>
+      <c r="F31" s="27">
+        <v>1</v>
+      </c>
+      <c r="G31" s="27">
+        <v>25</v>
+      </c>
+      <c r="H31" s="27">
+        <v>25</v>
+      </c>
+      <c r="I31" s="27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="K31" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="26" t="s">
+        <v>1517</v>
+      </c>
+      <c r="M31" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="N31" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="O31" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="P31" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q31" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D33" s="6">
+        <f>COUNTA(D3:D31)</f>
+        <v>28</v>
+      </c>
+      <c r="G33" s="6">
+        <f t="shared" ref="G33:Q33" si="1">SUBTOTAL(9,G3:G31)</f>
+        <v>20415</v>
+      </c>
+      <c r="H33" s="6">
+        <f t="shared" si="1"/>
+        <v>730</v>
+      </c>
+      <c r="I33" s="6">
+        <f t="shared" si="1"/>
+        <v>19685</v>
+      </c>
+      <c r="J33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q33" s="6">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H34">
+        <f>-4*17</f>
+        <v>-68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D35" s="5"/>
+      <c r="E35" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H35">
+        <f>-9*25</f>
+        <v>-225</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="O35" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C36" s="4">
+        <f>SUMIFS(I$3:I$31,B$3:B$31,A$35,L$3:L$31,A$36)</f>
+        <v>18100</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="8">
+        <f>SUMIFS(Q$3:Q$31,B$3:B$31,A$35,L$3:L$31,A$36)</f>
+        <v>26</v>
+      </c>
+      <c r="F36" t="s">
+        <v>196</v>
+      </c>
+      <c r="H36">
+        <f>-1*30</f>
+        <v>-30</v>
+      </c>
+      <c r="K36" t="s">
+        <v>197</v>
+      </c>
+      <c r="L36">
+        <f>SUMIFS(G$3:G$31,J$3:J$31,K$35)</f>
+        <v>5540</v>
+      </c>
+      <c r="M36">
+        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$35)-INT(COUNTIFS(J$3:J$31,K$35,M$3:M$31,"*gộp*")/2)</f>
+        <v>6</v>
+      </c>
+      <c r="O36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P36">
+        <f>L41</f>
+        <v>5357</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B37" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C37" s="3">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3"/>
+      <c r="K37" t="s">
+        <v>200</v>
+      </c>
+      <c r="L37">
+        <f>-SUMIFS(H$3:H$31,J$3:J$31,K$35)+M37*5</f>
+        <v>-135</v>
+      </c>
+      <c r="M37">
+        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$35)-INT(COUNTIFS(J$3:J$31,K$35,M$3:M$31,"*gộp*")/2)</f>
+        <v>6</v>
+      </c>
+      <c r="O37" t="s">
+        <v>135</v>
+      </c>
+      <c r="P37">
+        <f>L49</f>
+        <v>4485</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B38" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C38" s="3">
+        <f>-SUMIFS(I$3:I$31,B$3:B$31,A$35,P$3:P$31,"xx",N$3:N$31,"x")</f>
+        <v>-1585</v>
+      </c>
+      <c r="D38" s="3"/>
+      <c r="E38" s="7">
+        <f>SUMIFS(Q$3:Q$31,B$3:B$31,A$35,P$3:P$31,"xx",N$3:N$31,"x")</f>
+        <v>3</v>
+      </c>
+      <c r="K38" t="s">
+        <v>202</v>
+      </c>
+      <c r="L38">
+        <f>-M38*2</f>
+        <v>-48</v>
+      </c>
+      <c r="M38">
+        <f>E39-(COUNTIFS(M$3:M$31,"*gộp*")/2)-COUNTIFS(M$3:M$31,"*đơn trả*")-COUNTIFS(M$3:M$31,"*hàng tỉnh*")</f>
+        <v>24</v>
+      </c>
+      <c r="O38" t="s">
+        <v>1828</v>
+      </c>
+      <c r="P38">
+        <f>L57</f>
+        <v>6767</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B39" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C39" s="5">
+        <f>SUBTOTAL(9,C36:C38)</f>
+        <v>16515</v>
+      </c>
+      <c r="D39" s="5"/>
+      <c r="E39">
+        <f>E36</f>
+        <v>26</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="O39" t="s">
+        <v>207</v>
+      </c>
+      <c r="P39">
+        <f>-C43</f>
+        <v>-16515</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B40" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="K40" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O40" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P40" s="9">
+        <f>SUBTOTAL(9,P36:P39)</f>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B41" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="L41" s="18">
+        <f>SUBTOTAL(9,L36:L40)</f>
+        <v>5357</v>
+      </c>
+      <c r="M41" s="18">
+        <f>M36</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B43" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C43" s="1">
+        <f>C39+C40+C41</f>
+        <v>16515</v>
+      </c>
+      <c r="D43" s="1"/>
+      <c r="E43" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K44" t="s">
+        <v>197</v>
+      </c>
+      <c r="L44">
+        <f>SUMIFS(G$3:G$31,J$3:J$31,K$43)</f>
+        <v>4590</v>
+      </c>
+      <c r="M44">
+        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$43)-INT(COUNTIFS(J$3:J$31,K$43,M$3:M$31,"*gộp*")/2)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K45" t="s">
+        <v>200</v>
+      </c>
+      <c r="L45">
+        <f>-SUMIFS(H$3:H$31,J$3:J$31,K$43)+M45*5</f>
+        <v>-100</v>
+      </c>
+      <c r="M45">
+        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$43)-INT(COUNTIFS(J$3:J$31,K$43,M$3:M$31,"*gộp*")/2)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K46" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K47" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="L47" s="28">
+        <v>-5</v>
+      </c>
+      <c r="M47" s="28" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K48" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="49" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L49" s="18">
+        <f>SUBTOTAL(9,L44:L48)</f>
+        <v>4485</v>
+      </c>
+      <c r="M49" s="18">
+        <f>M44</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K51" s="16" t="s">
+        <v>1764</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="52" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K52" t="s">
+        <v>197</v>
+      </c>
+      <c r="L52">
+        <f>SUMIFS(G$3:G$31,J$3:J$31,K$51)</f>
+        <v>8675</v>
+      </c>
+      <c r="M52">
+        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$51)-INT(COUNTIFS(J$3:J$31,K$51,M$3:M$31,"*gộp*")/2)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K53" t="s">
+        <v>200</v>
+      </c>
+      <c r="L53">
+        <f>SUM(H34:H36)</f>
+        <v>-323</v>
+      </c>
+      <c r="M53">
+        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$51)-INT(COUNTIFS(J$3:J$31,K$51,M$3:M$31,"*gộp*")/2)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K54" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="55" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K55" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="56" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K56" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="L56" s="38">
+        <f>-SUM(I29:I30)</f>
+        <v>-1585</v>
+      </c>
+      <c r="M56" s="28" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="57" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L57" s="18">
+        <f>SUBTOTAL(9,L52:L56)</f>
+        <v>6767</v>
+      </c>
+      <c r="M57" s="18">
+        <f>M52</f>
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P31" xr:uid="{00000000-0009-0000-0000-000011000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P31">
+      <sortCondition ref="J2:J31"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+  <dimension ref="A2:R54"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="32.7109375" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="55.5703125" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="20"/>
+    </row>
+    <row r="3" spans="1:18" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>1846</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F3" s="23">
+        <v>12</v>
+      </c>
+      <c r="G3" s="23">
+        <v>785</v>
+      </c>
+      <c r="H3" s="23">
+        <v>30</v>
+      </c>
+      <c r="I3" s="23">
+        <f>G3-H3</f>
+        <v>755</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>1847</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M3" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>1848</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="21">
+        <v>1550</v>
+      </c>
+      <c r="H4" s="21">
+        <v>30</v>
+      </c>
+      <c r="I4" s="21">
+        <f>G4-H4</f>
+        <v>1520</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>1847</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>837</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>1857</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>1858</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="21">
+        <v>0</v>
+      </c>
+      <c r="H5" s="21">
+        <v>25</v>
+      </c>
+      <c r="I5" s="21">
+        <f>G5-H5</f>
+        <v>-25</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>1847</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20">
+        <v>1</v>
+      </c>
+      <c r="R5" s="15">
+        <f>H5</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>1868</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>1869</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>1870</v>
+      </c>
+      <c r="F6" s="21">
+        <v>8</v>
+      </c>
+      <c r="G6" s="21">
+        <v>820</v>
+      </c>
+      <c r="H6" s="21">
+        <v>30</v>
+      </c>
+      <c r="I6" s="21">
+        <f>G6-H6</f>
+        <v>790</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>1847</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>1888</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>1889</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="G7" s="21">
+        <v>1025</v>
+      </c>
+      <c r="H7" s="21">
+        <v>35</v>
+      </c>
+      <c r="I7" s="21">
+        <f>G7-H7</f>
+        <v>990</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>1847</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>1784</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>1890</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F8" s="21">
+        <v>7</v>
+      </c>
+      <c r="G8" s="21">
+        <v>820</v>
+      </c>
+      <c r="H8" s="21">
+        <v>30</v>
+      </c>
+      <c r="I8" s="21">
+        <f>G8-H8</f>
+        <v>790</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>1847</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M8" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20">
+        <v>1</v>
+      </c>
+      <c r="R8" s="15">
+        <f>H8</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20" t="s">
+        <v>1895</v>
+      </c>
+      <c r="F9" s="21">
+        <v>6</v>
+      </c>
+      <c r="G9" s="21">
+        <v>1400</v>
+      </c>
+      <c r="H9" s="21">
+        <v>30</v>
+      </c>
+      <c r="I9" s="21">
+        <f>G9-H9</f>
+        <v>1370</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>1847</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>1843</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>1844</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>1845</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" s="21">
+        <v>810</v>
+      </c>
+      <c r="H10" s="21">
         <v>20</v>
       </c>
-      <c r="C4" s="13">
-        <f t="shared" ref="C4:C27" ca="1" si="2">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D4" s="13" cm="1">
-        <f t="array" aca="1" ref="D4" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+      <c r="I10" s="21">
+        <f>G10-H10</f>
+        <v>790</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>1737</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G11" s="21">
+        <v>845</v>
+      </c>
+      <c r="H11" s="21">
+        <v>25</v>
+      </c>
+      <c r="I11" s="21">
+        <f>G11-H11</f>
+        <v>820</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="20"/>
+      <c r="B12" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>1859</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>1860</v>
+      </c>
+      <c r="F12" s="21">
+        <v>12</v>
+      </c>
+      <c r="G12" s="21">
+        <v>0</v>
+      </c>
+      <c r="H12" s="21">
+        <v>30</v>
+      </c>
+      <c r="I12" s="21">
+        <f>G12-H12</f>
+        <v>-30</v>
+      </c>
+      <c r="J12" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20">
+        <v>1</v>
+      </c>
+      <c r="R12" s="15">
+        <f t="shared" ref="R12:R13" si="0">H12</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>1862</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>1863</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="21">
+        <v>0</v>
+      </c>
+      <c r="H13" s="21">
+        <v>30</v>
+      </c>
+      <c r="I13" s="21">
+        <f>G13-H13</f>
+        <v>-30</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20">
+        <v>1</v>
+      </c>
+      <c r="R13" s="15">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>1864</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F14" s="21">
+        <v>2</v>
+      </c>
+      <c r="G14" s="21">
+        <v>920</v>
+      </c>
+      <c r="H14" s="21">
+        <v>30</v>
+      </c>
+      <c r="I14" s="21">
+        <f>G14-H14</f>
+        <v>890</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>1871</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>1872</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>1873</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" s="21">
+        <v>500</v>
+      </c>
+      <c r="H15" s="21">
+        <v>20</v>
+      </c>
+      <c r="I15" s="21">
+        <f>G15-H15</f>
+        <v>480</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>1882</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>1883</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="23">
+        <v>25</v>
+      </c>
+      <c r="H16" s="23">
+        <v>25</v>
+      </c>
+      <c r="I16" s="23">
+        <f>G16-H16</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M16" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>1891</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>1892</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="21">
+        <v>0</v>
+      </c>
+      <c r="H17" s="21">
+        <v>20</v>
+      </c>
+      <c r="I17" s="21">
+        <f>G17-H17</f>
+        <v>-20</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20">
+        <v>1</v>
+      </c>
+      <c r="R17" s="15">
+        <f>H17</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="21">
+        <v>30</v>
+      </c>
+      <c r="H18" s="21">
+        <v>30</v>
+      </c>
+      <c r="I18" s="21">
+        <f>G18-H18</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20" t="s">
+        <v>1897</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="21">
+        <v>1575</v>
+      </c>
+      <c r="H19" s="21">
+        <v>25</v>
+      </c>
+      <c r="I19" s="21">
+        <f>G19-H19</f>
+        <v>1550</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>1898</v>
+      </c>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="F20" s="21">
+        <v>12</v>
+      </c>
+      <c r="G20" s="21">
+        <v>0</v>
+      </c>
+      <c r="H20" s="21">
+        <v>40</v>
+      </c>
+      <c r="I20" s="21">
+        <f>G20-H20</f>
+        <v>-40</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20">
+        <v>1</v>
+      </c>
+      <c r="R20" s="15">
+        <f>H20</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>1840</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>1841</v>
+      </c>
+      <c r="F21" s="21">
+        <v>3</v>
+      </c>
+      <c r="G21" s="21">
+        <v>1830</v>
+      </c>
+      <c r="H21" s="21">
+        <v>25</v>
+      </c>
+      <c r="I21" s="21">
+        <f>G21-H21</f>
+        <v>1805</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M21" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20">
+        <v>1</v>
+      </c>
+      <c r="R21" s="15">
+        <f>H21</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>1852</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>1853</v>
+      </c>
+      <c r="F22" s="21">
+        <v>1</v>
+      </c>
+      <c r="G22" s="21">
+        <v>0</v>
+      </c>
+      <c r="H22" s="21">
+        <v>25</v>
+      </c>
+      <c r="I22" s="21">
+        <f>G22-H22</f>
+        <v>-25</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20">
+        <v>1</v>
+      </c>
+      <c r="R22" s="15">
+        <f t="shared" ref="R22:R25" si="1">H22</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>1855</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>1856</v>
+      </c>
+      <c r="F23" s="21">
         <v>4</v>
       </c>
-      <c r="E4" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
-        <v>46147</v>
-      </c>
-      <c r="B5" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>53</v>
-      </c>
-      <c r="C5" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="D5" s="13" cm="1">
-        <f t="array" aca="1" ref="D5" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A5,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="12">
-        <v>46148</v>
-      </c>
-      <c r="B6" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>32</v>
-      </c>
-      <c r="C6" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D6" s="13" cm="1">
-        <f t="array" aca="1" ref="D6" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A6,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
-        <v>46149</v>
-      </c>
-      <c r="B7" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>34</v>
-      </c>
-      <c r="C7" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="D7" s="13" cm="1">
-        <f t="array" aca="1" ref="D7" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A7,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="12">
-        <v>46150</v>
-      </c>
-      <c r="B8" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>36</v>
-      </c>
-      <c r="C8" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D8" s="13" cm="1">
-        <f t="array" aca="1" ref="D8" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A8,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
-        <v>46151</v>
-      </c>
-      <c r="B9" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>31</v>
-      </c>
-      <c r="C9" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D9" s="13" cm="1">
-        <f t="array" aca="1" ref="D9" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A9,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
-        <v>46153</v>
-      </c>
-      <c r="B10" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>56</v>
-      </c>
-      <c r="C10" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D10" s="13" cm="1">
-        <f t="array" aca="1" ref="D10" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A10,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>4</v>
-      </c>
-      <c r="E10" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
-        <v>46154</v>
-      </c>
-      <c r="B11" s="13">
-        <f t="shared" ca="1" si="1"/>
+      <c r="G23" s="21">
+        <v>0</v>
+      </c>
+      <c r="H23" s="21">
         <v>25</v>
       </c>
-      <c r="C11" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D11" s="13" cm="1">
-        <f t="array" aca="1" ref="D11" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A11,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="I23" s="21">
+        <f>G23-H23</f>
+        <v>-25</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20">
+        <v>1</v>
+      </c>
+      <c r="R23" s="15">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="12">
-        <v>46155</v>
-      </c>
-      <c r="B12" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>33</v>
-      </c>
-      <c r="C12" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="D12" s="13" cm="1">
-        <f t="array" aca="1" ref="D12" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A12,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="12">
-        <v>46156</v>
-      </c>
-      <c r="B13" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>37</v>
-      </c>
-      <c r="C13" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D13" s="13" cm="1">
-        <f t="array" aca="1" ref="D13" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A13,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="12">
-        <v>46157</v>
-      </c>
-      <c r="B14" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>32</v>
-      </c>
-      <c r="C14" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D14" s="13" cm="1">
-        <f t="array" aca="1" ref="D14" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A14,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="12">
-        <v>46158</v>
-      </c>
-      <c r="B15" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>37</v>
-      </c>
-      <c r="C15" s="13">
-        <f t="shared" ca="1" si="2"/>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="20"/>
+      <c r="B24" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>1865</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>1866</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>1867</v>
+      </c>
+      <c r="F24" s="21">
         <v>3</v>
       </c>
-      <c r="D15" s="13" cm="1">
-        <f t="array" aca="1" ref="D15" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A15,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>2</v>
-      </c>
-      <c r="E15" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="12">
-        <v>46160</v>
-      </c>
-      <c r="B16" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>39</v>
-      </c>
-      <c r="C16" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="D16" s="13" cm="1">
-        <f t="array" aca="1" ref="D16" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A16,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="12">
-        <v>46161</v>
-      </c>
-      <c r="B17" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>27</v>
-      </c>
-      <c r="C17" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D17" s="13" cm="1">
-        <f t="array" aca="1" ref="D17" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A17,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="12">
-        <v>46162</v>
-      </c>
-      <c r="B18" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>31</v>
-      </c>
-      <c r="C18" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="D18" s="13" cm="1">
-        <f t="array" aca="1" ref="D18" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A18,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+      <c r="G24" s="21">
+        <v>0</v>
+      </c>
+      <c r="H24" s="21">
+        <v>25</v>
+      </c>
+      <c r="I24" s="21">
+        <f>G24-H24</f>
+        <v>-25</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20">
+        <v>1</v>
+      </c>
+      <c r="R24" s="15">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>953</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>1874</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>1875</v>
+      </c>
+      <c r="F25" s="21">
+        <v>5</v>
+      </c>
+      <c r="G25" s="21">
+        <v>0</v>
+      </c>
+      <c r="H25" s="21">
+        <v>25</v>
+      </c>
+      <c r="I25" s="21">
+        <f>G25-H25</f>
+        <v>-25</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K25" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20">
+        <v>1</v>
+      </c>
+      <c r="R25" s="15">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="20"/>
+      <c r="B26" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>1877</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>1878</v>
+      </c>
+      <c r="F26" s="21">
         <v>3</v>
       </c>
-      <c r="E18" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="12">
-        <v>46163</v>
-      </c>
-      <c r="B19" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="C19" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D19" s="13" cm="1">
-        <f t="array" aca="1" ref="D19" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A19,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>1</v>
-      </c>
-      <c r="E19" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="12">
-        <v>46164</v>
-      </c>
-      <c r="B20" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C20" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D20" s="13" cm="1">
-        <f t="array" aca="1" ref="D20" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A20,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="12">
-        <v>46165</v>
-      </c>
-      <c r="B21" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C21" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D21" s="13" cm="1">
-        <f t="array" aca="1" ref="D21" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A21,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="12">
-        <v>46167</v>
-      </c>
-      <c r="B22" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C22" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D22" s="13" cm="1">
-        <f t="array" aca="1" ref="D22" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A22,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E22" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="12">
-        <v>46168</v>
-      </c>
-      <c r="B23" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C23" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D23" s="13" cm="1">
-        <f t="array" aca="1" ref="D23" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A23,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="12">
-        <v>46169</v>
-      </c>
-      <c r="B24" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C24" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D24" s="13" cm="1">
-        <f t="array" aca="1" ref="D24" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A24,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="12">
-        <v>46170</v>
-      </c>
-      <c r="B25" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C25" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D25" s="13" cm="1">
-        <f t="array" aca="1" ref="D25" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A25,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="12">
-        <v>46171</v>
-      </c>
-      <c r="B26" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C26" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D26" s="13" cm="1">
-        <f t="array" aca="1" ref="D26" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A26,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="12">
-        <v>46172</v>
-      </c>
-      <c r="B27" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C27" s="13">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D27" s="13" cm="1">
-        <f t="array" aca="1" ref="D27" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A27,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D28" s="14" t="s">
-        <v>1666</v>
-      </c>
-      <c r="E28" s="14">
-        <f ca="1">SUBTOTAL(9,E4:E27)</f>
-        <v>540</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D29" s="14" t="s">
-        <v>1667</v>
-      </c>
-      <c r="E29" s="14" cm="1">
-        <f t="array" ref="E29" ca="1">SUMPRODUCT(
-    IFERROR(
-        SUMIF(
-            INDIRECT("'"&amp;TEXT(A4:A27,"dd-mm")&amp;"'!O:O"),
-            "tổng",
-            INDIRECT("'"&amp;TEXT(A4:A27,"dd-mm")&amp;"'!P:P")
-        ),
-    0)
-)</f>
-        <v>2228</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D30" s="14" t="s">
-        <v>1668</v>
-      </c>
-      <c r="E30" s="14">
-        <f ca="1">-E28*2</f>
-        <v>-1080</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D31" s="14" t="s">
-        <v>1669</v>
-      </c>
-      <c r="E31" s="14">
-        <f ca="1">SUBTOTAL(9,E29:E30)</f>
-        <v>1148</v>
+      <c r="G26" s="21">
+        <v>845</v>
+      </c>
+      <c r="H26" s="21">
+        <v>25</v>
+      </c>
+      <c r="I26" s="21">
+        <f>G26-H26</f>
+        <v>820</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K26" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="20"/>
+      <c r="B27" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>1880</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>1881</v>
+      </c>
+      <c r="F27" s="21">
+        <v>1</v>
+      </c>
+      <c r="G27" s="21">
+        <v>0</v>
+      </c>
+      <c r="H27" s="21">
+        <v>25</v>
+      </c>
+      <c r="I27" s="21">
+        <f>G27-H27</f>
+        <v>-25</v>
+      </c>
+      <c r="J27" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K27" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20">
+        <v>1</v>
+      </c>
+      <c r="R27" s="15">
+        <f t="shared" ref="R27:R28" si="2">H27</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="20"/>
+      <c r="B28" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>1884</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>1885</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>1886</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G28" s="21">
+        <v>0</v>
+      </c>
+      <c r="H28" s="21">
+        <v>25</v>
+      </c>
+      <c r="I28" s="21">
+        <f>G28-H28</f>
+        <v>-25</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K28" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>1842</v>
+      </c>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20">
+        <v>1</v>
+      </c>
+      <c r="R28" s="15">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D30" s="6">
+        <f>COUNTA(D3:D28)</f>
+        <v>22</v>
+      </c>
+      <c r="G30" s="6">
+        <f t="shared" ref="G30:Q30" si="3">SUBTOTAL(9,G3:G28)</f>
+        <v>13780</v>
+      </c>
+      <c r="H30" s="6">
+        <f t="shared" si="3"/>
+        <v>705</v>
+      </c>
+      <c r="I30" s="6">
+        <f t="shared" si="3"/>
+        <v>13075</v>
+      </c>
+      <c r="J30" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M30" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N30" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O30" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P30" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="6">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H31">
+        <f>-4*17</f>
+        <v>-68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D32" s="5"/>
+      <c r="E32" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H32">
+        <f>-2*25</f>
+        <v>-50</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="O32" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C33" s="4">
+        <f>SUMIFS(I$3:I$28,B$3:B$28,A$32,L$3:L$28,A$33)</f>
+        <v>13075</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="8">
+        <f>SUMIFS(Q$3:Q$28,B$3:B$28,A$32,L$3:L$28,A$33)</f>
+        <v>26</v>
+      </c>
+      <c r="F33" t="s">
+        <v>196</v>
+      </c>
+      <c r="H33">
+        <f>-1*30</f>
+        <v>-30</v>
+      </c>
+      <c r="K33" t="s">
+        <v>197</v>
+      </c>
+      <c r="L33">
+        <f>SUMIFS(G$3:G$28,J$3:J$28,K$32)</f>
+        <v>2675</v>
+      </c>
+      <c r="M33">
+        <f>SUMIFS(Q$3:Q$28,J$3:J$28,K$32)-INT(COUNTIFS(J$3:J$28,K$32,M$3:M$28,"*gộp*")/2)</f>
+        <v>8</v>
+      </c>
+      <c r="O33" t="s">
+        <v>135</v>
+      </c>
+      <c r="P33">
+        <f>L38</f>
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B34" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C34" s="3">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3"/>
+      <c r="K34" t="s">
+        <v>200</v>
+      </c>
+      <c r="L34">
+        <f>-SUMIFS(H$3:H$28,J$3:J$28,K$32)+M34*5</f>
+        <v>-160</v>
+      </c>
+      <c r="M34">
+        <f>SUMIFS(Q$3:Q$28,J$3:J$28,K$32)-INT(COUNTIFS(J$3:J$28,K$32,M$3:M$28,"*gộp*")/2)</f>
+        <v>8</v>
+      </c>
+      <c r="O34" t="s">
+        <v>21</v>
+      </c>
+      <c r="P34">
+        <f>L46</f>
+        <v>4413</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B35" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C35" s="3">
+        <f>-SUMIFS(I$3:I$28,B$3:B$28,A$32,P$3:P$28,"xx",N$3:N$28,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="D35" s="3"/>
+      <c r="E35" s="7">
+        <f>SUMIFS(Q$3:Q$28,B$3:B$28,A$32,P$3:P$28,"xx",N$3:N$28,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="K35" t="s">
+        <v>202</v>
+      </c>
+      <c r="O35" t="s">
+        <v>1899</v>
+      </c>
+      <c r="P35">
+        <f>L54</f>
+        <v>6252</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B36" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C36" s="5">
+        <f>SUBTOTAL(9,C33:C35)</f>
+        <v>13075</v>
+      </c>
+      <c r="D36" s="5"/>
+      <c r="E36">
+        <f>E33</f>
+        <v>26</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="O36" t="s">
+        <v>207</v>
+      </c>
+      <c r="P36">
+        <f>-C40</f>
+        <v>-13075</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B37" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="K37" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O37" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P37" s="9">
+        <f>SUBTOTAL(9,P33:P36)</f>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B38" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="L38" s="18">
+        <f>SUBTOTAL(9,L33:L37)</f>
+        <v>2515</v>
+      </c>
+      <c r="M38" s="18">
+        <f>M33</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B40" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C40" s="1">
+        <f>C36+C37+C38</f>
+        <v>13075</v>
+      </c>
+      <c r="D40" s="1"/>
+      <c r="E40" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K41" t="s">
+        <v>197</v>
+      </c>
+      <c r="L41">
+        <f>SUMIFS(G$3:G$28,J$3:J$28,K$40)</f>
+        <v>4705</v>
+      </c>
+      <c r="M41">
+        <f>SUMIFS(Q$3:Q$28,J$3:J$28,K$40)-INT(COUNTIFS(J$3:J$28,K$40,M$3:M$28,"*gộp*")/2)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K42" t="s">
+        <v>200</v>
+      </c>
+      <c r="L42">
+        <f>-SUMIFS(H$3:H$28,J$3:J$28,K$40)+M42*5</f>
+        <v>-240</v>
+      </c>
+      <c r="M42">
+        <f>SUMIFS(Q$3:Q$28,J$3:J$28,K$40)-INT(COUNTIFS(J$3:J$28,K$40,M$3:M$28,"*gộp*")/2)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K43" t="s">
+        <v>202</v>
+      </c>
+      <c r="L43">
+        <f>-M43*2</f>
+        <v>-52</v>
+      </c>
+      <c r="M43">
+        <f>E36-(COUNTIFS(M$3:M$28,"*gộp*")/2)-COUNTIFS(M$3:M$28,"*đơn trả*")-COUNTIFS(M$3:M$28,"*hàng tỉnh*")</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K44" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K45" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L46" s="18">
+        <f>SUBTOTAL(9,L41:L45)</f>
+        <v>4413</v>
+      </c>
+      <c r="M46" s="18">
+        <f>M41</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K48" s="16" t="s">
+        <v>1847</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="49" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K49" t="s">
+        <v>197</v>
+      </c>
+      <c r="L49">
+        <f>SUMIFS(G$3:G$28,J$3:J$28,K$48)</f>
+        <v>6400</v>
+      </c>
+      <c r="M49">
+        <f>SUMIFS(Q$3:Q$28,J$3:J$28,K$48)-INT(COUNTIFS(J$3:J$28,K$48,M$3:M$28,"*gộp*")/2)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K50" t="s">
+        <v>200</v>
+      </c>
+      <c r="L50">
+        <f>SUM(H31:H33)</f>
+        <v>-148</v>
+      </c>
+      <c r="M50">
+        <f>SUMIFS(Q$3:Q$28,J$3:J$28,K$48)-INT(COUNTIFS(J$3:J$28,K$48,M$3:M$28,"*gộp*")/2)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K51" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="52" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K52" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="53" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K53" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="54" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L54" s="18">
+        <f>SUBTOTAL(9,L49:L53)</f>
+        <v>6252</v>
+      </c>
+      <c r="M54" s="18">
+        <f>M49</f>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E27" xr:uid="{00000000-0009-0000-0000-000010000000}"/>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C3:D27">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>C3&lt;&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <autoFilter ref="A2:P28" xr:uid="{00000000-0009-0000-0000-000013000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P28">
+      <sortCondition ref="J2:J28"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
 </file>
 
@@ -28138,6 +31447,630 @@
     <mergeCell ref="C34:D34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D9B982-EAEB-4F31-86BF-4D059AFDEA27}">
+  <sheetPr>
+    <tabColor rgb="FF0070C0"/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="10" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B1" s="10">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>1833</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="12">
+        <v>46143</v>
+      </c>
+      <c r="B3" s="13">
+        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A3,"dd-mm")&amp;"'!L3:L200"),TEXT(A3,"dd-mm")&amp;"-"&amp;B$1),0)</f>
+        <v>54</v>
+      </c>
+      <c r="C3" s="13">
+        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A3,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="13" cm="1">
+        <f t="array" ref="D3" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A3,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="13">
+        <f t="shared" ref="E3:E27" ca="1" si="0">B3-C3-D3</f>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="12">
+        <v>46146</v>
+      </c>
+      <c r="B4" s="13">
+        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A4,"dd-mm")&amp;"-"&amp;B$1),0)</f>
+        <v>20</v>
+      </c>
+      <c r="C4" s="13">
+        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="13" cm="1">
+        <f t="array" ref="D4" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>4</v>
+      </c>
+      <c r="E4" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="12">
+        <v>46147</v>
+      </c>
+      <c r="B5" s="13">
+        <f t="shared" ref="B5:B27" ca="1" si="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A5,"dd-mm")&amp;"'!L3:L200"),TEXT(A5,"dd-mm")&amp;"-"&amp;B$1),0)</f>
+        <v>53</v>
+      </c>
+      <c r="C5" s="13">
+        <f t="shared" ref="C5:C27" ca="1" si="2">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A5,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
+        <v>2</v>
+      </c>
+      <c r="D5" s="13" cm="1">
+        <f t="array" aca="1" ref="D5" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A5,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="12">
+        <v>46148</v>
+      </c>
+      <c r="B6" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="C6" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D6" s="13" cm="1">
+        <f t="array" aca="1" ref="D6" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A6,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
+        <v>46149</v>
+      </c>
+      <c r="B7" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="C7" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="D7" s="13" cm="1">
+        <f t="array" aca="1" ref="D7" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A7,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <v>46150</v>
+      </c>
+      <c r="B8" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="C8" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D8" s="13" cm="1">
+        <f t="array" aca="1" ref="D8" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A8,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="12">
+        <v>46151</v>
+      </c>
+      <c r="B9" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="C9" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D9" s="13" cm="1">
+        <f t="array" aca="1" ref="D9" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A9,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
+        <v>46153</v>
+      </c>
+      <c r="B10" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>56</v>
+      </c>
+      <c r="C10" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D10" s="13" cm="1">
+        <f t="array" aca="1" ref="D10" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A10,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>4</v>
+      </c>
+      <c r="E10" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="12">
+        <v>46154</v>
+      </c>
+      <c r="B11" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="C11" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D11" s="13" cm="1">
+        <f t="array" aca="1" ref="D11" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A11,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="12">
+        <v>46155</v>
+      </c>
+      <c r="B12" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="C12" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="D12" s="13" cm="1">
+        <f t="array" aca="1" ref="D12" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A12,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="12">
+        <v>46156</v>
+      </c>
+      <c r="B13" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="C13" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D13" s="13" cm="1">
+        <f t="array" aca="1" ref="D13" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A13,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="12">
+        <v>46157</v>
+      </c>
+      <c r="B14" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="C14" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D14" s="13" cm="1">
+        <f t="array" aca="1" ref="D14" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A14,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="12">
+        <v>46158</v>
+      </c>
+      <c r="B15" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="C15" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="D15" s="13" cm="1">
+        <f t="array" aca="1" ref="D15" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A15,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>2</v>
+      </c>
+      <c r="E15" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="12">
+        <v>46160</v>
+      </c>
+      <c r="B16" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="C16" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="D16" s="13" cm="1">
+        <f t="array" aca="1" ref="D16" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A16,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="12">
+        <v>46161</v>
+      </c>
+      <c r="B17" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="C17" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D17" s="13" cm="1">
+        <f t="array" aca="1" ref="D17" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A17,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="12">
+        <v>46162</v>
+      </c>
+      <c r="B18" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="C18" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="D18" s="13" cm="1">
+        <f t="array" aca="1" ref="D18" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A18,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>3</v>
+      </c>
+      <c r="E18" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="12">
+        <v>46163</v>
+      </c>
+      <c r="B19" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="C19" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D19" s="13" cm="1">
+        <f t="array" aca="1" ref="D19" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A19,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>1</v>
+      </c>
+      <c r="E19" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="12">
+        <v>46164</v>
+      </c>
+      <c r="B20" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="C20" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="D20" s="13" cm="1">
+        <f t="array" aca="1" ref="D20" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A20,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>1</v>
+      </c>
+      <c r="E20" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="12">
+        <v>46165</v>
+      </c>
+      <c r="B21" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="C21" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D21" s="13" cm="1">
+        <f t="array" aca="1" ref="D21" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A21,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="12">
+        <v>46167</v>
+      </c>
+      <c r="B22" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C22" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D22" s="13" cm="1">
+        <f t="array" aca="1" ref="D22" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A22,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="12">
+        <v>46168</v>
+      </c>
+      <c r="B23" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C23" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D23" s="13" cm="1">
+        <f t="array" aca="1" ref="D23" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A23,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="12">
+        <v>46169</v>
+      </c>
+      <c r="B24" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C24" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D24" s="13" cm="1">
+        <f t="array" aca="1" ref="D24" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A24,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="12">
+        <v>46170</v>
+      </c>
+      <c r="B25" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C25" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D25" s="13" cm="1">
+        <f t="array" aca="1" ref="D25" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A25,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="12">
+        <v>46171</v>
+      </c>
+      <c r="B26" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C26" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D26" s="13" cm="1">
+        <f t="array" aca="1" ref="D26" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A26,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="12">
+        <v>46172</v>
+      </c>
+      <c r="B27" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C27" s="13">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D27" s="13" cm="1">
+        <f t="array" aca="1" ref="D27" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A27,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D28" s="14" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E28" s="14">
+        <f ca="1">SUBTOTAL(9,E4:E27)</f>
+        <v>590</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D29" s="14" t="s">
+        <v>1836</v>
+      </c>
+      <c r="E29" s="14" cm="1">
+        <f t="array" ref="E29" ca="1">SUMPRODUCT(
+    IFERROR(
+        SUMIF(
+            INDIRECT("'"&amp;TEXT(A4:A27,"dd-mm")&amp;"'!O:O"),
+            "tổng",
+            INDIRECT("'"&amp;TEXT(A4:A27,"dd-mm")&amp;"'!P:P")
+        ),
+    0)
+)</f>
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D30" s="14" t="s">
+        <v>1837</v>
+      </c>
+      <c r="E30" s="14">
+        <f ca="1">-E28*2</f>
+        <v>-1180</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D31" s="14" t="s">
+        <v>1838</v>
+      </c>
+      <c r="E31" s="14">
+        <f ca="1">SUBTOTAL(9,E29:E30)</f>
+        <v>1247</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:E27" xr:uid="{00000000-0009-0000-0000-000012000000}"/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="C3:D27">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>C3&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data/May/InternalDailyReport_May.xlsx
+++ b/data/May/InternalDailyReport_May.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0DCD8D2-C8D5-41CF-B06C-E8B0E1A095DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9274F5FF-29D3-4AB1-A06F-8EEC7A242585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="7" r:id="rId1"/>
@@ -32,7 +32,10 @@
     <sheet name="21-05" sheetId="25" r:id="rId17"/>
     <sheet name="22-05" sheetId="26" r:id="rId18"/>
     <sheet name="23-05" sheetId="27" r:id="rId19"/>
-    <sheet name="Sheet1" sheetId="19" r:id="rId20"/>
+    <sheet name="25-05" sheetId="28" r:id="rId20"/>
+    <sheet name="26-05" sheetId="29" r:id="rId21"/>
+    <sheet name="27-05" sheetId="30" r:id="rId22"/>
+    <sheet name="Sheet1" sheetId="19" r:id="rId23"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01-05'!$A$2:$P$56</definedName>
@@ -54,7 +57,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'21-05'!$A$2:$P$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'22-05'!$A$2:$P$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'23-05'!$A$2:$P$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">Sheet1!$A$2:$E$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'25-05'!$A$2:$P$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'26-05'!$A$2:$P$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'27-05'!$A$2:$P$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">Sheet1!$A$2:$E$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -96,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6574" uniqueCount="1900">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7578" uniqueCount="2143">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -5585,6 +5591,741 @@
     <t>at 22-05</t>
   </si>
   <si>
+    <t>HD023055</t>
+  </si>
+  <si>
+    <t>AT 23-05</t>
+  </si>
+  <si>
+    <t>23-05-2026</t>
+  </si>
+  <si>
+    <t>HD023069</t>
+  </si>
+  <si>
+    <t>HD023108</t>
+  </si>
+  <si>
+    <t>41 Lê Quang Chiểu, Hiệp Tân</t>
+  </si>
+  <si>
+    <t>Lê Chi</t>
+  </si>
+  <si>
+    <t>HD023140</t>
+  </si>
+  <si>
+    <t>270 quốc lộ 50 p6</t>
+  </si>
+  <si>
+    <t>Cúc Phan</t>
+  </si>
+  <si>
+    <t>HD023112</t>
+  </si>
+  <si>
+    <t>A 12 liên ấp 1-2 vĩnh lộc b</t>
+  </si>
+  <si>
+    <t>HD023096</t>
+  </si>
+  <si>
+    <t>NGÂN HÀ</t>
+  </si>
+  <si>
+    <t>40 đường 53 p10</t>
+  </si>
+  <si>
+    <t>Bảo Như</t>
+  </si>
+  <si>
+    <t>HD023066</t>
+  </si>
+  <si>
+    <t>e208 nguyễn hữu cảnh p22 toà nhà landmark 3</t>
+  </si>
+  <si>
+    <t>HƯNG (hàng của Huyền Jendy)</t>
+  </si>
+  <si>
+    <t>HD023099</t>
+  </si>
+  <si>
+    <t>HD023121</t>
+  </si>
+  <si>
+    <t>624 Lê Thị Riêng, thới an</t>
+  </si>
+  <si>
+    <t>TONY ĐI ÚC</t>
+  </si>
+  <si>
+    <t>HD023116</t>
+  </si>
+  <si>
+    <t>965/16/11 QUANG TRUNG</t>
+  </si>
+  <si>
+    <t>HD022813</t>
+  </si>
+  <si>
+    <t>Ngọc Nhi</t>
+  </si>
+  <si>
+    <t>HD023141</t>
+  </si>
+  <si>
+    <t>92 nguyễn hữu cảnh p.22 (cc sg pearl toà sapphire 1)</t>
+  </si>
+  <si>
+    <t>HD023045</t>
+  </si>
+  <si>
+    <t>22/31/4 đường số 21, Phường 8 (phường Thông Tây Hội mới)</t>
+  </si>
+  <si>
+    <t>Trang Lê (note nhận đồ giúp chang)</t>
+  </si>
+  <si>
+    <t>HD023127</t>
+  </si>
+  <si>
+    <t>183/26 nguyễn hữu cảnh, f22</t>
+  </si>
+  <si>
+    <t>HÀ VY</t>
+  </si>
+  <si>
+    <t>482/10/26 nơ trang Long, p13</t>
+  </si>
+  <si>
+    <t>CAYLA</t>
+  </si>
+  <si>
+    <t>thanh (NHẬN HÀNG CHO TRÀ LY)</t>
+  </si>
+  <si>
+    <t>HD023142</t>
+  </si>
+  <si>
+    <t>404 VÕ VĂN TẦN</t>
+  </si>
+  <si>
+    <t>borameyyy</t>
+  </si>
+  <si>
+    <t>HD023106</t>
+  </si>
+  <si>
+    <t>Express M Village Nguyễn Du, Phòng 602</t>
+  </si>
+  <si>
+    <t>oanh fb Duong Tram</t>
+  </si>
+  <si>
+    <t>HD023118</t>
+  </si>
+  <si>
+    <t>346 bến vân đồn p1 Chung cư goldview a2</t>
+  </si>
+  <si>
+    <t>Trinh Trần</t>
+  </si>
+  <si>
+    <t>HD022990</t>
+  </si>
+  <si>
+    <t>22A truong dinh</t>
+  </si>
+  <si>
+    <t>HD023115</t>
+  </si>
+  <si>
+    <t>363 Hùng Vương, An Đông</t>
+  </si>
+  <si>
+    <t>Mai Chi</t>
+  </si>
+  <si>
+    <t>HD023061</t>
+  </si>
+  <si>
+    <t>215 nguyễn thị minh khai</t>
+  </si>
+  <si>
+    <t>Phương Trang</t>
+  </si>
+  <si>
+    <t>HD023132</t>
+  </si>
+  <si>
+    <t>189b/a29 công quỳnh phường nguyễn cư trinh</t>
+  </si>
+  <si>
+    <t>Như Ý Nguyễn</t>
+  </si>
+  <si>
+    <t>HD023113</t>
+  </si>
+  <si>
+    <t>24 Yên Thế, Phường 2</t>
+  </si>
+  <si>
+    <t>at 23-05</t>
+  </si>
+  <si>
+    <t>Trần Mai Phương</t>
+  </si>
+  <si>
+    <t>HD023562</t>
+  </si>
+  <si>
+    <t>442 Tô Ký- Tân Chánh Hiệp</t>
+  </si>
+  <si>
+    <t>AT 25-05</t>
+  </si>
+  <si>
+    <t>25-05-2026</t>
+  </si>
+  <si>
+    <t>HD023204</t>
+  </si>
+  <si>
+    <t>Phương Thảo TA</t>
+  </si>
+  <si>
+    <t>HD023551</t>
+  </si>
+  <si>
+    <t>HD022939</t>
+  </si>
+  <si>
+    <t>Chung cư aview KDC 13C ấp 5 xã phong phú</t>
+  </si>
+  <si>
+    <t>QP</t>
+  </si>
+  <si>
+    <t>HD021978</t>
+  </si>
+  <si>
+    <t>Số 28 KDC Nam Long, Thạnh Lộc</t>
+  </si>
+  <si>
+    <t>HD023578</t>
+  </si>
+  <si>
+    <t>Linh Phạm</t>
+  </si>
+  <si>
+    <t>HD023385</t>
+  </si>
+  <si>
+    <t>80/17 miếu gò xoài bình hưng hoà a</t>
+  </si>
+  <si>
+    <t>Thanh Hoài Hoàng</t>
+  </si>
+  <si>
+    <t>HD023530</t>
+  </si>
+  <si>
+    <t>7-9 Hải Thượng Lãn Ông, P chợ lớn</t>
+  </si>
+  <si>
+    <t>Minh Thoan</t>
+  </si>
+  <si>
+    <t>HD023208</t>
+  </si>
+  <si>
+    <t>195 tân hương p phú thọ hoà</t>
+  </si>
+  <si>
+    <t>Thanh Nhàn</t>
+  </si>
+  <si>
+    <t>HD023483</t>
+  </si>
+  <si>
+    <t>59 trần hưng đạo, p.tân thành</t>
+  </si>
+  <si>
+    <t>HD023291</t>
+  </si>
+  <si>
+    <t>Block d2, chung cư sài gòn riverside (số 4 đào trí, phú thuận)</t>
+  </si>
+  <si>
+    <t>Phương Anna</t>
+  </si>
+  <si>
+    <t>HD023553</t>
+  </si>
+  <si>
+    <t>258/77/2 dương bá trạc, P2</t>
+  </si>
+  <si>
+    <t>HD023457</t>
+  </si>
+  <si>
+    <t>Số 2 đường 75, khu phố 2, tân phong</t>
+  </si>
+  <si>
+    <t>HD022968</t>
+  </si>
+  <si>
+    <t>Gia Hue</t>
+  </si>
+  <si>
+    <t>HD023414</t>
+  </si>
+  <si>
+    <t>24 tân hoà đông p14</t>
+  </si>
+  <si>
+    <t>HD023330</t>
+  </si>
+  <si>
+    <t>Lê Nhật Tâm</t>
+  </si>
+  <si>
+    <t>HD023331</t>
+  </si>
+  <si>
+    <t>271 Mã Lò phường Bình Trị Đông</t>
+  </si>
+  <si>
+    <t>Phạm Tuyết</t>
+  </si>
+  <si>
+    <t>HD023561</t>
+  </si>
+  <si>
+    <t>Chung Cư Gia Phú (lô A),cuối Hẻm 219 đường Số 5, Khu Phố 7, Phường Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>Julia Julia</t>
+  </si>
+  <si>
+    <t>HD023227</t>
+  </si>
+  <si>
+    <t>lô z01-02-03a KCN trong KCX tân thuận, phường tân thuận đông</t>
+  </si>
+  <si>
+    <t>HD023565</t>
+  </si>
+  <si>
+    <t>Số 242, Tân Kỳ Tân Quý, Phường Tân Sơn Nhì</t>
+  </si>
+  <si>
+    <t>HD023334</t>
+  </si>
+  <si>
+    <t>0967000176</t>
+  </si>
+  <si>
+    <t>HD023380</t>
+  </si>
+  <si>
+    <t>8/5b đỗ văn dậy</t>
+  </si>
+  <si>
+    <t>NGỌC DIỆP - fb Jenny Uyên</t>
+  </si>
+  <si>
+    <t>HD023210</t>
+  </si>
+  <si>
+    <t>30 trịnh đình thảo chung cư trung đông plaza</t>
+  </si>
+  <si>
+    <t>Anna Nguyen</t>
+  </si>
+  <si>
+    <t>HD023476</t>
+  </si>
+  <si>
+    <t>12a Nguyễn hữu thọ Phước kiểng Cc the park resident tòa b5</t>
+  </si>
+  <si>
+    <t>HD023571</t>
+  </si>
+  <si>
+    <t>Scenic Valley 1, Cổng Số 2, Kdc Phú Mỹ Hưng, Phường Tân Phú</t>
+  </si>
+  <si>
+    <t>Nguyễn thị ánh ngọc</t>
+  </si>
+  <si>
+    <t>HD023541</t>
+  </si>
+  <si>
+    <t>B1805-B1806 block B ecogreen 39B nguyễn văn linh - tân thuận tây</t>
+  </si>
+  <si>
+    <t>(Tuấn) Nhận Dùm Xiaomei</t>
+  </si>
+  <si>
+    <t>HD023332</t>
+  </si>
+  <si>
+    <t>77/8/2 đường số 1, khu phố ông nhiêu, phường long trường</t>
+  </si>
+  <si>
+    <t>HD023484</t>
+  </si>
+  <si>
+    <t>Thơm Thơm</t>
+  </si>
+  <si>
+    <t>HD023336</t>
+  </si>
+  <si>
+    <t>119 nguyễn văn công p. Hạnh thông</t>
+  </si>
+  <si>
+    <t>Nguyễn Phùng Thảo Như - fb Karen Van</t>
+  </si>
+  <si>
+    <t>HD023580</t>
+  </si>
+  <si>
+    <t>799/2 Nguyễn kiệm p3</t>
+  </si>
+  <si>
+    <t>Khánh Ly</t>
+  </si>
+  <si>
+    <t>HD023225</t>
+  </si>
+  <si>
+    <t>67 Đg số 6, Kp4, phường Bình Trưng Tây</t>
+  </si>
+  <si>
+    <t>HD023568</t>
+  </si>
+  <si>
+    <t>Vũ Thị Hà</t>
+  </si>
+  <si>
+    <t>HD023340</t>
+  </si>
+  <si>
+    <t>20 Vũ Tông Phan, phường bình trưng</t>
+  </si>
+  <si>
+    <t>HD023455</t>
+  </si>
+  <si>
+    <t>433/11/2 Lê Đức Thọ, Phường Gò Vấp (phường 17 cũ)</t>
+  </si>
+  <si>
+    <t>HD023569</t>
+  </si>
+  <si>
+    <t>HD023507</t>
+  </si>
+  <si>
+    <t>Hồ Thanh Phương</t>
+  </si>
+  <si>
+    <t>HD023466</t>
+  </si>
+  <si>
+    <t>158/56/21 Phạm Văn Chiêu, phường 8</t>
+  </si>
+  <si>
+    <t>Hang</t>
+  </si>
+  <si>
+    <t>HD023317</t>
+  </si>
+  <si>
+    <t>75/2A nguyễn sỹ sách,p.15 cũ(tân sơn mới)</t>
+  </si>
+  <si>
+    <t>Hồng Vân</t>
+  </si>
+  <si>
+    <t>HD023071</t>
+  </si>
+  <si>
+    <t>233 đồng khởi phường sài gòn</t>
+  </si>
+  <si>
+    <t>HD023217</t>
+  </si>
+  <si>
+    <t>Em hồng thuỷ, hàng của chị AMyp</t>
+  </si>
+  <si>
+    <t>HD023235</t>
+  </si>
+  <si>
+    <t>38 Giải Phóng, phường 4</t>
+  </si>
+  <si>
+    <t>Zy Ka</t>
+  </si>
+  <si>
+    <t>HD023410</t>
+  </si>
+  <si>
+    <t>9 nguyễn trường tộ, p12</t>
+  </si>
+  <si>
+    <t>Chế Vân</t>
+  </si>
+  <si>
+    <t>HD023327</t>
+  </si>
+  <si>
+    <t>140b nguyễn văn trỗi p8</t>
+  </si>
+  <si>
+    <t>Tiger Nhỏ _ Gia Huy</t>
+  </si>
+  <si>
+    <t>HD023468</t>
+  </si>
+  <si>
+    <t>2/11 đường Thiên Phước, phường 9</t>
+  </si>
+  <si>
+    <t>HD023354</t>
+  </si>
+  <si>
+    <t>kh ck shop 2230k</t>
+  </si>
+  <si>
+    <t>Khuê</t>
+  </si>
+  <si>
+    <t>HD021688</t>
+  </si>
+  <si>
+    <t>38/9 thích quảng đức p15</t>
+  </si>
+  <si>
+    <t>HD023415</t>
+  </si>
+  <si>
+    <t>672 đường 3/2 P14</t>
+  </si>
+  <si>
+    <t>HD022967</t>
+  </si>
+  <si>
+    <t>Trần Thị Anh Đào</t>
+  </si>
+  <si>
+    <t>HD023440</t>
+  </si>
+  <si>
+    <t>333/35 Lý Thái Tổ, Phường 9</t>
+  </si>
+  <si>
+    <t>at 25-05</t>
+  </si>
+  <si>
+    <t>NGÂN KIM</t>
+  </si>
+  <si>
+    <t>T8-20 mahattan vinhomes grand park, phường long bình</t>
+  </si>
+  <si>
+    <t>26-05-2026</t>
+  </si>
+  <si>
+    <t>Kỳ Kỳ</t>
+  </si>
+  <si>
+    <t>HD023748</t>
+  </si>
+  <si>
+    <t>Trường Tiểu học Vinschool Grand Park, Vinhome Grand Park</t>
+  </si>
+  <si>
+    <t>AT 26-05</t>
+  </si>
+  <si>
+    <t>66 đường 17 p10</t>
+  </si>
+  <si>
+    <t>Minh Thư</t>
+  </si>
+  <si>
+    <t>HD023706</t>
+  </si>
+  <si>
+    <t>6/24 tân chánh hiệp 36, p trung mỹ tây</t>
+  </si>
+  <si>
+    <t>Trang Angels</t>
+  </si>
+  <si>
+    <t>HD023627</t>
+  </si>
+  <si>
+    <t>nhà 20 đường 2B phường Tân mỹ</t>
+  </si>
+  <si>
+    <t>Nhi Le</t>
+  </si>
+  <si>
+    <t>HD023579</t>
+  </si>
+  <si>
+    <t>743/11/10 hong bang p6</t>
+  </si>
+  <si>
+    <t>HDO1779701391142_472517</t>
+  </si>
+  <si>
+    <t>169/15 đường số 11 phường bình hưng hoà</t>
+  </si>
+  <si>
+    <t>HD023631</t>
+  </si>
+  <si>
+    <t>Huyền Trang Trần</t>
+  </si>
+  <si>
+    <t>HD023630</t>
+  </si>
+  <si>
+    <t>39/34 dạ nam</t>
+  </si>
+  <si>
+    <t>Annie Annie</t>
+  </si>
+  <si>
+    <t>HD023732</t>
+  </si>
+  <si>
+    <t>110 đường 14 Him Lam tân hưng</t>
+  </si>
+  <si>
+    <t>Linh Mỹ</t>
+  </si>
+  <si>
+    <t>HD023715</t>
+  </si>
+  <si>
+    <t>50/2/8 đường số 2, phường 3</t>
+  </si>
+  <si>
+    <t>이 우준</t>
+  </si>
+  <si>
+    <t>HD023636</t>
+  </si>
+  <si>
+    <t>Linh P Pham</t>
+  </si>
+  <si>
+    <t>HD023620</t>
+  </si>
+  <si>
+    <t>129/34 Nguyễn Văn Công, phường 3, Phường Gò Vấp</t>
+  </si>
+  <si>
+    <t>Thanh Thanh</t>
+  </si>
+  <si>
+    <t>HD023734</t>
+  </si>
+  <si>
+    <t>Cozrum Homes Premier Residences 135/4 Nguyễn Cửu Vân, P.Gia Định</t>
+  </si>
+  <si>
+    <t>Truc Le</t>
+  </si>
+  <si>
+    <t>HD023726</t>
+  </si>
+  <si>
+    <t>69 đường số 2 khu phố 1 p tam bình</t>
+  </si>
+  <si>
+    <t>Nguyen Minh Thu</t>
+  </si>
+  <si>
+    <t>HD023677</t>
+  </si>
+  <si>
+    <t>Số 2 đường số 51 p bình trưng đông</t>
+  </si>
+  <si>
+    <t>BN1356</t>
+  </si>
+  <si>
+    <t>HD023491</t>
+  </si>
+  <si>
+    <t>HD023733</t>
+  </si>
+  <si>
+    <t>32/11 Bùi Đình Tuý f12</t>
+  </si>
+  <si>
+    <t>NGUYÊN NGUYÊN</t>
+  </si>
+  <si>
+    <t>12 TÔN ĐẢN P13</t>
+  </si>
+  <si>
+    <t>Nga Nga</t>
+  </si>
+  <si>
+    <t>HD023717</t>
+  </si>
+  <si>
+    <t>29b Nguyễn đình chiểu dakao</t>
+  </si>
+  <si>
+    <t>Ngọc Thư</t>
+  </si>
+  <si>
+    <t>HD023656</t>
+  </si>
+  <si>
+    <t>400cd lê hồng phong p1</t>
+  </si>
+  <si>
+    <t>Kim ngân</t>
+  </si>
+  <si>
+    <t>HD023657</t>
+  </si>
+  <si>
+    <t>50 An Dương Vương,P.9</t>
+  </si>
+  <si>
+    <t>Thảo Ngân</t>
+  </si>
+  <si>
+    <t>HD023768</t>
+  </si>
+  <si>
+    <t>44/139 trần bình trọng</t>
+  </si>
+  <si>
+    <t>FB HOÀNG THỦY</t>
+  </si>
+  <si>
+    <t>HD023619</t>
+  </si>
+  <si>
+    <t>86/36/3 PHỔ QUANG TÂN SƠN HÒA</t>
+  </si>
+  <si>
+    <t>at 26-05</t>
+  </si>
+  <si>
     <t>THÁNG 5</t>
   </si>
   <si>
@@ -5615,187 +6356,181 @@
     <t>Lợi nhuận</t>
   </si>
   <si>
-    <t>thanh (NHẬN HÀNG CHO TRÀ LY)</t>
-  </si>
-  <si>
-    <t>HD023142</t>
-  </si>
-  <si>
-    <t>404 VÕ VĂN TẦN</t>
-  </si>
-  <si>
-    <t>23-05-2026</t>
-  </si>
-  <si>
-    <t>Bảo Như</t>
-  </si>
-  <si>
-    <t>HD023066</t>
-  </si>
-  <si>
-    <t>e208 nguyễn hữu cảnh p22 toà nhà landmark 3</t>
-  </si>
-  <si>
-    <t>HD023055</t>
-  </si>
-  <si>
-    <t>AT 23-05</t>
-  </si>
-  <si>
-    <t>HD023069</t>
-  </si>
-  <si>
-    <t>HƯNG (hàng của Huyền Jendy)</t>
-  </si>
-  <si>
-    <t>HD023099</t>
-  </si>
-  <si>
-    <t>borameyyy</t>
-  </si>
-  <si>
-    <t>HD023106</t>
-  </si>
-  <si>
-    <t>Express M Village Nguyễn Du, Phòng 602</t>
-  </si>
-  <si>
-    <t>oanh fb Duong Tram</t>
-  </si>
-  <si>
-    <t>HD023118</t>
-  </si>
-  <si>
-    <t>346 bến vân đồn p1 Chung cư goldview a2</t>
-  </si>
-  <si>
-    <t>HD023108</t>
-  </si>
-  <si>
-    <t>41 Lê Quang Chiểu, Hiệp Tân</t>
-  </si>
-  <si>
-    <t>HD023121</t>
-  </si>
-  <si>
-    <t>624 Lê Thị Riêng, thới an</t>
-  </si>
-  <si>
-    <t>TONY ĐI ÚC</t>
-  </si>
-  <si>
-    <t>HD023116</t>
-  </si>
-  <si>
-    <t>965/16/11 QUANG TRUNG</t>
-  </si>
-  <si>
-    <t>HD022813</t>
-  </si>
-  <si>
-    <t>Trinh Trần</t>
-  </si>
-  <si>
-    <t>HD022990</t>
-  </si>
-  <si>
-    <t>22A truong dinh</t>
-  </si>
-  <si>
-    <t>Lê Chi</t>
-  </si>
-  <si>
-    <t>HD023140</t>
-  </si>
-  <si>
-    <t>270 quốc lộ 50 p6</t>
-  </si>
-  <si>
-    <t>Ngọc Nhi</t>
-  </si>
-  <si>
-    <t>HD023141</t>
-  </si>
-  <si>
-    <t>92 nguyễn hữu cảnh p.22 (cc sg pearl toà sapphire 1)</t>
-  </si>
-  <si>
-    <t>HD023115</t>
-  </si>
-  <si>
-    <t>363 Hùng Vương, An Đông</t>
-  </si>
-  <si>
-    <t>Mai Chi</t>
-  </si>
-  <si>
-    <t>HD023061</t>
-  </si>
-  <si>
-    <t>215 nguyễn thị minh khai</t>
-  </si>
-  <si>
-    <t>Phương Trang</t>
-  </si>
-  <si>
-    <t>HD023132</t>
-  </si>
-  <si>
-    <t>189b/a29 công quỳnh phường nguyễn cư trinh</t>
-  </si>
-  <si>
-    <t>HD023045</t>
-  </si>
-  <si>
-    <t>22/31/4 đường số 21, Phường 8 (phường Thông Tây Hội mới)</t>
-  </si>
-  <si>
-    <t>Như Ý Nguyễn</t>
-  </si>
-  <si>
-    <t>HD023113</t>
-  </si>
-  <si>
-    <t>24 Yên Thế, Phường 2</t>
-  </si>
-  <si>
-    <t>Cúc Phan</t>
-  </si>
-  <si>
-    <t>HD023112</t>
-  </si>
-  <si>
-    <t>A 12 liên ấp 1-2 vĩnh lộc b</t>
-  </si>
-  <si>
-    <t>HD023096</t>
-  </si>
-  <si>
-    <t>Trang Lê (note nhận đồ giúp chang)</t>
-  </si>
-  <si>
-    <t>HD023127</t>
-  </si>
-  <si>
-    <t>183/26 nguyễn hữu cảnh, f22</t>
-  </si>
-  <si>
-    <t>NGÂN HÀ</t>
-  </si>
-  <si>
-    <t>40 đường 53 p10</t>
-  </si>
-  <si>
-    <t>HÀ VY</t>
-  </si>
-  <si>
-    <t>482/10/26 nơ trang Long, p13</t>
-  </si>
-  <si>
-    <t>CAYLA</t>
-  </si>
-  <si>
-    <t>at 23-05</t>
+    <t>Nhận hộ fb Nguyễn Hà</t>
+  </si>
+  <si>
+    <t>HD023711</t>
+  </si>
+  <si>
+    <t>27-05-2026</t>
+  </si>
+  <si>
+    <t>Thúy Nguyễn</t>
+  </si>
+  <si>
+    <t>HD023794</t>
+  </si>
+  <si>
+    <t>598/10 điện biên phủ, p.22</t>
+  </si>
+  <si>
+    <t>ng nhận QP</t>
+  </si>
+  <si>
+    <t>HD023827</t>
+  </si>
+  <si>
+    <t>số 28 khu kdc nam long thạnh lộc</t>
+  </si>
+  <si>
+    <t>HUYỀN NGUYỄN</t>
+  </si>
+  <si>
+    <t>HD023936</t>
+  </si>
+  <si>
+    <t>Số 8 Ba Vì, P4</t>
+  </si>
+  <si>
+    <t>Giang Phạm</t>
+  </si>
+  <si>
+    <t>HD023787</t>
+  </si>
+  <si>
+    <t>136 hoàng hoa thám, p7</t>
+  </si>
+  <si>
+    <t>HD023906</t>
+  </si>
+  <si>
+    <t>77-89 nam kỳ khởi nghĩa bến thành</t>
+  </si>
+  <si>
+    <t>KimVy Phương Anh</t>
+  </si>
+  <si>
+    <t>HD023841</t>
+  </si>
+  <si>
+    <t>214/B14A nguyễn trãi, cầu ông lãnh</t>
+  </si>
+  <si>
+    <t>HD023837</t>
+  </si>
+  <si>
+    <t>Can 32.07 - the Pegasuite 1- số 1002 tạ quang bửu, phường 5</t>
+  </si>
+  <si>
+    <t>AT 27-05</t>
+  </si>
+  <si>
+    <t>HD023572</t>
+  </si>
+  <si>
+    <t>HD023905</t>
+  </si>
+  <si>
+    <t>HD023917</t>
+  </si>
+  <si>
+    <t>195 tân hương P phú thọ hoà</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Ngọc Hân</t>
+  </si>
+  <si>
+    <t>HD023783</t>
+  </si>
+  <si>
+    <t>512 phạm thế hiển p4</t>
+  </si>
+  <si>
+    <t>W24130 Miki (Chou)</t>
+  </si>
+  <si>
+    <t>HD023903</t>
+  </si>
+  <si>
+    <t>624 Lê thị riêng, thới an</t>
+  </si>
+  <si>
+    <t>Thiên An</t>
+  </si>
+  <si>
+    <t>HD023884</t>
+  </si>
+  <si>
+    <t>D aqua 301 bình động, phú định</t>
+  </si>
+  <si>
+    <t>Thao Thanh Nguyen</t>
+  </si>
+  <si>
+    <t>HD023781</t>
+  </si>
+  <si>
+    <t>53 trần đình xu p cầu kho</t>
+  </si>
+  <si>
+    <t>S$3164-Mrskill)</t>
+  </si>
+  <si>
+    <t>HD022602</t>
+  </si>
+  <si>
+    <t>674 đường số 2, Phường 13</t>
+  </si>
+  <si>
+    <t>Khánh Như</t>
+  </si>
+  <si>
+    <t>HD023944</t>
+  </si>
+  <si>
+    <t>688/23/1c Hương Lộ 2, phường Bình Trị Đông A</t>
+  </si>
+  <si>
+    <t>GIA HUY nhận hộ ELIS NGUYỄN (singapore)</t>
+  </si>
+  <si>
+    <t>HD023838</t>
+  </si>
+  <si>
+    <t>Hoàng Trang</t>
+  </si>
+  <si>
+    <t>HD023850</t>
+  </si>
+  <si>
+    <t>1041/80/3/5 trần xuân soạn phường tân hưng</t>
+  </si>
+  <si>
+    <t>cô Loan fb Trịnh Trâm</t>
+  </si>
+  <si>
+    <t>HD023930</t>
+  </si>
+  <si>
+    <t>124/18/12 võ văn hát p long trường</t>
+  </si>
+  <si>
+    <t>NHƯ THẢO</t>
+  </si>
+  <si>
+    <t>259 đường 9a kdc Trung Sơn, Bình Hưng</t>
+  </si>
+  <si>
+    <t>Ellie Quach</t>
+  </si>
+  <si>
+    <t>8A Sông thương, Phường 2</t>
+  </si>
+  <si>
+    <t>SỈ HƯƠNG TRẦN</t>
+  </si>
+  <si>
+    <t>at 27-05</t>
   </si>
 </sst>
 </file>
@@ -5949,7 +6684,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -5995,6 +6730,7 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -28083,7 +28819,7 @@
         <v>-1585</v>
       </c>
       <c r="M56" s="28" t="s">
-        <v>288</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="57" spans="11:13" x14ac:dyDescent="0.25">
@@ -28200,7 +28936,7 @@
         <v>1611</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>1846</v>
+        <v>1829</v>
       </c>
       <c r="E3" s="22" t="s">
         <v>1613</v>
@@ -28215,17 +28951,17 @@
         <v>30</v>
       </c>
       <c r="I3" s="23">
-        <f>G3-H3</f>
+        <f t="shared" ref="I3:I28" si="0">G3-H3</f>
         <v>755</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>1847</v>
+        <v>1830</v>
       </c>
       <c r="K3" s="22" t="s">
         <v>21</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M3" s="22" t="s">
         <v>126</v>
@@ -28246,7 +28982,7 @@
         <v>53</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>1848</v>
+        <v>1832</v>
       </c>
       <c r="E4" s="20" t="s">
         <v>55</v>
@@ -28261,17 +28997,17 @@
         <v>30</v>
       </c>
       <c r="I4" s="21">
-        <f>G4-H4</f>
+        <f t="shared" si="0"/>
         <v>1520</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>1847</v>
+        <v>1830</v>
       </c>
       <c r="K4" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L4" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M4" s="20"/>
       <c r="N4" s="20"/>
@@ -28290,10 +29026,10 @@
         <v>837</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>1857</v>
+        <v>1833</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>1858</v>
+        <v>1834</v>
       </c>
       <c r="F5" s="20" t="s">
         <v>46</v>
@@ -28305,17 +29041,17 @@
         <v>25</v>
       </c>
       <c r="I5" s="21">
-        <f>G5-H5</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J5" s="20" t="s">
-        <v>1847</v>
+        <v>1830</v>
       </c>
       <c r="K5" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L5" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M5" s="20"/>
       <c r="N5" s="20"/>
@@ -28335,13 +29071,13 @@
         <v>17</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>1868</v>
+        <v>1835</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>1869</v>
+        <v>1836</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>1870</v>
+        <v>1837</v>
       </c>
       <c r="F6" s="21">
         <v>8</v>
@@ -28353,17 +29089,17 @@
         <v>30</v>
       </c>
       <c r="I6" s="21">
-        <f>G6-H6</f>
+        <f t="shared" si="0"/>
         <v>790</v>
       </c>
       <c r="J6" s="20" t="s">
-        <v>1847</v>
+        <v>1830</v>
       </c>
       <c r="K6" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M6" s="20"/>
       <c r="N6" s="20"/>
@@ -28379,13 +29115,13 @@
         <v>17</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>1887</v>
+        <v>1838</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>1888</v>
+        <v>1839</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>1889</v>
+        <v>1840</v>
       </c>
       <c r="F7" s="20" t="s">
         <v>139</v>
@@ -28397,17 +29133,17 @@
         <v>35</v>
       </c>
       <c r="I7" s="21">
-        <f>G7-H7</f>
+        <f t="shared" si="0"/>
         <v>990</v>
       </c>
       <c r="J7" s="20" t="s">
-        <v>1847</v>
+        <v>1830</v>
       </c>
       <c r="K7" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L7" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M7" s="20"/>
       <c r="N7" s="20"/>
@@ -28426,7 +29162,7 @@
         <v>1784</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>1890</v>
+        <v>1841</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>1786</v>
@@ -28441,17 +29177,17 @@
         <v>30</v>
       </c>
       <c r="I8" s="21">
-        <f>G8-H8</f>
+        <f t="shared" si="0"/>
         <v>790</v>
       </c>
       <c r="J8" s="20" t="s">
-        <v>1847</v>
+        <v>1830</v>
       </c>
       <c r="K8" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L8" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M8" s="25" t="s">
         <v>167</v>
@@ -28475,11 +29211,11 @@
         <v>17</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>1894</v>
+        <v>1842</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20" t="s">
-        <v>1895</v>
+        <v>1843</v>
       </c>
       <c r="F9" s="21">
         <v>6</v>
@@ -28491,17 +29227,17 @@
         <v>30</v>
       </c>
       <c r="I9" s="21">
-        <f>G9-H9</f>
+        <f t="shared" si="0"/>
         <v>1370</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>1847</v>
+        <v>1830</v>
       </c>
       <c r="K9" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L9" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M9" s="20"/>
       <c r="N9" s="20"/>
@@ -28517,13 +29253,13 @@
         <v>17</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="F10" s="20" t="s">
         <v>85</v>
@@ -28535,7 +29271,7 @@
         <v>20</v>
       </c>
       <c r="I10" s="21">
-        <f>G10-H10</f>
+        <f t="shared" si="0"/>
         <v>790</v>
       </c>
       <c r="J10" s="20" t="s">
@@ -28545,7 +29281,7 @@
         <v>21</v>
       </c>
       <c r="L10" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M10" s="20"/>
       <c r="N10" s="20"/>
@@ -28561,10 +29297,10 @@
         <v>17</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="E11" s="20" t="s">
         <v>1737</v>
@@ -28579,7 +29315,7 @@
         <v>25</v>
       </c>
       <c r="I11" s="21">
-        <f>G11-H11</f>
+        <f t="shared" si="0"/>
         <v>820</v>
       </c>
       <c r="J11" s="20" t="s">
@@ -28589,7 +29325,7 @@
         <v>21</v>
       </c>
       <c r="L11" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M11" s="20"/>
       <c r="N11" s="20"/>
@@ -28608,10 +29344,10 @@
         <v>40</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>1859</v>
+        <v>1849</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>1860</v>
+        <v>1850</v>
       </c>
       <c r="F12" s="21">
         <v>12</v>
@@ -28623,7 +29359,7 @@
         <v>30</v>
       </c>
       <c r="I12" s="21">
-        <f>G12-H12</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J12" s="20" t="s">
@@ -28633,7 +29369,7 @@
         <v>21</v>
       </c>
       <c r="L12" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M12" s="20"/>
       <c r="N12" s="20"/>
@@ -28643,7 +29379,7 @@
         <v>1</v>
       </c>
       <c r="R12" s="15">
-        <f t="shared" ref="R12:R13" si="0">H12</f>
+        <f>H12</f>
         <v>30</v>
       </c>
     </row>
@@ -28653,13 +29389,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>1861</v>
+        <v>1851</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>1862</v>
+        <v>1852</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>1863</v>
+        <v>1853</v>
       </c>
       <c r="F13" s="20" t="s">
         <v>77</v>
@@ -28671,7 +29407,7 @@
         <v>30</v>
       </c>
       <c r="I13" s="21">
-        <f>G13-H13</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J13" s="20" t="s">
@@ -28681,7 +29417,7 @@
         <v>21</v>
       </c>
       <c r="L13" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M13" s="20"/>
       <c r="N13" s="20"/>
@@ -28691,7 +29427,7 @@
         <v>1</v>
       </c>
       <c r="R13" s="15">
-        <f t="shared" si="0"/>
+        <f>H13</f>
         <v>30</v>
       </c>
     </row>
@@ -28704,7 +29440,7 @@
         <v>1391</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>1864</v>
+        <v>1854</v>
       </c>
       <c r="E14" s="20" t="s">
         <v>1393</v>
@@ -28719,7 +29455,7 @@
         <v>30</v>
       </c>
       <c r="I14" s="21">
-        <f>G14-H14</f>
+        <f t="shared" si="0"/>
         <v>890</v>
       </c>
       <c r="J14" s="20" t="s">
@@ -28729,7 +29465,7 @@
         <v>21</v>
       </c>
       <c r="L14" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M14" s="20"/>
       <c r="N14" s="20"/>
@@ -28745,13 +29481,13 @@
         <v>17</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>1871</v>
+        <v>1855</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>1872</v>
+        <v>1856</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>1873</v>
+        <v>1857</v>
       </c>
       <c r="F15" s="20" t="s">
         <v>85</v>
@@ -28763,7 +29499,7 @@
         <v>20</v>
       </c>
       <c r="I15" s="21">
-        <f>G15-H15</f>
+        <f t="shared" si="0"/>
         <v>480</v>
       </c>
       <c r="J15" s="20" t="s">
@@ -28773,7 +29509,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M15" s="20"/>
       <c r="N15" s="20"/>
@@ -28792,10 +29528,10 @@
         <v>1802</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>1882</v>
+        <v>1858</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>1883</v>
+        <v>1859</v>
       </c>
       <c r="F16" s="22" t="s">
         <v>77</v>
@@ -28807,7 +29543,7 @@
         <v>25</v>
       </c>
       <c r="I16" s="23">
-        <f>G16-H16</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J16" s="22" t="s">
@@ -28817,7 +29553,7 @@
         <v>21</v>
       </c>
       <c r="L16" s="22" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M16" s="22" t="s">
         <v>126</v>
@@ -28835,13 +29571,13 @@
         <v>17</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>1891</v>
+        <v>1860</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>1892</v>
+        <v>1861</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>1893</v>
+        <v>1862</v>
       </c>
       <c r="F17" s="20" t="s">
         <v>85</v>
@@ -28853,7 +29589,7 @@
         <v>20</v>
       </c>
       <c r="I17" s="21">
-        <f>G17-H17</f>
+        <f t="shared" si="0"/>
         <v>-20</v>
       </c>
       <c r="J17" s="20" t="s">
@@ -28863,7 +29599,7 @@
         <v>21</v>
       </c>
       <c r="L17" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M17" s="20"/>
       <c r="N17" s="20"/>
@@ -28901,7 +29637,7 @@
         <v>30</v>
       </c>
       <c r="I18" s="21">
-        <f>G18-H18</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J18" s="20" t="s">
@@ -28911,7 +29647,7 @@
         <v>21</v>
       </c>
       <c r="L18" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M18" s="20"/>
       <c r="N18" s="20"/>
@@ -28929,11 +29665,11 @@
         <v>17</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>1896</v>
+        <v>1863</v>
       </c>
       <c r="D19" s="20"/>
       <c r="E19" s="20" t="s">
-        <v>1897</v>
+        <v>1864</v>
       </c>
       <c r="F19" s="20" t="s">
         <v>85</v>
@@ -28945,7 +29681,7 @@
         <v>25</v>
       </c>
       <c r="I19" s="21">
-        <f>G19-H19</f>
+        <f t="shared" si="0"/>
         <v>1550</v>
       </c>
       <c r="J19" s="20" t="s">
@@ -28955,7 +29691,7 @@
         <v>21</v>
       </c>
       <c r="L19" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M19" s="20"/>
       <c r="N19" s="20"/>
@@ -28973,7 +29709,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>1898</v>
+        <v>1865</v>
       </c>
       <c r="D20" s="20"/>
       <c r="E20" s="20" t="s">
@@ -28989,7 +29725,7 @@
         <v>40</v>
       </c>
       <c r="I20" s="21">
-        <f>G20-H20</f>
+        <f t="shared" si="0"/>
         <v>-40</v>
       </c>
       <c r="J20" s="20" t="s">
@@ -28999,7 +29735,7 @@
         <v>21</v>
       </c>
       <c r="L20" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M20" s="20"/>
       <c r="N20" s="20"/>
@@ -29009,7 +29745,7 @@
         <v>1</v>
       </c>
       <c r="R20" s="15">
-        <f>H20</f>
+        <f t="shared" ref="R20:R25" si="1">H20</f>
         <v>40</v>
       </c>
     </row>
@@ -29019,13 +29755,13 @@
         <v>17</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>1839</v>
+        <v>1866</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>1840</v>
+        <v>1867</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>1841</v>
+        <v>1868</v>
       </c>
       <c r="F21" s="21">
         <v>3</v>
@@ -29037,7 +29773,7 @@
         <v>25</v>
       </c>
       <c r="I21" s="21">
-        <f>G21-H21</f>
+        <f t="shared" si="0"/>
         <v>1805</v>
       </c>
       <c r="J21" s="20" t="s">
@@ -29047,7 +29783,7 @@
         <v>21</v>
       </c>
       <c r="L21" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M21" s="25" t="s">
         <v>167</v>
@@ -29059,7 +29795,7 @@
         <v>1</v>
       </c>
       <c r="R21" s="15">
-        <f>H21</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
     </row>
@@ -29069,13 +29805,13 @@
         <v>17</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>1851</v>
+        <v>1869</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>1852</v>
+        <v>1870</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>1853</v>
+        <v>1871</v>
       </c>
       <c r="F22" s="21">
         <v>1</v>
@@ -29087,7 +29823,7 @@
         <v>25</v>
       </c>
       <c r="I22" s="21">
-        <f>G22-H22</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J22" s="20" t="s">
@@ -29097,7 +29833,7 @@
         <v>21</v>
       </c>
       <c r="L22" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M22" s="20"/>
       <c r="N22" s="20"/>
@@ -29107,7 +29843,7 @@
         <v>1</v>
       </c>
       <c r="R22" s="15">
-        <f t="shared" ref="R22:R25" si="1">H22</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
     </row>
@@ -29117,13 +29853,13 @@
         <v>17</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>1854</v>
+        <v>1872</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>1855</v>
+        <v>1873</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>1856</v>
+        <v>1874</v>
       </c>
       <c r="F23" s="21">
         <v>4</v>
@@ -29135,7 +29871,7 @@
         <v>25</v>
       </c>
       <c r="I23" s="21">
-        <f>G23-H23</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J23" s="20" t="s">
@@ -29145,7 +29881,7 @@
         <v>21</v>
       </c>
       <c r="L23" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M23" s="20"/>
       <c r="N23" s="20"/>
@@ -29165,13 +29901,13 @@
         <v>17</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>1865</v>
+        <v>1875</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>1866</v>
+        <v>1876</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="F24" s="21">
         <v>3</v>
@@ -29183,7 +29919,7 @@
         <v>25</v>
       </c>
       <c r="I24" s="21">
-        <f>G24-H24</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J24" s="20" t="s">
@@ -29193,7 +29929,7 @@
         <v>21</v>
       </c>
       <c r="L24" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M24" s="20"/>
       <c r="N24" s="20"/>
@@ -29216,10 +29952,10 @@
         <v>953</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>1874</v>
+        <v>1878</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>1875</v>
+        <v>1879</v>
       </c>
       <c r="F25" s="21">
         <v>5</v>
@@ -29231,7 +29967,7 @@
         <v>25</v>
       </c>
       <c r="I25" s="21">
-        <f>G25-H25</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J25" s="20" t="s">
@@ -29241,7 +29977,7 @@
         <v>21</v>
       </c>
       <c r="L25" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M25" s="20"/>
       <c r="N25" s="20"/>
@@ -29261,13 +29997,13 @@
         <v>17</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>1876</v>
+        <v>1880</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>1877</v>
+        <v>1881</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>1878</v>
+        <v>1882</v>
       </c>
       <c r="F26" s="21">
         <v>3</v>
@@ -29279,7 +30015,7 @@
         <v>25</v>
       </c>
       <c r="I26" s="21">
-        <f>G26-H26</f>
+        <f t="shared" si="0"/>
         <v>820</v>
       </c>
       <c r="J26" s="20" t="s">
@@ -29289,7 +30025,7 @@
         <v>21</v>
       </c>
       <c r="L26" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M26" s="20"/>
       <c r="N26" s="20"/>
@@ -29305,13 +30041,13 @@
         <v>17</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>1879</v>
+        <v>1883</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>1880</v>
+        <v>1884</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>1881</v>
+        <v>1885</v>
       </c>
       <c r="F27" s="21">
         <v>1</v>
@@ -29323,7 +30059,7 @@
         <v>25</v>
       </c>
       <c r="I27" s="21">
-        <f>G27-H27</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J27" s="20" t="s">
@@ -29333,7 +30069,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M27" s="20"/>
       <c r="N27" s="20"/>
@@ -29343,7 +30079,7 @@
         <v>1</v>
       </c>
       <c r="R27" s="15">
-        <f t="shared" ref="R27:R28" si="2">H27</f>
+        <f>H27</f>
         <v>25</v>
       </c>
     </row>
@@ -29353,13 +30089,13 @@
         <v>17</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>1884</v>
+        <v>1886</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>1885</v>
+        <v>1887</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
       <c r="F28" s="20" t="s">
         <v>95</v>
@@ -29371,7 +30107,7 @@
         <v>25</v>
       </c>
       <c r="I28" s="21">
-        <f>G28-H28</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J28" s="20" t="s">
@@ -29381,7 +30117,7 @@
         <v>21</v>
       </c>
       <c r="L28" s="20" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="M28" s="20"/>
       <c r="N28" s="20"/>
@@ -29391,7 +30127,7 @@
         <v>1</v>
       </c>
       <c r="R28" s="15">
-        <f t="shared" si="2"/>
+        <f>H28</f>
         <v>25</v>
       </c>
     </row>
@@ -29401,47 +30137,47 @@
         <v>22</v>
       </c>
       <c r="G30" s="6">
-        <f t="shared" ref="G30:Q30" si="3">SUBTOTAL(9,G3:G28)</f>
+        <f t="shared" ref="G30:Q30" si="2">SUBTOTAL(9,G3:G28)</f>
         <v>13780</v>
       </c>
       <c r="H30" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>705</v>
       </c>
       <c r="I30" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>13075</v>
       </c>
       <c r="J30" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K30" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L30" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M30" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N30" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O30" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P30" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q30" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
     </row>
@@ -29481,7 +30217,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>195</v>
@@ -29565,7 +30301,7 @@
         <v>202</v>
       </c>
       <c r="O35" t="s">
-        <v>1899</v>
+        <v>1889</v>
       </c>
       <c r="P35">
         <f>L54</f>
@@ -29711,7 +30447,7 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K48" s="16" t="s">
-        <v>1847</v>
+        <v>1830</v>
       </c>
       <c r="L48" s="16" t="s">
         <v>193</v>
@@ -29772,7 +30508,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P28" xr:uid="{00000000-0009-0000-0000-000013000000}">
+  <autoFilter ref="A2:P28" xr:uid="{00000000-0009-0000-0000-000012000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P28">
       <sortCondition ref="J2:J28"/>
     </sortState>
@@ -31451,6 +32187,6276 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
+  <dimension ref="A2:Q81"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="77.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="20"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>1892</v>
+      </c>
+      <c r="F3" s="21">
+        <v>12</v>
+      </c>
+      <c r="G3" s="21">
+        <v>820</v>
+      </c>
+      <c r="H3" s="21">
+        <v>30</v>
+      </c>
+      <c r="I3" s="21">
+        <f t="shared" ref="I3:I34" si="0">G3-H3</f>
+        <v>790</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>1895</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="F4" s="21">
+        <v>7</v>
+      </c>
+      <c r="G4" s="21">
+        <v>470</v>
+      </c>
+      <c r="H4" s="21">
+        <v>30</v>
+      </c>
+      <c r="I4" s="21">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>1897</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="21">
+        <v>6</v>
+      </c>
+      <c r="G5" s="21">
+        <v>505</v>
+      </c>
+      <c r="H5" s="21">
+        <v>25</v>
+      </c>
+      <c r="I5" s="21">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>1898</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>1899</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="G6" s="21">
+        <v>5640</v>
+      </c>
+      <c r="H6" s="21">
+        <v>55</v>
+      </c>
+      <c r="I6" s="21">
+        <f t="shared" si="0"/>
+        <v>5585</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M6" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F7" s="21">
+        <v>12</v>
+      </c>
+      <c r="G7" s="21">
+        <v>0</v>
+      </c>
+      <c r="H7" s="21">
+        <v>30</v>
+      </c>
+      <c r="I7" s="21">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>1903</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F8" s="21">
+        <v>8</v>
+      </c>
+      <c r="G8" s="21">
+        <v>850</v>
+      </c>
+      <c r="H8" s="21">
+        <v>30</v>
+      </c>
+      <c r="I8" s="21">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>1904</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>1905</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>1906</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="21">
+        <v>690</v>
+      </c>
+      <c r="H9" s="21">
+        <v>30</v>
+      </c>
+      <c r="I9" s="21">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>1907</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>1908</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>1909</v>
+      </c>
+      <c r="F10" s="21">
+        <v>5</v>
+      </c>
+      <c r="G10" s="21">
+        <v>845</v>
+      </c>
+      <c r="H10" s="21">
+        <v>25</v>
+      </c>
+      <c r="I10" s="21">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>1910</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>1911</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>1912</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="21">
+        <v>465</v>
+      </c>
+      <c r="H11" s="21">
+        <v>25</v>
+      </c>
+      <c r="I11" s="21">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="20"/>
+      <c r="B12" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>1913</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>1914</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>1915</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="21">
+        <v>845</v>
+      </c>
+      <c r="H12" s="21">
+        <v>25</v>
+      </c>
+      <c r="I12" s="21">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J12" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>315</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>1916</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F13" s="21">
+        <v>7</v>
+      </c>
+      <c r="G13" s="21">
+        <v>990</v>
+      </c>
+      <c r="H13" s="21">
+        <v>30</v>
+      </c>
+      <c r="I13" s="21">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>1918</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>1919</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>1920</v>
+      </c>
+      <c r="F14" s="21">
+        <v>8</v>
+      </c>
+      <c r="G14" s="21">
+        <v>1640</v>
+      </c>
+      <c r="H14" s="21">
+        <v>30</v>
+      </c>
+      <c r="I14" s="21">
+        <f t="shared" si="0"/>
+        <v>1610</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>745</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>1921</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>1922</v>
+      </c>
+      <c r="F15" s="21">
+        <v>7</v>
+      </c>
+      <c r="G15" s="21">
+        <v>1260</v>
+      </c>
+      <c r="H15" s="21">
+        <v>30</v>
+      </c>
+      <c r="I15" s="21">
+        <f t="shared" si="0"/>
+        <v>1230</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>1588</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>1590</v>
+      </c>
+      <c r="F16" s="21">
+        <v>6</v>
+      </c>
+      <c r="G16" s="21">
+        <v>1735</v>
+      </c>
+      <c r="H16" s="21">
+        <v>25</v>
+      </c>
+      <c r="I16" s="21">
+        <f t="shared" si="0"/>
+        <v>1710</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>1924</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>1925</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>1926</v>
+      </c>
+      <c r="F17" s="21">
+        <v>6</v>
+      </c>
+      <c r="G17" s="21">
+        <v>995</v>
+      </c>
+      <c r="H17" s="21">
+        <v>25</v>
+      </c>
+      <c r="I17" s="21">
+        <f t="shared" si="0"/>
+        <v>970</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>999</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>1927</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="21">
+        <v>470</v>
+      </c>
+      <c r="H18" s="21">
+        <v>30</v>
+      </c>
+      <c r="I18" s="21">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>1928</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>1929</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>1930</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="21">
+        <v>520</v>
+      </c>
+      <c r="H19" s="21">
+        <v>30</v>
+      </c>
+      <c r="I19" s="21">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>1931</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>1932</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>1933</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="21">
+        <v>0</v>
+      </c>
+      <c r="H20" s="21">
+        <v>30</v>
+      </c>
+      <c r="I20" s="21">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>1934</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>1935</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>1936</v>
+      </c>
+      <c r="F21" s="21">
+        <v>7</v>
+      </c>
+      <c r="G21" s="21">
+        <v>810</v>
+      </c>
+      <c r="H21" s="21">
+        <v>30</v>
+      </c>
+      <c r="I21" s="21">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>1937</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" s="21">
+        <v>795</v>
+      </c>
+      <c r="H22" s="21">
+        <v>25</v>
+      </c>
+      <c r="I22" s="21">
+        <f t="shared" si="0"/>
+        <v>770</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>657</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>1939</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>659</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" s="21">
+        <v>995</v>
+      </c>
+      <c r="H23" s="21">
+        <v>25</v>
+      </c>
+      <c r="I23" s="21">
+        <f t="shared" si="0"/>
+        <v>970</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="20"/>
+      <c r="B24" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="39" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>1942</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G24" s="21">
+        <v>865</v>
+      </c>
+      <c r="H24" s="21">
+        <v>35</v>
+      </c>
+      <c r="I24" s="21">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>1943</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>1944</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>1945</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G25" s="21">
+        <v>0</v>
+      </c>
+      <c r="H25" s="21">
+        <v>25</v>
+      </c>
+      <c r="I25" s="21">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K25" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" s="20"/>
+      <c r="B26" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>1946</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>1948</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="G26" s="21">
+        <v>2760</v>
+      </c>
+      <c r="H26" s="21">
+        <v>35</v>
+      </c>
+      <c r="I26" s="21">
+        <f t="shared" si="0"/>
+        <v>2725</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K26" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M26" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="20"/>
+      <c r="B27" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>610</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F27" s="21">
+        <v>7</v>
+      </c>
+      <c r="G27" s="21">
+        <v>820</v>
+      </c>
+      <c r="H27" s="21">
+        <v>30</v>
+      </c>
+      <c r="I27" s="21">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J27" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K27" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="20"/>
+      <c r="B28" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>1951</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>1952</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>1953</v>
+      </c>
+      <c r="F28" s="21">
+        <v>7</v>
+      </c>
+      <c r="G28" s="21">
+        <v>810</v>
+      </c>
+      <c r="H28" s="21">
+        <v>30</v>
+      </c>
+      <c r="I28" s="21">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K28" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>1955</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>1956</v>
+      </c>
+      <c r="F29" s="21">
+        <v>9</v>
+      </c>
+      <c r="G29" s="21">
+        <v>0</v>
+      </c>
+      <c r="H29" s="21">
+        <v>30</v>
+      </c>
+      <c r="I29" s="21">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J29" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K29" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>870</v>
+      </c>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20" t="s">
+        <v>632</v>
+      </c>
+      <c r="F30" s="21">
+        <v>6</v>
+      </c>
+      <c r="G30" s="21">
+        <v>0</v>
+      </c>
+      <c r="H30" s="21">
+        <v>30</v>
+      </c>
+      <c r="I30" s="21">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J30" s="20" t="s">
+        <v>1893</v>
+      </c>
+      <c r="K30" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>1546</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>1957</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>1548</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G31" s="21">
+        <v>0</v>
+      </c>
+      <c r="H31" s="21">
+        <v>20</v>
+      </c>
+      <c r="I31" s="21">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K31" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="20"/>
+      <c r="B32" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>1959</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G32" s="21">
+        <v>1855</v>
+      </c>
+      <c r="H32" s="21">
+        <v>25</v>
+      </c>
+      <c r="I32" s="21">
+        <f t="shared" si="0"/>
+        <v>1830</v>
+      </c>
+      <c r="J32" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K32" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" s="20"/>
+      <c r="B33" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>1962</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>1963</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G33" s="21">
+        <v>785</v>
+      </c>
+      <c r="H33" s="21">
+        <v>25</v>
+      </c>
+      <c r="I33" s="21">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="J33" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K33" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A34" s="20"/>
+      <c r="B34" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>1964</v>
+      </c>
+      <c r="D34" s="20" t="s">
+        <v>1965</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>1966</v>
+      </c>
+      <c r="F34" s="21">
+        <v>2</v>
+      </c>
+      <c r="G34" s="21">
+        <v>1110</v>
+      </c>
+      <c r="H34" s="21">
+        <v>30</v>
+      </c>
+      <c r="I34" s="21">
+        <f t="shared" si="0"/>
+        <v>1080</v>
+      </c>
+      <c r="J34" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K34" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M34" s="20"/>
+      <c r="N34" s="20"/>
+      <c r="O34" s="20"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" s="20"/>
+      <c r="B35" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>1967</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>1862</v>
+      </c>
+      <c r="F35" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G35" s="21">
+        <v>60</v>
+      </c>
+      <c r="H35" s="21">
+        <v>20</v>
+      </c>
+      <c r="I35" s="21">
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <v>40</v>
+      </c>
+      <c r="J35" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K35" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M35" s="20"/>
+      <c r="N35" s="20"/>
+      <c r="O35" s="20"/>
+      <c r="P35" s="20"/>
+      <c r="Q35" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A36" s="20"/>
+      <c r="B36" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>1968</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>1969</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F36" s="21">
+        <v>2</v>
+      </c>
+      <c r="G36" s="21">
+        <v>880</v>
+      </c>
+      <c r="H36" s="21">
+        <v>30</v>
+      </c>
+      <c r="I36" s="21">
+        <f t="shared" si="1"/>
+        <v>850</v>
+      </c>
+      <c r="J36" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K36" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M36" s="20"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
+      <c r="P36" s="20"/>
+      <c r="Q36" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A37" s="20"/>
+      <c r="B37" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>1971</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>1972</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G37" s="21">
+        <v>995</v>
+      </c>
+      <c r="H37" s="21">
+        <v>25</v>
+      </c>
+      <c r="I37" s="21">
+        <f t="shared" si="1"/>
+        <v>970</v>
+      </c>
+      <c r="J37" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K37" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M37" s="20"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="20"/>
+      <c r="P37" s="20"/>
+      <c r="Q37" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A38" s="20"/>
+      <c r="B38" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>871</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>1973</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>873</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G38" s="21">
+        <v>725</v>
+      </c>
+      <c r="H38" s="21">
+        <v>25</v>
+      </c>
+      <c r="I38" s="21">
+        <f t="shared" si="1"/>
+        <v>700</v>
+      </c>
+      <c r="J38" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K38" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L38" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M38" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="N38" s="20"/>
+      <c r="O38" s="20"/>
+      <c r="P38" s="20"/>
+      <c r="Q38" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" s="20"/>
+      <c r="B39" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>871</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>1974</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>873</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G39" s="21">
+        <v>850</v>
+      </c>
+      <c r="H39" s="21">
+        <v>0</v>
+      </c>
+      <c r="I39" s="21">
+        <f t="shared" si="1"/>
+        <v>850</v>
+      </c>
+      <c r="J39" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K39" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L39" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M39" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="N39" s="20"/>
+      <c r="O39" s="20"/>
+      <c r="P39" s="20"/>
+      <c r="Q39" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40" s="20"/>
+      <c r="B40" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>1975</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>1976</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>1977</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G40" s="21">
+        <v>845</v>
+      </c>
+      <c r="H40" s="21">
+        <v>25</v>
+      </c>
+      <c r="I40" s="21">
+        <f t="shared" si="1"/>
+        <v>820</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K40" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M40" s="20"/>
+      <c r="N40" s="20"/>
+      <c r="O40" s="20"/>
+      <c r="P40" s="20"/>
+      <c r="Q40" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41" s="20"/>
+      <c r="B41" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>1979</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>1980</v>
+      </c>
+      <c r="F41" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G41" s="21">
+        <v>715</v>
+      </c>
+      <c r="H41" s="21">
+        <v>25</v>
+      </c>
+      <c r="I41" s="21">
+        <f t="shared" si="1"/>
+        <v>690</v>
+      </c>
+      <c r="J41" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K41" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L41" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M41" s="20"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="20"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A42" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G42" s="21">
+        <v>2450</v>
+      </c>
+      <c r="H42" s="21">
+        <v>30</v>
+      </c>
+      <c r="I42" s="21">
+        <f t="shared" si="1"/>
+        <v>2420</v>
+      </c>
+      <c r="J42" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K42" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L42" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M42" s="20"/>
+      <c r="N42" s="20"/>
+      <c r="O42" s="20"/>
+      <c r="P42" s="20"/>
+      <c r="Q42" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20" t="s">
+        <v>1321</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G43" s="21">
+        <v>0</v>
+      </c>
+      <c r="H43" s="21">
+        <v>30</v>
+      </c>
+      <c r="I43" s="21">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J43" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K43" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L43" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M43" s="20"/>
+      <c r="N43" s="20"/>
+      <c r="O43" s="20"/>
+      <c r="P43" s="20"/>
+      <c r="Q43" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A44" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G44" s="21">
+        <v>370</v>
+      </c>
+      <c r="H44" s="21">
+        <v>30</v>
+      </c>
+      <c r="I44" s="21">
+        <f t="shared" si="1"/>
+        <v>340</v>
+      </c>
+      <c r="J44" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K44" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L44" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M44" s="20"/>
+      <c r="N44" s="20"/>
+      <c r="O44" s="20"/>
+      <c r="P44" s="20"/>
+      <c r="Q44" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A45" s="20"/>
+      <c r="B45" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D45" s="20" t="s">
+        <v>1982</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>1983</v>
+      </c>
+      <c r="F45" s="21">
+        <v>1</v>
+      </c>
+      <c r="G45" s="21">
+        <v>0</v>
+      </c>
+      <c r="H45" s="21">
+        <v>25</v>
+      </c>
+      <c r="I45" s="21">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J45" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K45" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L45" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M45" s="20"/>
+      <c r="N45" s="20"/>
+      <c r="O45" s="20"/>
+      <c r="P45" s="20"/>
+      <c r="Q45" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A46" s="20"/>
+      <c r="B46" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>1984</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>1279</v>
+      </c>
+      <c r="F46" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="G46" s="21">
+        <v>1100</v>
+      </c>
+      <c r="H46" s="21">
+        <v>20</v>
+      </c>
+      <c r="I46" s="21">
+        <f t="shared" si="1"/>
+        <v>1080</v>
+      </c>
+      <c r="J46" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K46" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L46" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M46" s="20"/>
+      <c r="N46" s="20"/>
+      <c r="O46" s="20"/>
+      <c r="P46" s="20"/>
+      <c r="Q46" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A47" s="20"/>
+      <c r="B47" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>1985</v>
+      </c>
+      <c r="D47" s="20" t="s">
+        <v>1986</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>1987</v>
+      </c>
+      <c r="F47" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G47" s="21">
+        <v>995</v>
+      </c>
+      <c r="H47" s="21">
+        <v>25</v>
+      </c>
+      <c r="I47" s="21">
+        <f t="shared" si="1"/>
+        <v>970</v>
+      </c>
+      <c r="J47" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K47" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L47" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M47" s="20"/>
+      <c r="N47" s="20"/>
+      <c r="O47" s="20"/>
+      <c r="P47" s="20"/>
+      <c r="Q47" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A48" s="20"/>
+      <c r="B48" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" s="20" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>1989</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>1990</v>
+      </c>
+      <c r="F48" s="21">
+        <v>4</v>
+      </c>
+      <c r="G48" s="21">
+        <v>845</v>
+      </c>
+      <c r="H48" s="21">
+        <v>25</v>
+      </c>
+      <c r="I48" s="21">
+        <f t="shared" si="1"/>
+        <v>820</v>
+      </c>
+      <c r="J48" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K48" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L48" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M48" s="20"/>
+      <c r="N48" s="20"/>
+      <c r="O48" s="20"/>
+      <c r="P48" s="20"/>
+      <c r="Q48" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A49" s="20"/>
+      <c r="B49" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D49" s="20" t="s">
+        <v>1992</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>1993</v>
+      </c>
+      <c r="F49" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="G49" s="21">
+        <v>1010</v>
+      </c>
+      <c r="H49" s="21">
+        <v>20</v>
+      </c>
+      <c r="I49" s="21">
+        <f t="shared" si="1"/>
+        <v>990</v>
+      </c>
+      <c r="J49" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K49" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L49" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M49" s="20"/>
+      <c r="N49" s="20"/>
+      <c r="O49" s="20"/>
+      <c r="P49" s="20"/>
+      <c r="Q49" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A50" s="20"/>
+      <c r="B50" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>1994</v>
+      </c>
+      <c r="D50" s="20" t="s">
+        <v>1995</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>1996</v>
+      </c>
+      <c r="F50" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G50" s="21">
+        <v>0</v>
+      </c>
+      <c r="H50" s="21">
+        <v>25</v>
+      </c>
+      <c r="I50" s="21">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J50" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K50" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L50" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M50" s="20"/>
+      <c r="N50" s="20"/>
+      <c r="O50" s="20"/>
+      <c r="P50" s="20"/>
+      <c r="Q50" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A51" s="20"/>
+      <c r="B51" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" s="20" t="s">
+        <v>1875</v>
+      </c>
+      <c r="D51" s="20" t="s">
+        <v>1997</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>1877</v>
+      </c>
+      <c r="F51" s="21">
+        <v>3</v>
+      </c>
+      <c r="G51" s="21">
+        <v>0</v>
+      </c>
+      <c r="H51" s="21">
+        <v>25</v>
+      </c>
+      <c r="I51" s="21">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J51" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K51" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L51" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M51" s="25" t="s">
+        <v>1998</v>
+      </c>
+      <c r="N51" s="20"/>
+      <c r="O51" s="20"/>
+      <c r="P51" s="20"/>
+      <c r="Q51" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A52" s="20"/>
+      <c r="B52" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" s="20" t="s">
+        <v>1999</v>
+      </c>
+      <c r="D52" s="20" t="s">
+        <v>2000</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>2001</v>
+      </c>
+      <c r="F52" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="G52" s="21">
+        <v>390</v>
+      </c>
+      <c r="H52" s="21">
+        <v>20</v>
+      </c>
+      <c r="I52" s="21">
+        <f t="shared" si="1"/>
+        <v>370</v>
+      </c>
+      <c r="J52" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K52" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L52" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M52" s="20"/>
+      <c r="N52" s="20"/>
+      <c r="O52" s="20"/>
+      <c r="P52" s="20"/>
+      <c r="Q52" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A53" s="20"/>
+      <c r="B53" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" s="20" t="s">
+        <v>721</v>
+      </c>
+      <c r="D53" s="20" t="s">
+        <v>2002</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>2003</v>
+      </c>
+      <c r="F53" s="21">
+        <v>10</v>
+      </c>
+      <c r="G53" s="21">
+        <v>845</v>
+      </c>
+      <c r="H53" s="21">
+        <v>25</v>
+      </c>
+      <c r="I53" s="21">
+        <f t="shared" si="1"/>
+        <v>820</v>
+      </c>
+      <c r="J53" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K53" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L53" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M53" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="N53" s="20"/>
+      <c r="O53" s="20"/>
+      <c r="P53" s="20"/>
+      <c r="Q53" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A54" s="20"/>
+      <c r="B54" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" s="20" t="s">
+        <v>721</v>
+      </c>
+      <c r="D54" s="20" t="s">
+        <v>2004</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>2003</v>
+      </c>
+      <c r="F54" s="21">
+        <v>10</v>
+      </c>
+      <c r="G54" s="21">
+        <v>770</v>
+      </c>
+      <c r="H54" s="21">
+        <v>0</v>
+      </c>
+      <c r="I54" s="21">
+        <f t="shared" si="1"/>
+        <v>770</v>
+      </c>
+      <c r="J54" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K54" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L54" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M54" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="N54" s="20"/>
+      <c r="O54" s="20"/>
+      <c r="P54" s="20"/>
+      <c r="Q54" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A55" s="20"/>
+      <c r="B55" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" s="20" t="s">
+        <v>2005</v>
+      </c>
+      <c r="D55" s="20" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E55" s="20" t="s">
+        <v>2007</v>
+      </c>
+      <c r="F55" s="21">
+        <v>10</v>
+      </c>
+      <c r="G55" s="21">
+        <v>465</v>
+      </c>
+      <c r="H55" s="21">
+        <v>25</v>
+      </c>
+      <c r="I55" s="21">
+        <f t="shared" si="1"/>
+        <v>440</v>
+      </c>
+      <c r="J55" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K55" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L55" s="20" t="s">
+        <v>1894</v>
+      </c>
+      <c r="M55" s="20"/>
+      <c r="N55" s="20"/>
+      <c r="O55" s="20"/>
+      <c r="P55" s="20"/>
+      <c r="Q55" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D57" s="6">
+        <f>COUNTA(D3:D55)</f>
+        <v>49</v>
+      </c>
+      <c r="G57" s="6">
+        <f t="shared" ref="G57:Q57" si="2">SUBTOTAL(9,G3:G55)</f>
+        <v>44655</v>
+      </c>
+      <c r="H57" s="6">
+        <f t="shared" si="2"/>
+        <v>1405</v>
+      </c>
+      <c r="I57" s="6">
+        <f t="shared" si="2"/>
+        <v>43250</v>
+      </c>
+      <c r="J57" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L57" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M57" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N57" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O57" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P57" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q57" s="6">
+        <f t="shared" si="2"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H58">
+        <f>-18*17</f>
+        <v>-306</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A59" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D59" s="5"/>
+      <c r="E59" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H59">
+        <f>-7*25</f>
+        <v>-175</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="O59" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>1894</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C60" s="4">
+        <f>SUMIFS(I$3:I$55,B$3:B$55,A$59,L$3:L$55,A$60)</f>
+        <v>43250</v>
+      </c>
+      <c r="D60" s="4"/>
+      <c r="E60" s="8">
+        <f>SUMIFS(Q$3:Q$55,B$3:B$55,A$59,L$3:L$55,A$60)</f>
+        <v>53</v>
+      </c>
+      <c r="F60" t="s">
+        <v>196</v>
+      </c>
+      <c r="H60">
+        <f>-3*30</f>
+        <v>-90</v>
+      </c>
+      <c r="K60" t="s">
+        <v>197</v>
+      </c>
+      <c r="L60">
+        <f>SUMIFS(G$3:G$55,J$3:J$55,K$59)</f>
+        <v>11640</v>
+      </c>
+      <c r="M60">
+        <f>SUMIFS(Q$3:Q$55,J$3:J$55,K$59)-INT(COUNTIFS(J$3:J$55,K$59,M$3:M$55,"*gộp*")/2)</f>
+        <v>13</v>
+      </c>
+      <c r="O60" t="s">
+        <v>21</v>
+      </c>
+      <c r="P60">
+        <f>L65</f>
+        <v>11263</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B61" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C61" s="3">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3"/>
+      <c r="K61" t="s">
+        <v>200</v>
+      </c>
+      <c r="L61">
+        <f>-SUMIFS(H$3:H$55,J$3:J$55,K$59)+M61*5</f>
+        <v>-275</v>
+      </c>
+      <c r="M61">
+        <f>SUMIFS(Q$3:Q$55,J$3:J$55,K$59)-INT(COUNTIFS(J$3:J$55,K$59,M$3:M$55,"*gộp*")/2)</f>
+        <v>13</v>
+      </c>
+      <c r="O61" t="s">
+        <v>135</v>
+      </c>
+      <c r="P61">
+        <f>L73</f>
+        <v>6235</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B62" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C62" s="3">
+        <f>-SUMIFS(I$3:I$55,B$3:B$55,A$59,P$3:P$55,"xx",N$3:N$55,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="3"/>
+      <c r="E62" s="7">
+        <f>SUMIFS(Q$3:Q$55,B$3:B$55,A$59,P$3:P$55,"xx",N$3:N$55,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="K62" t="s">
+        <v>202</v>
+      </c>
+      <c r="L62">
+        <f>-M62*2</f>
+        <v>-102</v>
+      </c>
+      <c r="M62">
+        <f>E63-(COUNTIFS(M$3:M$55,"*gộp*")/2)-COUNTIFS(M$3:M$55,"*đơn trả*")-COUNTIFS(M$3:M$55,"*hàng tỉnh*")</f>
+        <v>51</v>
+      </c>
+      <c r="O62" t="s">
+        <v>2008</v>
+      </c>
+      <c r="P62">
+        <f>L81</f>
+        <v>26024</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B63" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C63" s="5">
+        <f>SUBTOTAL(9,C60:C62)</f>
+        <v>43250</v>
+      </c>
+      <c r="D63" s="5"/>
+      <c r="E63">
+        <f>E60</f>
+        <v>53</v>
+      </c>
+      <c r="K63" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="O63" t="s">
+        <v>207</v>
+      </c>
+      <c r="P63">
+        <f>-C67</f>
+        <v>-43250</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B64" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="K64" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O64" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P64" s="9">
+        <f>SUBTOTAL(9,P60:P63)</f>
+        <v>272</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B65" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="L65" s="18">
+        <f>SUBTOTAL(9,L60:L64)</f>
+        <v>11263</v>
+      </c>
+      <c r="M65" s="18">
+        <f>M60</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B67" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C67" s="1">
+        <f>C63+C64+C65</f>
+        <v>43250</v>
+      </c>
+      <c r="D67" s="1"/>
+      <c r="E67" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K68" t="s">
+        <v>197</v>
+      </c>
+      <c r="L68">
+        <f>SUMIFS(G$3:G$55,J$3:J$55,K$67)</f>
+        <v>6420</v>
+      </c>
+      <c r="M68">
+        <f>SUMIFS(Q$3:Q$55,J$3:J$55,K$67)-INT(COUNTIFS(J$3:J$55,K$67,M$3:M$55,"*gộp*")/2)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K69" t="s">
+        <v>200</v>
+      </c>
+      <c r="L69">
+        <f>-SUMIFS(H$3:H$55,J$3:J$55,K$67)+M69*5</f>
+        <v>-185</v>
+      </c>
+      <c r="M69">
+        <f>SUMIFS(Q$3:Q$55,J$3:J$55,K$67)-INT(COUNTIFS(J$3:J$55,K$67,M$3:M$55,"*gộp*")/2)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K70" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K71" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K72" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="L73" s="18">
+        <f>SUBTOTAL(9,L68:L72)</f>
+        <v>6235</v>
+      </c>
+      <c r="M73" s="18">
+        <f>M68</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K75" s="16" t="s">
+        <v>1893</v>
+      </c>
+      <c r="L75" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M75" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K76" t="s">
+        <v>197</v>
+      </c>
+      <c r="L76">
+        <f>SUMIFS(G$3:G$55,J$3:J$55,K$75)</f>
+        <v>26595</v>
+      </c>
+      <c r="M76">
+        <f>SUMIFS(Q$3:Q$55,J$3:J$55,K$75)-INT(COUNTIFS(J$3:J$55,K$75,M$3:M$55,"*gộp*")/2)</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K77" t="s">
+        <v>200</v>
+      </c>
+      <c r="L77">
+        <f>SUM(H58:H60)</f>
+        <v>-571</v>
+      </c>
+      <c r="M77">
+        <f>SUMIFS(Q$3:Q$55,J$3:J$55,K$75)-INT(COUNTIFS(J$3:J$55,K$75,M$3:M$55,"*gộp*")/2)</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="78" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K78" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K79" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="80" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K80" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="81" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L81" s="18">
+        <f>SUBTOTAL(9,L76:L80)</f>
+        <v>26024</v>
+      </c>
+      <c r="M81" s="18">
+        <f>M76</f>
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P55" xr:uid="{00000000-0009-0000-0000-000013000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P55">
+      <sortCondition ref="J2:J55"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C63:D63"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
+  <dimension ref="A2:R65"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="34.5703125" customWidth="1"/>
+    <col min="4" max="4" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="19" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>2009</v>
+      </c>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20" t="s">
+        <v>2010</v>
+      </c>
+      <c r="F3" s="21">
+        <v>9</v>
+      </c>
+      <c r="G3" s="21">
+        <v>1545</v>
+      </c>
+      <c r="H3" s="21">
+        <v>35</v>
+      </c>
+      <c r="I3" s="21">
+        <f t="shared" ref="I3:I31" si="0">G3-H3</f>
+        <v>1510</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>2013</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>2014</v>
+      </c>
+      <c r="F4" s="21">
+        <v>9</v>
+      </c>
+      <c r="G4" s="21">
+        <v>880</v>
+      </c>
+      <c r="H4" s="21">
+        <v>30</v>
+      </c>
+      <c r="I4" s="21">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20" t="s">
+        <v>869</v>
+      </c>
+      <c r="F5" s="21">
+        <v>5</v>
+      </c>
+      <c r="G5" s="21">
+        <v>30</v>
+      </c>
+      <c r="H5" s="21">
+        <v>30</v>
+      </c>
+      <c r="I5" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>2015</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20" t="s">
+        <v>2016</v>
+      </c>
+      <c r="F6" s="21">
+        <v>6</v>
+      </c>
+      <c r="G6" s="21">
+        <v>0</v>
+      </c>
+      <c r="H6" s="21">
+        <v>30</v>
+      </c>
+      <c r="I6" s="21">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>2015</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20">
+        <v>1</v>
+      </c>
+      <c r="R6" s="15">
+        <f>H6</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>2018</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>2019</v>
+      </c>
+      <c r="F7" s="21">
+        <v>12</v>
+      </c>
+      <c r="G7" s="21">
+        <v>2270</v>
+      </c>
+      <c r="H7" s="21">
+        <v>30</v>
+      </c>
+      <c r="I7" s="21">
+        <f t="shared" si="0"/>
+        <v>2240</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>2015</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M7" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20">
+        <v>1</v>
+      </c>
+      <c r="R7" s="15">
+        <f>H7</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>2020</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>2021</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>2022</v>
+      </c>
+      <c r="F8" s="21">
+        <v>7</v>
+      </c>
+      <c r="G8" s="21">
+        <v>2110</v>
+      </c>
+      <c r="H8" s="21">
+        <v>30</v>
+      </c>
+      <c r="I8" s="21">
+        <f t="shared" si="0"/>
+        <v>2080</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>2015</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M8" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20">
+        <v>1</v>
+      </c>
+      <c r="R8" s="15">
+        <f>H8</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>2023</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>2024</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>2025</v>
+      </c>
+      <c r="F9" s="21">
+        <v>6</v>
+      </c>
+      <c r="G9" s="21">
+        <v>0</v>
+      </c>
+      <c r="H9" s="21">
+        <v>25</v>
+      </c>
+      <c r="I9" s="21">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>2015</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20">
+        <v>1</v>
+      </c>
+      <c r="R9" s="15">
+        <f>H9</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>2026</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>2027</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="21">
+        <v>380</v>
+      </c>
+      <c r="H10" s="21">
+        <v>30</v>
+      </c>
+      <c r="I10" s="21">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>2015</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>2028</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="F11" s="21">
+        <v>7</v>
+      </c>
+      <c r="G11" s="21">
+        <v>510</v>
+      </c>
+      <c r="H11" s="21">
+        <v>30</v>
+      </c>
+      <c r="I11" s="21">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>2015</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>2029</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>2030</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>2031</v>
+      </c>
+      <c r="F12" s="23">
+        <v>8</v>
+      </c>
+      <c r="G12" s="23">
+        <v>0</v>
+      </c>
+      <c r="H12" s="23">
+        <v>30</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>2015</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M12" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22">
+        <v>1</v>
+      </c>
+      <c r="R12" s="30">
+        <f>H12</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>2032</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>2033</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>2034</v>
+      </c>
+      <c r="F13" s="21">
+        <v>7</v>
+      </c>
+      <c r="G13" s="21">
+        <v>920</v>
+      </c>
+      <c r="H13" s="21">
+        <v>30</v>
+      </c>
+      <c r="I13" s="21">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>2015</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>2035</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>2036</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>2037</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="21">
+        <v>0</v>
+      </c>
+      <c r="H14" s="21">
+        <v>25</v>
+      </c>
+      <c r="I14" s="21">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20">
+        <v>1</v>
+      </c>
+      <c r="R14" s="15">
+        <f>H14</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>2039</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>1724</v>
+      </c>
+      <c r="F15" s="21">
+        <v>2</v>
+      </c>
+      <c r="G15" s="21">
+        <v>510</v>
+      </c>
+      <c r="H15" s="21">
+        <v>30</v>
+      </c>
+      <c r="I15" s="21">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>2040</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>2030</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" s="21">
+        <v>870</v>
+      </c>
+      <c r="H16" s="21">
+        <v>20</v>
+      </c>
+      <c r="I16" s="21">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>483</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>2041</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>2042</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="21">
+        <v>685</v>
+      </c>
+      <c r="H17" s="21">
+        <v>25</v>
+      </c>
+      <c r="I17" s="21">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>2043</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>2044</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" s="21">
+        <v>740</v>
+      </c>
+      <c r="H18" s="21">
+        <v>20</v>
+      </c>
+      <c r="I18" s="21">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" s="21">
+        <v>920</v>
+      </c>
+      <c r="H19" s="21">
+        <v>30</v>
+      </c>
+      <c r="I19" s="21">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>2051</v>
+      </c>
+      <c r="F20" s="21">
+        <v>2</v>
+      </c>
+      <c r="G20" s="21">
+        <v>2410</v>
+      </c>
+      <c r="H20" s="21">
+        <v>35</v>
+      </c>
+      <c r="I20" s="21">
+        <f t="shared" si="0"/>
+        <v>2375</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M20" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20">
+        <v>1</v>
+      </c>
+      <c r="R20" s="15">
+        <f>H20</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>2052</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="F21" s="21">
+        <v>12</v>
+      </c>
+      <c r="G21" s="21">
+        <v>0</v>
+      </c>
+      <c r="H21" s="21">
+        <v>30</v>
+      </c>
+      <c r="I21" s="21">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20">
+        <v>1</v>
+      </c>
+      <c r="R21" s="15">
+        <f>H21</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>2054</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>2055</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G22" s="21">
+        <v>890</v>
+      </c>
+      <c r="H22" s="21">
+        <v>20</v>
+      </c>
+      <c r="I22" s="21">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F23" s="21">
+        <v>4</v>
+      </c>
+      <c r="G23" s="21">
+        <v>30</v>
+      </c>
+      <c r="H23" s="21">
+        <v>30</v>
+      </c>
+      <c r="I23" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20" t="s">
+        <v>507</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="21">
+        <v>0</v>
+      </c>
+      <c r="H24" s="21">
+        <v>30</v>
+      </c>
+      <c r="I24" s="21">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20">
+        <v>1</v>
+      </c>
+      <c r="R24" s="15">
+        <f>H24</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>2058</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>2060</v>
+      </c>
+      <c r="F25" s="21">
+        <v>1</v>
+      </c>
+      <c r="G25" s="21">
+        <v>855</v>
+      </c>
+      <c r="H25" s="21">
+        <v>25</v>
+      </c>
+      <c r="I25" s="21">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K25" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="20"/>
+      <c r="B26" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>2061</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>2062</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>2063</v>
+      </c>
+      <c r="F26" s="21">
+        <v>10</v>
+      </c>
+      <c r="G26" s="21">
+        <v>1145</v>
+      </c>
+      <c r="H26" s="21">
+        <v>25</v>
+      </c>
+      <c r="I26" s="21">
+        <f t="shared" si="0"/>
+        <v>1120</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K26" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="20"/>
+      <c r="B27" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>2064</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>2065</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>2066</v>
+      </c>
+      <c r="F27" s="21">
+        <v>5</v>
+      </c>
+      <c r="G27" s="21">
+        <v>1015</v>
+      </c>
+      <c r="H27" s="21">
+        <v>25</v>
+      </c>
+      <c r="I27" s="21">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J27" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K27" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="20"/>
+      <c r="B28" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>2067</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>2068</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>2069</v>
+      </c>
+      <c r="F28" s="21">
+        <v>5</v>
+      </c>
+      <c r="G28" s="21">
+        <v>1115</v>
+      </c>
+      <c r="H28" s="21">
+        <v>25</v>
+      </c>
+      <c r="I28" s="21">
+        <f t="shared" si="0"/>
+        <v>1090</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K28" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>2070</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>2071</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>2072</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G29" s="21">
+        <v>0</v>
+      </c>
+      <c r="H29" s="21">
+        <v>25</v>
+      </c>
+      <c r="I29" s="21">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J29" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K29" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="20" t="s">
+        <v>2011</v>
+      </c>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20">
+        <v>1</v>
+      </c>
+      <c r="R29" s="15">
+        <f>H29</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="26"/>
+      <c r="B30" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>1740</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>1741</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>1742</v>
+      </c>
+      <c r="F30" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="G30" s="27">
+        <v>4400</v>
+      </c>
+      <c r="H30" s="27">
+        <v>35</v>
+      </c>
+      <c r="I30" s="27">
+        <f t="shared" si="0"/>
+        <v>4365</v>
+      </c>
+      <c r="J30" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="K30" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="26" t="s">
+        <v>1664</v>
+      </c>
+      <c r="M30" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="N30" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="O30" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="P30" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q30" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="26" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26" t="s">
+        <v>1445</v>
+      </c>
+      <c r="F31" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="G31" s="27">
+        <v>0</v>
+      </c>
+      <c r="H31" s="27">
+        <v>35</v>
+      </c>
+      <c r="I31" s="27">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J31" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="K31" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="26" t="s">
+        <v>1424</v>
+      </c>
+      <c r="M31" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="N31" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="O31" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="P31" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q31" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D33" s="6">
+        <f>COUNTA(D3:D31)</f>
+        <v>23</v>
+      </c>
+      <c r="G33" s="6">
+        <f t="shared" ref="G33:Q33" si="1">SUBTOTAL(9,G3:G31)</f>
+        <v>24230</v>
+      </c>
+      <c r="H33" s="6">
+        <f t="shared" si="1"/>
+        <v>820</v>
+      </c>
+      <c r="I33" s="6">
+        <f t="shared" si="1"/>
+        <v>23410</v>
+      </c>
+      <c r="J33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q33" s="6">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H34">
+        <f>-7*17</f>
+        <v>-119</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D35" s="5"/>
+      <c r="E35" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H35">
+        <f>-2*25</f>
+        <v>-50</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="O35" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C36" s="4">
+        <f>SUMIFS(I$3:I$31,B$3:B$31,A$35,L$3:L$31,A$36)</f>
+        <v>19080</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="8">
+        <f>SUMIFS(Q$3:Q$31,B$3:B$31,A$35,L$3:L$31,A$36)</f>
+        <v>27</v>
+      </c>
+      <c r="F36" t="s">
+        <v>196</v>
+      </c>
+      <c r="K36" t="s">
+        <v>197</v>
+      </c>
+      <c r="L36">
+        <f>SUMIFS(G$3:G$31,J$3:J$31,K$35)</f>
+        <v>4160</v>
+      </c>
+      <c r="M36">
+        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$35)-INT(COUNTIFS(J$3:J$31,K$35,M$3:M$31,"*gộp*")/2)</f>
+        <v>7</v>
+      </c>
+      <c r="O36" t="s">
+        <v>135</v>
+      </c>
+      <c r="P36">
+        <f>L41</f>
+        <v>-360</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B37" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C37" s="3">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3"/>
+      <c r="K37" t="s">
+        <v>200</v>
+      </c>
+      <c r="L37">
+        <f>-SUMIFS(H$3:H$31,J$3:J$31,K$35)+M37*5</f>
+        <v>-150</v>
+      </c>
+      <c r="M37">
+        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$35)-INT(COUNTIFS(J$3:J$31,K$35,M$3:M$31,"*gộp*")/2)</f>
+        <v>7</v>
+      </c>
+      <c r="O37" t="s">
+        <v>2073</v>
+      </c>
+      <c r="P37">
+        <f>L49</f>
+        <v>6081</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B38" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C38" s="3">
+        <f>-SUMIFS(I$3:I$31,B$3:B$31,A$35,P$3:P$31,"xx",N$3:N$31,"x")</f>
+        <v>-4330</v>
+      </c>
+      <c r="D38" s="3"/>
+      <c r="E38" s="7">
+        <f>SUMIFS(Q$3:Q$31,B$3:B$31,A$35,P$3:P$31,"xx",N$3:N$31,"x")</f>
+        <v>2</v>
+      </c>
+      <c r="K38" t="s">
+        <v>202</v>
+      </c>
+      <c r="O38" t="s">
+        <v>20</v>
+      </c>
+      <c r="P38">
+        <f>L57</f>
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B39" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C39" s="5">
+        <f>SUBTOTAL(9,C36:C38)</f>
+        <v>14750</v>
+      </c>
+      <c r="D39" s="5"/>
+      <c r="E39">
+        <f>E36</f>
+        <v>27</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="L39" s="28">
+        <v>-4370</v>
+      </c>
+      <c r="M39" s="28" t="s">
+        <v>288</v>
+      </c>
+      <c r="O39" t="s">
+        <v>21</v>
+      </c>
+      <c r="P39">
+        <f>L65</f>
+        <v>6785</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B40" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="K40" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O40" t="s">
+        <v>207</v>
+      </c>
+      <c r="P40">
+        <f>-C43</f>
+        <v>-14750</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B41" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="L41" s="18">
+        <f>SUBTOTAL(9,L36:L40)</f>
+        <v>-360</v>
+      </c>
+      <c r="M41" s="18">
+        <f>M36</f>
+        <v>7</v>
+      </c>
+      <c r="O41" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P41" s="9">
+        <f>SUBTOTAL(9,P36:P40)</f>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B43" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C43" s="1">
+        <f>C39+C40+C41</f>
+        <v>14750</v>
+      </c>
+      <c r="D43" s="1"/>
+      <c r="E43" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>2015</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K44" t="s">
+        <v>197</v>
+      </c>
+      <c r="L44">
+        <f>SUMIFS(G$3:G$31,J$3:J$31,K$43)</f>
+        <v>6220</v>
+      </c>
+      <c r="M44">
+        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$43)-INT(COUNTIFS(J$3:J$31,K$43,M$3:M$31,"*gộp*")/2)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K45" t="s">
+        <v>200</v>
+      </c>
+      <c r="L45">
+        <f>SUM(H34:H35)</f>
+        <v>-169</v>
+      </c>
+      <c r="M45">
+        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$43)-INT(COUNTIFS(J$3:J$31,K$43,M$3:M$31,"*gộp*")/2)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K46" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K47" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="L47" s="28">
+        <v>30</v>
+      </c>
+      <c r="M47" s="28" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K48" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="49" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L49" s="18">
+        <f>SUBTOTAL(9,L44:L48)</f>
+        <v>6081</v>
+      </c>
+      <c r="M49" s="18">
+        <f>M44</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K51" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="52" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K52" t="s">
+        <v>197</v>
+      </c>
+      <c r="L52">
+        <f>SUMIFS(G$3:G$31,J$3:J$31,K$51)</f>
+        <v>2425</v>
+      </c>
+      <c r="M52">
+        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$51)-INT(COUNTIFS(J$3:J$31,K$51,M$3:M$31,"*gộp*")/2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K53" t="s">
+        <v>200</v>
+      </c>
+      <c r="L53">
+        <f>-SUMIFS(H$3:H$31,J$3:J$31,K$51)+M53*5</f>
+        <v>-55</v>
+      </c>
+      <c r="M53">
+        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$51)-INT(COUNTIFS(J$3:J$31,K$51,M$3:M$31,"*gộp*")/2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K54" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="55" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K55" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="56" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K56" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="57" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L57" s="18">
+        <f>SUBTOTAL(9,L52:L56)</f>
+        <v>2370</v>
+      </c>
+      <c r="M57" s="18">
+        <f>M52</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K59" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="60" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K60" t="s">
+        <v>197</v>
+      </c>
+      <c r="L60">
+        <f>SUMIFS(G$3:G$31,J$3:J$31,K$59)</f>
+        <v>7025</v>
+      </c>
+      <c r="M60">
+        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$59)-INT(COUNTIFS(J$3:J$31,K$59,M$3:M$31,"*gộp*")/2)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K61" t="s">
+        <v>200</v>
+      </c>
+      <c r="L61">
+        <f>-SUMIFS(H$3:H$31,J$3:J$31,K$59)+M61*5</f>
+        <v>-190</v>
+      </c>
+      <c r="M61">
+        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$59)-INT(COUNTIFS(J$3:J$31,K$59,M$3:M$31,"*gộp*")/2)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K62" t="s">
+        <v>202</v>
+      </c>
+      <c r="L62">
+        <f>-M62*2</f>
+        <v>-50</v>
+      </c>
+      <c r="M62">
+        <f>E39-(COUNTIFS(M$3:M$31,"*gộp*")/2)-COUNTIFS(M$3:M$31,"*đơn trả*")-COUNTIFS(M$3:M$31,"*hàng tỉnh*")</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K63" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="64" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K64" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="65" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L65" s="18">
+        <f>SUBTOTAL(9,L60:L64)</f>
+        <v>6785</v>
+      </c>
+      <c r="M65" s="18">
+        <f>M60</f>
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P31" xr:uid="{00000000-0009-0000-0000-000014000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P31">
+      <sortCondition ref="J2:J31"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
+  <dimension ref="A2:R52"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="39" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="55.28515625" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="8.7109375" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="20"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>2104</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>2105</v>
+      </c>
+      <c r="F3" s="21">
+        <v>8</v>
+      </c>
+      <c r="G3" s="21">
+        <v>810</v>
+      </c>
+      <c r="H3" s="21">
+        <v>30</v>
+      </c>
+      <c r="I3" s="21">
+        <f>G3-H3</f>
+        <v>780</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>2106</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>2107</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>744</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="21">
+        <v>0</v>
+      </c>
+      <c r="H4" s="21">
+        <v>30</v>
+      </c>
+      <c r="I4" s="21">
+        <f>G4-H4</f>
+        <v>-30</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>2106</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20">
+        <v>1</v>
+      </c>
+      <c r="R4" s="15">
+        <f>H4</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>2108</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>1443</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="21">
+        <v>0</v>
+      </c>
+      <c r="H5" s="21">
+        <v>30</v>
+      </c>
+      <c r="I5" s="21">
+        <f>G5-H5</f>
+        <v>-30</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>2106</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20">
+        <v>1</v>
+      </c>
+      <c r="R5" s="15">
+        <f t="shared" ref="R5:R6" si="0">H5</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>1910</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>2109</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>2110</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="21">
+        <v>0</v>
+      </c>
+      <c r="H6" s="21">
+        <v>25</v>
+      </c>
+      <c r="I6" s="21">
+        <f>G6-H6</f>
+        <v>-25</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>2106</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20">
+        <v>1</v>
+      </c>
+      <c r="R6" s="15">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>2111</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="F7" s="21">
+        <v>8</v>
+      </c>
+      <c r="G7" s="21">
+        <v>470</v>
+      </c>
+      <c r="H7" s="21">
+        <v>30</v>
+      </c>
+      <c r="I7" s="21">
+        <f>G7-H7</f>
+        <v>440</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>2106</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>2119</v>
+      </c>
+      <c r="F8" s="23">
+        <v>8</v>
+      </c>
+      <c r="G8" s="23">
+        <v>740</v>
+      </c>
+      <c r="H8" s="23">
+        <v>30</v>
+      </c>
+      <c r="I8" s="23">
+        <f>G8-H8</f>
+        <v>710</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>2106</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M8" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>2123</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>2124</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>2125</v>
+      </c>
+      <c r="F9" s="21">
+        <v>6</v>
+      </c>
+      <c r="G9" s="21">
+        <v>0</v>
+      </c>
+      <c r="H9" s="21">
+        <v>25</v>
+      </c>
+      <c r="I9" s="21">
+        <f>G9-H9</f>
+        <v>-25</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>2106</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20">
+        <v>1</v>
+      </c>
+      <c r="R9" s="15">
+        <f>H9</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>2126</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>2127</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>2128</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="21">
+        <v>850</v>
+      </c>
+      <c r="H10" s="21">
+        <v>30</v>
+      </c>
+      <c r="I10" s="21">
+        <f>G10-H10</f>
+        <v>820</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>2106</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>2131</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>2132</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F11" s="21">
+        <v>7</v>
+      </c>
+      <c r="G11" s="21">
+        <v>820</v>
+      </c>
+      <c r="H11" s="21">
+        <v>30</v>
+      </c>
+      <c r="I11" s="21">
+        <f>G11-H11</f>
+        <v>790</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>2106</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="20"/>
+      <c r="B12" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>2135</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>2136</v>
+      </c>
+      <c r="F12" s="21">
+        <v>9</v>
+      </c>
+      <c r="G12" s="21">
+        <v>920</v>
+      </c>
+      <c r="H12" s="21">
+        <v>30</v>
+      </c>
+      <c r="I12" s="21">
+        <f>G12-H12</f>
+        <v>890</v>
+      </c>
+      <c r="J12" s="20" t="s">
+        <v>2106</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>2137</v>
+      </c>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20" t="s">
+        <v>2138</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="G13" s="21">
+        <v>700</v>
+      </c>
+      <c r="H13" s="21">
+        <v>40</v>
+      </c>
+      <c r="I13" s="21">
+        <f>G13-H13</f>
+        <v>660</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>2106</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>2084</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="21">
+        <v>1765</v>
+      </c>
+      <c r="H14" s="21">
+        <v>25</v>
+      </c>
+      <c r="I14" s="21">
+        <f>G14-H14</f>
+        <v>1740</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>2087</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>2089</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" s="21">
+        <v>940</v>
+      </c>
+      <c r="H15" s="21">
+        <v>20</v>
+      </c>
+      <c r="I15" s="21">
+        <f>G15-H15</f>
+        <v>920</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>2090</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>2092</v>
+      </c>
+      <c r="F16" s="21">
+        <v>12</v>
+      </c>
+      <c r="G16" s="21">
+        <v>0</v>
+      </c>
+      <c r="H16" s="21">
+        <v>30</v>
+      </c>
+      <c r="I16" s="21">
+        <f>G16-H16</f>
+        <v>-30</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20">
+        <v>1</v>
+      </c>
+      <c r="R16" s="15">
+        <f>H16</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>2097</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="21">
+        <v>680</v>
+      </c>
+      <c r="H17" s="21">
+        <v>20</v>
+      </c>
+      <c r="I17" s="21">
+        <f>G17-H17</f>
+        <v>660</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>2114</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>2116</v>
+      </c>
+      <c r="F18" s="21">
+        <v>12</v>
+      </c>
+      <c r="G18" s="21">
+        <v>0</v>
+      </c>
+      <c r="H18" s="21">
+        <v>30</v>
+      </c>
+      <c r="I18" s="21">
+        <f>G18-H18</f>
+        <v>-30</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20">
+        <v>1</v>
+      </c>
+      <c r="R18" s="15">
+        <f>H18</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20" t="s">
+        <v>910</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="21">
+        <v>735</v>
+      </c>
+      <c r="H19" s="21">
+        <v>25</v>
+      </c>
+      <c r="I19" s="21">
+        <f>G19-H19</f>
+        <v>710</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>2093</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>2094</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G20" s="21">
+        <v>310</v>
+      </c>
+      <c r="H20" s="21">
+        <v>25</v>
+      </c>
+      <c r="I20" s="21">
+        <f>G20-H20</f>
+        <v>285</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>570</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>2099</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>2100</v>
+      </c>
+      <c r="F21" s="21">
+        <v>1</v>
+      </c>
+      <c r="G21" s="21">
+        <v>805</v>
+      </c>
+      <c r="H21" s="21">
+        <v>25</v>
+      </c>
+      <c r="I21" s="21">
+        <f>G21-H21</f>
+        <v>780</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>2101</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>2102</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>2103</v>
+      </c>
+      <c r="F22" s="21">
+        <v>1</v>
+      </c>
+      <c r="G22" s="21">
+        <v>845</v>
+      </c>
+      <c r="H22" s="21">
+        <v>25</v>
+      </c>
+      <c r="I22" s="21">
+        <f>G22-H22</f>
+        <v>820</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>2120</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>2121</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>2122</v>
+      </c>
+      <c r="F23" s="21">
+        <v>1</v>
+      </c>
+      <c r="G23" s="21">
+        <v>845</v>
+      </c>
+      <c r="H23" s="21">
+        <v>25</v>
+      </c>
+      <c r="I23" s="21">
+        <f>G23-H23</f>
+        <v>820</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="20"/>
+      <c r="B24" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>2129</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>2130</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>1496</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="21">
+        <v>0</v>
+      </c>
+      <c r="H24" s="21">
+        <v>25</v>
+      </c>
+      <c r="I24" s="21">
+        <f>G24-H24</f>
+        <v>-25</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20">
+        <v>1</v>
+      </c>
+      <c r="R24" s="15">
+        <f t="shared" ref="R24:R26" si="1">H24</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20" t="s">
+        <v>507</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G25" s="21">
+        <v>0</v>
+      </c>
+      <c r="H25" s="21">
+        <v>30</v>
+      </c>
+      <c r="I25" s="21">
+        <f>G25-H25</f>
+        <v>-30</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K25" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20">
+        <v>1</v>
+      </c>
+      <c r="R25" s="15">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>2139</v>
+      </c>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20" t="s">
+        <v>2140</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G26" s="21">
+        <v>0</v>
+      </c>
+      <c r="H26" s="21">
+        <v>30</v>
+      </c>
+      <c r="I26" s="21">
+        <f>G26-H26</f>
+        <v>-30</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K26" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20">
+        <v>1</v>
+      </c>
+      <c r="R26" s="15">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D28" s="6">
+        <f>COUNTA(D3:D26)</f>
+        <v>20</v>
+      </c>
+      <c r="G28" s="6">
+        <f t="shared" ref="G28:Q28" si="2">SUBTOTAL(9,G3:G26)</f>
+        <v>12235</v>
+      </c>
+      <c r="H28" s="6">
+        <f t="shared" si="2"/>
+        <v>665</v>
+      </c>
+      <c r="I28" s="6">
+        <f t="shared" si="2"/>
+        <v>11570</v>
+      </c>
+      <c r="J28" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M28" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N28" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O28" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P28" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="6">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H29">
+        <f>-6*17</f>
+        <v>-102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D30" s="5"/>
+      <c r="E30" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H30">
+        <f>-4*25</f>
+        <v>-100</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="O30" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C31" s="4">
+        <f>SUMIFS(I$3:I$26,B$3:B$26,A$30,L$3:L$26,A$31)</f>
+        <v>11570</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="8">
+        <f>SUMIFS(Q$3:Q$26,B$3:B$26,A$30,L$3:L$26,A$31)</f>
+        <v>24</v>
+      </c>
+      <c r="F31" t="s">
+        <v>196</v>
+      </c>
+      <c r="H31">
+        <f>-1*30</f>
+        <v>-30</v>
+      </c>
+      <c r="K31" t="s">
+        <v>197</v>
+      </c>
+      <c r="L31">
+        <f>SUMIFS(G$3:G$26,J$3:J$26,K$30)</f>
+        <v>4120</v>
+      </c>
+      <c r="M31">
+        <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$30)-INT(COUNTIFS(J$3:J$26,K$30,M$3:M$26,"*gộp*")/2)</f>
+        <v>6</v>
+      </c>
+      <c r="O31" t="s">
+        <v>21</v>
+      </c>
+      <c r="P31">
+        <f>L36</f>
+        <v>3952</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B32" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C32" s="3">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="K32" t="s">
+        <v>200</v>
+      </c>
+      <c r="L32">
+        <f>-SUMIFS(H$3:H$26,J$3:J$26,K$30)+M32*5</f>
+        <v>-120</v>
+      </c>
+      <c r="M32">
+        <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$30)-INT(COUNTIFS(J$3:J$26,K$30,M$3:M$26,"*gộp*")/2)</f>
+        <v>6</v>
+      </c>
+      <c r="O32" t="s">
+        <v>135</v>
+      </c>
+      <c r="P32">
+        <f>L44</f>
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B33" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C33" s="3">
+        <f>-SUMIFS(I$3:I$26,B$3:B$26,A$30,P$3:P$26,"xx",N$3:N$26,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="3"/>
+      <c r="E33" s="7">
+        <f>SUMIFS(Q$3:Q$26,B$3:B$26,A$30,P$3:P$26,"xx",N$3:N$26,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
+        <v>202</v>
+      </c>
+      <c r="L33">
+        <f>-M33*2</f>
+        <v>-48</v>
+      </c>
+      <c r="M33">
+        <f>E34-(COUNTIFS(M$3:M$26,"*gộp*")/2)-COUNTIFS(M$3:M$26,"*đơn trả*")-COUNTIFS(M$3:M$26,"*hàng tỉnh*")</f>
+        <v>24</v>
+      </c>
+      <c r="O33" t="s">
+        <v>2142</v>
+      </c>
+      <c r="P33">
+        <f>L52</f>
+        <v>5078</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B34" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C34" s="5">
+        <f>SUBTOTAL(9,C31:C33)</f>
+        <v>11570</v>
+      </c>
+      <c r="D34" s="5"/>
+      <c r="E34">
+        <f>E31</f>
+        <v>24</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="O34" t="s">
+        <v>207</v>
+      </c>
+      <c r="P34">
+        <f>-C38</f>
+        <v>-11570</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B35" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="K35" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O35" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P35" s="9">
+        <f>SUBTOTAL(9,P31:P34)</f>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B36" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="L36" s="18">
+        <f>SUBTOTAL(9,L31:L35)</f>
+        <v>3952</v>
+      </c>
+      <c r="M36" s="18">
+        <f>M31</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B38" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C38" s="1">
+        <f>C34+C35+C36</f>
+        <v>11570</v>
+      </c>
+      <c r="D38" s="1"/>
+      <c r="E38" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K39" t="s">
+        <v>197</v>
+      </c>
+      <c r="L39">
+        <f>SUMIFS(G$3:G$26,J$3:J$26,K$38)</f>
+        <v>2805</v>
+      </c>
+      <c r="M39">
+        <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$38)-INT(COUNTIFS(J$3:J$26,K$38,M$3:M$26,"*gộp*")/2)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K40" t="s">
+        <v>200</v>
+      </c>
+      <c r="L40">
+        <f>-SUMIFS(H$3:H$26,J$3:J$26,K$38)+M40*5</f>
+        <v>-150</v>
+      </c>
+      <c r="M40">
+        <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$38)-INT(COUNTIFS(J$3:J$26,K$38,M$3:M$26,"*gộp*")/2)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K41" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K42" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K43" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="L44" s="18">
+        <f>SUBTOTAL(9,L39:L43)</f>
+        <v>2655</v>
+      </c>
+      <c r="M44" s="18">
+        <f>M39</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K46" s="16" t="s">
+        <v>2106</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K47" t="s">
+        <v>197</v>
+      </c>
+      <c r="L47">
+        <f>SUMIFS(G$3:G$26,J$3:J$26,K$46)</f>
+        <v>5310</v>
+      </c>
+      <c r="M47">
+        <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$46)-INT(COUNTIFS(J$3:J$26,K$46,M$3:M$26,"*gộp*")/2)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K48" t="s">
+        <v>200</v>
+      </c>
+      <c r="L48">
+        <f>SUM(H29:H31)</f>
+        <v>-232</v>
+      </c>
+      <c r="M48">
+        <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$46)-INT(COUNTIFS(J$3:J$26,K$46,M$3:M$26,"*gộp*")/2)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K49" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="50" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K50" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="51" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K51" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="52" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L52" s="18">
+        <f>SUBTOTAL(9,L47:L51)</f>
+        <v>5078</v>
+      </c>
+      <c r="M52" s="18">
+        <f>M47</f>
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P26" xr:uid="{00000000-0009-0000-0000-000016000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P26">
+      <sortCondition ref="J2:J26"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D9B982-EAEB-4F31-86BF-4D059AFDEA27}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
@@ -31469,7 +38475,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>1829</v>
+        <v>2074</v>
       </c>
       <c r="B1" s="10">
         <v>2026</v>
@@ -31477,19 +38483,19 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>1830</v>
+        <v>2075</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>1831</v>
+        <v>2076</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>1832</v>
+        <v>2077</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>1833</v>
+        <v>2078</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>1834</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -31518,15 +38524,15 @@
         <v>46146</v>
       </c>
       <c r="B4" s="13">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A4,"dd-mm")&amp;"-"&amp;B$1),0)</f>
+        <f t="shared" ref="B4:B27" ca="1" si="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A4,"dd-mm")&amp;"-"&amp;B$1),0)</f>
         <v>20</v>
       </c>
       <c r="C4" s="13">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
+        <f t="shared" ref="C4:C27" ca="1" si="2">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
         <v>0</v>
       </c>
       <c r="D4" s="13" cm="1">
-        <f t="array" ref="D4" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D4" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>4</v>
       </c>
       <c r="E4" s="13">
@@ -31539,11 +38545,11 @@
         <v>46147</v>
       </c>
       <c r="B5" s="13">
-        <f t="shared" ref="B5:B27" ca="1" si="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A5,"dd-mm")&amp;"'!L3:L200"),TEXT(A5,"dd-mm")&amp;"-"&amp;B$1),0)</f>
+        <f t="shared" ca="1" si="1"/>
         <v>53</v>
       </c>
       <c r="C5" s="13">
-        <f t="shared" ref="C5:C27" ca="1" si="2">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A5,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
+        <f t="shared" ca="1" si="2"/>
         <v>2</v>
       </c>
       <c r="D5" s="13" cm="1">
@@ -31897,11 +38903,11 @@
       </c>
       <c r="B22" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="C22" s="13">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22" s="13" cm="1">
         <f t="array" aca="1" ref="D22" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A22,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
@@ -31909,7 +38915,7 @@
       </c>
       <c r="E22" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -31918,7 +38924,7 @@
       </c>
       <c r="B23" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C23" s="13">
         <f t="shared" ca="1" si="2"/>
@@ -31926,11 +38932,11 @@
       </c>
       <c r="D23" s="13" cm="1">
         <f t="array" aca="1" ref="D23" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A23,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -31939,7 +38945,7 @@
       </c>
       <c r="B24" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C24" s="13">
         <f t="shared" ca="1" si="2"/>
@@ -31951,7 +38957,7 @@
       </c>
       <c r="E24" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -32019,16 +39025,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D28" s="14" t="s">
-        <v>1835</v>
+        <v>2080</v>
       </c>
       <c r="E28" s="14">
         <f ca="1">SUBTOTAL(9,E4:E27)</f>
-        <v>590</v>
+        <v>690</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D29" s="14" t="s">
-        <v>1836</v>
+        <v>2081</v>
       </c>
       <c r="E29" s="14" cm="1">
         <f t="array" ref="E29" ca="1">SUMPRODUCT(
@@ -32040,29 +39046,29 @@
         ),
     0)
 )</f>
-        <v>2427</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D30" s="14" t="s">
-        <v>1837</v>
+        <v>2082</v>
       </c>
       <c r="E30" s="14">
         <f ca="1">-E28*2</f>
-        <v>-1180</v>
+        <v>-1380</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D31" s="14" t="s">
-        <v>1838</v>
+        <v>2083</v>
       </c>
       <c r="E31" s="14">
         <f ca="1">SUBTOTAL(9,E29:E30)</f>
-        <v>1247</v>
+        <v>1560</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E27" xr:uid="{00000000-0009-0000-0000-000012000000}"/>
+  <autoFilter ref="A2:E27" xr:uid="{00000000-0009-0000-0000-000015000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C3:D27">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/data/May/InternalDailyReport_May.xlsx
+++ b/data/May/InternalDailyReport_May.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE7F174-5B7E-4039-95F5-19C83E682F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC58D0A-4972-4BA7-B7D5-B79F70F80CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,9 @@
     <sheet name="26-05" sheetId="29" r:id="rId21"/>
     <sheet name="27-05" sheetId="30" r:id="rId22"/>
     <sheet name="28-05" sheetId="31" r:id="rId23"/>
-    <sheet name="Sheet1" sheetId="19" r:id="rId24"/>
+    <sheet name="29-05" sheetId="32" r:id="rId24"/>
+    <sheet name="30-05" sheetId="33" r:id="rId25"/>
+    <sheet name="Sheet1" sheetId="19" r:id="rId26"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01-05'!$A$2:$P$56</definedName>
@@ -59,10 +61,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'22-05'!$A$2:$P$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'23-05'!$A$2:$P$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'25-05'!$A$2:$P$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'26-05'!$A$2:$P$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'26-05'!$A$2:$P$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'27-05'!$A$2:$P$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'28-05'!$A$2:$P$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">Sheet1!$A$2:$E$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'29-05'!$A$2:$P$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'30-05'!$A$2:$P$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">Sheet1!$A$2:$E$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -104,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7850" uniqueCount="2216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8343" uniqueCount="2353">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -6505,6 +6509,402 @@
     <t>at 27-05</t>
   </si>
   <si>
+    <t>Uyên Trần</t>
+  </si>
+  <si>
+    <t>HD024168</t>
+  </si>
+  <si>
+    <t>137/84D âu dương lân - p2</t>
+  </si>
+  <si>
+    <t>AT 28-05</t>
+  </si>
+  <si>
+    <t>28-05-2026</t>
+  </si>
+  <si>
+    <t>Thanh Vy</t>
+  </si>
+  <si>
+    <t>HD024163</t>
+  </si>
+  <si>
+    <t>20B Trần Văn Quang, Phường Bảy Hiền</t>
+  </si>
+  <si>
+    <t>Thủy Heri</t>
+  </si>
+  <si>
+    <t>HD024145</t>
+  </si>
+  <si>
+    <t>184/17/35 bãi sậy phường bình tiên</t>
+  </si>
+  <si>
+    <t>Ngân</t>
+  </si>
+  <si>
+    <t>HD023968</t>
+  </si>
+  <si>
+    <t>Toà A2 Alnata diamond đường N1 Tân Sơn Nhì</t>
+  </si>
+  <si>
+    <t>HD023918</t>
+  </si>
+  <si>
+    <t>Diễm Phúc</t>
+  </si>
+  <si>
+    <t>HD024175</t>
+  </si>
+  <si>
+    <t>314/138 đường âu dương lân, p3</t>
+  </si>
+  <si>
+    <t>khả trinh</t>
+  </si>
+  <si>
+    <t>HD024033</t>
+  </si>
+  <si>
+    <t>82/17/20đinh tiên hoàng p1</t>
+  </si>
+  <si>
+    <t>Linh fb Phan Thị Tuyết Nhung</t>
+  </si>
+  <si>
+    <t>HD023982</t>
+  </si>
+  <si>
+    <t>201 Đường Hoàng Hoa Thám, Phường 13</t>
+  </si>
+  <si>
+    <t>Nguyễn Châu Tuệ Lâm</t>
+  </si>
+  <si>
+    <t>HD024027</t>
+  </si>
+  <si>
+    <t>74/1h ds9 linh trung</t>
+  </si>
+  <si>
+    <t>HD024142</t>
+  </si>
+  <si>
+    <t>Nguyễn Trinh</t>
+  </si>
+  <si>
+    <t>HD024157</t>
+  </si>
+  <si>
+    <t>29/10c trần thái tông</t>
+  </si>
+  <si>
+    <t>Minh Thư nhận hộ ( water) fb Thuỷ Vũ</t>
+  </si>
+  <si>
+    <t>HD024179</t>
+  </si>
+  <si>
+    <t>22, TÂN THỚI NHẤT 1B, Phường Tân Thới Nhất</t>
+  </si>
+  <si>
+    <t>HD023972</t>
+  </si>
+  <si>
+    <t>433/11, Lê Đức Thọ, Phường 17</t>
+  </si>
+  <si>
+    <t>chị hương fb Kim Tien Pham</t>
+  </si>
+  <si>
+    <t>HD024001</t>
+  </si>
+  <si>
+    <t>Trần Lan</t>
+  </si>
+  <si>
+    <t>HD024017</t>
+  </si>
+  <si>
+    <t>190 võ văn ngân</t>
+  </si>
+  <si>
+    <t>phạm minh phi_F3: Theer To Lao</t>
+  </si>
+  <si>
+    <t>HD024093</t>
+  </si>
+  <si>
+    <t>33 đường số 6 p26</t>
+  </si>
+  <si>
+    <t>Đậu Đậu</t>
+  </si>
+  <si>
+    <t>HD024181</t>
+  </si>
+  <si>
+    <t>106/4 phan van tri phường 12</t>
+  </si>
+  <si>
+    <t>kh ck shop 2020k</t>
+  </si>
+  <si>
+    <t>HD024164</t>
+  </si>
+  <si>
+    <t>Toà Aster - Urbun Green (đối diện Vạn Phúc)</t>
+  </si>
+  <si>
+    <t>Linh Nga Anna</t>
+  </si>
+  <si>
+    <t>Thảo My</t>
+  </si>
+  <si>
+    <t>HD024170</t>
+  </si>
+  <si>
+    <t>91/12 nguyễn thanh tuyền p1</t>
+  </si>
+  <si>
+    <t>Kelly Phan</t>
+  </si>
+  <si>
+    <t>HD024129</t>
+  </si>
+  <si>
+    <t>240/6A lê thánh tôn phường bến thành</t>
+  </si>
+  <si>
+    <t>Tuệ Nhi</t>
+  </si>
+  <si>
+    <t>HD024045</t>
+  </si>
+  <si>
+    <t>92-94 nam kỳ khởi nghĩa- bến nghé</t>
+  </si>
+  <si>
+    <t>kh ck shop 845k</t>
+  </si>
+  <si>
+    <t>HD024006</t>
+  </si>
+  <si>
+    <t>24 Lê Thánh Tôn (BIDV), P.Bến Nghé</t>
+  </si>
+  <si>
+    <t>kh ck shop 465k</t>
+  </si>
+  <si>
+    <t>Tất Phú</t>
+  </si>
+  <si>
+    <t>HD023941</t>
+  </si>
+  <si>
+    <t>Bệnh viện Nhi đồng 1: 532 Lý Thái Tổ, P10</t>
+  </si>
+  <si>
+    <t>Cô Kiều Hương fb Vân Trần</t>
+  </si>
+  <si>
+    <t>HD023954</t>
+  </si>
+  <si>
+    <t>168A Trần Huy Liệu Phường 15</t>
+  </si>
+  <si>
+    <t>HD023966</t>
+  </si>
+  <si>
+    <t>12 nguyễn công trứ, thái bình</t>
+  </si>
+  <si>
+    <t>at 28-05</t>
+  </si>
+  <si>
+    <t>Cẩm Tiên</t>
+  </si>
+  <si>
+    <t>HD024200</t>
+  </si>
+  <si>
+    <t>Chung cư topaz dragon 2A 457-459 tạ quang bửu - phường 4</t>
+  </si>
+  <si>
+    <t>AT 29-05</t>
+  </si>
+  <si>
+    <t>29-05-2026</t>
+  </si>
+  <si>
+    <t>HD024203</t>
+  </si>
+  <si>
+    <t>Phương Đoan</t>
+  </si>
+  <si>
+    <t>HD024459</t>
+  </si>
+  <si>
+    <t>số 17 đường số 13 bình hưng hòa</t>
+  </si>
+  <si>
+    <t>Út Nhỏ (thu trần ) (Malaysia)</t>
+  </si>
+  <si>
+    <t>HD024433</t>
+  </si>
+  <si>
+    <t>24/5F, Ấp Đông Lân, Xã Bà Điểm</t>
+  </si>
+  <si>
+    <t>HD024304</t>
+  </si>
+  <si>
+    <t>Block d2, chung cư sài gòn riverside (số 4 đào trí phú thuận)</t>
+  </si>
+  <si>
+    <t>Kim Anh Phạm</t>
+  </si>
+  <si>
+    <t>HD024302</t>
+  </si>
+  <si>
+    <t>16 cư xá bình minh, dương Bá Trạc, phường 1</t>
+  </si>
+  <si>
+    <t>Thúy Duy</t>
+  </si>
+  <si>
+    <t>HD024294</t>
+  </si>
+  <si>
+    <t>539,22 hương lộ 3 phường bình hưng hòa</t>
+  </si>
+  <si>
+    <t>Kim Tuyền</t>
+  </si>
+  <si>
+    <t>HD024441</t>
+  </si>
+  <si>
+    <t>451/40 phạm thế hiển phường 3</t>
+  </si>
+  <si>
+    <t>Chan (inst char importshop) -BN2441</t>
+  </si>
+  <si>
+    <t>HD024246</t>
+  </si>
+  <si>
+    <t>163 Trương Thị Hoa phường Tân Thới Hiệp</t>
+  </si>
+  <si>
+    <t>Uyên</t>
+  </si>
+  <si>
+    <t>HD024442</t>
+  </si>
+  <si>
+    <t>98 Vườn Lài, phường An Phú Đông</t>
+  </si>
+  <si>
+    <t>Nguyễn Huỳnh Cẩm Tú</t>
+  </si>
+  <si>
+    <t>HD024247</t>
+  </si>
+  <si>
+    <t>78/63 đường số 11, phường thông tây hội</t>
+  </si>
+  <si>
+    <t>Thùy</t>
+  </si>
+  <si>
+    <t>HD024086</t>
+  </si>
+  <si>
+    <t>175 quốc lộ 1k, linh xuân</t>
+  </si>
+  <si>
+    <t>Tuyen Nguyen</t>
+  </si>
+  <si>
+    <t>HD024412</t>
+  </si>
+  <si>
+    <t>39/44/6 hoàng bật đạt p15</t>
+  </si>
+  <si>
+    <t>Đào thị thanh tâm</t>
+  </si>
+  <si>
+    <t>HD024429</t>
+  </si>
+  <si>
+    <t>320/16 đường ĐHT 02 Phường đông hưng thuận</t>
+  </si>
+  <si>
+    <t>HD024270</t>
+  </si>
+  <si>
+    <t>Tạ Ngọc Mai</t>
+  </si>
+  <si>
+    <t>HD024430</t>
+  </si>
+  <si>
+    <t>Sarimi B1, khu chung cư Sala, P. An Lợi Đông</t>
+  </si>
+  <si>
+    <t>BN1B2 mini chouchou Fb.</t>
+  </si>
+  <si>
+    <t>HD024453</t>
+  </si>
+  <si>
+    <t>401 Quang Trung f10</t>
+  </si>
+  <si>
+    <t>Minh Hồng Nguyễn</t>
+  </si>
+  <si>
+    <t>HD024438</t>
+  </si>
+  <si>
+    <t>Jasmine 1 Hà đô - 118 Đường 3/2, phường 12</t>
+  </si>
+  <si>
+    <t>Daisy Le</t>
+  </si>
+  <si>
+    <t>HD024416</t>
+  </si>
+  <si>
+    <t>418 Trường Sa, p2</t>
+  </si>
+  <si>
+    <t>Ngọc Quyên</t>
+  </si>
+  <si>
+    <t>HD024258</t>
+  </si>
+  <si>
+    <t>148a hòa hưng p13</t>
+  </si>
+  <si>
+    <t>HD024290</t>
+  </si>
+  <si>
+    <t>at 29-05</t>
+  </si>
+  <si>
     <t>THÁNG 5</t>
   </si>
   <si>
@@ -6535,223 +6935,238 @@
     <t>Lợi nhuận</t>
   </si>
   <si>
-    <t>Uyên Trần</t>
-  </si>
-  <si>
-    <t>HD024168</t>
-  </si>
-  <si>
-    <t>137/84D âu dương lân - p2</t>
-  </si>
-  <si>
-    <t>AT 28-05</t>
-  </si>
-  <si>
-    <t>28-05-2026</t>
-  </si>
-  <si>
-    <t>Thanh Vy</t>
-  </si>
-  <si>
-    <t>HD024163</t>
-  </si>
-  <si>
-    <t>20B Trần Văn Quang, Phường Bảy Hiền</t>
-  </si>
-  <si>
-    <t>Thảo My</t>
-  </si>
-  <si>
-    <t>HD024170</t>
-  </si>
-  <si>
-    <t>91/12 nguyễn thanh tuyền p1</t>
-  </si>
-  <si>
-    <t>khả trinh</t>
-  </si>
-  <si>
-    <t>HD024033</t>
-  </si>
-  <si>
-    <t>82/17/20đinh tiên hoàng p1</t>
-  </si>
-  <si>
-    <t>Kelly Phan</t>
-  </si>
-  <si>
-    <t>HD024129</t>
-  </si>
-  <si>
-    <t>240/6A lê thánh tôn phường bến thành</t>
-  </si>
-  <si>
-    <t>Tuệ Nhi</t>
-  </si>
-  <si>
-    <t>HD024045</t>
-  </si>
-  <si>
-    <t>92-94 nam kỳ khởi nghĩa- bến nghé</t>
-  </si>
-  <si>
-    <t>HD024006</t>
-  </si>
-  <si>
-    <t>24 Lê Thánh Tôn (BIDV), P.Bến Nghé</t>
-  </si>
-  <si>
-    <t>Thủy Heri</t>
-  </si>
-  <si>
-    <t>HD024145</t>
-  </si>
-  <si>
-    <t>184/17/35 bãi sậy phường bình tiên</t>
-  </si>
-  <si>
-    <t>Linh fb Phan Thị Tuyết Nhung</t>
-  </si>
-  <si>
-    <t>HD023982</t>
-  </si>
-  <si>
-    <t>201 Đường Hoàng Hoa Thám, Phường 13</t>
-  </si>
-  <si>
-    <t>Nguyễn Châu Tuệ Lâm</t>
-  </si>
-  <si>
-    <t>HD024027</t>
-  </si>
-  <si>
-    <t>74/1h ds9 linh trung</t>
-  </si>
-  <si>
-    <t>Ngân</t>
-  </si>
-  <si>
-    <t>HD023968</t>
-  </si>
-  <si>
-    <t>Toà A2 Alnata diamond đường N1 Tân Sơn Nhì</t>
-  </si>
-  <si>
-    <t>HD024142</t>
-  </si>
-  <si>
-    <t>Nguyễn Trinh</t>
-  </si>
-  <si>
-    <t>HD024157</t>
-  </si>
-  <si>
-    <t>29/10c trần thái tông</t>
-  </si>
-  <si>
-    <t>HD023918</t>
-  </si>
-  <si>
-    <t>Minh Thư nhận hộ ( water) fb Thuỷ Vũ</t>
-  </si>
-  <si>
-    <t>HD024179</t>
-  </si>
-  <si>
-    <t>22, TÂN THỚI NHẤT 1B, Phường Tân Thới Nhất</t>
-  </si>
-  <si>
-    <t>Tất Phú</t>
-  </si>
-  <si>
-    <t>HD023941</t>
-  </si>
-  <si>
-    <t>Bệnh viện Nhi đồng 1: 532 Lý Thái Tổ, P10</t>
-  </si>
-  <si>
-    <t>HD023972</t>
-  </si>
-  <si>
-    <t>433/11, Lê Đức Thọ, Phường 17</t>
-  </si>
-  <si>
-    <t>chị hương fb Kim Tien Pham</t>
-  </si>
-  <si>
-    <t>Trần Lan</t>
-  </si>
-  <si>
-    <t>HD024017</t>
-  </si>
-  <si>
-    <t>190 võ văn ngân</t>
-  </si>
-  <si>
-    <t>Cô Kiều Hương fb Vân Trần</t>
-  </si>
-  <si>
-    <t>HD023954</t>
-  </si>
-  <si>
-    <t>168A Trần Huy Liệu Phường 15</t>
-  </si>
-  <si>
-    <t>HD023966</t>
-  </si>
-  <si>
-    <t>12 nguyễn công trứ, thái bình</t>
-  </si>
-  <si>
-    <t>phạm minh phi_F3: Theer To Lao</t>
-  </si>
-  <si>
-    <t>HD024093</t>
-  </si>
-  <si>
-    <t>33 đường số 6 p26</t>
-  </si>
-  <si>
-    <t>Diễm Phúc</t>
-  </si>
-  <si>
-    <t>HD024175</t>
-  </si>
-  <si>
-    <t>314/138 đường âu dương lân, p3</t>
-  </si>
-  <si>
-    <t>Đậu Đậu</t>
-  </si>
-  <si>
-    <t>HD024181</t>
-  </si>
-  <si>
-    <t>106/4 phan van tri phường 12</t>
-  </si>
-  <si>
-    <t>HD024164</t>
-  </si>
-  <si>
-    <t>Toà Aster - Urbun Green (đối diện Vạn Phúc)</t>
-  </si>
-  <si>
-    <t>Linh Nga Anna</t>
-  </si>
-  <si>
-    <t>at 28-05</t>
-  </si>
-  <si>
-    <t>HD024001</t>
-  </si>
-  <si>
-    <t>kh ck shop 845k</t>
-  </si>
-  <si>
-    <t>kh ck shop 465k</t>
-  </si>
-  <si>
-    <t>kh ck shop 2020k</t>
+    <t>ĐỨC - FB MT MI Ngo</t>
+  </si>
+  <si>
+    <t>HD024678</t>
+  </si>
+  <si>
+    <t>39 an nhơn phường 17</t>
+  </si>
+  <si>
+    <t>30-05-2026</t>
+  </si>
+  <si>
+    <t>Phạm Thị Thanh Hồng</t>
+  </si>
+  <si>
+    <t>HD024697</t>
+  </si>
+  <si>
+    <t>Hẻm 95, nhà 95/5D, đường 15, phường tân hưng</t>
+  </si>
+  <si>
+    <t>Ngọc Vũ</t>
+  </si>
+  <si>
+    <t>HD024689</t>
+  </si>
+  <si>
+    <t>42 đương so 6 binh trưng đông</t>
+  </si>
+  <si>
+    <t>Nguyễn Cẩm Tú</t>
+  </si>
+  <si>
+    <t>HD024680</t>
+  </si>
+  <si>
+    <t>Sky garden 2, cổng đông 3, phường tân phong</t>
+  </si>
+  <si>
+    <t>Ái Linh</t>
+  </si>
+  <si>
+    <t>HD024455</t>
+  </si>
+  <si>
+    <t>17/2 đường số 10 p bình trưng tây</t>
+  </si>
+  <si>
+    <t>Irire Intara (phòng 505)</t>
+  </si>
+  <si>
+    <t>HD024607</t>
+  </si>
+  <si>
+    <t>A25 Hotel - 51-53-55 Cách Mạng Tháng 8, Phường Bến Thành</t>
+  </si>
+  <si>
+    <t>Kiều Nhi</t>
+  </si>
+  <si>
+    <t>HD024623</t>
+  </si>
+  <si>
+    <t>4/2b đường số 26 phương an khánh</t>
+  </si>
+  <si>
+    <t>Nguyễn Thu Phương</t>
+  </si>
+  <si>
+    <t>HD024563</t>
+  </si>
+  <si>
+    <t>Sunrise riverside tháp H Đường Nguyễn hữu thọ</t>
+  </si>
+  <si>
+    <t>Hoàng Thu Thủy</t>
+  </si>
+  <si>
+    <t>HD024597</t>
+  </si>
+  <si>
+    <t>583 Nguyễn Thị Thập, phường Bình Thuận</t>
+  </si>
+  <si>
+    <t>Ngô Hoàng Ánh</t>
+  </si>
+  <si>
+    <t>HD024510</t>
+  </si>
+  <si>
+    <t>235 QL13 Cũ, HBP</t>
+  </si>
+  <si>
+    <t>Panhaketya (zalo_thiemuyen)</t>
+  </si>
+  <si>
+    <t>HD024702</t>
+  </si>
+  <si>
+    <t>Pham Ngu Lao A67 Nguyen Trai</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Thùy Tiên</t>
+  </si>
+  <si>
+    <t>HD024686</t>
+  </si>
+  <si>
+    <t>1/10/2 nguyễn văn yến phường phú thạnh</t>
+  </si>
+  <si>
+    <t>AT 30-05</t>
+  </si>
+  <si>
+    <t>Trần Thị Mỹ Duyên</t>
+  </si>
+  <si>
+    <t>HD024528</t>
+  </si>
+  <si>
+    <t>84 song hành phường an phú</t>
+  </si>
+  <si>
+    <t>HD024599</t>
+  </si>
+  <si>
+    <t>Chị Bảo Châu</t>
+  </si>
+  <si>
+    <t>HD024669</t>
+  </si>
+  <si>
+    <t>W3370</t>
+  </si>
+  <si>
+    <t>HD024406</t>
+  </si>
+  <si>
+    <t>Ngọc Diệu</t>
+  </si>
+  <si>
+    <t>HD024379</t>
+  </si>
+  <si>
+    <t>132 Le van quoi p bình hưng hòa a</t>
+  </si>
+  <si>
+    <t>HD024538</t>
+  </si>
+  <si>
+    <t>320/16 đường ĐHT 02 phường đông hưng thuận</t>
+  </si>
+  <si>
+    <t>Võ Hằng</t>
+  </si>
+  <si>
+    <t>HD024527</t>
+  </si>
+  <si>
+    <t>Cty leading star, lô C đường số 3, KCN Đồng An, Bình Hoà</t>
+  </si>
+  <si>
+    <t>tinh</t>
+  </si>
+  <si>
+    <t>hàng tỉnh</t>
+  </si>
+  <si>
+    <t>Nhân (fb Cam Phu)</t>
+  </si>
+  <si>
+    <t>HD024666</t>
+  </si>
+  <si>
+    <t>11 đường 18 phường 4</t>
+  </si>
+  <si>
+    <t>BN6352</t>
+  </si>
+  <si>
+    <t>HD024138</t>
+  </si>
+  <si>
+    <t>HD024704</t>
+  </si>
+  <si>
+    <t>HD024659</t>
+  </si>
+  <si>
+    <t>HD024670</t>
+  </si>
+  <si>
+    <t>Phạm Duyên</t>
+  </si>
+  <si>
+    <t>HD024075</t>
+  </si>
+  <si>
+    <t>Số 107, Đường Dương Quảng Hàm phường 7 (tiệm rửa xe)</t>
+  </si>
+  <si>
+    <t>An Nguyen - fb Nguyễn Hoàng Thúy An</t>
+  </si>
+  <si>
+    <t>HD024454</t>
+  </si>
+  <si>
+    <t>105/48 Nguyễn tư giản f12</t>
+  </si>
+  <si>
+    <t>Đặng Trung</t>
+  </si>
+  <si>
+    <t>HD023933</t>
+  </si>
+  <si>
+    <t>206 khu phố Mỹ Hào, Hà Huy tập, P. Tân Phong</t>
+  </si>
+  <si>
+    <t>Anh Hải nhận hàng (Thảo Trần)</t>
+  </si>
+  <si>
+    <t>HD024613</t>
+  </si>
+  <si>
+    <t>số 17 đường số 13 phường bình hưng hòa</t>
+  </si>
+  <si>
+    <t>at 30-05</t>
+  </si>
+  <si>
+    <t>z</t>
   </si>
 </sst>
 </file>
@@ -35225,7 +35640,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
-  <dimension ref="A2:R65"/>
+  <dimension ref="A2:R64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -35324,7 +35739,7 @@
         <v>35</v>
       </c>
       <c r="I3" s="16">
-        <f t="shared" ref="I3:I31" si="0">G3-H3</f>
+        <f t="shared" ref="I3:I30" si="0">G3-H3</f>
         <v>1510</v>
       </c>
       <c r="J3" s="15" t="s">
@@ -36588,526 +37003,474 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B31" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31" s="21" t="s">
-        <v>1444</v>
-      </c>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21" t="s">
-        <v>1445</v>
-      </c>
-      <c r="F31" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="G31" s="22">
-        <v>0</v>
-      </c>
-      <c r="H31" s="22">
-        <v>35</v>
-      </c>
-      <c r="I31" s="22">
-        <f t="shared" si="0"/>
-        <v>-35</v>
-      </c>
-      <c r="J31" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="K31" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="L31" s="21" t="s">
-        <v>1424</v>
-      </c>
-      <c r="M31" s="21" t="s">
-        <v>204</v>
-      </c>
-      <c r="N31" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="O31" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="P31" s="21" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q31" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D33" s="1">
-        <f>COUNTA(D3:D31)</f>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D32" s="1">
+        <f>COUNTA(D3:D30)</f>
         <v>23</v>
       </c>
-      <c r="G33" s="1">
-        <f t="shared" ref="G33:Q33" si="1">SUBTOTAL(9,G3:G31)</f>
+      <c r="G32" s="1">
+        <f t="shared" ref="G32:Q32" si="1">SUBTOTAL(9,G3:G30)</f>
         <v>24230</v>
       </c>
-      <c r="H33" s="1">
+      <c r="H32" s="1">
         <f t="shared" si="1"/>
-        <v>820</v>
-      </c>
-      <c r="I33" s="1">
+        <v>785</v>
+      </c>
+      <c r="I32" s="1">
         <f t="shared" si="1"/>
-        <v>23410</v>
-      </c>
-      <c r="J33" s="1">
+        <v>23445</v>
+      </c>
+      <c r="J32" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K33" s="1">
+      <c r="K32" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L33" s="1">
+      <c r="L32" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M33" s="1">
+      <c r="M32" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N33" s="1">
+      <c r="N32" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O33" s="1">
+      <c r="O32" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P33" s="1">
+      <c r="P32" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q33" s="1">
+      <c r="Q32" s="1">
         <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H34">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H33">
         <f>-7*17</f>
         <v>-119</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" s="37" t="s">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="37" t="s">
         <v>191</v>
       </c>
-      <c r="D35" s="37"/>
-      <c r="E35" s="4" t="s">
+      <c r="D34" s="37"/>
+      <c r="E34" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="H35">
+      <c r="H34">
         <f>-2*25</f>
         <v>-50</v>
       </c>
-      <c r="K35" s="11" t="s">
+      <c r="K34" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="L35" s="11" t="s">
+      <c r="L34" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="M35" s="11" t="s">
+      <c r="M34" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="O35" s="4" t="s">
+      <c r="O34" s="4" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>2011</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B35" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C36" s="38">
-        <f>SUMIFS(I$3:I$31,B$3:B$31,A$35,L$3:L$31,A$36)</f>
+      <c r="C35" s="38">
+        <f>SUMIFS(I$3:I$30,B$3:B$30,A$34,L$3:L$30,A$35)</f>
         <v>19080</v>
       </c>
-      <c r="D36" s="38"/>
-      <c r="E36" s="3">
-        <f>SUMIFS(Q$3:Q$31,B$3:B$31,A$35,L$3:L$31,A$36)</f>
+      <c r="D35" s="38"/>
+      <c r="E35" s="3">
+        <f>SUMIFS(Q$3:Q$30,B$3:B$30,A$34,L$3:L$30,A$35)</f>
         <v>27</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F35" t="s">
         <v>196</v>
       </c>
+      <c r="K35" t="s">
+        <v>197</v>
+      </c>
+      <c r="L35">
+        <f>SUMIFS(G$3:G$30,J$3:J$30,K$34)</f>
+        <v>4160</v>
+      </c>
+      <c r="M35">
+        <f>SUMIFS(Q$3:Q$30,J$3:J$30,K$34)-INT(COUNTIFS(J$3:J$30,K$34,M$3:M$30,"*gộp*")/2)</f>
+        <v>7</v>
+      </c>
+      <c r="O35" t="s">
+        <v>135</v>
+      </c>
+      <c r="P35">
+        <f>L40</f>
+        <v>-360</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C36" s="39">
+        <v>0</v>
+      </c>
+      <c r="D36" s="39"/>
       <c r="K36" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="L36">
-        <f>SUMIFS(G$3:G$31,J$3:J$31,K$35)</f>
-        <v>4160</v>
+        <f>-SUMIFS(H$3:H$30,J$3:J$30,K$34)+M36*5</f>
+        <v>-150</v>
       </c>
       <c r="M36">
-        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$35)-INT(COUNTIFS(J$3:J$31,K$35,M$3:M$31,"*gộp*")/2)</f>
+        <f>SUMIFS(Q$3:Q$30,J$3:J$30,K$34)-INT(COUNTIFS(J$3:J$30,K$34,M$3:M$30,"*gộp*")/2)</f>
         <v>7</v>
       </c>
       <c r="O36" t="s">
-        <v>135</v>
+        <v>2073</v>
       </c>
       <c r="P36">
-        <f>L41</f>
-        <v>-360</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+        <f>L48</f>
+        <v>6081</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C37" s="39">
-        <v>0</v>
+        <f>-SUMIFS(I$3:I$30,B$3:B$30,A$34,P$3:P$30,"xx",N$3:N$30,"x")</f>
+        <v>-4365</v>
       </c>
       <c r="D37" s="39"/>
+      <c r="E37" s="2">
+        <f>SUMIFS(Q$3:Q$30,B$3:B$30,A$34,P$3:P$30,"xx",N$3:N$30,"x")</f>
+        <v>1</v>
+      </c>
       <c r="K37" t="s">
-        <v>200</v>
-      </c>
-      <c r="L37">
-        <f>-SUMIFS(H$3:H$31,J$3:J$31,K$35)+M37*5</f>
-        <v>-150</v>
-      </c>
-      <c r="M37">
-        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$35)-INT(COUNTIFS(J$3:J$31,K$35,M$3:M$31,"*gộp*")/2)</f>
-        <v>7</v>
+        <v>202</v>
       </c>
       <c r="O37" t="s">
-        <v>2073</v>
+        <v>20</v>
       </c>
       <c r="P37">
-        <f>L49</f>
-        <v>6081</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B38" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C38" s="39">
-        <f>-SUMIFS(I$3:I$31,B$3:B$31,A$35,P$3:P$31,"xx",N$3:N$31,"x")</f>
-        <v>-4330</v>
-      </c>
-      <c r="D38" s="39"/>
-      <c r="E38" s="2">
-        <f>SUMIFS(Q$3:Q$31,B$3:B$31,A$35,P$3:P$31,"xx",N$3:N$31,"x")</f>
-        <v>2</v>
-      </c>
-      <c r="K38" t="s">
-        <v>202</v>
+        <f>L56</f>
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B38" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C38" s="37">
+        <f>SUBTOTAL(9,C35:C37)</f>
+        <v>14715</v>
+      </c>
+      <c r="D38" s="37"/>
+      <c r="E38">
+        <f>E35</f>
+        <v>27</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="L38" s="23">
+        <v>-4370</v>
+      </c>
+      <c r="M38" s="23" t="s">
+        <v>288</v>
       </c>
       <c r="O38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P38">
-        <f>L57</f>
-        <v>2370</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B39" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="C39" s="37">
-        <f>SUBTOTAL(9,C36:C38)</f>
-        <v>14750</v>
-      </c>
-      <c r="D39" s="37"/>
-      <c r="E39">
-        <f>E36</f>
-        <v>27</v>
-      </c>
+        <f>L64</f>
+        <v>6783</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B39" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
       <c r="K39" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="L39" s="23">
-        <v>-4370</v>
-      </c>
-      <c r="M39" s="23" t="s">
-        <v>288</v>
+        <v>206</v>
       </c>
       <c r="O39" t="s">
-        <v>21</v>
+        <v>207</v>
       </c>
       <c r="P39">
-        <f>L65</f>
-        <v>6785</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B40" s="2" t="s">
-        <v>205</v>
+        <f>-C42</f>
+        <v>-14715</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B40" s="12" t="s">
+        <v>208</v>
       </c>
       <c r="C40" s="35"/>
       <c r="D40" s="35"/>
-      <c r="K40" s="2" t="s">
+      <c r="L40" s="13">
+        <f>SUBTOTAL(9,L35:L39)</f>
+        <v>-360</v>
+      </c>
+      <c r="M40" s="13">
+        <f>M35</f>
+        <v>7</v>
+      </c>
+      <c r="O40" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="P40" s="4">
+        <f>SUBTOTAL(9,P35:P39)</f>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B42" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C42" s="36">
+        <f>C38+C39+C40</f>
+        <v>14715</v>
+      </c>
+      <c r="D42" s="36"/>
+      <c r="E42" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>2015</v>
+      </c>
+      <c r="L42" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="M42" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K43" t="s">
+        <v>197</v>
+      </c>
+      <c r="L43">
+        <f>SUMIFS(G$3:G$30,J$3:J$30,K$42)</f>
+        <v>6220</v>
+      </c>
+      <c r="M43">
+        <f>SUMIFS(Q$3:Q$30,J$3:J$30,K$42)-INT(COUNTIFS(J$3:J$30,K$42,M$3:M$30,"*gộp*")/2)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K44" t="s">
+        <v>200</v>
+      </c>
+      <c r="L44">
+        <f>SUM(H33:H34)</f>
+        <v>-169</v>
+      </c>
+      <c r="M44">
+        <f>SUMIFS(Q$3:Q$30,J$3:J$30,K$42)-INT(COUNTIFS(J$3:J$30,K$42,M$3:M$30,"*gộp*")/2)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K45" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K46" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="L46" s="23">
+        <v>30</v>
+      </c>
+      <c r="M46" s="23" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K47" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="O40" t="s">
-        <v>207</v>
-      </c>
-      <c r="P40">
-        <f>-C43</f>
-        <v>-14750</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B41" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="C41" s="35"/>
-      <c r="D41" s="35"/>
-      <c r="L41" s="13">
-        <f>SUBTOTAL(9,L36:L40)</f>
-        <v>-360</v>
-      </c>
-      <c r="M41" s="13">
-        <f>M36</f>
-        <v>7</v>
-      </c>
-      <c r="O41" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="P41" s="4">
-        <f>SUBTOTAL(9,P36:P40)</f>
-        <v>126</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B43" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C43" s="36">
-        <f>C39+C40+C41</f>
-        <v>14750</v>
-      </c>
-      <c r="D43" s="36"/>
-      <c r="E43" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="K43" s="11" t="s">
-        <v>2015</v>
-      </c>
-      <c r="L43" s="11" t="s">
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L48" s="13">
+        <f>SUBTOTAL(9,L43:L47)</f>
+        <v>6081</v>
+      </c>
+      <c r="M48" s="13">
+        <f>M43</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K50" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L50" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="M43" s="11" t="s">
+      <c r="M50" s="11" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K44" t="s">
+    <row r="51" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K51" t="s">
         <v>197</v>
       </c>
-      <c r="L44">
-        <f>SUMIFS(G$3:G$31,J$3:J$31,K$43)</f>
-        <v>6220</v>
-      </c>
-      <c r="M44">
-        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$43)-INT(COUNTIFS(J$3:J$31,K$43,M$3:M$31,"*gộp*")/2)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K45" t="s">
-        <v>200</v>
-      </c>
-      <c r="L45">
-        <f>SUM(H34:H35)</f>
-        <v>-169</v>
-      </c>
-      <c r="M45">
-        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$43)-INT(COUNTIFS(J$3:J$31,K$43,M$3:M$31,"*gộp*")/2)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K46" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K47" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="L47" s="23">
-        <v>30</v>
-      </c>
-      <c r="M47" s="23" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K48" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="49" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="L49" s="13">
-        <f>SUBTOTAL(9,L44:L48)</f>
-        <v>6081</v>
-      </c>
-      <c r="M49" s="13">
-        <f>M44</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="51" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K51" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L51" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="M51" s="11" t="s">
-        <v>192</v>
+      <c r="L51">
+        <f>SUMIFS(G$3:G$30,J$3:J$30,K$50)</f>
+        <v>2425</v>
+      </c>
+      <c r="M51">
+        <f>SUMIFS(Q$3:Q$30,J$3:J$30,K$50)-INT(COUNTIFS(J$3:J$30,K$50,M$3:M$30,"*gộp*")/2)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K52" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="L52">
-        <f>SUMIFS(G$3:G$31,J$3:J$31,K$51)</f>
-        <v>2425</v>
+        <f>-SUMIFS(H$3:H$30,J$3:J$30,K$50)+M52*5</f>
+        <v>-55</v>
       </c>
       <c r="M52">
-        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$51)-INT(COUNTIFS(J$3:J$31,K$51,M$3:M$31,"*gộp*")/2)</f>
+        <f>SUMIFS(Q$3:Q$30,J$3:J$30,K$50)-INT(COUNTIFS(J$3:J$30,K$50,M$3:M$30,"*gộp*")/2)</f>
         <v>2</v>
       </c>
     </row>
     <row r="53" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K53" t="s">
-        <v>200</v>
-      </c>
-      <c r="L53">
-        <f>-SUMIFS(H$3:H$31,J$3:J$31,K$51)+M53*5</f>
-        <v>-55</v>
-      </c>
-      <c r="M53">
-        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$51)-INT(COUNTIFS(J$3:J$31,K$51,M$3:M$31,"*gộp*")/2)</f>
-        <v>2</v>
+        <v>202</v>
       </c>
     </row>
     <row r="54" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K54" t="s">
-        <v>202</v>
+      <c r="K54" s="2" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="55" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K55" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="56" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K56" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="57" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="L57" s="13">
-        <f>SUBTOTAL(9,L52:L56)</f>
+      <c r="L56" s="13">
+        <f>SUBTOTAL(9,L51:L55)</f>
         <v>2370</v>
       </c>
-      <c r="M57" s="13">
-        <f>M52</f>
+      <c r="M56" s="13">
+        <f>M51</f>
         <v>2</v>
       </c>
     </row>
+    <row r="58" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K58" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L58" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="M58" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
     <row r="59" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K59" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L59" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="M59" s="11" t="s">
-        <v>192</v>
+      <c r="K59" t="s">
+        <v>197</v>
+      </c>
+      <c r="L59">
+        <f>SUMIFS(G$3:G$30,J$3:J$30,K$58)</f>
+        <v>7025</v>
+      </c>
+      <c r="M59">
+        <f>SUMIFS(Q$3:Q$30,J$3:J$30,K$58)-INT(COUNTIFS(J$3:J$30,K$58,M$3:M$30,"*gộp*")/2)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K60" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="L60">
-        <f>SUMIFS(G$3:G$31,J$3:J$31,K$59)</f>
-        <v>7025</v>
+        <f>-SUMIFS(H$3:H$30,J$3:J$30,K$58)+M60*5</f>
+        <v>-190</v>
       </c>
       <c r="M60">
-        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$59)-INT(COUNTIFS(J$3:J$31,K$59,M$3:M$31,"*gộp*")/2)</f>
+        <f>SUMIFS(Q$3:Q$30,J$3:J$30,K$58)-INT(COUNTIFS(J$3:J$30,K$58,M$3:M$30,"*gộp*")/2)</f>
         <v>9</v>
       </c>
     </row>
     <row r="61" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K61" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L61">
-        <f>-SUMIFS(H$3:H$31,J$3:J$31,K$59)+M61*5</f>
-        <v>-190</v>
+        <f>-M61*2</f>
+        <v>-52</v>
       </c>
       <c r="M61">
-        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$59)-INT(COUNTIFS(J$3:J$31,K$59,M$3:M$31,"*gộp*")/2)</f>
-        <v>9</v>
+        <f>E38-(COUNTIFS(M$3:M$30,"*gộp*")/2)-COUNTIFS(M$3:M$30,"*đơn trả*")-COUNTIFS(M$3:M$30,"*hàng tỉnh*")</f>
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K62" t="s">
-        <v>202</v>
-      </c>
-      <c r="L62">
-        <f>-M62*2</f>
-        <v>-50</v>
-      </c>
-      <c r="M62">
-        <f>E39-(COUNTIFS(M$3:M$31,"*gộp*")/2)-COUNTIFS(M$3:M$31,"*đơn trả*")-COUNTIFS(M$3:M$31,"*hàng tỉnh*")</f>
-        <v>25</v>
+      <c r="K62" s="2" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="63" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K63" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="64" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K64" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="65" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L65" s="13">
-        <f>SUBTOTAL(9,L60:L64)</f>
-        <v>6785</v>
-      </c>
-      <c r="M65" s="13">
-        <f>M60</f>
+      <c r="L64" s="13">
+        <f>SUBTOTAL(9,L59:L63)</f>
+        <v>6783</v>
+      </c>
+      <c r="M64" s="13">
+        <f>M59</f>
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P31" xr:uid="{00000000-0009-0000-0000-000014000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P31">
-      <sortCondition ref="J2:J31"/>
+  <autoFilter ref="A2:P30" xr:uid="{00000000-0009-0000-0000-000014000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P30">
+      <sortCondition ref="J2:J30"/>
     </sortState>
   </autoFilter>
   <mergeCells count="8">
+    <mergeCell ref="C39:D39"/>
     <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C34:D34"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
@@ -38760,13 +39123,13 @@
         <v>17</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>2143</v>
+        <v>2133</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>2144</v>
+        <v>2134</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>2145</v>
+        <v>2135</v>
       </c>
       <c r="F3" s="16">
         <v>8</v>
@@ -38782,13 +39145,13 @@
         <v>690</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>2146</v>
+        <v>2136</v>
       </c>
       <c r="K3" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M3" s="15"/>
       <c r="N3" s="15"/>
@@ -38804,13 +39167,13 @@
         <v>17</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>2148</v>
+        <v>2138</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>2149</v>
+        <v>2139</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>2150</v>
+        <v>2140</v>
       </c>
       <c r="F4" s="15" t="s">
         <v>95</v>
@@ -38826,13 +39189,13 @@
         <v>1140</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>2146</v>
+        <v>2136</v>
       </c>
       <c r="K4" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M4" s="15"/>
       <c r="N4" s="15"/>
@@ -38848,13 +39211,13 @@
         <v>17</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>2165</v>
+        <v>2141</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>2166</v>
+        <v>2142</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>2167</v>
+        <v>2143</v>
       </c>
       <c r="F5" s="16">
         <v>6</v>
@@ -38870,13 +39233,13 @@
         <v>-25</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>2146</v>
+        <v>2136</v>
       </c>
       <c r="K5" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M5" s="15"/>
       <c r="N5" s="15"/>
@@ -38896,13 +39259,13 @@
         <v>17</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>2174</v>
+        <v>2144</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>2175</v>
+        <v>2145</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>2176</v>
+        <v>2146</v>
       </c>
       <c r="F6" s="15" t="s">
         <v>46</v>
@@ -38918,13 +39281,13 @@
         <v>820</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>2146</v>
+        <v>2136</v>
       </c>
       <c r="K6" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M6" s="15"/>
       <c r="N6" s="15"/>
@@ -38943,7 +39306,7 @@
         <v>1918</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>2181</v>
+        <v>2147</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>1920</v>
@@ -38962,13 +39325,13 @@
         <v>820</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>2146</v>
+        <v>2136</v>
       </c>
       <c r="K7" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M7" s="15"/>
       <c r="N7" s="15"/>
@@ -38984,13 +39347,13 @@
         <v>17</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>2202</v>
+        <v>2148</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>2203</v>
+        <v>2149</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>2204</v>
+        <v>2150</v>
       </c>
       <c r="F8" s="16">
         <v>8</v>
@@ -39006,13 +39369,13 @@
         <v>820</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>2146</v>
+        <v>2136</v>
       </c>
       <c r="K8" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
@@ -39028,13 +39391,13 @@
         <v>17</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>2154</v>
+        <v>2151</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>2156</v>
+        <v>2153</v>
       </c>
       <c r="F9" s="15" t="s">
         <v>85</v>
@@ -39056,7 +39419,7 @@
         <v>21</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M9" s="15"/>
       <c r="N9" s="15"/>
@@ -39072,13 +39435,13 @@
         <v>17</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>2168</v>
+        <v>2154</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>2169</v>
+        <v>2155</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>2170</v>
+        <v>2156</v>
       </c>
       <c r="F10" s="15" t="s">
         <v>95</v>
@@ -39100,7 +39463,7 @@
         <v>21</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M10" s="15"/>
       <c r="N10" s="15"/>
@@ -39120,13 +39483,13 @@
         <v>17</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>2171</v>
+        <v>2157</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>2172</v>
+        <v>2158</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>2173</v>
+        <v>2159</v>
       </c>
       <c r="F11" s="15" t="s">
         <v>81</v>
@@ -39148,7 +39511,7 @@
         <v>21</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M11" s="20" t="s">
         <v>167</v>
@@ -39173,7 +39536,7 @@
         <v>2113</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>2177</v>
+        <v>2160</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>2115</v>
@@ -39198,7 +39561,7 @@
         <v>21</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M12" s="15"/>
       <c r="N12" s="15"/>
@@ -39218,13 +39581,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>2178</v>
+        <v>2161</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>2179</v>
+        <v>2162</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>2180</v>
+        <v>2163</v>
       </c>
       <c r="F13" s="15" t="s">
         <v>95</v>
@@ -39246,7 +39609,7 @@
         <v>21</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M13" s="15"/>
       <c r="N13" s="15"/>
@@ -39262,13 +39625,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>2182</v>
+        <v>2164</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>2183</v>
+        <v>2165</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>2184</v>
+        <v>2166</v>
       </c>
       <c r="F14" s="16">
         <v>12</v>
@@ -39290,7 +39653,7 @@
         <v>21</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M14" s="15"/>
       <c r="N14" s="15"/>
@@ -39313,10 +39676,10 @@
         <v>738</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>2188</v>
+        <v>2167</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>2189</v>
+        <v>2168</v>
       </c>
       <c r="F15" s="15" t="s">
         <v>77</v>
@@ -39338,7 +39701,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M15" s="15"/>
       <c r="N15" s="15"/>
@@ -39354,10 +39717,10 @@
         <v>17</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>2190</v>
+        <v>2169</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>2212</v>
+        <v>2170</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>250</v>
@@ -39382,7 +39745,7 @@
         <v>21</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M16" s="15"/>
       <c r="N16" s="15"/>
@@ -39402,13 +39765,13 @@
         <v>17</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>2191</v>
+        <v>2171</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>2192</v>
+        <v>2172</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>2193</v>
+        <v>2173</v>
       </c>
       <c r="F17" s="15" t="s">
         <v>81</v>
@@ -39430,7 +39793,7 @@
         <v>21</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M17" s="15"/>
       <c r="N17" s="15"/>
@@ -39446,13 +39809,13 @@
         <v>17</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>2199</v>
+        <v>2174</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>2200</v>
+        <v>2175</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>2201</v>
+        <v>2176</v>
       </c>
       <c r="F18" s="15" t="s">
         <v>85</v>
@@ -39474,7 +39837,7 @@
         <v>21</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M18" s="15"/>
       <c r="N18" s="15"/>
@@ -39490,13 +39853,13 @@
         <v>17</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>2205</v>
+        <v>2177</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>2206</v>
+        <v>2178</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>2207</v>
+        <v>2179</v>
       </c>
       <c r="F19" s="15" t="s">
         <v>85</v>
@@ -39518,10 +39881,10 @@
         <v>21</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M19" s="20" t="s">
-        <v>2215</v>
+        <v>2180</v>
       </c>
       <c r="N19" s="15"/>
       <c r="O19" s="15"/>
@@ -39543,10 +39906,10 @@
         <v>111</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>2208</v>
+        <v>2181</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>2209</v>
+        <v>2182</v>
       </c>
       <c r="F20" s="15" t="s">
         <v>81</v>
@@ -39568,7 +39931,7 @@
         <v>21</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M20" s="15"/>
       <c r="N20" s="15"/>
@@ -39586,7 +39949,7 @@
         <v>17</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>2210</v>
+        <v>2183</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="15" t="s">
@@ -39612,7 +39975,7 @@
         <v>21</v>
       </c>
       <c r="L21" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M21" s="15"/>
       <c r="N21" s="15"/>
@@ -39632,13 +39995,13 @@
         <v>17</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>2151</v>
+        <v>2184</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>2152</v>
+        <v>2185</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>2153</v>
+        <v>2186</v>
       </c>
       <c r="F22" s="15" t="s">
         <v>95</v>
@@ -39660,7 +40023,7 @@
         <v>21</v>
       </c>
       <c r="L22" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M22" s="15"/>
       <c r="N22" s="15"/>
@@ -39676,13 +40039,13 @@
         <v>17</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>2157</v>
+        <v>2187</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>2158</v>
+        <v>2188</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>2159</v>
+        <v>2189</v>
       </c>
       <c r="F23" s="16">
         <v>1</v>
@@ -39704,7 +40067,7 @@
         <v>21</v>
       </c>
       <c r="L23" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M23" s="15"/>
       <c r="N23" s="15"/>
@@ -39724,13 +40087,13 @@
         <v>17</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>2160</v>
+        <v>2190</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>2161</v>
+        <v>2191</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>2162</v>
+        <v>2192</v>
       </c>
       <c r="F24" s="16">
         <v>1</v>
@@ -39752,10 +40115,10 @@
         <v>21</v>
       </c>
       <c r="L24" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M24" s="20" t="s">
-        <v>2213</v>
+        <v>2193</v>
       </c>
       <c r="N24" s="15"/>
       <c r="O24" s="15"/>
@@ -39763,6 +40126,10 @@
       <c r="Q24" s="15">
         <v>1</v>
       </c>
+      <c r="R24" s="10">
+        <f>H24</f>
+        <v>25</v>
+      </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="15"/>
@@ -39773,10 +40140,10 @@
         <v>1621</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>2163</v>
+        <v>2194</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>2164</v>
+        <v>2195</v>
       </c>
       <c r="F25" s="16">
         <v>1</v>
@@ -39798,10 +40165,10 @@
         <v>21</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M25" s="20" t="s">
-        <v>2214</v>
+        <v>2196</v>
       </c>
       <c r="N25" s="15"/>
       <c r="O25" s="15"/>
@@ -39809,6 +40176,10 @@
       <c r="Q25" s="15">
         <v>1</v>
       </c>
+      <c r="R25" s="10">
+        <f>H25</f>
+        <v>25</v>
+      </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="15"/>
@@ -39816,13 +40187,13 @@
         <v>17</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>2185</v>
+        <v>2197</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>2186</v>
+        <v>2198</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>2187</v>
+        <v>2199</v>
       </c>
       <c r="F26" s="16">
         <v>10</v>
@@ -39844,7 +40215,7 @@
         <v>21</v>
       </c>
       <c r="L26" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M26" s="15"/>
       <c r="N26" s="15"/>
@@ -39860,13 +40231,13 @@
         <v>17</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>2194</v>
+        <v>2200</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>2195</v>
+        <v>2201</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>2196</v>
+        <v>2202</v>
       </c>
       <c r="F27" s="15" t="s">
         <v>406</v>
@@ -39888,7 +40259,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M27" s="15"/>
       <c r="N27" s="15"/>
@@ -39907,10 +40278,10 @@
         <v>1186</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>2197</v>
+        <v>2203</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>2198</v>
+        <v>2204</v>
       </c>
       <c r="F28" s="16">
         <v>1</v>
@@ -39932,7 +40303,7 @@
         <v>21</v>
       </c>
       <c r="L28" s="15" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="M28" s="15"/>
       <c r="N28" s="15"/>
@@ -40006,7 +40377,7 @@
         <v>26</v>
       </c>
       <c r="G31" s="1">
-        <f t="shared" ref="G31:Q31" si="1">SUBTOTAL(9,G3:G29)</f>
+        <f t="shared" ref="G31:M31" si="1">SUBTOTAL(9,G3:G29)</f>
         <v>19400</v>
       </c>
       <c r="H31" s="1">
@@ -40034,15 +40405,15 @@
         <v>0</v>
       </c>
       <c r="O31" s="1">
-        <f t="shared" si="1"/>
+        <f>SUBTOTAL(9,O3:O29)</f>
         <v>0</v>
       </c>
       <c r="P31" s="1">
-        <f t="shared" si="1"/>
+        <f>SUBTOTAL(9,P3:P29)</f>
         <v>0</v>
       </c>
       <c r="Q31" s="1">
-        <f t="shared" si="1"/>
+        <f>SUBTOTAL(9,Q3:Q29)</f>
         <v>27</v>
       </c>
     </row>
@@ -40064,7 +40435,7 @@
         <v>192</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>2146</v>
+        <v>2136</v>
       </c>
       <c r="L33" s="11" t="s">
         <v>193</v>
@@ -40078,7 +40449,7 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>195</v>
@@ -40107,7 +40478,7 @@
         <v>6</v>
       </c>
       <c r="O34" t="s">
-        <v>2211</v>
+        <v>2205</v>
       </c>
       <c r="P34">
         <f>L39</f>
@@ -40371,9 +40742,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P38" xr:uid="{00000000-0009-0000-0000-000017000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P29">
-      <sortCondition ref="J2:J29"/>
+  <autoFilter ref="A2:P38" xr:uid="{00000000-0009-0000-0000-000016000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P38">
+      <sortCondition ref="J2:J38"/>
     </sortState>
   </autoFilter>
   <mergeCells count="8">
@@ -40392,6 +40763,3233 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A2:R50"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="56.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="15"/>
+    </row>
+    <row r="3" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15"/>
+      <c r="B3" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>2206</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>2207</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>2208</v>
+      </c>
+      <c r="F3" s="16">
+        <v>8</v>
+      </c>
+      <c r="G3" s="16">
+        <v>920</v>
+      </c>
+      <c r="H3" s="16">
+        <v>30</v>
+      </c>
+      <c r="I3" s="16">
+        <f t="shared" ref="I3:I24" si="0">G3-H3</f>
+        <v>890</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>2209</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>2211</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="G4" s="16">
+        <v>1875</v>
+      </c>
+      <c r="H4" s="16">
+        <v>35</v>
+      </c>
+      <c r="I4" s="16">
+        <f t="shared" si="0"/>
+        <v>1840</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>2209</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="15"/>
+      <c r="B5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>2212</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>2213</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>2214</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="16">
+        <v>1770</v>
+      </c>
+      <c r="H5" s="16">
+        <v>30</v>
+      </c>
+      <c r="I5" s="16">
+        <f t="shared" si="0"/>
+        <v>1740</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>2209</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="15"/>
+      <c r="B6" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>2215</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>2216</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>2217</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G6" s="16">
+        <v>825</v>
+      </c>
+      <c r="H6" s="16">
+        <v>35</v>
+      </c>
+      <c r="I6" s="16">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>2209</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>2218</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>2219</v>
+      </c>
+      <c r="F7" s="16">
+        <v>7</v>
+      </c>
+      <c r="G7" s="16">
+        <v>1690</v>
+      </c>
+      <c r="H7" s="16">
+        <v>30</v>
+      </c>
+      <c r="I7" s="16">
+        <f t="shared" si="0"/>
+        <v>1660</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>2209</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15"/>
+      <c r="B8" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>2220</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>2221</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>2222</v>
+      </c>
+      <c r="F8" s="16">
+        <v>8</v>
+      </c>
+      <c r="G8" s="16">
+        <v>620</v>
+      </c>
+      <c r="H8" s="16">
+        <v>30</v>
+      </c>
+      <c r="I8" s="16">
+        <f t="shared" si="0"/>
+        <v>590</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>2209</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="15"/>
+      <c r="B9" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>2223</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>2225</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="16">
+        <v>8559</v>
+      </c>
+      <c r="H9" s="16">
+        <v>65</v>
+      </c>
+      <c r="I9" s="16">
+        <f t="shared" si="0"/>
+        <v>8494</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>2209</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M9" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="15">
+        <v>1</v>
+      </c>
+      <c r="R9" s="10">
+        <f>H9</f>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>2226</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>2227</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>2228</v>
+      </c>
+      <c r="F10" s="16">
+        <v>8</v>
+      </c>
+      <c r="G10" s="16">
+        <v>2620</v>
+      </c>
+      <c r="H10" s="16">
+        <v>35</v>
+      </c>
+      <c r="I10" s="16">
+        <f t="shared" si="0"/>
+        <v>2585</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>2209</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M10" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15">
+        <v>1</v>
+      </c>
+      <c r="R10" s="10">
+        <f>H10</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="15"/>
+      <c r="B11" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>2229</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>2230</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>2231</v>
+      </c>
+      <c r="F11" s="16">
+        <v>12</v>
+      </c>
+      <c r="G11" s="16">
+        <v>0</v>
+      </c>
+      <c r="H11" s="16">
+        <v>40</v>
+      </c>
+      <c r="I11" s="16">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="15">
+        <v>1</v>
+      </c>
+      <c r="R11" s="10">
+        <f>H11</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="15"/>
+      <c r="B12" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>2233</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>2234</v>
+      </c>
+      <c r="F12" s="16">
+        <v>12</v>
+      </c>
+      <c r="G12" s="16">
+        <v>910</v>
+      </c>
+      <c r="H12" s="16">
+        <v>30</v>
+      </c>
+      <c r="I12" s="16">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>2235</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>2236</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>2237</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="16">
+        <v>615</v>
+      </c>
+      <c r="H13" s="16">
+        <v>25</v>
+      </c>
+      <c r="I13" s="16">
+        <f t="shared" si="0"/>
+        <v>590</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="15"/>
+      <c r="B14" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>2239</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>2240</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" s="16">
+        <v>1120</v>
+      </c>
+      <c r="H14" s="16">
+        <v>30</v>
+      </c>
+      <c r="I14" s="16">
+        <f t="shared" si="0"/>
+        <v>1090</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="15"/>
+      <c r="B15" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>2242</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>2243</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G15" s="16">
+        <v>1145</v>
+      </c>
+      <c r="H15" s="16">
+        <v>25</v>
+      </c>
+      <c r="I15" s="16">
+        <f t="shared" si="0"/>
+        <v>1120</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>2244</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>2245</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>2246</v>
+      </c>
+      <c r="F16" s="16">
+        <v>12</v>
+      </c>
+      <c r="G16" s="16">
+        <v>30</v>
+      </c>
+      <c r="H16" s="16">
+        <v>30</v>
+      </c>
+      <c r="I16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="15"/>
+      <c r="B17" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>2247</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F17" s="16">
+        <v>12</v>
+      </c>
+      <c r="G17" s="16">
+        <v>1290</v>
+      </c>
+      <c r="H17" s="16">
+        <v>30</v>
+      </c>
+      <c r="I17" s="16">
+        <f t="shared" si="0"/>
+        <v>1260</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="15"/>
+      <c r="B18" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>2248</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>2250</v>
+      </c>
+      <c r="F18" s="16">
+        <v>2</v>
+      </c>
+      <c r="G18" s="16">
+        <v>1020</v>
+      </c>
+      <c r="H18" s="16">
+        <v>30</v>
+      </c>
+      <c r="I18" s="16">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>2251</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>2252</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>503</v>
+      </c>
+      <c r="F19" s="16">
+        <v>12</v>
+      </c>
+      <c r="G19" s="16">
+        <v>0</v>
+      </c>
+      <c r="H19" s="16">
+        <v>30</v>
+      </c>
+      <c r="I19" s="16">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="15"/>
+      <c r="Q19" s="15">
+        <v>1</v>
+      </c>
+      <c r="R19" s="10">
+        <f>H19</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15" t="s">
+        <v>2253</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="16">
+        <v>4440</v>
+      </c>
+      <c r="H20" s="16">
+        <v>40</v>
+      </c>
+      <c r="I20" s="16">
+        <f t="shared" si="0"/>
+        <v>4400</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="15"/>
+      <c r="Q20" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="15"/>
+      <c r="B21" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>2254</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>2255</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>2256</v>
+      </c>
+      <c r="F21" s="16">
+        <v>10</v>
+      </c>
+      <c r="G21" s="16">
+        <v>795</v>
+      </c>
+      <c r="H21" s="16">
+        <v>25</v>
+      </c>
+      <c r="I21" s="16">
+        <f t="shared" si="0"/>
+        <v>770</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>2257</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>2258</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>2259</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="G22" s="16">
+        <v>850</v>
+      </c>
+      <c r="H22" s="16">
+        <v>20</v>
+      </c>
+      <c r="I22" s="16">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="15"/>
+      <c r="B23" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>2260</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>2261</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>2262</v>
+      </c>
+      <c r="F23" s="16">
+        <v>10</v>
+      </c>
+      <c r="G23" s="16">
+        <v>0</v>
+      </c>
+      <c r="H23" s="16">
+        <v>25</v>
+      </c>
+      <c r="I23" s="16">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K23" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="15">
+        <v>1</v>
+      </c>
+      <c r="R23" s="10">
+        <f>H23</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="15"/>
+      <c r="B24" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>2263</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F24" s="16">
+        <v>10</v>
+      </c>
+      <c r="G24" s="16">
+        <v>915</v>
+      </c>
+      <c r="H24" s="16">
+        <v>25</v>
+      </c>
+      <c r="I24" s="16">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D26" s="1">
+        <f>COUNTA(D3:D24)</f>
+        <v>21</v>
+      </c>
+      <c r="G26" s="1">
+        <f t="shared" ref="G26:Q26" si="1">SUBTOTAL(9,G3:G24)</f>
+        <v>10570</v>
+      </c>
+      <c r="H26" s="1">
+        <f t="shared" si="1"/>
+        <v>310</v>
+      </c>
+      <c r="I26" s="1">
+        <f t="shared" si="1"/>
+        <v>10260</v>
+      </c>
+      <c r="J26" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M26" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N26" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O26" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P26" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="1">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H27">
+        <f>-4*17</f>
+        <v>-68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="D28" s="37"/>
+      <c r="E28" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="H28">
+        <f>-2*25</f>
+        <v>-50</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>2209</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="O28" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>2210</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C29" s="38">
+        <f>SUMIFS(I$3:I$24,B$3:B$24,A$28,L$3:L$24,A$29)</f>
+        <v>31314</v>
+      </c>
+      <c r="D29" s="38"/>
+      <c r="E29" s="3">
+        <f>SUMIFS(Q$3:Q$24,B$3:B$24,A$28,L$3:L$24,A$29)</f>
+        <v>22</v>
+      </c>
+      <c r="F29" t="s">
+        <v>196</v>
+      </c>
+      <c r="H29">
+        <f>-2*30</f>
+        <v>-60</v>
+      </c>
+      <c r="K29" t="s">
+        <v>197</v>
+      </c>
+      <c r="L29">
+        <f>SUMIFS(G$3:G$24,J$3:J$24,K$28)</f>
+        <v>18879</v>
+      </c>
+      <c r="M29">
+        <f>SUMIFS(Q$3:Q$24,J$3:J$24,K$28)-INT(COUNTIFS(J$3:J$24,K$28,M$3:M$24,"*gộp*")/2)</f>
+        <v>8</v>
+      </c>
+      <c r="O29" t="s">
+        <v>2264</v>
+      </c>
+      <c r="P29">
+        <f>L34</f>
+        <v>18701</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C30" s="39">
+        <v>0</v>
+      </c>
+      <c r="D30" s="39"/>
+      <c r="K30" t="s">
+        <v>200</v>
+      </c>
+      <c r="L30">
+        <f>SUM(H27:H29)</f>
+        <v>-178</v>
+      </c>
+      <c r="M30">
+        <f>SUMIFS(Q$3:Q$24,J$3:J$24,K$28)-INT(COUNTIFS(J$3:J$24,K$28,M$3:M$24,"*gộp*")/2)</f>
+        <v>8</v>
+      </c>
+      <c r="O30" t="s">
+        <v>21</v>
+      </c>
+      <c r="P30">
+        <f>L42</f>
+        <v>10266</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B31" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C31" s="39">
+        <f>-SUMIFS(I$3:I$24,B$3:B$24,A$28,P$3:P$24,"xx",N$3:N$24,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="D31" s="39"/>
+      <c r="E31" s="2">
+        <f>SUMIFS(Q$3:Q$24,B$3:B$24,A$28,P$3:P$24,"xx",N$3:N$24,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
+        <v>202</v>
+      </c>
+      <c r="O31" t="s">
+        <v>135</v>
+      </c>
+      <c r="P31">
+        <f>L50</f>
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B32" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C32" s="37">
+        <f>SUBTOTAL(9,C29:C31)</f>
+        <v>31314</v>
+      </c>
+      <c r="D32" s="37"/>
+      <c r="E32">
+        <f>E29</f>
+        <v>22</v>
+      </c>
+      <c r="K32" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="O32" t="s">
+        <v>207</v>
+      </c>
+      <c r="P32">
+        <f>-C36</f>
+        <v>-31314</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B33" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C33" s="35"/>
+      <c r="D33" s="35"/>
+      <c r="K33" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="O33" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="P33" s="4">
+        <f>SUBTOTAL(9,P29:P32)</f>
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B34" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="L34" s="13">
+        <f>SUBTOTAL(9,L29:L33)</f>
+        <v>18701</v>
+      </c>
+      <c r="M34" s="13">
+        <f>M29</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B36" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C36" s="36">
+        <f>C32+C33+C34</f>
+        <v>31314</v>
+      </c>
+      <c r="D36" s="36"/>
+      <c r="E36" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="M36" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K37" t="s">
+        <v>197</v>
+      </c>
+      <c r="L37">
+        <f>SUMIFS(G$3:G$24,J$3:J$24,K$36)</f>
+        <v>10570</v>
+      </c>
+      <c r="M37">
+        <f>SUMIFS(Q$3:Q$24,J$3:J$24,K$36)-INT(COUNTIFS(J$3:J$24,K$36,M$3:M$24,"*gộp*")/2)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K38" t="s">
+        <v>200</v>
+      </c>
+      <c r="L38">
+        <f>-SUMIFS(H$3:H$24,J$3:J$24,K$36)+M38*5</f>
+        <v>-260</v>
+      </c>
+      <c r="M38">
+        <f>SUMIFS(Q$3:Q$24,J$3:J$24,K$36)-INT(COUNTIFS(J$3:J$24,K$36,M$3:M$24,"*gộp*")/2)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K39" t="s">
+        <v>202</v>
+      </c>
+      <c r="L39">
+        <f>-M39*2</f>
+        <v>-44</v>
+      </c>
+      <c r="M39">
+        <f>E32-(COUNTIFS(M$3:M$24,"*gộp*")/2)-COUNTIFS(M$3:M$24,"*đơn trả*")-COUNTIFS(M$3:M$24,"*hàng tỉnh*")</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K40" s="31" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K41" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="L42" s="13">
+        <f>SUBTOTAL(9,L37:L41)</f>
+        <v>10266</v>
+      </c>
+      <c r="M42" s="13">
+        <f>M37</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K44" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="L44" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K45" t="s">
+        <v>197</v>
+      </c>
+      <c r="L45">
+        <f>SUMIFS(G$3:G$24,J$3:J$24,K$44)</f>
+        <v>2560</v>
+      </c>
+      <c r="M45">
+        <f>SUMIFS(Q$3:Q$24,J$3:J$24,K$44)-INT(COUNTIFS(J$3:J$24,K$44,M$3:M$24,"*gộp*")/2)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K46" t="s">
+        <v>200</v>
+      </c>
+      <c r="L46">
+        <f>-SUMIFS(H$3:H$24,J$3:J$24,K$44)+M46*5</f>
+        <v>-75</v>
+      </c>
+      <c r="M46">
+        <f>SUMIFS(Q$3:Q$24,J$3:J$24,K$44)-INT(COUNTIFS(J$3:J$24,K$44,M$3:M$24,"*gộp*")/2)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K47" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K48" s="31" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="49" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K49" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="50" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L50" s="13">
+        <f>SUBTOTAL(9,L45:L49)</f>
+        <v>2485</v>
+      </c>
+      <c r="M50" s="13">
+        <f>M45</f>
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P24" xr:uid="{00000000-0009-0000-0000-000017000000}">
+    <filterColumn colId="9">
+      <filters>
+        <filter val="c.cuong"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P24">
+      <sortCondition ref="J2:J24"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
+  <dimension ref="A2:Q57"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="35.5703125" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="55.140625" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="9.42578125" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="15"/>
+      <c r="B3" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>2309</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>2310</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>2311</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="16">
+        <v>845</v>
+      </c>
+      <c r="H3" s="16">
+        <v>25</v>
+      </c>
+      <c r="I3" s="16">
+        <f t="shared" ref="I3:I31" si="0">G3-H3</f>
+        <v>820</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>2312</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>2317</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>2318</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G4" s="16">
+        <v>915</v>
+      </c>
+      <c r="H4" s="16">
+        <v>25</v>
+      </c>
+      <c r="I4" s="16">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>2312</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="15"/>
+      <c r="B5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>2321</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>2322</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>2323</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="16">
+        <v>1640</v>
+      </c>
+      <c r="H5" s="16">
+        <v>30</v>
+      </c>
+      <c r="I5" s="16">
+        <f t="shared" si="0"/>
+        <v>1610</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>2312</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="15"/>
+      <c r="B6" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>2331</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>2332</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>2333</v>
+      </c>
+      <c r="F6" s="16">
+        <v>8</v>
+      </c>
+      <c r="G6" s="16">
+        <v>0</v>
+      </c>
+      <c r="H6" s="16">
+        <v>30</v>
+      </c>
+      <c r="I6" s="16">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>2312</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>2336</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>1443</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="16">
+        <v>0</v>
+      </c>
+      <c r="H7" s="16">
+        <v>30</v>
+      </c>
+      <c r="I7" s="16">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>2312</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="15"/>
+      <c r="B8" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>2348</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>2349</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>2350</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="16">
+        <v>0</v>
+      </c>
+      <c r="H8" s="16">
+        <v>30</v>
+      </c>
+      <c r="I8" s="16">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>2312</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>1585</v>
+      </c>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15" t="s">
+        <v>632</v>
+      </c>
+      <c r="F9" s="16">
+        <v>6</v>
+      </c>
+      <c r="G9" s="16">
+        <v>0</v>
+      </c>
+      <c r="H9" s="16">
+        <v>30</v>
+      </c>
+      <c r="I9" s="16">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>2312</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>2275</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>2276</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>2277</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="16">
+        <v>1825</v>
+      </c>
+      <c r="H10" s="16">
+        <v>25</v>
+      </c>
+      <c r="I10" s="16">
+        <f t="shared" si="0"/>
+        <v>1800</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="15"/>
+      <c r="B11" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>2282</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>2283</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>2284</v>
+      </c>
+      <c r="F11" s="16">
+        <v>2</v>
+      </c>
+      <c r="G11" s="16">
+        <v>850</v>
+      </c>
+      <c r="H11" s="16">
+        <v>30</v>
+      </c>
+      <c r="I11" s="16">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="15"/>
+      <c r="B12" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>2288</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>2289</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>2290</v>
+      </c>
+      <c r="F12" s="16">
+        <v>2</v>
+      </c>
+      <c r="G12" s="16">
+        <v>1110</v>
+      </c>
+      <c r="H12" s="16">
+        <v>30</v>
+      </c>
+      <c r="I12" s="16">
+        <f t="shared" si="0"/>
+        <v>1080</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>2294</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>2295</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>2296</v>
+      </c>
+      <c r="F13" s="16">
+        <v>2</v>
+      </c>
+      <c r="G13" s="16">
+        <v>1740</v>
+      </c>
+      <c r="H13" s="16">
+        <v>30</v>
+      </c>
+      <c r="I13" s="16">
+        <f t="shared" si="0"/>
+        <v>1710</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="15"/>
+      <c r="B14" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>2303</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>2304</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>2305</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" s="16">
+        <v>520</v>
+      </c>
+      <c r="H14" s="16">
+        <v>30</v>
+      </c>
+      <c r="I14" s="16">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="15"/>
+      <c r="B15" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>2313</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>2314</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>2315</v>
+      </c>
+      <c r="F15" s="16">
+        <v>2</v>
+      </c>
+      <c r="G15" s="16">
+        <v>550</v>
+      </c>
+      <c r="H15" s="16">
+        <v>30</v>
+      </c>
+      <c r="I15" s="16">
+        <f t="shared" si="0"/>
+        <v>520</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>2320</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>2115</v>
+      </c>
+      <c r="F16" s="16">
+        <v>12</v>
+      </c>
+      <c r="G16" s="16">
+        <v>0</v>
+      </c>
+      <c r="H16" s="16">
+        <v>30</v>
+      </c>
+      <c r="I16" s="16">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>2244</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>2324</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>2325</v>
+      </c>
+      <c r="F17" s="18">
+        <v>12</v>
+      </c>
+      <c r="G17" s="18">
+        <v>130</v>
+      </c>
+      <c r="H17" s="18">
+        <v>30</v>
+      </c>
+      <c r="I17" s="18">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="17" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M17" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="15"/>
+      <c r="B18" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>2334</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>2335</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>503</v>
+      </c>
+      <c r="F18" s="16">
+        <v>12</v>
+      </c>
+      <c r="G18" s="16">
+        <v>0</v>
+      </c>
+      <c r="H18" s="16">
+        <v>0</v>
+      </c>
+      <c r="I18" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M18" s="20" t="s">
+        <v>377</v>
+      </c>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>2334</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>2338</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>503</v>
+      </c>
+      <c r="F19" s="16">
+        <v>12</v>
+      </c>
+      <c r="G19" s="16">
+        <v>0</v>
+      </c>
+      <c r="H19" s="16">
+        <v>40</v>
+      </c>
+      <c r="I19" s="16">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M19" s="20" t="s">
+        <v>377</v>
+      </c>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="15"/>
+      <c r="Q19" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="15"/>
+      <c r="B20" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>2339</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>2340</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>2341</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="16">
+        <v>775</v>
+      </c>
+      <c r="H20" s="16">
+        <v>25</v>
+      </c>
+      <c r="I20" s="16">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="15"/>
+      <c r="Q20" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="15"/>
+      <c r="B21" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>2342</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>2343</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>2344</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="16">
+        <v>0</v>
+      </c>
+      <c r="H21" s="16">
+        <v>25</v>
+      </c>
+      <c r="I21" s="16">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>2279</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>2280</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>2281</v>
+      </c>
+      <c r="F22" s="16">
+        <v>7</v>
+      </c>
+      <c r="G22" s="16">
+        <v>0</v>
+      </c>
+      <c r="H22" s="16">
+        <v>30</v>
+      </c>
+      <c r="I22" s="16">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" s="15"/>
+      <c r="B23" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>2285</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>2286</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>2287</v>
+      </c>
+      <c r="F23" s="16">
+        <v>7</v>
+      </c>
+      <c r="G23" s="16">
+        <v>1730</v>
+      </c>
+      <c r="H23" s="16">
+        <v>30</v>
+      </c>
+      <c r="I23" s="16">
+        <f t="shared" si="0"/>
+        <v>1700</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K23" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="15"/>
+      <c r="B24" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>2291</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>2292</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>2293</v>
+      </c>
+      <c r="F24" s="16">
+        <v>1</v>
+      </c>
+      <c r="G24" s="16">
+        <v>0</v>
+      </c>
+      <c r="H24" s="16">
+        <v>25</v>
+      </c>
+      <c r="I24" s="16">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="15"/>
+      <c r="B25" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>2297</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>2298</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>2299</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="G25" s="16">
+        <v>525</v>
+      </c>
+      <c r="H25" s="16">
+        <v>35</v>
+      </c>
+      <c r="I25" s="16">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M25" s="15"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="15"/>
+      <c r="P25" s="15"/>
+      <c r="Q25" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" s="15"/>
+      <c r="B26" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>2300</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>2301</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>2302</v>
+      </c>
+      <c r="F26" s="16">
+        <v>7</v>
+      </c>
+      <c r="G26" s="16">
+        <v>1110</v>
+      </c>
+      <c r="H26" s="16">
+        <v>30</v>
+      </c>
+      <c r="I26" s="16">
+        <f t="shared" si="0"/>
+        <v>1080</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>2306</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>2307</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>2308</v>
+      </c>
+      <c r="F27" s="16">
+        <v>1</v>
+      </c>
+      <c r="G27" s="16">
+        <v>0</v>
+      </c>
+      <c r="H27" s="16">
+        <v>25</v>
+      </c>
+      <c r="I27" s="16">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J27" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K27" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>2316</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="F28" s="16">
+        <v>3</v>
+      </c>
+      <c r="G28" s="16">
+        <v>0</v>
+      </c>
+      <c r="H28" s="16">
+        <v>25</v>
+      </c>
+      <c r="I28" s="16">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>2337</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F29" s="16">
+        <v>4</v>
+      </c>
+      <c r="G29" s="16">
+        <v>1185</v>
+      </c>
+      <c r="H29" s="16">
+        <v>25</v>
+      </c>
+      <c r="I29" s="16">
+        <f t="shared" si="0"/>
+        <v>1160</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="15"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="15"/>
+      <c r="B30" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>2345</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>2346</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>2347</v>
+      </c>
+      <c r="F30" s="16">
+        <v>7</v>
+      </c>
+      <c r="G30" s="16">
+        <v>1600</v>
+      </c>
+      <c r="H30" s="16">
+        <v>30</v>
+      </c>
+      <c r="I30" s="16">
+        <f t="shared" si="0"/>
+        <v>1570</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M30" s="15"/>
+      <c r="N30" s="15"/>
+      <c r="O30" s="15"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="21" t="s">
+        <v>2352</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>2326</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>2327</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>2328</v>
+      </c>
+      <c r="F31" s="21" t="s">
+        <v>2329</v>
+      </c>
+      <c r="G31" s="22">
+        <v>570</v>
+      </c>
+      <c r="H31" s="22">
+        <v>0</v>
+      </c>
+      <c r="I31" s="22">
+        <f t="shared" si="0"/>
+        <v>570</v>
+      </c>
+      <c r="J31" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="K31" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="21" t="s">
+        <v>2278</v>
+      </c>
+      <c r="M31" s="21" t="s">
+        <v>2330</v>
+      </c>
+      <c r="N31" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="O31" s="21"/>
+      <c r="P31" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q31" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D33" s="1">
+        <f>COUNTA(D3:D31)</f>
+        <v>28</v>
+      </c>
+      <c r="G33" s="1">
+        <f t="shared" ref="G33:Q33" si="1">SUBTOTAL(9,G3:G31)</f>
+        <v>17620</v>
+      </c>
+      <c r="H33" s="1">
+        <f t="shared" si="1"/>
+        <v>780</v>
+      </c>
+      <c r="I33" s="1">
+        <f t="shared" si="1"/>
+        <v>16840</v>
+      </c>
+      <c r="J33" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M33" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N33" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O33" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P33" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q33" s="1">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H34">
+        <f>-4*17</f>
+        <v>-68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="D35" s="37"/>
+      <c r="E35" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="H35">
+        <f>-3*25</f>
+        <v>-75</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="O35" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C36" s="38">
+        <f>SUMIFS(I$3:I$31,B$3:B$31,A$35,L$3:L$31,A$36)</f>
+        <v>16840</v>
+      </c>
+      <c r="D36" s="38"/>
+      <c r="E36" s="3">
+        <f>SUMIFS(Q$3:Q$31,B$3:B$31,A$35,L$3:L$31,A$36)</f>
+        <v>29</v>
+      </c>
+      <c r="F36" t="s">
+        <v>196</v>
+      </c>
+      <c r="K36" t="s">
+        <v>197</v>
+      </c>
+      <c r="L36">
+        <f>SUMIFS(G$3:G$31,J$3:J$31,K$35)</f>
+        <v>7500</v>
+      </c>
+      <c r="M36">
+        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$35)-INT(COUNTIFS(J$3:J$31,K$35,M$3:M$31,"*gộp*")/2)</f>
+        <v>11</v>
+      </c>
+      <c r="O36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P36">
+        <f>L41</f>
+        <v>7176</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B37" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C37" s="39">
+        <v>0</v>
+      </c>
+      <c r="D37" s="39"/>
+      <c r="K37" t="s">
+        <v>200</v>
+      </c>
+      <c r="L37">
+        <f>-SUMIFS(H$3:H$31,J$3:J$31,K$35)+M37*5</f>
+        <v>-270</v>
+      </c>
+      <c r="M37">
+        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$35)-INT(COUNTIFS(J$3:J$31,K$35,M$3:M$31,"*gộp*")/2)</f>
+        <v>11</v>
+      </c>
+      <c r="O37" t="s">
+        <v>135</v>
+      </c>
+      <c r="P37">
+        <f>L49</f>
+        <v>5940</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B38" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C38" s="39">
+        <f>-SUMIFS(I$3:I$31,B$3:B$31,A$35,P$3:P$31,"xx",N$3:N$31,"x")</f>
+        <v>-570</v>
+      </c>
+      <c r="D38" s="39"/>
+      <c r="E38" s="2">
+        <f>SUMIFS(Q$3:Q$31,B$3:B$31,A$35,P$3:P$31,"xx",N$3:N$31,"x")</f>
+        <v>1</v>
+      </c>
+      <c r="K38" t="s">
+        <v>202</v>
+      </c>
+      <c r="L38">
+        <f>-M38*2</f>
+        <v>-54</v>
+      </c>
+      <c r="M38">
+        <f>E39-(COUNTIFS(M$3:M$31,"*gộp*")/2)-COUNTIFS(M$3:M$31,"*đơn trả*")-COUNTIFS(M$3:M$31,"*hàng tỉnh*")</f>
+        <v>27</v>
+      </c>
+      <c r="O38" t="s">
+        <v>2351</v>
+      </c>
+      <c r="P38">
+        <f>L57</f>
+        <v>3257</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B39" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C39" s="37">
+        <f>SUBTOTAL(9,C36:C38)</f>
+        <v>16270</v>
+      </c>
+      <c r="D39" s="37"/>
+      <c r="E39">
+        <f>E36</f>
+        <v>29</v>
+      </c>
+      <c r="K39" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="O39" t="s">
+        <v>207</v>
+      </c>
+      <c r="P39">
+        <f>-C43</f>
+        <v>-16270</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B40" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C40" s="35"/>
+      <c r="D40" s="35"/>
+      <c r="K40" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="O40" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="P40" s="4">
+        <f>SUBTOTAL(9,P36:P39)</f>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B41" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C41" s="35"/>
+      <c r="D41" s="35"/>
+      <c r="L41" s="13">
+        <f>SUBTOTAL(9,L36:L40)</f>
+        <v>7176</v>
+      </c>
+      <c r="M41" s="13">
+        <f>M36</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B43" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C43" s="36">
+        <f>C39+C40+C41</f>
+        <v>16270</v>
+      </c>
+      <c r="D43" s="36"/>
+      <c r="E43" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="M43" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K44" t="s">
+        <v>197</v>
+      </c>
+      <c r="L44">
+        <f>SUMIFS(G$3:G$31,J$3:J$31,K$43)</f>
+        <v>6150</v>
+      </c>
+      <c r="M44">
+        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$43)-INT(COUNTIFS(J$3:J$31,K$43,M$3:M$31,"*gộp*")/2)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K45" t="s">
+        <v>200</v>
+      </c>
+      <c r="L45">
+        <f>-SUMIFS(H$3:H$31,J$3:J$31,K$43)+M45*5</f>
+        <v>-210</v>
+      </c>
+      <c r="M45">
+        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$43)-INT(COUNTIFS(J$3:J$31,K$43,M$3:M$31,"*gộp*")/2)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K46" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K47" s="31" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K48" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="49" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L49" s="13">
+        <f>SUBTOTAL(9,L44:L48)</f>
+        <v>5940</v>
+      </c>
+      <c r="M49" s="13">
+        <f>M44</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K51" s="11" t="s">
+        <v>2312</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="52" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K52" t="s">
+        <v>197</v>
+      </c>
+      <c r="L52">
+        <f>SUMIFS(G$3:G$31,J$3:J$31,K$51)</f>
+        <v>3400</v>
+      </c>
+      <c r="M52">
+        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$51)-INT(COUNTIFS(J$3:J$31,K$51,M$3:M$31,"*gộp*")/2)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K53" t="s">
+        <v>200</v>
+      </c>
+      <c r="L53">
+        <f>SUM(H34:H35)</f>
+        <v>-143</v>
+      </c>
+      <c r="M53">
+        <f>SUMIFS(Q$3:Q$31,J$3:J$31,K$51)-INT(COUNTIFS(J$3:J$31,K$51,M$3:M$31,"*gộp*")/2)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K54" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="55" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K55" s="31" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="56" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K56" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="57" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L57" s="13">
+        <f>SUBTOTAL(9,L52:L56)</f>
+        <v>3257</v>
+      </c>
+      <c r="M57" s="13">
+        <f>M52</f>
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P31" xr:uid="{00000000-0009-0000-0000-000019000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P31">
+      <sortCondition ref="J2:J31"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D9B982-EAEB-4F31-86BF-4D059AFDEA27}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
@@ -40410,7 +44008,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>2133</v>
+        <v>2265</v>
       </c>
       <c r="B1" s="5">
         <v>2026</v>
@@ -40418,19 +44016,19 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>2134</v>
+        <v>2266</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2135</v>
+        <v>2267</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>2136</v>
+        <v>2268</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>2137</v>
+        <v>2269</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>2138</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -40459,15 +44057,15 @@
         <v>46146</v>
       </c>
       <c r="B4" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A4,"dd-mm")&amp;"-"&amp;B$1),0)</f>
+        <f t="shared" ref="B4:B27" ca="1" si="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A4,"dd-mm")&amp;"-"&amp;B$1),0)</f>
         <v>20</v>
       </c>
       <c r="C4" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
+        <f t="shared" ref="C4:C27" ca="1" si="2">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
         <v>0</v>
       </c>
       <c r="D4" s="8" cm="1">
-        <f t="array" ref="D4" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D4" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>4</v>
       </c>
       <c r="E4" s="8">
@@ -40480,20 +44078,20 @@
         <v>46147</v>
       </c>
       <c r="B5" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A5,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>53</v>
       </c>
       <c r="C5" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
       </c>
       <c r="D5" s="8" cm="1">
-        <f t="array" ref="D5" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A5,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D5" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A5,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>0</v>
       </c>
       <c r="E5" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -40501,20 +44099,20 @@
         <v>46148</v>
       </c>
       <c r="B6" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A6,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>32</v>
       </c>
       <c r="C6" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="D6" s="8" cm="1">
-        <f t="array" ref="D6" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A6,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D6" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A6,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>0</v>
       </c>
       <c r="E6" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -40522,20 +44120,20 @@
         <v>46149</v>
       </c>
       <c r="B7" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A7,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>34</v>
       </c>
       <c r="C7" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="D7" s="8" cm="1">
-        <f t="array" ref="D7" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A7,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D7" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A7,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>0</v>
       </c>
       <c r="E7" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -40543,20 +44141,20 @@
         <v>46150</v>
       </c>
       <c r="B8" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A8,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>36</v>
       </c>
       <c r="C8" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="D8" s="8" cm="1">
-        <f t="array" ref="D8" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A8,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D8" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A8,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>0</v>
       </c>
       <c r="E8" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -40564,20 +44162,20 @@
         <v>46151</v>
       </c>
       <c r="B9" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A9,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>31</v>
       </c>
       <c r="C9" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="D9" s="8" cm="1">
-        <f t="array" ref="D9" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A9,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D9" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A9,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>0</v>
       </c>
       <c r="E9" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -40585,20 +44183,20 @@
         <v>46153</v>
       </c>
       <c r="B10" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A10,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>56</v>
       </c>
       <c r="C10" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="D10" s="8" cm="1">
-        <f t="array" ref="D10" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A10,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D10" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A10,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>4</v>
       </c>
       <c r="E10" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -40606,20 +44204,20 @@
         <v>46154</v>
       </c>
       <c r="B11" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A11,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>25</v>
       </c>
       <c r="C11" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="D11" s="8" cm="1">
-        <f t="array" ref="D11" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A11,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D11" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A11,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>0</v>
       </c>
       <c r="E11" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -40627,20 +44225,20 @@
         <v>46155</v>
       </c>
       <c r="B12" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A12,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>33</v>
       </c>
       <c r="C12" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="D12" s="8" cm="1">
-        <f t="array" ref="D12" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A12,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D12" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A12,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>0</v>
       </c>
       <c r="E12" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -40648,20 +44246,20 @@
         <v>46156</v>
       </c>
       <c r="B13" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A13,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>37</v>
       </c>
       <c r="C13" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="D13" s="8" cm="1">
-        <f t="array" ref="D13" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A13,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D13" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A13,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>0</v>
       </c>
       <c r="E13" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -40669,20 +44267,20 @@
         <v>46157</v>
       </c>
       <c r="B14" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A14,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>32</v>
       </c>
       <c r="C14" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="D14" s="8" cm="1">
-        <f t="array" ref="D14" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A14,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D14" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A14,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>0</v>
       </c>
       <c r="E14" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -40690,20 +44288,20 @@
         <v>46158</v>
       </c>
       <c r="B15" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A15,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>37</v>
       </c>
       <c r="C15" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
       </c>
       <c r="D15" s="8" cm="1">
-        <f t="array" ref="D15" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A15,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D15" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A15,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>2</v>
       </c>
       <c r="E15" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -40711,20 +44309,20 @@
         <v>46160</v>
       </c>
       <c r="B16" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A16,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>39</v>
       </c>
       <c r="C16" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="D16" s="8" cm="1">
-        <f t="array" ref="D16" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A16,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D16" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A16,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>0</v>
       </c>
       <c r="E16" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -40732,20 +44330,20 @@
         <v>46161</v>
       </c>
       <c r="B17" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A17,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>27</v>
       </c>
       <c r="C17" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="D17" s="8" cm="1">
-        <f t="array" ref="D17" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A17,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D17" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A17,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>0</v>
       </c>
       <c r="E17" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -40753,20 +44351,20 @@
         <v>46162</v>
       </c>
       <c r="B18" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A18,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>31</v>
       </c>
       <c r="C18" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="D18" s="8" cm="1">
-        <f t="array" ref="D18" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A18,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D18" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A18,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>3</v>
       </c>
       <c r="E18" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -40774,20 +44372,20 @@
         <v>46163</v>
       </c>
       <c r="B19" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A19,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>40</v>
       </c>
       <c r="C19" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="D19" s="8" cm="1">
-        <f t="array" ref="D19" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A19,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D19" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A19,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>1</v>
       </c>
       <c r="E19" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -40795,20 +44393,20 @@
         <v>46164</v>
       </c>
       <c r="B20" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A20,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>26</v>
       </c>
       <c r="C20" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="D20" s="8" cm="1">
-        <f t="array" ref="D20" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A20,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D20" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A20,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>1</v>
       </c>
       <c r="E20" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -40816,20 +44414,20 @@
         <v>46165</v>
       </c>
       <c r="B21" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A21,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>26</v>
       </c>
       <c r="C21" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="D21" s="8" cm="1">
-        <f t="array" ref="D21" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A21,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D21" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A21,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>0</v>
       </c>
       <c r="E21" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -40837,20 +44435,20 @@
         <v>46167</v>
       </c>
       <c r="B22" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A22,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>53</v>
       </c>
       <c r="C22" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
       </c>
       <c r="D22" s="8" cm="1">
-        <f t="array" ref="D22" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A22,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D22" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A22,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>0</v>
       </c>
       <c r="E22" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -40858,20 +44456,20 @@
         <v>46168</v>
       </c>
       <c r="B23" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A23,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>27</v>
       </c>
       <c r="C23" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="D23" s="8" cm="1">
-        <f t="array" ref="D23" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A23,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>2</v>
+        <f t="array" aca="1" ref="D23" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A23,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>1</v>
       </c>
       <c r="E23" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -40879,20 +44477,20 @@
         <v>46169</v>
       </c>
       <c r="B24" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A24,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>24</v>
       </c>
       <c r="C24" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="D24" s="8" cm="1">
-        <f t="array" ref="D24" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A24,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D24" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A24,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>0</v>
       </c>
       <c r="E24" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -40900,20 +44498,20 @@
         <v>46170</v>
       </c>
       <c r="B25" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A25,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>26</v>
       </c>
       <c r="C25" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="D25" s="8" cm="1">
-        <f t="array" ref="D25" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A25,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D25" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A25,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>1</v>
       </c>
       <c r="E25" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -40921,20 +44519,20 @@
         <v>46171</v>
       </c>
       <c r="B26" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A26,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>22</v>
       </c>
       <c r="C26" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
       <c r="D26" s="8" cm="1">
-        <f t="array" ref="D26" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A26,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <f t="array" aca="1" ref="D26" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A26,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
         <v>0</v>
       </c>
       <c r="E26" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -40942,34 +44540,34 @@
         <v>46172</v>
       </c>
       <c r="B27" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A27,"dd-mm")&amp;"-"&amp;B$1),0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>29</v>
       </c>
       <c r="C27" s="8">
-        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
       <c r="D27" s="8" cm="1">
-        <f t="array" ref="D27" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A27,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
+        <f t="array" aca="1" ref="D27" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A27,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
+        <v>1</v>
       </c>
       <c r="E27" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D28" s="9" t="s">
-        <v>2139</v>
+        <v>2271</v>
       </c>
       <c r="E28" s="9">
         <f ca="1">SUBTOTAL(9,E4:E27)</f>
-        <v>2</v>
+        <v>765</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D29" s="9" t="s">
-        <v>2140</v>
+        <v>2272</v>
       </c>
       <c r="E29" s="9" cm="1">
         <f t="array" ref="E29" ca="1">SUMPRODUCT(
@@ -40981,29 +44579,29 @@
         ),
     0)
 )</f>
-        <v>3048</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D30" s="9" t="s">
-        <v>2141</v>
+        <v>2273</v>
       </c>
       <c r="E30" s="9">
         <f ca="1">-E28*2</f>
-        <v>-4</v>
+        <v>-1530</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D31" s="9" t="s">
-        <v>2142</v>
+        <v>2274</v>
       </c>
       <c r="E31" s="9">
         <f ca="1">SUBTOTAL(9,E29:E30)</f>
-        <v>3044</v>
+        <v>1792</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E27" xr:uid="{00000000-0009-0000-0000-000016000000}"/>
+  <autoFilter ref="A2:E27" xr:uid="{00000000-0009-0000-0000-000018000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C3:D27">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/data/May/InternalDailyReport_May.xlsx
+++ b/data/May/InternalDailyReport_May.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC58D0A-4972-4BA7-B7D5-B79F70F80CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16340A31-F214-4BD7-93EC-685331CF5B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="7" r:id="rId1"/>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8343" uniqueCount="2353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8330" uniqueCount="2353">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -7320,7 +7320,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7367,6 +7367,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -44561,8 +44567,8 @@
         <v>2271</v>
       </c>
       <c r="E28" s="9">
-        <f ca="1">SUBTOTAL(9,E4:E27)</f>
-        <v>765</v>
+        <f ca="1">SUBTOTAL(9,E3:E27)</f>
+        <v>819</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -44570,16 +44576,16 @@
         <v>2272</v>
       </c>
       <c r="E29" s="9" cm="1">
-        <f t="array" ref="E29" ca="1">SUMPRODUCT(
+        <f t="array" aca="1" ref="E29" ca="1">SUMPRODUCT(
     IFERROR(
         SUMIF(
-            INDIRECT("'"&amp;TEXT(A4:A27,"dd-mm")&amp;"'!O:O"),
+            INDIRECT("'"&amp;TEXT(A3:A27,"dd-mm")&amp;"'!O:O"),
             "tổng",
-            INDIRECT("'"&amp;TEXT(A4:A27,"dd-mm")&amp;"'!P:P")
+            INDIRECT("'"&amp;TEXT(A3:A27,"dd-mm")&amp;"'!P:P")
         ),
     0)
 )</f>
-        <v>3322</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -44588,7 +44594,7 @@
       </c>
       <c r="E30" s="9">
         <f ca="1">-E28*2</f>
-        <v>-1530</v>
+        <v>-1638</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -44597,7 +44603,7 @@
       </c>
       <c r="E31" s="9">
         <f ca="1">SUBTOTAL(9,E29:E30)</f>
-        <v>1792</v>
+        <v>1876</v>
       </c>
     </row>
   </sheetData>
@@ -60184,16 +60190,12 @@
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C42" s="37" t="s">
-        <v>191</v>
-      </c>
-      <c r="D42" s="37"/>
-      <c r="E42" s="4" t="s">
-        <v>192</v>
-      </c>
+      <c r="A42" s="40"/>
+      <c r="B42" s="41"/>
+      <c r="C42" s="42"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="41"/>
       <c r="K42" t="s">
         <v>200</v>
       </c>
@@ -60207,70 +60209,45 @@
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>813</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C43" s="38">
-        <f>SUMIFS(I$3:I$28,B$3:B$28,A$42,L$3:L$28,A$43)</f>
-        <v>890</v>
-      </c>
-      <c r="D43" s="38"/>
-      <c r="E43" s="3">
-        <f>SUMIFS(Q$3:Q$28,B$3:B$28,A$42,L$3:L$28,A$43)</f>
-        <v>1</v>
-      </c>
-      <c r="F43" t="s">
-        <v>196</v>
-      </c>
+      <c r="A43" s="41"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="41"/>
       <c r="K43" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B44" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C44" s="39">
-        <v>0</v>
-      </c>
-      <c r="D44" s="39"/>
+      <c r="A44" s="41"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="45"/>
+      <c r="D44" s="45"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="41"/>
       <c r="K44" s="2" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B45" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C45" s="39">
-        <f>-SUMIFS(I$3:I$28,B$3:B$28,A$42,P$3:P$28,"xx",N$3:N$28,"x")</f>
-        <v>0</v>
-      </c>
-      <c r="D45" s="39"/>
-      <c r="E45" s="2">
-        <f>SUMIFS(Q$3:Q$28,B$3:B$28,A$42,P$3:P$28,"xx",N$3:N$28,"x")</f>
-        <v>0</v>
-      </c>
+      <c r="A45" s="41"/>
+      <c r="B45" s="44"/>
+      <c r="C45" s="45"/>
+      <c r="D45" s="45"/>
+      <c r="E45" s="44"/>
+      <c r="F45" s="41"/>
       <c r="K45" s="2" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B46" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="C46" s="37">
-        <f>SUBTOTAL(9,C43:C45)</f>
-        <v>890</v>
-      </c>
-      <c r="D46" s="37"/>
-      <c r="E46">
-        <f>E43</f>
-        <v>1</v>
-      </c>
+      <c r="A46" s="41"/>
+      <c r="B46" s="40"/>
+      <c r="C46" s="42"/>
+      <c r="D46" s="42"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="41"/>
       <c r="L46" s="13">
         <f>SUBTOTAL(9,L41:L45)</f>
         <v>7451</v>
@@ -60281,18 +60258,20 @@
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B47" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C47" s="35"/>
-      <c r="D47" s="35"/>
+      <c r="A47" s="41"/>
+      <c r="B47" s="44"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="41"/>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B48" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="C48" s="35"/>
-      <c r="D48" s="35"/>
+      <c r="A48" s="41"/>
+      <c r="B48" s="41"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="41"/>
       <c r="K48" s="11" t="s">
         <v>135</v>
       </c>
@@ -60303,7 +60282,13 @@
         <v>192</v>
       </c>
     </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" s="41"/>
+      <c r="B49" s="41"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
       <c r="K49" t="s">
         <v>197</v>
       </c>
@@ -60316,18 +60301,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B50" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C50" s="36">
-        <f>C46+C47+C48</f>
-        <v>890</v>
-      </c>
-      <c r="D50" s="36"/>
-      <c r="E50" s="1" t="s">
-        <v>211</v>
-      </c>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" s="41"/>
+      <c r="B50" s="40"/>
+      <c r="C50" s="42"/>
+      <c r="D50" s="42"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="41"/>
       <c r="K50" t="s">
         <v>200</v>
       </c>
@@ -60340,24 +60320,30 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" s="41"/>
+      <c r="B51" s="41"/>
+      <c r="C51" s="41"/>
+      <c r="D51" s="41"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="41"/>
       <c r="K51" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="K52" s="2" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="K53" s="31" t="s">
         <v>206</v>
       </c>
       <c r="L53" s="23"/>
       <c r="M53" s="23"/>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="K54" s="2" t="s">
         <v>1005</v>
       </c>
@@ -60368,7 +60354,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="L55" s="13">
         <f>SUBTOTAL(9,L49:L54)</f>
         <v>3945</v>
@@ -60378,7 +60364,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="K57" s="11" t="s">
         <v>20</v>
       </c>
@@ -60389,7 +60375,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="K58" t="s">
         <v>197</v>
       </c>
@@ -60402,7 +60388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="K59" t="s">
         <v>200</v>
       </c>
@@ -60415,22 +60401,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="K60" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="K61" s="2" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="K62" s="2" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="L63" s="13">
         <f>SUBTOTAL(9,L58:L62)</f>
         <v>795</v>

--- a/data/May/InternalDailyReport_May.xlsx
+++ b/data/May/InternalDailyReport_May.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16340A31-F214-4BD7-93EC-685331CF5B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71246334-DEB9-4A5A-9730-E792706298FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="7" r:id="rId1"/>
@@ -7362,6 +7362,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7369,9 +7372,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -10255,10 +10255,10 @@
       <c r="A60" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C60" s="37" t="s">
+      <c r="C60" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D60" s="37"/>
+      <c r="D60" s="40"/>
       <c r="E60" s="4" t="s">
         <v>192</v>
       </c>
@@ -10286,11 +10286,11 @@
       <c r="B61" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="38">
+      <c r="C61" s="41">
         <f>SUMIFS(I$3:I$56,B$3:B$56,A$60,L$3:L$56,A$61)</f>
         <v>35295</v>
       </c>
-      <c r="D61" s="38"/>
+      <c r="D61" s="41"/>
       <c r="E61" s="3">
         <f>SUMIFS(Q$3:Q$56,B$3:B$56,A$60,L$3:L$56,A$61)</f>
         <v>54</v>
@@ -10321,10 +10321,10 @@
       <c r="B62" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C62" s="39">
-        <v>0</v>
-      </c>
-      <c r="D62" s="39"/>
+      <c r="C62" s="42">
+        <v>0</v>
+      </c>
+      <c r="D62" s="42"/>
       <c r="K62" t="s">
         <v>200</v>
       </c>
@@ -10348,11 +10348,11 @@
       <c r="B63" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C63" s="39">
+      <c r="C63" s="42">
         <f>-SUMIFS(I$3:I$56,B$3:B$56,A$60,P$3:P$56,"xx",N$3:N$56,"x")</f>
         <v>0</v>
       </c>
-      <c r="D63" s="39"/>
+      <c r="D63" s="42"/>
       <c r="E63" s="2">
         <f>SUMIFS(Q$3:Q$56,B$3:B$56,A$60,P$3:P$56,"xx",N$3:N$56,"x")</f>
         <v>0</v>
@@ -10372,11 +10372,11 @@
       <c r="B64" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C64" s="37">
+      <c r="C64" s="40">
         <f>SUBTOTAL(9,C61:C63)</f>
         <v>35295</v>
       </c>
-      <c r="D64" s="37"/>
+      <c r="D64" s="40"/>
       <c r="E64">
         <f>E61</f>
         <v>54</v>
@@ -10396,8 +10396,8 @@
       <c r="B65" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C65" s="35"/>
-      <c r="D65" s="35"/>
+      <c r="C65" s="38"/>
+      <c r="D65" s="38"/>
       <c r="K65" s="2" t="s">
         <v>206</v>
       </c>
@@ -10413,8 +10413,8 @@
       <c r="B66" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C66" s="35"/>
-      <c r="D66" s="35"/>
+      <c r="C66" s="38"/>
+      <c r="D66" s="38"/>
       <c r="L66" s="13">
         <f>SUBTOTAL(9,L61:L65)</f>
         <v>9140</v>
@@ -10435,11 +10435,11 @@
       <c r="B68" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C68" s="36">
+      <c r="C68" s="39">
         <f>C64+C65+C66</f>
         <v>35295</v>
       </c>
-      <c r="D68" s="36"/>
+      <c r="D68" s="39"/>
       <c r="E68" s="1" t="s">
         <v>211</v>
       </c>
@@ -12278,10 +12278,10 @@
       <c r="A39" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C39" s="37" t="s">
+      <c r="C39" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D39" s="37"/>
+      <c r="D39" s="40"/>
       <c r="E39" s="4" t="s">
         <v>192</v>
       </c>
@@ -12309,11 +12309,11 @@
       <c r="B40" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C40" s="38">
+      <c r="C40" s="41">
         <f>SUMIFS(I$3:I$35,B$3:B$35,A$39,L$3:L$35,A$40)</f>
         <v>24170</v>
       </c>
-      <c r="D40" s="38"/>
+      <c r="D40" s="41"/>
       <c r="E40" s="3">
         <f>SUMIFS(Q$3:Q$35,B$3:B$35,A$39,L$3:L$35,A$40)</f>
         <v>33</v>
@@ -12348,10 +12348,10 @@
       <c r="B41" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C41" s="39">
-        <v>0</v>
-      </c>
-      <c r="D41" s="39"/>
+      <c r="C41" s="42">
+        <v>0</v>
+      </c>
+      <c r="D41" s="42"/>
       <c r="K41" t="s">
         <v>200</v>
       </c>
@@ -12375,11 +12375,11 @@
       <c r="B42" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C42" s="39">
+      <c r="C42" s="42">
         <f>-SUMIFS(I$3:I$35,B$3:B$35,A$39,P$3:P$35,"xx",N$3:N$35,"x")</f>
         <v>0</v>
       </c>
-      <c r="D42" s="39"/>
+      <c r="D42" s="42"/>
       <c r="E42" s="2">
         <f>SUMIFS(Q$3:Q$35,B$3:B$35,A$39,P$3:P$35,"xx",N$3:N$35,"x")</f>
         <v>0</v>
@@ -12399,11 +12399,11 @@
       <c r="B43" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C43" s="37">
+      <c r="C43" s="40">
         <f>SUBTOTAL(9,C40:C42)</f>
         <v>24170</v>
       </c>
-      <c r="D43" s="37"/>
+      <c r="D43" s="40"/>
       <c r="E43">
         <f>E40</f>
         <v>33</v>
@@ -12423,8 +12423,8 @@
       <c r="B44" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C44" s="35"/>
-      <c r="D44" s="35"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="38"/>
       <c r="K44" s="2" t="s">
         <v>206</v>
       </c>
@@ -12440,8 +12440,8 @@
       <c r="B45" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C45" s="35"/>
-      <c r="D45" s="35"/>
+      <c r="C45" s="38"/>
+      <c r="D45" s="38"/>
       <c r="L45" s="13">
         <f>SUBTOTAL(9,L40:L44)</f>
         <v>5655</v>
@@ -12455,11 +12455,11 @@
       <c r="B47" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C47" s="36">
+      <c r="C47" s="39">
         <f>C43+C44+C45</f>
         <v>24170</v>
       </c>
-      <c r="D47" s="36"/>
+      <c r="D47" s="39"/>
       <c r="E47" s="1" t="s">
         <v>211</v>
       </c>
@@ -14402,10 +14402,10 @@
       <c r="A43" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C43" s="37" t="s">
+      <c r="C43" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D43" s="37"/>
+      <c r="D43" s="40"/>
       <c r="E43" s="4" t="s">
         <v>192</v>
       </c>
@@ -14433,11 +14433,11 @@
       <c r="B44" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C44" s="38">
+      <c r="C44" s="41">
         <f>SUMIFS(I$3:I$39,B$3:B$39,A$43,L$3:L$39,A$44)</f>
         <v>20340</v>
       </c>
-      <c r="D44" s="38"/>
+      <c r="D44" s="41"/>
       <c r="E44" s="3">
         <f>SUMIFS(Q$3:Q$39,B$3:B$39,A$43,L$3:L$39,A$44)</f>
         <v>37</v>
@@ -14468,10 +14468,10 @@
       <c r="B45" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C45" s="39">
-        <v>0</v>
-      </c>
-      <c r="D45" s="39"/>
+      <c r="C45" s="42">
+        <v>0</v>
+      </c>
+      <c r="D45" s="42"/>
       <c r="K45" t="s">
         <v>200</v>
       </c>
@@ -14495,11 +14495,11 @@
       <c r="B46" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C46" s="39">
+      <c r="C46" s="42">
         <f>-SUMIFS(I$3:I$39,B$3:B$39,A$43,P$3:P$39,"xx",N$3:N$39,"x")</f>
         <v>0</v>
       </c>
-      <c r="D46" s="39"/>
+      <c r="D46" s="42"/>
       <c r="E46" s="2">
         <f>SUMIFS(Q$3:Q$39,B$3:B$39,A$43,P$3:P$39,"xx",N$3:N$39,"x")</f>
         <v>0</v>
@@ -14527,11 +14527,11 @@
       <c r="B47" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C47" s="37">
+      <c r="C47" s="40">
         <f>SUBTOTAL(9,C44:C46)</f>
         <v>20340</v>
       </c>
-      <c r="D47" s="37"/>
+      <c r="D47" s="40"/>
       <c r="E47">
         <f>E44</f>
         <v>37</v>
@@ -14551,8 +14551,8 @@
       <c r="B48" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C48" s="35"/>
-      <c r="D48" s="35"/>
+      <c r="C48" s="38"/>
+      <c r="D48" s="38"/>
       <c r="K48" s="2" t="s">
         <v>206</v>
       </c>
@@ -14568,8 +14568,8 @@
       <c r="B49" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C49" s="35"/>
-      <c r="D49" s="35"/>
+      <c r="C49" s="38"/>
+      <c r="D49" s="38"/>
       <c r="L49" s="13">
         <f>SUBTOTAL(9,L44:L48)</f>
         <v>3176</v>
@@ -14590,11 +14590,11 @@
       <c r="B51" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C51" s="36">
+      <c r="C51" s="39">
         <f>C47+C48+C49</f>
         <v>20340</v>
       </c>
-      <c r="D51" s="36"/>
+      <c r="D51" s="39"/>
       <c r="E51" s="1" t="s">
         <v>211</v>
       </c>
@@ -16378,10 +16378,10 @@
       <c r="A38" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C38" s="37" t="s">
+      <c r="C38" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D38" s="37"/>
+      <c r="D38" s="40"/>
       <c r="E38" s="4" t="s">
         <v>192</v>
       </c>
@@ -16409,11 +16409,11 @@
       <c r="B39" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C39" s="38">
+      <c r="C39" s="41">
         <f>SUMIFS(I$3:I$34,B$3:B$34,A$38,L$3:L$34,A$39)</f>
         <v>26110</v>
       </c>
-      <c r="D39" s="38"/>
+      <c r="D39" s="41"/>
       <c r="E39" s="3">
         <f>SUMIFS(Q$3:Q$34,B$3:B$34,A$38,L$3:L$34,A$39)</f>
         <v>32</v>
@@ -16448,10 +16448,10 @@
       <c r="B40" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C40" s="39">
-        <v>0</v>
-      </c>
-      <c r="D40" s="39"/>
+      <c r="C40" s="42">
+        <v>0</v>
+      </c>
+      <c r="D40" s="42"/>
       <c r="K40" t="s">
         <v>200</v>
       </c>
@@ -16475,11 +16475,11 @@
       <c r="B41" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C41" s="39">
+      <c r="C41" s="42">
         <f>-SUMIFS(I$3:I$34,B$3:B$34,A$38,P$3:P$34,"xx",N$3:N$34,"x")</f>
         <v>0</v>
       </c>
-      <c r="D41" s="39"/>
+      <c r="D41" s="42"/>
       <c r="E41" s="2">
         <f>SUMIFS(Q$3:Q$34,B$3:B$34,A$38,P$3:P$34,"xx",N$3:N$34,"x")</f>
         <v>0</v>
@@ -16499,11 +16499,11 @@
       <c r="B42" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C42" s="37">
+      <c r="C42" s="40">
         <f>SUBTOTAL(9,C39:C41)</f>
         <v>26110</v>
       </c>
-      <c r="D42" s="37"/>
+      <c r="D42" s="40"/>
       <c r="E42">
         <f>E39</f>
         <v>32</v>
@@ -16523,8 +16523,8 @@
       <c r="B43" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="35"/>
-      <c r="D43" s="35"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="38"/>
       <c r="K43" s="2" t="s">
         <v>206</v>
       </c>
@@ -16540,8 +16540,8 @@
       <c r="B44" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C44" s="35"/>
-      <c r="D44" s="35"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="38"/>
       <c r="L44" s="13">
         <f>SUBTOTAL(9,L39:L43)</f>
         <v>13503</v>
@@ -16555,11 +16555,11 @@
       <c r="B46" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C46" s="36">
+      <c r="C46" s="39">
         <f>C42+C43+C44</f>
         <v>26110</v>
       </c>
-      <c r="D46" s="36"/>
+      <c r="D46" s="39"/>
       <c r="E46" s="1" t="s">
         <v>211</v>
       </c>
@@ -18695,10 +18695,10 @@
       <c r="A46" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="37" t="s">
+      <c r="C46" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D46" s="37"/>
+      <c r="D46" s="40"/>
       <c r="E46" s="4" t="s">
         <v>192</v>
       </c>
@@ -18726,11 +18726,11 @@
       <c r="B47" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C47" s="38">
+      <c r="C47" s="41">
         <f>SUMIFS(I$3:I$42,B$3:B$42,A$46,L$3:L$42,A$47)</f>
         <v>21680</v>
       </c>
-      <c r="D47" s="38"/>
+      <c r="D47" s="41"/>
       <c r="E47" s="3">
         <f>SUMIFS(Q$3:Q$42,B$3:B$42,A$46,L$3:L$42,A$47)</f>
         <v>37</v>
@@ -18765,10 +18765,10 @@
       <c r="B48" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C48" s="39">
-        <v>0</v>
-      </c>
-      <c r="D48" s="39"/>
+      <c r="C48" s="42">
+        <v>0</v>
+      </c>
+      <c r="D48" s="42"/>
       <c r="K48" t="s">
         <v>200</v>
       </c>
@@ -18792,11 +18792,11 @@
       <c r="B49" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C49" s="39">
+      <c r="C49" s="42">
         <f>-SUMIFS(I$3:I$42,B$3:B$42,A$46,P$3:P$42,"xx",N$3:N$42,"x")</f>
         <v>-2880</v>
       </c>
-      <c r="D49" s="39"/>
+      <c r="D49" s="42"/>
       <c r="E49" s="2">
         <f>SUMIFS(Q$3:Q$42,B$3:B$42,A$46,P$3:P$42,"xx",N$3:N$42,"x")</f>
         <v>3</v>
@@ -18824,11 +18824,11 @@
       <c r="B50" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C50" s="37">
+      <c r="C50" s="40">
         <f>SUBTOTAL(9,C47:C49)</f>
         <v>18800</v>
       </c>
-      <c r="D50" s="37"/>
+      <c r="D50" s="40"/>
       <c r="E50">
         <f>E47</f>
         <v>37</v>
@@ -18854,8 +18854,8 @@
       <c r="B51" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="35"/>
-      <c r="D51" s="35"/>
+      <c r="C51" s="38"/>
+      <c r="D51" s="38"/>
       <c r="K51" s="2" t="s">
         <v>206</v>
       </c>
@@ -18871,8 +18871,8 @@
       <c r="B52" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C52" s="35"/>
-      <c r="D52" s="35"/>
+      <c r="C52" s="38"/>
+      <c r="D52" s="38"/>
       <c r="L52" s="13">
         <f>SUBTOTAL(9,L47:L51)</f>
         <v>8506</v>
@@ -18886,11 +18886,11 @@
       <c r="B54" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C54" s="36">
+      <c r="C54" s="39">
         <f>C50+C51+C52</f>
         <v>18800</v>
       </c>
-      <c r="D54" s="36"/>
+      <c r="D54" s="39"/>
       <c r="E54" s="1" t="s">
         <v>211</v>
       </c>
@@ -20961,10 +20961,10 @@
       <c r="A45" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C45" s="37" t="s">
+      <c r="C45" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D45" s="37"/>
+      <c r="D45" s="40"/>
       <c r="E45" s="4" t="s">
         <v>192</v>
       </c>
@@ -20992,11 +20992,11 @@
       <c r="B46" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C46" s="38">
+      <c r="C46" s="41">
         <f>SUMIFS(I$3:I$41,B$3:B$41,A$45,L$3:L$41,A$46)</f>
         <v>17310</v>
       </c>
-      <c r="D46" s="38"/>
+      <c r="D46" s="41"/>
       <c r="E46" s="3">
         <f>SUMIFS(Q$3:Q$41,B$3:B$41,A$45,L$3:L$41,A$46)</f>
         <v>39</v>
@@ -21031,10 +21031,10 @@
       <c r="B47" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C47" s="39">
-        <v>0</v>
-      </c>
-      <c r="D47" s="39"/>
+      <c r="C47" s="42">
+        <v>0</v>
+      </c>
+      <c r="D47" s="42"/>
       <c r="K47" t="s">
         <v>200</v>
       </c>
@@ -21058,11 +21058,11 @@
       <c r="B48" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C48" s="39">
+      <c r="C48" s="42">
         <f>-SUMIFS(I$3:I$41,B$3:B$41,A$45,P$3:P$41,"xx",N$3:N$41,"x")</f>
         <v>0</v>
       </c>
-      <c r="D48" s="39"/>
+      <c r="D48" s="42"/>
       <c r="E48" s="2">
         <f>SUMIFS(Q$3:Q$41,B$3:B$41,A$45,P$3:P$41,"xx",N$3:N$41,"x")</f>
         <v>0</v>
@@ -21082,11 +21082,11 @@
       <c r="B49" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C49" s="37">
+      <c r="C49" s="40">
         <f>SUBTOTAL(9,C46:C48)</f>
         <v>17310</v>
       </c>
-      <c r="D49" s="37"/>
+      <c r="D49" s="40"/>
       <c r="E49">
         <f>E46</f>
         <v>39</v>
@@ -21106,8 +21106,8 @@
       <c r="B50" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C50" s="35"/>
-      <c r="D50" s="35"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="38"/>
       <c r="K50" s="2" t="s">
         <v>206</v>
       </c>
@@ -21123,8 +21123,8 @@
       <c r="B51" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C51" s="35"/>
-      <c r="D51" s="35"/>
+      <c r="C51" s="38"/>
+      <c r="D51" s="38"/>
       <c r="L51" s="13">
         <f>SUBTOTAL(9,L46:L50)</f>
         <v>4540</v>
@@ -21145,11 +21145,11 @@
       <c r="B53" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C53" s="36">
+      <c r="C53" s="39">
         <f>C49+C50+C51</f>
         <v>17310</v>
       </c>
-      <c r="D53" s="36"/>
+      <c r="D53" s="39"/>
       <c r="E53" s="1" t="s">
         <v>211</v>
       </c>
@@ -22734,10 +22734,10 @@
       <c r="A33" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C33" s="37" t="s">
+      <c r="C33" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D33" s="37"/>
+      <c r="D33" s="40"/>
       <c r="E33" s="4" t="s">
         <v>192</v>
       </c>
@@ -22765,11 +22765,11 @@
       <c r="B34" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C34" s="38">
+      <c r="C34" s="41">
         <f>SUMIFS(I$3:I$29,B$3:B$29,A$33,L$3:L$29,A$34)</f>
         <v>12760</v>
       </c>
-      <c r="D34" s="38"/>
+      <c r="D34" s="41"/>
       <c r="E34" s="3">
         <f>SUMIFS(Q$3:Q$29,B$3:B$29,A$33,L$3:L$29,A$34)</f>
         <v>27</v>
@@ -22800,10 +22800,10 @@
       <c r="B35" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C35" s="39">
-        <v>0</v>
-      </c>
-      <c r="D35" s="39"/>
+      <c r="C35" s="42">
+        <v>0</v>
+      </c>
+      <c r="D35" s="42"/>
       <c r="K35" t="s">
         <v>200</v>
       </c>
@@ -22827,11 +22827,11 @@
       <c r="B36" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C36" s="39">
+      <c r="C36" s="42">
         <f>-SUMIFS(I$3:I$29,B$3:B$29,A$33,P$3:P$29,"xx",N$3:N$29,"x")</f>
         <v>0</v>
       </c>
-      <c r="D36" s="39"/>
+      <c r="D36" s="42"/>
       <c r="E36" s="2">
         <f>SUMIFS(Q$3:Q$29,B$3:B$29,A$33,P$3:P$29,"xx",N$3:N$29,"x")</f>
         <v>0</v>
@@ -22859,11 +22859,11 @@
       <c r="B37" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C37" s="37">
+      <c r="C37" s="40">
         <f>SUBTOTAL(9,C34:C36)</f>
         <v>12760</v>
       </c>
-      <c r="D37" s="37"/>
+      <c r="D37" s="40"/>
       <c r="E37">
         <f>E34</f>
         <v>27</v>
@@ -22883,8 +22883,8 @@
       <c r="B38" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C38" s="35"/>
-      <c r="D38" s="35"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
       <c r="K38" s="2" t="s">
         <v>206</v>
       </c>
@@ -22900,8 +22900,8 @@
       <c r="B39" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C39" s="35"/>
-      <c r="D39" s="35"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="38"/>
       <c r="L39" s="13">
         <f>SUBTOTAL(9,L34:L38)</f>
         <v>3141</v>
@@ -22922,11 +22922,11 @@
       <c r="B41" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C41" s="36">
+      <c r="C41" s="39">
         <f>C37+C38+C39</f>
         <v>12760</v>
       </c>
-      <c r="D41" s="36"/>
+      <c r="D41" s="39"/>
       <c r="E41" s="1" t="s">
         <v>211</v>
       </c>
@@ -24855,10 +24855,10 @@
       <c r="A40" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C40" s="37" t="s">
+      <c r="C40" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D40" s="37"/>
+      <c r="D40" s="40"/>
       <c r="E40" s="4" t="s">
         <v>192</v>
       </c>
@@ -24889,11 +24889,11 @@
       <c r="B41" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C41" s="38">
+      <c r="C41" s="41">
         <f>SUMIFS(I$3:I$36,B$3:B$36,A$40,L$3:L$36,A$41)</f>
         <v>18400</v>
       </c>
-      <c r="D41" s="38"/>
+      <c r="D41" s="41"/>
       <c r="E41" s="3">
         <f>SUMIFS(Q$3:Q$36,B$3:B$36,A$40,L$3:L$36,A$41)</f>
         <v>31</v>
@@ -24928,10 +24928,10 @@
       <c r="B42" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C42" s="39">
-        <v>0</v>
-      </c>
-      <c r="D42" s="39"/>
+      <c r="C42" s="42">
+        <v>0</v>
+      </c>
+      <c r="D42" s="42"/>
       <c r="K42" t="s">
         <v>200</v>
       </c>
@@ -24955,11 +24955,11 @@
       <c r="B43" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C43" s="39">
+      <c r="C43" s="42">
         <f>-SUMIFS(I$3:I$36,B$3:B$36,A$40,P$3:P$36,"xx",N$3:N$36,"x")</f>
         <v>-2930</v>
       </c>
-      <c r="D43" s="39"/>
+      <c r="D43" s="42"/>
       <c r="E43" s="2">
         <f>SUMIFS(Q$3:Q$36,B$3:B$36,A$40,P$3:P$36,"xx",N$3:N$36,"x")</f>
         <v>3</v>
@@ -24987,11 +24987,11 @@
       <c r="B44" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C44" s="37">
+      <c r="C44" s="40">
         <f>SUBTOTAL(9,C41:C43)</f>
         <v>15470</v>
       </c>
-      <c r="D44" s="37"/>
+      <c r="D44" s="40"/>
       <c r="E44">
         <f>E41</f>
         <v>31</v>
@@ -25017,8 +25017,8 @@
       <c r="B45" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C45" s="35"/>
-      <c r="D45" s="35"/>
+      <c r="C45" s="38"/>
+      <c r="D45" s="38"/>
       <c r="K45" s="2" t="s">
         <v>206</v>
       </c>
@@ -25034,8 +25034,8 @@
       <c r="B46" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C46" s="35"/>
-      <c r="D46" s="35"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="38"/>
       <c r="L46" s="13">
         <f>SUBTOTAL(9,L41:L45)</f>
         <v>-524</v>
@@ -25056,11 +25056,11 @@
       <c r="B48" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C48" s="36">
+      <c r="C48" s="39">
         <f>C44+C45+C46</f>
         <v>15470</v>
       </c>
-      <c r="D48" s="36"/>
+      <c r="D48" s="39"/>
       <c r="E48" s="1" t="s">
         <v>211</v>
       </c>
@@ -27331,10 +27331,10 @@
       <c r="A48" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C48" s="37" t="s">
+      <c r="C48" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D48" s="37"/>
+      <c r="D48" s="40"/>
       <c r="E48" s="4" t="s">
         <v>192</v>
       </c>
@@ -27362,11 +27362,11 @@
       <c r="B49" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C49" s="38">
+      <c r="C49" s="41">
         <f>SUMIFS(I$3:I$44,B$3:B$44,A$48,L$3:L$44,A$49)</f>
         <v>24900</v>
       </c>
-      <c r="D49" s="38"/>
+      <c r="D49" s="41"/>
       <c r="E49" s="3">
         <f>SUMIFS(Q$3:Q$44,B$3:B$44,A$48,L$3:L$44,A$49)</f>
         <v>40</v>
@@ -27401,10 +27401,10 @@
       <c r="B50" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C50" s="39">
-        <v>0</v>
-      </c>
-      <c r="D50" s="39"/>
+      <c r="C50" s="42">
+        <v>0</v>
+      </c>
+      <c r="D50" s="42"/>
       <c r="K50" t="s">
         <v>200</v>
       </c>
@@ -27428,11 +27428,11 @@
       <c r="B51" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C51" s="39">
+      <c r="C51" s="42">
         <f>-SUMIFS(I$3:I$44,B$3:B$44,A$48,P$3:P$44,"xx",N$3:N$44,"x")</f>
         <v>-1155</v>
       </c>
-      <c r="D51" s="39"/>
+      <c r="D51" s="42"/>
       <c r="E51" s="2">
         <f>SUMIFS(Q$3:Q$44,B$3:B$44,A$48,P$3:P$44,"xx",N$3:N$44,"x")</f>
         <v>2</v>
@@ -27452,11 +27452,11 @@
       <c r="B52" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C52" s="37">
+      <c r="C52" s="40">
         <f>SUBTOTAL(9,C49:C51)</f>
         <v>23745</v>
       </c>
-      <c r="D52" s="37"/>
+      <c r="D52" s="40"/>
       <c r="E52">
         <f>E49</f>
         <v>40</v>
@@ -27482,8 +27482,8 @@
       <c r="B53" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C53" s="35"/>
-      <c r="D53" s="35"/>
+      <c r="C53" s="38"/>
+      <c r="D53" s="38"/>
       <c r="K53" s="2" t="s">
         <v>206</v>
       </c>
@@ -27505,8 +27505,8 @@
       <c r="B54" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C54" s="35"/>
-      <c r="D54" s="35"/>
+      <c r="C54" s="38"/>
+      <c r="D54" s="38"/>
       <c r="L54" s="13">
         <f>SUBTOTAL(9,L49:L53)</f>
         <v>10724</v>
@@ -27520,11 +27520,11 @@
       <c r="B56" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C56" s="36">
+      <c r="C56" s="39">
         <f>C52+C53+C54</f>
         <v>23745</v>
       </c>
-      <c r="D56" s="36"/>
+      <c r="D56" s="39"/>
       <c r="E56" s="1" t="s">
         <v>211</v>
       </c>
@@ -29145,10 +29145,10 @@
       <c r="A35" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="37" t="s">
+      <c r="C35" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D35" s="37"/>
+      <c r="D35" s="40"/>
       <c r="E35" s="4" t="s">
         <v>192</v>
       </c>
@@ -29176,11 +29176,11 @@
       <c r="B36" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C36" s="38">
+      <c r="C36" s="41">
         <f>SUMIFS(I$3:I$31,B$3:B$31,A$35,L$3:L$31,A$36)</f>
         <v>18100</v>
       </c>
-      <c r="D36" s="38"/>
+      <c r="D36" s="41"/>
       <c r="E36" s="3">
         <f>SUMIFS(Q$3:Q$31,B$3:B$31,A$35,L$3:L$31,A$36)</f>
         <v>26</v>
@@ -29215,10 +29215,10 @@
       <c r="B37" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C37" s="39">
-        <v>0</v>
-      </c>
-      <c r="D37" s="39"/>
+      <c r="C37" s="42">
+        <v>0</v>
+      </c>
+      <c r="D37" s="42"/>
       <c r="K37" t="s">
         <v>200</v>
       </c>
@@ -29242,11 +29242,11 @@
       <c r="B38" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C38" s="39">
+      <c r="C38" s="42">
         <f>-SUMIFS(I$3:I$31,B$3:B$31,A$35,P$3:P$31,"xx",N$3:N$31,"x")</f>
         <v>-1585</v>
       </c>
-      <c r="D38" s="39"/>
+      <c r="D38" s="42"/>
       <c r="E38" s="2">
         <f>SUMIFS(Q$3:Q$31,B$3:B$31,A$35,P$3:P$31,"xx",N$3:N$31,"x")</f>
         <v>3</v>
@@ -29274,11 +29274,11 @@
       <c r="B39" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C39" s="37">
+      <c r="C39" s="40">
         <f>SUBTOTAL(9,C36:C38)</f>
         <v>16515</v>
       </c>
-      <c r="D39" s="37"/>
+      <c r="D39" s="40"/>
       <c r="E39">
         <f>E36</f>
         <v>26</v>
@@ -29298,8 +29298,8 @@
       <c r="B40" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C40" s="35"/>
-      <c r="D40" s="35"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="38"/>
       <c r="K40" s="2" t="s">
         <v>206</v>
       </c>
@@ -29315,8 +29315,8 @@
       <c r="B41" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C41" s="35"/>
-      <c r="D41" s="35"/>
+      <c r="C41" s="38"/>
+      <c r="D41" s="38"/>
       <c r="L41" s="13">
         <f>SUBTOTAL(9,L36:L40)</f>
         <v>5357</v>
@@ -29330,11 +29330,11 @@
       <c r="B43" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C43" s="36">
+      <c r="C43" s="39">
         <f>C39+C40+C41</f>
         <v>16515</v>
       </c>
-      <c r="D43" s="36"/>
+      <c r="D43" s="39"/>
       <c r="E43" s="1" t="s">
         <v>211</v>
       </c>
@@ -30833,10 +30833,10 @@
       <c r="A32" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C32" s="37" t="s">
+      <c r="C32" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D32" s="37"/>
+      <c r="D32" s="40"/>
       <c r="E32" s="4" t="s">
         <v>192</v>
       </c>
@@ -30864,11 +30864,11 @@
       <c r="B33" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="38">
+      <c r="C33" s="41">
         <f>SUMIFS(I$3:I$28,B$3:B$28,A$32,L$3:L$28,A$33)</f>
         <v>13075</v>
       </c>
-      <c r="D33" s="38"/>
+      <c r="D33" s="41"/>
       <c r="E33" s="3">
         <f>SUMIFS(Q$3:Q$28,B$3:B$28,A$32,L$3:L$28,A$33)</f>
         <v>26</v>
@@ -30903,10 +30903,10 @@
       <c r="B34" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C34" s="39">
-        <v>0</v>
-      </c>
-      <c r="D34" s="39"/>
+      <c r="C34" s="42">
+        <v>0</v>
+      </c>
+      <c r="D34" s="42"/>
       <c r="K34" t="s">
         <v>200</v>
       </c>
@@ -30930,11 +30930,11 @@
       <c r="B35" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C35" s="39">
+      <c r="C35" s="42">
         <f>-SUMIFS(I$3:I$28,B$3:B$28,A$32,P$3:P$28,"xx",N$3:N$28,"x")</f>
         <v>0</v>
       </c>
-      <c r="D35" s="39"/>
+      <c r="D35" s="42"/>
       <c r="E35" s="2">
         <f>SUMIFS(Q$3:Q$28,B$3:B$28,A$32,P$3:P$28,"xx",N$3:N$28,"x")</f>
         <v>0</v>
@@ -30954,11 +30954,11 @@
       <c r="B36" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C36" s="37">
+      <c r="C36" s="40">
         <f>SUBTOTAL(9,C33:C35)</f>
         <v>13075</v>
       </c>
-      <c r="D36" s="37"/>
+      <c r="D36" s="40"/>
       <c r="E36">
         <f>E33</f>
         <v>26</v>
@@ -30978,8 +30978,8 @@
       <c r="B37" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C37" s="35"/>
-      <c r="D37" s="35"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="38"/>
       <c r="K37" s="2" t="s">
         <v>206</v>
       </c>
@@ -30995,8 +30995,8 @@
       <c r="B38" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C38" s="35"/>
-      <c r="D38" s="35"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
       <c r="L38" s="13">
         <f>SUBTOTAL(9,L33:L37)</f>
         <v>2515</v>
@@ -31010,11 +31010,11 @@
       <c r="B40" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C40" s="36">
+      <c r="C40" s="39">
         <f>C36+C37+C38</f>
         <v>13075</v>
       </c>
-      <c r="D40" s="36"/>
+      <c r="D40" s="39"/>
       <c r="E40" s="1" t="s">
         <v>211</v>
       </c>
@@ -32405,10 +32405,10 @@
       <c r="A30" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="37" t="s">
+      <c r="C30" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D30" s="37"/>
+      <c r="D30" s="40"/>
       <c r="E30" s="4" t="s">
         <v>192</v>
       </c>
@@ -32439,11 +32439,11 @@
       <c r="B31" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C31" s="38">
+      <c r="C31" s="41">
         <f>SUMIFS(I$3:I$26,B$3:B$26,A$30,L$3:L$26,A$31)</f>
         <v>9280</v>
       </c>
-      <c r="D31" s="38"/>
+      <c r="D31" s="41"/>
       <c r="E31" s="3">
         <f>SUMIFS(Q$3:Q$26,B$3:B$26,A$30,L$3:L$26,A$31)</f>
         <v>20</v>
@@ -32481,10 +32481,10 @@
       <c r="B32" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C32" s="39">
-        <v>0</v>
-      </c>
-      <c r="D32" s="39"/>
+      <c r="C32" s="42">
+        <v>0</v>
+      </c>
+      <c r="D32" s="42"/>
       <c r="K32" t="s">
         <v>200</v>
       </c>
@@ -32508,11 +32508,11 @@
       <c r="B33" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C33" s="39">
+      <c r="C33" s="42">
         <f>-SUMIFS(I$3:I$26,B$3:B$26,A$30,P$3:P$26,"xx",N$3:N$26,"x")</f>
         <v>-3055</v>
       </c>
-      <c r="D33" s="39"/>
+      <c r="D33" s="42"/>
       <c r="E33" s="2">
         <f>SUMIFS(Q$3:Q$26,B$3:B$26,A$30,P$3:P$26,"xx",N$3:N$26,"x")</f>
         <v>4</v>
@@ -32532,11 +32532,11 @@
       <c r="B34" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C34" s="37">
+      <c r="C34" s="40">
         <f>SUBTOTAL(9,C31:C33)</f>
         <v>6225</v>
       </c>
-      <c r="D34" s="37"/>
+      <c r="D34" s="40"/>
       <c r="E34">
         <f>E31</f>
         <v>20</v>
@@ -32562,8 +32562,8 @@
       <c r="B35" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C35" s="35"/>
-      <c r="D35" s="35"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
       <c r="K35" s="2" t="s">
         <v>206</v>
       </c>
@@ -32579,8 +32579,8 @@
       <c r="B36" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C36" s="35"/>
-      <c r="D36" s="35"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
       <c r="L36" s="13">
         <f>SUBTOTAL(9,L31:L35)</f>
         <v>2401</v>
@@ -32601,11 +32601,11 @@
       <c r="B38" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C38" s="36">
+      <c r="C38" s="39">
         <f>C34+C35+C36</f>
         <v>6225</v>
       </c>
-      <c r="D38" s="36"/>
+      <c r="D38" s="39"/>
       <c r="E38" s="1" t="s">
         <v>211</v>
       </c>
@@ -35308,10 +35308,10 @@
       <c r="A59" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C59" s="37" t="s">
+      <c r="C59" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D59" s="37"/>
+      <c r="D59" s="40"/>
       <c r="E59" s="4" t="s">
         <v>192</v>
       </c>
@@ -35339,11 +35339,11 @@
       <c r="B60" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C60" s="38">
+      <c r="C60" s="41">
         <f>SUMIFS(I$3:I$55,B$3:B$55,A$59,L$3:L$55,A$60)</f>
         <v>43250</v>
       </c>
-      <c r="D60" s="38"/>
+      <c r="D60" s="41"/>
       <c r="E60" s="3">
         <f>SUMIFS(Q$3:Q$55,B$3:B$55,A$59,L$3:L$55,A$60)</f>
         <v>53</v>
@@ -35378,10 +35378,10 @@
       <c r="B61" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C61" s="39">
-        <v>0</v>
-      </c>
-      <c r="D61" s="39"/>
+      <c r="C61" s="42">
+        <v>0</v>
+      </c>
+      <c r="D61" s="42"/>
       <c r="K61" t="s">
         <v>200</v>
       </c>
@@ -35405,11 +35405,11 @@
       <c r="B62" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C62" s="39">
+      <c r="C62" s="42">
         <f>-SUMIFS(I$3:I$55,B$3:B$55,A$59,P$3:P$55,"xx",N$3:N$55,"x")</f>
         <v>0</v>
       </c>
-      <c r="D62" s="39"/>
+      <c r="D62" s="42"/>
       <c r="E62" s="2">
         <f>SUMIFS(Q$3:Q$55,B$3:B$55,A$59,P$3:P$55,"xx",N$3:N$55,"x")</f>
         <v>0</v>
@@ -35437,11 +35437,11 @@
       <c r="B63" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C63" s="37">
+      <c r="C63" s="40">
         <f>SUBTOTAL(9,C60:C62)</f>
         <v>43250</v>
       </c>
-      <c r="D63" s="37"/>
+      <c r="D63" s="40"/>
       <c r="E63">
         <f>E60</f>
         <v>53</v>
@@ -35461,8 +35461,8 @@
       <c r="B64" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C64" s="35"/>
-      <c r="D64" s="35"/>
+      <c r="C64" s="38"/>
+      <c r="D64" s="38"/>
       <c r="K64" s="2" t="s">
         <v>206</v>
       </c>
@@ -35478,8 +35478,8 @@
       <c r="B65" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C65" s="35"/>
-      <c r="D65" s="35"/>
+      <c r="C65" s="38"/>
+      <c r="D65" s="38"/>
       <c r="L65" s="13">
         <f>SUBTOTAL(9,L60:L64)</f>
         <v>11263</v>
@@ -35493,11 +35493,11 @@
       <c r="B67" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C67" s="36">
+      <c r="C67" s="39">
         <f>C63+C64+C65</f>
         <v>43250</v>
       </c>
-      <c r="D67" s="36"/>
+      <c r="D67" s="39"/>
       <c r="E67" s="1" t="s">
         <v>211</v>
       </c>
@@ -37069,10 +37069,10 @@
       <c r="A34" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="37" t="s">
+      <c r="C34" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D34" s="37"/>
+      <c r="D34" s="40"/>
       <c r="E34" s="4" t="s">
         <v>192</v>
       </c>
@@ -37100,11 +37100,11 @@
       <c r="B35" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C35" s="38">
+      <c r="C35" s="41">
         <f>SUMIFS(I$3:I$30,B$3:B$30,A$34,L$3:L$30,A$35)</f>
         <v>19080</v>
       </c>
-      <c r="D35" s="38"/>
+      <c r="D35" s="41"/>
       <c r="E35" s="3">
         <f>SUMIFS(Q$3:Q$30,B$3:B$30,A$34,L$3:L$30,A$35)</f>
         <v>27</v>
@@ -37135,10 +37135,10 @@
       <c r="B36" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C36" s="39">
-        <v>0</v>
-      </c>
-      <c r="D36" s="39"/>
+      <c r="C36" s="42">
+        <v>0</v>
+      </c>
+      <c r="D36" s="42"/>
       <c r="K36" t="s">
         <v>200</v>
       </c>
@@ -37162,11 +37162,11 @@
       <c r="B37" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C37" s="39">
+      <c r="C37" s="42">
         <f>-SUMIFS(I$3:I$30,B$3:B$30,A$34,P$3:P$30,"xx",N$3:N$30,"x")</f>
         <v>-4365</v>
       </c>
-      <c r="D37" s="39"/>
+      <c r="D37" s="42"/>
       <c r="E37" s="2">
         <f>SUMIFS(Q$3:Q$30,B$3:B$30,A$34,P$3:P$30,"xx",N$3:N$30,"x")</f>
         <v>1</v>
@@ -37186,11 +37186,11 @@
       <c r="B38" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C38" s="37">
+      <c r="C38" s="40">
         <f>SUBTOTAL(9,C35:C37)</f>
         <v>14715</v>
       </c>
-      <c r="D38" s="37"/>
+      <c r="D38" s="40"/>
       <c r="E38">
         <f>E35</f>
         <v>27</v>
@@ -37216,8 +37216,8 @@
       <c r="B39" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C39" s="35"/>
-      <c r="D39" s="35"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="38"/>
       <c r="K39" s="2" t="s">
         <v>206</v>
       </c>
@@ -37233,8 +37233,8 @@
       <c r="B40" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C40" s="35"/>
-      <c r="D40" s="35"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="38"/>
       <c r="L40" s="13">
         <f>SUBTOTAL(9,L35:L39)</f>
         <v>-360</v>
@@ -37255,11 +37255,11 @@
       <c r="B42" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C42" s="36">
+      <c r="C42" s="39">
         <f>C38+C39+C40</f>
         <v>14715</v>
       </c>
-      <c r="D42" s="36"/>
+      <c r="D42" s="39"/>
       <c r="E42" s="1" t="s">
         <v>211</v>
       </c>
@@ -37498,7 +37498,7 @@
     <col min="9" max="9" width="10.5703125" customWidth="1"/>
     <col min="10" max="10" width="9.7109375" customWidth="1"/>
     <col min="11" max="11" width="10.85546875" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.7109375" customWidth="1"/>
     <col min="14" max="14" width="9.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.42578125" customWidth="1"/>
@@ -38710,10 +38710,10 @@
       <c r="A30" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="37" t="s">
+      <c r="C30" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D30" s="37"/>
+      <c r="D30" s="40"/>
       <c r="E30" s="4" t="s">
         <v>192</v>
       </c>
@@ -38741,11 +38741,11 @@
       <c r="B31" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C31" s="38">
+      <c r="C31" s="41">
         <f>SUMIFS(I$3:I$26,B$3:B$26,A$30,L$3:L$26,A$31)</f>
         <v>11570</v>
       </c>
-      <c r="D31" s="38"/>
+      <c r="D31" s="41"/>
       <c r="E31" s="3">
         <f>SUMIFS(Q$3:Q$26,B$3:B$26,A$30,L$3:L$26,A$31)</f>
         <v>24</v>
@@ -38780,10 +38780,10 @@
       <c r="B32" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C32" s="39">
-        <v>0</v>
-      </c>
-      <c r="D32" s="39"/>
+      <c r="C32" s="42">
+        <v>0</v>
+      </c>
+      <c r="D32" s="42"/>
       <c r="K32" t="s">
         <v>200</v>
       </c>
@@ -38807,11 +38807,11 @@
       <c r="B33" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C33" s="39">
+      <c r="C33" s="42">
         <f>-SUMIFS(I$3:I$26,B$3:B$26,A$30,P$3:P$26,"xx",N$3:N$26,"x")</f>
         <v>0</v>
       </c>
-      <c r="D33" s="39"/>
+      <c r="D33" s="42"/>
       <c r="E33" s="2">
         <f>SUMIFS(Q$3:Q$26,B$3:B$26,A$30,P$3:P$26,"xx",N$3:N$26,"x")</f>
         <v>0</v>
@@ -38839,11 +38839,11 @@
       <c r="B34" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C34" s="37">
+      <c r="C34" s="40">
         <f>SUBTOTAL(9,C31:C33)</f>
         <v>11570</v>
       </c>
-      <c r="D34" s="37"/>
+      <c r="D34" s="40"/>
       <c r="E34">
         <f>E31</f>
         <v>24</v>
@@ -38863,8 +38863,8 @@
       <c r="B35" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C35" s="35"/>
-      <c r="D35" s="35"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
       <c r="K35" s="2" t="s">
         <v>206</v>
       </c>
@@ -38880,8 +38880,8 @@
       <c r="B36" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C36" s="35"/>
-      <c r="D36" s="35"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
       <c r="L36" s="13">
         <f>SUBTOTAL(9,L31:L35)</f>
         <v>3952</v>
@@ -38895,11 +38895,11 @@
       <c r="B38" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C38" s="36">
+      <c r="C38" s="39">
         <f>C34+C35+C36</f>
         <v>11570</v>
       </c>
-      <c r="D38" s="36"/>
+      <c r="D38" s="39"/>
       <c r="E38" s="1" t="s">
         <v>211</v>
       </c>
@@ -40433,10 +40433,10 @@
       <c r="A33" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C33" s="37" t="s">
+      <c r="C33" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D33" s="37"/>
+      <c r="D33" s="40"/>
       <c r="E33" s="4" t="s">
         <v>192</v>
       </c>
@@ -40460,11 +40460,11 @@
       <c r="B34" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C34" s="38">
+      <c r="C34" s="41">
         <f>SUMIFS(I$3:I$29,B$3:B$29,A$33,L$3:L$29,A$34)</f>
         <v>17840</v>
       </c>
-      <c r="D34" s="38"/>
+      <c r="D34" s="41"/>
       <c r="E34" s="3">
         <f>SUMIFS(Q$3:Q$29,B$3:B$29,A$33,L$3:L$29,A$34)</f>
         <v>26</v>
@@ -40495,10 +40495,10 @@
       <c r="B35" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C35" s="39">
-        <v>0</v>
-      </c>
-      <c r="D35" s="39"/>
+      <c r="C35" s="42">
+        <v>0</v>
+      </c>
+      <c r="D35" s="42"/>
       <c r="K35" t="s">
         <v>200</v>
       </c>
@@ -40522,11 +40522,11 @@
       <c r="B36" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C36" s="39">
+      <c r="C36" s="42">
         <f>-SUMIFS(I$3:I$29,B$3:B$29,A$33,P$3:P$29,"xx",N$3:N$29,"x")</f>
         <v>-820</v>
       </c>
-      <c r="D36" s="39"/>
+      <c r="D36" s="42"/>
       <c r="E36" s="2">
         <f>SUMIFS(Q$3:Q$29,B$3:B$29,A$33,P$3:P$29,"xx",N$3:N$29,"x")</f>
         <v>1</v>
@@ -40546,11 +40546,11 @@
       <c r="B37" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C37" s="37">
+      <c r="C37" s="40">
         <f>SUBTOTAL(9,C34:C36)</f>
         <v>17020</v>
       </c>
-      <c r="D37" s="37"/>
+      <c r="D37" s="40"/>
       <c r="E37">
         <f>E34</f>
         <v>26</v>
@@ -40570,8 +40570,8 @@
       <c r="B38" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C38" s="35"/>
-      <c r="D38" s="35"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
       <c r="K38" s="2" t="s">
         <v>206</v>
       </c>
@@ -40587,8 +40587,8 @@
       <c r="B39" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C39" s="35"/>
-      <c r="D39" s="35"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="38"/>
       <c r="L39" s="13">
         <f>SUBTOTAL(9,L34:L38)</f>
         <v>4328</v>
@@ -40602,11 +40602,11 @@
       <c r="B41" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C41" s="36">
+      <c r="C41" s="39">
         <f>C37+C38+C39</f>
         <v>17020</v>
       </c>
-      <c r="D41" s="36"/>
+      <c r="D41" s="39"/>
       <c r="E41" s="1" t="s">
         <v>211</v>
       </c>
@@ -40770,7 +40770,6 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A2:R50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -40843,7 +40842,7 @@
       </c>
       <c r="Q2" s="15"/>
     </row>
-    <row r="3" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="15"/>
       <c r="B3" s="15" t="s">
         <v>17</v>
@@ -40887,7 +40886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="15"/>
       <c r="B4" s="15" t="s">
         <v>17</v>
@@ -40931,7 +40930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="15"/>
       <c r="B5" s="15" t="s">
         <v>17</v>
@@ -40975,7 +40974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="15"/>
       <c r="B6" s="15" t="s">
         <v>17</v>
@@ -41019,7 +41018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="15"/>
       <c r="B7" s="15" t="s">
         <v>17</v>
@@ -41063,7 +41062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="15"/>
       <c r="B8" s="15" t="s">
         <v>17</v>
@@ -41107,7 +41106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="15"/>
       <c r="B9" s="15" t="s">
         <v>17</v>
@@ -41157,7 +41156,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="15"/>
       <c r="B10" s="15" t="s">
         <v>17</v>
@@ -41655,7 +41654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="15"/>
       <c r="B21" s="15" t="s">
         <v>17</v>
@@ -41699,7 +41698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="15"/>
       <c r="B22" s="15" t="s">
         <v>17</v>
@@ -41743,7 +41742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="15"/>
       <c r="B23" s="15" t="s">
         <v>17</v>
@@ -41791,7 +41790,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="15"/>
       <c r="B24" s="15" t="s">
         <v>17</v>
@@ -41842,15 +41841,15 @@
       </c>
       <c r="G26" s="1">
         <f t="shared" ref="G26:Q26" si="1">SUBTOTAL(9,G3:G24)</f>
-        <v>10570</v>
+        <v>32009</v>
       </c>
       <c r="H26" s="1">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>695</v>
       </c>
       <c r="I26" s="1">
         <f t="shared" si="1"/>
-        <v>10260</v>
+        <v>31314</v>
       </c>
       <c r="J26" s="1">
         <f t="shared" si="1"/>
@@ -41882,7 +41881,7 @@
       </c>
       <c r="Q26" s="1">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -41895,10 +41894,10 @@
       <c r="A28" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="37" t="s">
+      <c r="C28" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D28" s="37"/>
+      <c r="D28" s="40"/>
       <c r="E28" s="4" t="s">
         <v>192</v>
       </c>
@@ -41926,11 +41925,11 @@
       <c r="B29" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C29" s="38">
+      <c r="C29" s="41">
         <f>SUMIFS(I$3:I$24,B$3:B$24,A$28,L$3:L$24,A$29)</f>
         <v>31314</v>
       </c>
-      <c r="D29" s="38"/>
+      <c r="D29" s="41"/>
       <c r="E29" s="3">
         <f>SUMIFS(Q$3:Q$24,B$3:B$24,A$28,L$3:L$24,A$29)</f>
         <v>22</v>
@@ -41965,10 +41964,10 @@
       <c r="B30" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C30" s="39">
-        <v>0</v>
-      </c>
-      <c r="D30" s="39"/>
+      <c r="C30" s="42">
+        <v>0</v>
+      </c>
+      <c r="D30" s="42"/>
       <c r="K30" t="s">
         <v>200</v>
       </c>
@@ -41992,11 +41991,11 @@
       <c r="B31" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C31" s="39">
+      <c r="C31" s="42">
         <f>-SUMIFS(I$3:I$24,B$3:B$24,A$28,P$3:P$24,"xx",N$3:N$24,"x")</f>
         <v>0</v>
       </c>
-      <c r="D31" s="39"/>
+      <c r="D31" s="42"/>
       <c r="E31" s="2">
         <f>SUMIFS(Q$3:Q$24,B$3:B$24,A$28,P$3:P$24,"xx",N$3:N$24,"x")</f>
         <v>0</v>
@@ -42016,11 +42015,11 @@
       <c r="B32" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C32" s="37">
+      <c r="C32" s="40">
         <f>SUBTOTAL(9,C29:C31)</f>
         <v>31314</v>
       </c>
-      <c r="D32" s="37"/>
+      <c r="D32" s="40"/>
       <c r="E32">
         <f>E29</f>
         <v>22</v>
@@ -42040,8 +42039,8 @@
       <c r="B33" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="38"/>
       <c r="K33" s="2" t="s">
         <v>206</v>
       </c>
@@ -42057,8 +42056,8 @@
       <c r="B34" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C34" s="35"/>
-      <c r="D34" s="35"/>
+      <c r="C34" s="38"/>
+      <c r="D34" s="38"/>
       <c r="L34" s="13">
         <f>SUBTOTAL(9,L29:L33)</f>
         <v>18701</v>
@@ -42072,11 +42071,11 @@
       <c r="B36" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C36" s="36">
+      <c r="C36" s="39">
         <f>C32+C33+C34</f>
         <v>31314</v>
       </c>
-      <c r="D36" s="36"/>
+      <c r="D36" s="39"/>
       <c r="E36" s="1" t="s">
         <v>211</v>
       </c>
@@ -42213,11 +42212,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:P24" xr:uid="{00000000-0009-0000-0000-000017000000}">
-    <filterColumn colId="9">
-      <filters>
-        <filter val="c.cuong"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P24">
       <sortCondition ref="J2:J24"/>
     </sortState>
@@ -43663,10 +43657,10 @@
       <c r="A35" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="37" t="s">
+      <c r="C35" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D35" s="37"/>
+      <c r="D35" s="40"/>
       <c r="E35" s="4" t="s">
         <v>192</v>
       </c>
@@ -43694,11 +43688,11 @@
       <c r="B36" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C36" s="38">
+      <c r="C36" s="41">
         <f>SUMIFS(I$3:I$31,B$3:B$31,A$35,L$3:L$31,A$36)</f>
         <v>16840</v>
       </c>
-      <c r="D36" s="38"/>
+      <c r="D36" s="41"/>
       <c r="E36" s="3">
         <f>SUMIFS(Q$3:Q$31,B$3:B$31,A$35,L$3:L$31,A$36)</f>
         <v>29</v>
@@ -43729,10 +43723,10 @@
       <c r="B37" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C37" s="39">
-        <v>0</v>
-      </c>
-      <c r="D37" s="39"/>
+      <c r="C37" s="42">
+        <v>0</v>
+      </c>
+      <c r="D37" s="42"/>
       <c r="K37" t="s">
         <v>200</v>
       </c>
@@ -43756,11 +43750,11 @@
       <c r="B38" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C38" s="39">
+      <c r="C38" s="42">
         <f>-SUMIFS(I$3:I$31,B$3:B$31,A$35,P$3:P$31,"xx",N$3:N$31,"x")</f>
         <v>-570</v>
       </c>
-      <c r="D38" s="39"/>
+      <c r="D38" s="42"/>
       <c r="E38" s="2">
         <f>SUMIFS(Q$3:Q$31,B$3:B$31,A$35,P$3:P$31,"xx",N$3:N$31,"x")</f>
         <v>1</v>
@@ -43788,11 +43782,11 @@
       <c r="B39" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C39" s="37">
+      <c r="C39" s="40">
         <f>SUBTOTAL(9,C36:C38)</f>
         <v>16270</v>
       </c>
-      <c r="D39" s="37"/>
+      <c r="D39" s="40"/>
       <c r="E39">
         <f>E36</f>
         <v>29</v>
@@ -43812,8 +43806,8 @@
       <c r="B40" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C40" s="35"/>
-      <c r="D40" s="35"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="38"/>
       <c r="K40" s="2" t="s">
         <v>206</v>
       </c>
@@ -43829,8 +43823,8 @@
       <c r="B41" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C41" s="35"/>
-      <c r="D41" s="35"/>
+      <c r="C41" s="38"/>
+      <c r="D41" s="38"/>
       <c r="L41" s="13">
         <f>SUBTOTAL(9,L36:L40)</f>
         <v>7176</v>
@@ -43844,11 +43838,11 @@
       <c r="B43" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C43" s="36">
+      <c r="C43" s="39">
         <f>C39+C40+C41</f>
         <v>16270</v>
       </c>
-      <c r="D43" s="36"/>
+      <c r="D43" s="39"/>
       <c r="E43" s="1" t="s">
         <v>211</v>
       </c>
@@ -47109,10 +47103,10 @@
       <c r="A59" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C59" s="37" t="s">
+      <c r="C59" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D59" s="37"/>
+      <c r="D59" s="40"/>
       <c r="E59" s="4" t="s">
         <v>192</v>
       </c>
@@ -47140,11 +47134,11 @@
       <c r="B60" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C60" s="38">
+      <c r="C60" s="41">
         <f>SUMIFS(I$3:I$55,B$3:B$55,A$59,L$3:L$55,A$60)</f>
         <v>37890</v>
       </c>
-      <c r="D60" s="38"/>
+      <c r="D60" s="41"/>
       <c r="E60" s="3">
         <f>SUMIFS(Q$3:Q$55,B$3:B$55,A$59,L$3:L$55,A$60)</f>
         <v>53</v>
@@ -47179,10 +47173,10 @@
       <c r="B61" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C61" s="39">
-        <v>0</v>
-      </c>
-      <c r="D61" s="39"/>
+      <c r="C61" s="42">
+        <v>0</v>
+      </c>
+      <c r="D61" s="42"/>
       <c r="K61" t="s">
         <v>200</v>
       </c>
@@ -47206,11 +47200,11 @@
       <c r="B62" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C62" s="39">
+      <c r="C62" s="42">
         <f>-SUMIFS(I$3:I$55,B$3:B$55,A$59,P$3:P$55,"xx",N$3:N$55,"x")</f>
         <v>0</v>
       </c>
-      <c r="D62" s="39"/>
+      <c r="D62" s="42"/>
       <c r="E62" s="2">
         <f>SUMIFS(Q$3:Q$55,B$3:B$55,A$59,P$3:P$55,"xx",N$3:N$55,"x")</f>
         <v>0</v>
@@ -47230,11 +47224,11 @@
       <c r="B63" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C63" s="37">
+      <c r="C63" s="40">
         <f>SUBTOTAL(9,C60:C62)</f>
         <v>37890</v>
       </c>
-      <c r="D63" s="37"/>
+      <c r="D63" s="40"/>
       <c r="E63">
         <f>E60</f>
         <v>53</v>
@@ -47254,8 +47248,8 @@
       <c r="B64" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C64" s="35"/>
-      <c r="D64" s="35"/>
+      <c r="C64" s="38"/>
+      <c r="D64" s="38"/>
       <c r="K64" s="2" t="s">
         <v>206</v>
       </c>
@@ -47271,10 +47265,10 @@
       <c r="B65" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C65" s="35">
+      <c r="C65" s="38">
         <v>-30</v>
       </c>
-      <c r="D65" s="35"/>
+      <c r="D65" s="38"/>
       <c r="L65" s="13">
         <f>SUBTOTAL(9,L60:L64)</f>
         <v>21245</v>
@@ -47288,11 +47282,11 @@
       <c r="B67" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C67" s="36">
+      <c r="C67" s="39">
         <f>C63+C64+C65</f>
         <v>37860</v>
       </c>
-      <c r="D67" s="36"/>
+      <c r="D67" s="39"/>
       <c r="E67" s="1" t="s">
         <v>211</v>
       </c>
@@ -48998,10 +48992,10 @@
       <c r="A38" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C38" s="37" t="s">
+      <c r="C38" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D38" s="37"/>
+      <c r="D38" s="40"/>
       <c r="E38" s="4" t="s">
         <v>192</v>
       </c>
@@ -49029,11 +49023,11 @@
       <c r="B39" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C39" s="38">
+      <c r="C39" s="41">
         <f>SUMIFS(I$3:I$34,B$3:B$34,A$38,L$3:L$34,A$39)</f>
         <v>22325</v>
       </c>
-      <c r="D39" s="38"/>
+      <c r="D39" s="41"/>
       <c r="E39" s="3">
         <f>SUMIFS(Q$3:Q$34,B$3:B$34,A$38,L$3:L$34,A$39)</f>
         <v>32</v>
@@ -49068,10 +49062,10 @@
       <c r="B40" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C40" s="39">
-        <v>0</v>
-      </c>
-      <c r="D40" s="39"/>
+      <c r="C40" s="42">
+        <v>0</v>
+      </c>
+      <c r="D40" s="42"/>
       <c r="K40" t="s">
         <v>200</v>
       </c>
@@ -49095,11 +49089,11 @@
       <c r="B41" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C41" s="39">
+      <c r="C41" s="42">
         <f>-SUMIFS(I$3:I$34,B$3:B$34,A$38,P$3:P$34,"xx",N$3:N$34,"x")</f>
         <v>0</v>
       </c>
-      <c r="D41" s="39"/>
+      <c r="D41" s="42"/>
       <c r="E41" s="2">
         <f>SUMIFS(Q$3:Q$34,B$3:B$34,A$38,P$3:P$34,"xx",N$3:N$34,"x")</f>
         <v>0</v>
@@ -49119,11 +49113,11 @@
       <c r="B42" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C42" s="37">
+      <c r="C42" s="40">
         <f>SUBTOTAL(9,C39:C41)</f>
         <v>22325</v>
       </c>
-      <c r="D42" s="37"/>
+      <c r="D42" s="40"/>
       <c r="E42">
         <f>E39</f>
         <v>32</v>
@@ -49143,8 +49137,8 @@
       <c r="B43" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="35"/>
-      <c r="D43" s="35"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="38"/>
       <c r="K43" s="2" t="s">
         <v>206</v>
       </c>
@@ -49160,8 +49154,8 @@
       <c r="B44" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C44" s="35"/>
-      <c r="D44" s="35"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="38"/>
       <c r="L44" s="13">
         <f>SUBTOTAL(9,L39:L43)</f>
         <v>11135</v>
@@ -49175,11 +49169,11 @@
       <c r="B46" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C46" s="36">
+      <c r="C46" s="39">
         <f>C42+C43+C44</f>
         <v>22325</v>
       </c>
-      <c r="D46" s="36"/>
+      <c r="D46" s="39"/>
       <c r="E46" s="1" t="s">
         <v>211</v>
       </c>
@@ -51028,10 +51022,10 @@
       <c r="A40" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C40" s="37" t="s">
+      <c r="C40" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D40" s="37"/>
+      <c r="D40" s="40"/>
       <c r="E40" s="4" t="s">
         <v>192</v>
       </c>
@@ -51059,11 +51053,11 @@
       <c r="B41" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C41" s="38">
+      <c r="C41" s="41">
         <f>SUMIFS(I$3:I$36,B$3:B$36,A$40,L$3:L$36,A$41)</f>
         <v>17615</v>
       </c>
-      <c r="D41" s="38"/>
+      <c r="D41" s="41"/>
       <c r="E41" s="3">
         <f>SUMIFS(Q$3:Q$36,B$3:B$36,A$40,L$3:L$36,A$41)</f>
         <v>34</v>
@@ -51098,10 +51092,10 @@
       <c r="B42" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C42" s="39">
-        <v>0</v>
-      </c>
-      <c r="D42" s="39"/>
+      <c r="C42" s="42">
+        <v>0</v>
+      </c>
+      <c r="D42" s="42"/>
       <c r="K42" t="s">
         <v>200</v>
       </c>
@@ -51125,11 +51119,11 @@
       <c r="B43" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C43" s="39">
+      <c r="C43" s="42">
         <f>-SUMIFS(I$3:I$36,B$3:B$36,A$40,P$3:P$36,"xx",N$3:N$36,"x")</f>
         <v>0</v>
       </c>
-      <c r="D43" s="39"/>
+      <c r="D43" s="42"/>
       <c r="E43" s="2">
         <f>SUMIFS(Q$3:Q$36,B$3:B$36,A$40,P$3:P$36,"xx",N$3:N$36,"x")</f>
         <v>0</v>
@@ -51149,11 +51143,11 @@
       <c r="B44" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C44" s="37">
+      <c r="C44" s="40">
         <f>SUBTOTAL(9,C41:C43)</f>
         <v>17615</v>
       </c>
-      <c r="D44" s="37"/>
+      <c r="D44" s="40"/>
       <c r="E44">
         <f>E41</f>
         <v>34</v>
@@ -51173,8 +51167,8 @@
       <c r="B45" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C45" s="35"/>
-      <c r="D45" s="35"/>
+      <c r="C45" s="38"/>
+      <c r="D45" s="38"/>
       <c r="K45" s="2" t="s">
         <v>206</v>
       </c>
@@ -51190,8 +51184,8 @@
       <c r="B46" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C46" s="35"/>
-      <c r="D46" s="35"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="38"/>
       <c r="L46" s="13">
         <f>SUBTOTAL(9,L41:L45)</f>
         <v>5021</v>
@@ -51212,11 +51206,11 @@
       <c r="B48" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C48" s="36">
+      <c r="C48" s="39">
         <f>C44+C45+C46</f>
         <v>17615</v>
       </c>
-      <c r="D48" s="36"/>
+      <c r="D48" s="39"/>
       <c r="E48" s="1" t="s">
         <v>211</v>
       </c>
@@ -53261,10 +53255,10 @@
       <c r="A43" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C43" s="37" t="s">
+      <c r="C43" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D43" s="37"/>
+      <c r="D43" s="40"/>
       <c r="E43" s="4" t="s">
         <v>192</v>
       </c>
@@ -53292,11 +53286,11 @@
       <c r="B44" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C44" s="38">
+      <c r="C44" s="41">
         <f>SUMIFS(I$3:I$39,B$3:B$39,A$43,L$3:L$39,A$44)</f>
         <v>17471</v>
       </c>
-      <c r="D44" s="38"/>
+      <c r="D44" s="41"/>
       <c r="E44" s="3">
         <f>SUMIFS(Q$3:Q$39,B$3:B$39,A$43,L$3:L$39,A$44)</f>
         <v>36</v>
@@ -53331,10 +53325,10 @@
       <c r="B45" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C45" s="39">
-        <v>0</v>
-      </c>
-      <c r="D45" s="39"/>
+      <c r="C45" s="42">
+        <v>0</v>
+      </c>
+      <c r="D45" s="42"/>
       <c r="K45" t="s">
         <v>200</v>
       </c>
@@ -53358,11 +53352,11 @@
       <c r="B46" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C46" s="39">
+      <c r="C46" s="42">
         <f>-SUMIFS(I$3:I$39,B$3:B$39,A$43,P$3:P$39,"xx",N$3:N$39,"x")</f>
         <v>-1980</v>
       </c>
-      <c r="D46" s="39"/>
+      <c r="D46" s="42"/>
       <c r="E46" s="2">
         <f>SUMIFS(Q$3:Q$39,B$3:B$39,A$43,P$3:P$39,"xx",N$3:N$39,"x")</f>
         <v>1</v>
@@ -53382,11 +53376,11 @@
       <c r="B47" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C47" s="37">
+      <c r="C47" s="40">
         <f>SUBTOTAL(9,C44:C46)</f>
         <v>15491</v>
       </c>
-      <c r="D47" s="37"/>
+      <c r="D47" s="40"/>
       <c r="E47">
         <f>E44</f>
         <v>36</v>
@@ -53406,8 +53400,8 @@
       <c r="B48" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C48" s="35"/>
-      <c r="D48" s="35"/>
+      <c r="C48" s="38"/>
+      <c r="D48" s="38"/>
       <c r="K48" s="2" t="s">
         <v>206</v>
       </c>
@@ -53423,8 +53417,8 @@
       <c r="B49" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C49" s="35"/>
-      <c r="D49" s="35"/>
+      <c r="C49" s="38"/>
+      <c r="D49" s="38"/>
       <c r="L49" s="13">
         <f>SUBTOTAL(9,L44:L48)</f>
         <v>3645</v>
@@ -53438,11 +53432,11 @@
       <c r="B51" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C51" s="36">
+      <c r="C51" s="39">
         <f>C47+C48+C49</f>
         <v>15491</v>
       </c>
-      <c r="D51" s="36"/>
+      <c r="D51" s="39"/>
       <c r="E51" s="1" t="s">
         <v>211</v>
       </c>
@@ -55155,10 +55149,10 @@
       <c r="A37" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C37" s="37" t="s">
+      <c r="C37" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D37" s="37"/>
+      <c r="D37" s="40"/>
       <c r="E37" s="4" t="s">
         <v>192</v>
       </c>
@@ -55186,11 +55180,11 @@
       <c r="B38" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C38" s="38">
+      <c r="C38" s="41">
         <f>SUMIFS(I$3:I$33,B$3:B$33,A$37,L$3:L$33,A$38)</f>
         <v>27540</v>
       </c>
-      <c r="D38" s="38"/>
+      <c r="D38" s="41"/>
       <c r="E38" s="3">
         <f>SUMIFS(Q$3:Q$33,B$3:B$33,A$37,L$3:L$33,A$38)</f>
         <v>31</v>
@@ -55225,10 +55219,10 @@
       <c r="B39" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C39" s="39">
-        <v>0</v>
-      </c>
-      <c r="D39" s="39"/>
+      <c r="C39" s="42">
+        <v>0</v>
+      </c>
+      <c r="D39" s="42"/>
       <c r="K39" t="s">
         <v>200</v>
       </c>
@@ -55252,11 +55246,11 @@
       <c r="B40" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="39">
+      <c r="C40" s="42">
         <f>-SUMIFS(I$3:I$33,B$3:B$33,A$37,P$3:P$33,"xx",N$3:N$33,"x")</f>
         <v>0</v>
       </c>
-      <c r="D40" s="39"/>
+      <c r="D40" s="42"/>
       <c r="E40" s="2">
         <f>SUMIFS(Q$3:Q$33,B$3:B$33,A$37,P$3:P$33,"xx",N$3:N$33,"x")</f>
         <v>0</v>
@@ -55276,11 +55270,11 @@
       <c r="B41" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C41" s="37">
+      <c r="C41" s="40">
         <f>SUBTOTAL(9,C38:C40)</f>
         <v>27540</v>
       </c>
-      <c r="D41" s="37"/>
+      <c r="D41" s="40"/>
       <c r="E41">
         <f>E38</f>
         <v>31</v>
@@ -55300,8 +55294,8 @@
       <c r="B42" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C42" s="35"/>
-      <c r="D42" s="35"/>
+      <c r="C42" s="38"/>
+      <c r="D42" s="38"/>
       <c r="K42" s="2" t="s">
         <v>206</v>
       </c>
@@ -55317,8 +55311,8 @@
       <c r="B43" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C43" s="35"/>
-      <c r="D43" s="35"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="38"/>
       <c r="L43" s="13">
         <f>SUBTOTAL(9,L38:L42)</f>
         <v>3183</v>
@@ -55332,11 +55326,11 @@
       <c r="B45" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C45" s="36">
+      <c r="C45" s="39">
         <f>C41+C42+C43</f>
         <v>27540</v>
       </c>
-      <c r="D45" s="36"/>
+      <c r="D45" s="39"/>
       <c r="E45" s="1" t="s">
         <v>211</v>
       </c>
@@ -58314,10 +58308,10 @@
       <c r="A66" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C66" s="37" t="s">
+      <c r="C66" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D66" s="37"/>
+      <c r="D66" s="40"/>
       <c r="E66" s="4" t="s">
         <v>192</v>
       </c>
@@ -58349,11 +58343,11 @@
       <c r="B67" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C67" s="38">
+      <c r="C67" s="41">
         <f>SUMIFS(I$3:I$62,B$3:B$62,A$66,L$3:L$62,A$67)</f>
         <v>38370</v>
       </c>
-      <c r="D67" s="38"/>
+      <c r="D67" s="41"/>
       <c r="E67" s="3">
         <f>SUMIFS(Q$3:Q$62,B$3:B$62,A$66,L$3:L$62,A$67)</f>
         <v>56</v>
@@ -58388,10 +58382,10 @@
       <c r="B68" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C68" s="39">
-        <v>0</v>
-      </c>
-      <c r="D68" s="39"/>
+      <c r="C68" s="42">
+        <v>0</v>
+      </c>
+      <c r="D68" s="42"/>
       <c r="K68" t="s">
         <v>200</v>
       </c>
@@ -58415,11 +58409,11 @@
       <c r="B69" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C69" s="39">
+      <c r="C69" s="42">
         <f>-SUMIFS(I$3:I$62,B$3:B$62,A$66,P$3:P$62,"xx",N$3:N$62,"x")</f>
         <v>-3360</v>
       </c>
-      <c r="D69" s="39"/>
+      <c r="D69" s="42"/>
       <c r="E69" s="2">
         <f>SUMIFS(Q$3:Q$62,B$3:B$62,A$66,P$3:P$62,"xx",N$3:N$62,"x")</f>
         <v>4</v>
@@ -58439,11 +58433,11 @@
       <c r="B70" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C70" s="37">
+      <c r="C70" s="40">
         <f>SUBTOTAL(9,C67:C69)</f>
         <v>35010</v>
       </c>
-      <c r="D70" s="37"/>
+      <c r="D70" s="40"/>
       <c r="E70">
         <f>E67</f>
         <v>56</v>
@@ -58463,8 +58457,8 @@
       <c r="B71" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C71" s="35"/>
-      <c r="D71" s="35"/>
+      <c r="C71" s="38"/>
+      <c r="D71" s="38"/>
       <c r="K71" s="2" t="s">
         <v>206</v>
       </c>
@@ -58480,8 +58474,8 @@
       <c r="B72" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C72" s="35"/>
-      <c r="D72" s="35"/>
+      <c r="C72" s="38"/>
+      <c r="D72" s="38"/>
       <c r="L72" s="13">
         <f>SUBTOTAL(9,L67:L71)</f>
         <v>15015</v>
@@ -58495,11 +58489,11 @@
       <c r="B74" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C74" s="36">
+      <c r="C74" s="39">
         <f>C70+C71+C72</f>
         <v>35010</v>
       </c>
-      <c r="D74" s="36"/>
+      <c r="D74" s="39"/>
       <c r="E74" s="1" t="s">
         <v>211</v>
       </c>
@@ -59970,10 +59964,10 @@
       <c r="A32" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C32" s="37" t="s">
+      <c r="C32" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="D32" s="37"/>
+      <c r="D32" s="40"/>
       <c r="E32" s="4" t="s">
         <v>192</v>
       </c>
@@ -60001,11 +59995,11 @@
       <c r="B33" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="38">
+      <c r="C33" s="41">
         <f>SUMIFS(I$3:I$28,B$3:B$28,A$32,L$3:L$28,A$33)</f>
         <v>17250</v>
       </c>
-      <c r="D33" s="38"/>
+      <c r="D33" s="41"/>
       <c r="E33" s="3">
         <f>SUMIFS(Q$3:Q$28,B$3:B$28,A$32,L$3:L$28,A$33)</f>
         <v>25</v>
@@ -60036,10 +60030,10 @@
       <c r="B34" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C34" s="39">
-        <v>0</v>
-      </c>
-      <c r="D34" s="39"/>
+      <c r="C34" s="42">
+        <v>0</v>
+      </c>
+      <c r="D34" s="42"/>
       <c r="K34" t="s">
         <v>200</v>
       </c>
@@ -60063,11 +60057,11 @@
       <c r="B35" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C35" s="39">
+      <c r="C35" s="42">
         <f>-SUMIFS(I$3:I$28,B$3:B$28,A$32,P$3:P$28,"xx",N$3:N$28,"x")</f>
         <v>0</v>
       </c>
-      <c r="D35" s="39"/>
+      <c r="D35" s="42"/>
       <c r="E35" s="2">
         <f>SUMIFS(Q$3:Q$28,B$3:B$28,A$32,P$3:P$28,"xx",N$3:N$28,"x")</f>
         <v>0</v>
@@ -60095,11 +60089,11 @@
       <c r="B36" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C36" s="37">
+      <c r="C36" s="40">
         <f>SUBTOTAL(9,C33:C35)</f>
         <v>17250</v>
       </c>
-      <c r="D36" s="37"/>
+      <c r="D36" s="40"/>
       <c r="E36">
         <f>E33</f>
         <v>25</v>
@@ -60119,8 +60113,8 @@
       <c r="B37" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C37" s="35"/>
-      <c r="D37" s="35"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="38"/>
       <c r="K37" s="2" t="s">
         <v>206</v>
       </c>
@@ -60136,8 +60130,8 @@
       <c r="B38" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C38" s="35"/>
-      <c r="D38" s="35"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
       <c r="L38" s="13">
         <f>SUBTOTAL(9,L33:L37)</f>
         <v>5160</v>
@@ -60158,11 +60152,11 @@
       <c r="B40" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C40" s="36">
+      <c r="C40" s="39">
         <f>C36+C37+C38</f>
         <v>17250</v>
       </c>
-      <c r="D40" s="36"/>
+      <c r="D40" s="39"/>
       <c r="E40" s="1" t="s">
         <v>211</v>
       </c>
@@ -60190,12 +60184,12 @@
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" s="40"/>
-      <c r="B42" s="41"/>
-      <c r="C42" s="42"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="40"/>
-      <c r="F42" s="41"/>
+      <c r="A42" s="35"/>
+      <c r="B42" s="36"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="35"/>
+      <c r="F42" s="36"/>
       <c r="K42" t="s">
         <v>200</v>
       </c>
@@ -60209,45 +60203,45 @@
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" s="41"/>
-      <c r="B43" s="41"/>
-      <c r="C43" s="43"/>
-      <c r="D43" s="43"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="41"/>
+      <c r="A43" s="36"/>
+      <c r="B43" s="36"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="36"/>
       <c r="K43" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="41"/>
-      <c r="B44" s="44"/>
+      <c r="A44" s="36"/>
+      <c r="B44" s="37"/>
       <c r="C44" s="45"/>
       <c r="D44" s="45"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="41"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="36"/>
       <c r="K44" s="2" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" s="41"/>
-      <c r="B45" s="44"/>
+      <c r="A45" s="36"/>
+      <c r="B45" s="37"/>
       <c r="C45" s="45"/>
       <c r="D45" s="45"/>
-      <c r="E45" s="44"/>
-      <c r="F45" s="41"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="36"/>
       <c r="K45" s="2" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" s="41"/>
-      <c r="B46" s="40"/>
-      <c r="C46" s="42"/>
-      <c r="D46" s="42"/>
-      <c r="E46" s="41"/>
-      <c r="F46" s="41"/>
+      <c r="A46" s="36"/>
+      <c r="B46" s="35"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
       <c r="L46" s="13">
         <f>SUBTOTAL(9,L41:L45)</f>
         <v>7451</v>
@@ -60258,20 +60252,20 @@
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" s="41"/>
-      <c r="B47" s="44"/>
-      <c r="C47" s="43"/>
-      <c r="D47" s="43"/>
-      <c r="E47" s="41"/>
-      <c r="F47" s="41"/>
+      <c r="A47" s="36"/>
+      <c r="B47" s="37"/>
+      <c r="C47" s="44"/>
+      <c r="D47" s="44"/>
+      <c r="E47" s="36"/>
+      <c r="F47" s="36"/>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48" s="41"/>
-      <c r="B48" s="41"/>
-      <c r="C48" s="43"/>
-      <c r="D48" s="43"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="41"/>
+      <c r="A48" s="36"/>
+      <c r="B48" s="36"/>
+      <c r="C48" s="44"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="36"/>
+      <c r="F48" s="36"/>
       <c r="K48" s="11" t="s">
         <v>135</v>
       </c>
@@ -60283,12 +60277,12 @@
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49" s="41"/>
-      <c r="B49" s="41"/>
-      <c r="C49" s="41"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
+      <c r="A49" s="36"/>
+      <c r="B49" s="36"/>
+      <c r="C49" s="36"/>
+      <c r="D49" s="36"/>
+      <c r="E49" s="36"/>
+      <c r="F49" s="36"/>
       <c r="K49" t="s">
         <v>197</v>
       </c>
@@ -60302,12 +60296,12 @@
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50" s="41"/>
-      <c r="B50" s="40"/>
-      <c r="C50" s="42"/>
-      <c r="D50" s="42"/>
-      <c r="E50" s="40"/>
-      <c r="F50" s="41"/>
+      <c r="A50" s="36"/>
+      <c r="B50" s="35"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="35"/>
+      <c r="F50" s="36"/>
       <c r="K50" t="s">
         <v>200</v>
       </c>
@@ -60321,12 +60315,12 @@
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51" s="41"/>
-      <c r="B51" s="41"/>
-      <c r="C51" s="41"/>
-      <c r="D51" s="41"/>
-      <c r="E51" s="41"/>
-      <c r="F51" s="41"/>
+      <c r="A51" s="36"/>
+      <c r="B51" s="36"/>
+      <c r="C51" s="36"/>
+      <c r="D51" s="36"/>
+      <c r="E51" s="36"/>
+      <c r="F51" s="36"/>
       <c r="K51" t="s">
         <v>202</v>
       </c>
@@ -60433,22 +60427,22 @@
     </sortState>
   </autoFilter>
   <mergeCells count="16">
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
     <mergeCell ref="C50:D50"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="C45:D45"/>
     <mergeCell ref="C46:D46"/>
     <mergeCell ref="C47:D47"/>
     <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
